--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="93">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -218,12 +218,90 @@
   </si>
   <si>
     <t>Nº</t>
+  </si>
+  <si>
+    <t>Finland Veikkausliiga</t>
+  </si>
+  <si>
+    <t>2025</t>
+  </si>
+  <si>
+    <t>Ilves</t>
+  </si>
+  <si>
+    <t>Inter Turku</t>
+  </si>
+  <si>
+    <t>Mariehamn</t>
+  </si>
+  <si>
+    <t>KTP</t>
+  </si>
+  <si>
+    <t>VPS</t>
+  </si>
+  <si>
+    <t>Haka</t>
+  </si>
+  <si>
+    <t>HJK</t>
+  </si>
+  <si>
+    <t>KuPS</t>
+  </si>
+  <si>
+    <t>Jaro</t>
+  </si>
+  <si>
+    <t>SJK</t>
+  </si>
+  <si>
+    <t>Oulu</t>
+  </si>
+  <si>
+    <t>Gnistan</t>
+  </si>
+  <si>
+    <t>['38', '68', '77']</t>
+  </si>
+  <si>
+    <t>['76']</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>['57', '69', '73', '90+1']</t>
+  </si>
+  <si>
+    <t>['19', '71', '90+1']</t>
+  </si>
+  <si>
+    <t>['4', '14']</t>
+  </si>
+  <si>
+    <t>['53']</t>
+  </si>
+  <si>
+    <t>['6', '55']</t>
+  </si>
+  <si>
+    <t>['73']</t>
+  </si>
+  <si>
+    <t>['33', '41', '90']</t>
+  </si>
+  <si>
+    <t>['56', '90+10']</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -276,11 +354,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -575,7 +654,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP1"/>
+  <dimension ref="A1:BP7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -784,6 +863,1242 @@
         <v>66</v>
       </c>
     </row>
+    <row r="2" spans="1:68">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>7811481</v>
+      </c>
+      <c r="C2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E2" s="2">
+        <v>45752.375</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H2" t="s">
+        <v>76</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>2</v>
+      </c>
+      <c r="K2">
+        <v>3</v>
+      </c>
+      <c r="L2">
+        <v>3</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+      <c r="N2">
+        <v>5</v>
+      </c>
+      <c r="O2" t="s">
+        <v>82</v>
+      </c>
+      <c r="P2" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q2">
+        <v>3.2</v>
+      </c>
+      <c r="R2">
+        <v>2.2</v>
+      </c>
+      <c r="S2">
+        <v>3.25</v>
+      </c>
+      <c r="T2">
+        <v>1.36</v>
+      </c>
+      <c r="U2">
+        <v>3</v>
+      </c>
+      <c r="V2">
+        <v>2.75</v>
+      </c>
+      <c r="W2">
+        <v>1.4</v>
+      </c>
+      <c r="X2">
+        <v>7</v>
+      </c>
+      <c r="Y2">
+        <v>1.1</v>
+      </c>
+      <c r="Z2">
+        <v>2.63</v>
+      </c>
+      <c r="AA2">
+        <v>3.43</v>
+      </c>
+      <c r="AB2">
+        <v>2.65</v>
+      </c>
+      <c r="AC2">
+        <v>1.05</v>
+      </c>
+      <c r="AD2">
+        <v>8.5</v>
+      </c>
+      <c r="AE2">
+        <v>1.25</v>
+      </c>
+      <c r="AF2">
+        <v>3.6</v>
+      </c>
+      <c r="AG2">
+        <v>1.85</v>
+      </c>
+      <c r="AH2">
+        <v>1.99</v>
+      </c>
+      <c r="AI2">
+        <v>1.67</v>
+      </c>
+      <c r="AJ2">
+        <v>2.1</v>
+      </c>
+      <c r="AK2">
+        <v>1.47</v>
+      </c>
+      <c r="AL2">
+        <v>1.29</v>
+      </c>
+      <c r="AM2">
+        <v>1.49</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>0</v>
+      </c>
+      <c r="AP2">
+        <v>3</v>
+      </c>
+      <c r="AQ2">
+        <v>0</v>
+      </c>
+      <c r="AR2">
+        <v>0</v>
+      </c>
+      <c r="AS2">
+        <v>0</v>
+      </c>
+      <c r="AT2">
+        <v>0</v>
+      </c>
+      <c r="AU2">
+        <v>6</v>
+      </c>
+      <c r="AV2">
+        <v>6</v>
+      </c>
+      <c r="AW2">
+        <v>5</v>
+      </c>
+      <c r="AX2">
+        <v>3</v>
+      </c>
+      <c r="AY2">
+        <v>14</v>
+      </c>
+      <c r="AZ2">
+        <v>9</v>
+      </c>
+      <c r="BA2">
+        <v>3</v>
+      </c>
+      <c r="BB2">
+        <v>2</v>
+      </c>
+      <c r="BC2">
+        <v>5</v>
+      </c>
+      <c r="BD2">
+        <v>1.74</v>
+      </c>
+      <c r="BE2">
+        <v>8.9</v>
+      </c>
+      <c r="BF2">
+        <v>2.46</v>
+      </c>
+      <c r="BG2">
+        <v>1.21</v>
+      </c>
+      <c r="BH2">
+        <v>3.8</v>
+      </c>
+      <c r="BI2">
+        <v>1.32</v>
+      </c>
+      <c r="BJ2">
+        <v>3</v>
+      </c>
+      <c r="BK2">
+        <v>1.58</v>
+      </c>
+      <c r="BL2">
+        <v>2.15</v>
+      </c>
+      <c r="BM2">
+        <v>2</v>
+      </c>
+      <c r="BN2">
+        <v>1.68</v>
+      </c>
+      <c r="BO2">
+        <v>2.65</v>
+      </c>
+      <c r="BP2">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:68">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>7811482</v>
+      </c>
+      <c r="C3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E3" s="2">
+        <v>45752.45833333334</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H3" t="s">
+        <v>77</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+      <c r="N3">
+        <v>2</v>
+      </c>
+      <c r="O3" t="s">
+        <v>83</v>
+      </c>
+      <c r="P3" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q3">
+        <v>3.25</v>
+      </c>
+      <c r="R3">
+        <v>2.05</v>
+      </c>
+      <c r="S3">
+        <v>3.5</v>
+      </c>
+      <c r="T3">
+        <v>1.44</v>
+      </c>
+      <c r="U3">
+        <v>2.63</v>
+      </c>
+      <c r="V3">
+        <v>3.25</v>
+      </c>
+      <c r="W3">
+        <v>1.33</v>
+      </c>
+      <c r="X3">
+        <v>10</v>
+      </c>
+      <c r="Y3">
+        <v>1.06</v>
+      </c>
+      <c r="Z3">
+        <v>2.55</v>
+      </c>
+      <c r="AA3">
+        <v>3.3</v>
+      </c>
+      <c r="AB3">
+        <v>2.7</v>
+      </c>
+      <c r="AC3">
+        <v>1.06</v>
+      </c>
+      <c r="AD3">
+        <v>8</v>
+      </c>
+      <c r="AE3">
+        <v>1.33</v>
+      </c>
+      <c r="AF3">
+        <v>3.1</v>
+      </c>
+      <c r="AG3">
+        <v>2.05</v>
+      </c>
+      <c r="AH3">
+        <v>1.75</v>
+      </c>
+      <c r="AI3">
+        <v>1.91</v>
+      </c>
+      <c r="AJ3">
+        <v>1.91</v>
+      </c>
+      <c r="AK3">
+        <v>1.42</v>
+      </c>
+      <c r="AL3">
+        <v>1.32</v>
+      </c>
+      <c r="AM3">
+        <v>1.5</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <v>1</v>
+      </c>
+      <c r="AQ3">
+        <v>1</v>
+      </c>
+      <c r="AR3">
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <v>3</v>
+      </c>
+      <c r="AV3">
+        <v>4</v>
+      </c>
+      <c r="AW3">
+        <v>14</v>
+      </c>
+      <c r="AX3">
+        <v>1</v>
+      </c>
+      <c r="AY3">
+        <v>25</v>
+      </c>
+      <c r="AZ3">
+        <v>5</v>
+      </c>
+      <c r="BA3">
+        <v>7</v>
+      </c>
+      <c r="BB3">
+        <v>1</v>
+      </c>
+      <c r="BC3">
+        <v>8</v>
+      </c>
+      <c r="BD3">
+        <v>1.86</v>
+      </c>
+      <c r="BE3">
+        <v>8.5</v>
+      </c>
+      <c r="BF3">
+        <v>2.28</v>
+      </c>
+      <c r="BG3">
+        <v>1.24</v>
+      </c>
+      <c r="BH3">
+        <v>3.5</v>
+      </c>
+      <c r="BI3">
+        <v>1.46</v>
+      </c>
+      <c r="BJ3">
+        <v>2.45</v>
+      </c>
+      <c r="BK3">
+        <v>1.8</v>
+      </c>
+      <c r="BL3">
+        <v>1.83</v>
+      </c>
+      <c r="BM3">
+        <v>2.37</v>
+      </c>
+      <c r="BN3">
+        <v>1.49</v>
+      </c>
+      <c r="BO3">
+        <v>3.3</v>
+      </c>
+      <c r="BP3">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:68">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>7811483</v>
+      </c>
+      <c r="C4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E4" s="2">
+        <v>45752.45833333334</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4" t="s">
+        <v>72</v>
+      </c>
+      <c r="H4" t="s">
+        <v>78</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
+      </c>
+      <c r="N4">
+        <v>2</v>
+      </c>
+      <c r="O4" t="s">
+        <v>84</v>
+      </c>
+      <c r="P4" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q4">
+        <v>3.1</v>
+      </c>
+      <c r="R4">
+        <v>2.05</v>
+      </c>
+      <c r="S4">
+        <v>3.75</v>
+      </c>
+      <c r="T4">
+        <v>1.5</v>
+      </c>
+      <c r="U4">
+        <v>2.5</v>
+      </c>
+      <c r="V4">
+        <v>3.4</v>
+      </c>
+      <c r="W4">
+        <v>1.3</v>
+      </c>
+      <c r="X4">
+        <v>10</v>
+      </c>
+      <c r="Y4">
+        <v>1.06</v>
+      </c>
+      <c r="Z4">
+        <v>2.09</v>
+      </c>
+      <c r="AA4">
+        <v>3.47</v>
+      </c>
+      <c r="AB4">
+        <v>3.28</v>
+      </c>
+      <c r="AC4">
+        <v>1.07</v>
+      </c>
+      <c r="AD4">
+        <v>7.5</v>
+      </c>
+      <c r="AE4">
+        <v>1.4</v>
+      </c>
+      <c r="AF4">
+        <v>2.8</v>
+      </c>
+      <c r="AG4">
+        <v>1.92</v>
+      </c>
+      <c r="AH4">
+        <v>1.82</v>
+      </c>
+      <c r="AI4">
+        <v>1.95</v>
+      </c>
+      <c r="AJ4">
+        <v>1.8</v>
+      </c>
+      <c r="AK4">
+        <v>1.34</v>
+      </c>
+      <c r="AL4">
+        <v>1.33</v>
+      </c>
+      <c r="AM4">
+        <v>1.58</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>0</v>
+      </c>
+      <c r="AQ4">
+        <v>3</v>
+      </c>
+      <c r="AR4">
+        <v>0</v>
+      </c>
+      <c r="AS4">
+        <v>0</v>
+      </c>
+      <c r="AT4">
+        <v>0</v>
+      </c>
+      <c r="AU4">
+        <v>5</v>
+      </c>
+      <c r="AV4">
+        <v>5</v>
+      </c>
+      <c r="AW4">
+        <v>4</v>
+      </c>
+      <c r="AX4">
+        <v>2</v>
+      </c>
+      <c r="AY4">
+        <v>11</v>
+      </c>
+      <c r="AZ4">
+        <v>7</v>
+      </c>
+      <c r="BA4">
+        <v>7</v>
+      </c>
+      <c r="BB4">
+        <v>3</v>
+      </c>
+      <c r="BC4">
+        <v>10</v>
+      </c>
+      <c r="BD4">
+        <v>1.92</v>
+      </c>
+      <c r="BE4">
+        <v>8.5</v>
+      </c>
+      <c r="BF4">
+        <v>2.2</v>
+      </c>
+      <c r="BG4">
+        <v>1.21</v>
+      </c>
+      <c r="BH4">
+        <v>3.8</v>
+      </c>
+      <c r="BI4">
+        <v>1.41</v>
+      </c>
+      <c r="BJ4">
+        <v>2.6</v>
+      </c>
+      <c r="BK4">
+        <v>1.72</v>
+      </c>
+      <c r="BL4">
+        <v>1.93</v>
+      </c>
+      <c r="BM4">
+        <v>2.25</v>
+      </c>
+      <c r="BN4">
+        <v>1.55</v>
+      </c>
+      <c r="BO4">
+        <v>3</v>
+      </c>
+      <c r="BP4">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:68">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>7811484</v>
+      </c>
+      <c r="C5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" s="2">
+        <v>45752.45833333334</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5" t="s">
+        <v>73</v>
+      </c>
+      <c r="H5" t="s">
+        <v>79</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+      <c r="N5">
+        <v>1</v>
+      </c>
+      <c r="O5" t="s">
+        <v>84</v>
+      </c>
+      <c r="P5" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q5">
+        <v>4</v>
+      </c>
+      <c r="R5">
+        <v>2.38</v>
+      </c>
+      <c r="S5">
+        <v>2.4</v>
+      </c>
+      <c r="T5">
+        <v>1.3</v>
+      </c>
+      <c r="U5">
+        <v>3.4</v>
+      </c>
+      <c r="V5">
+        <v>2.38</v>
+      </c>
+      <c r="W5">
+        <v>1.53</v>
+      </c>
+      <c r="X5">
+        <v>6</v>
+      </c>
+      <c r="Y5">
+        <v>1.13</v>
+      </c>
+      <c r="Z5">
+        <v>4.2</v>
+      </c>
+      <c r="AA5">
+        <v>3.71</v>
+      </c>
+      <c r="AB5">
+        <v>1.79</v>
+      </c>
+      <c r="AC5">
+        <v>1.04</v>
+      </c>
+      <c r="AD5">
+        <v>9</v>
+      </c>
+      <c r="AE5">
+        <v>1.2</v>
+      </c>
+      <c r="AF5">
+        <v>4.2</v>
+      </c>
+      <c r="AG5">
+        <v>1.54</v>
+      </c>
+      <c r="AH5">
+        <v>2.26</v>
+      </c>
+      <c r="AI5">
+        <v>1.57</v>
+      </c>
+      <c r="AJ5">
+        <v>2.25</v>
+      </c>
+      <c r="AK5">
+        <v>1.88</v>
+      </c>
+      <c r="AL5">
+        <v>1.25</v>
+      </c>
+      <c r="AM5">
+        <v>1.26</v>
+      </c>
+      <c r="AN5">
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <v>0</v>
+      </c>
+      <c r="AQ5">
+        <v>3</v>
+      </c>
+      <c r="AR5">
+        <v>0</v>
+      </c>
+      <c r="AS5">
+        <v>0</v>
+      </c>
+      <c r="AT5">
+        <v>0</v>
+      </c>
+      <c r="AU5">
+        <v>5</v>
+      </c>
+      <c r="AV5">
+        <v>9</v>
+      </c>
+      <c r="AW5">
+        <v>8</v>
+      </c>
+      <c r="AX5">
+        <v>11</v>
+      </c>
+      <c r="AY5">
+        <v>15</v>
+      </c>
+      <c r="AZ5">
+        <v>25</v>
+      </c>
+      <c r="BA5">
+        <v>4</v>
+      </c>
+      <c r="BB5">
+        <v>5</v>
+      </c>
+      <c r="BC5">
+        <v>9</v>
+      </c>
+      <c r="BD5">
+        <v>2.66</v>
+      </c>
+      <c r="BE5">
+        <v>9</v>
+      </c>
+      <c r="BF5">
+        <v>1.65</v>
+      </c>
+      <c r="BG5">
+        <v>1.15</v>
+      </c>
+      <c r="BH5">
+        <v>4.25</v>
+      </c>
+      <c r="BI5">
+        <v>1.32</v>
+      </c>
+      <c r="BJ5">
+        <v>3</v>
+      </c>
+      <c r="BK5">
+        <v>1.58</v>
+      </c>
+      <c r="BL5">
+        <v>2.15</v>
+      </c>
+      <c r="BM5">
+        <v>2</v>
+      </c>
+      <c r="BN5">
+        <v>1.68</v>
+      </c>
+      <c r="BO5">
+        <v>2.65</v>
+      </c>
+      <c r="BP5">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:68">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>7811485</v>
+      </c>
+      <c r="C6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E6" s="2">
+        <v>45752.45833333334</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H6" t="s">
+        <v>80</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+      <c r="K6">
+        <v>2</v>
+      </c>
+      <c r="L6">
+        <v>4</v>
+      </c>
+      <c r="M6">
+        <v>3</v>
+      </c>
+      <c r="N6">
+        <v>7</v>
+      </c>
+      <c r="O6" t="s">
+        <v>85</v>
+      </c>
+      <c r="P6" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q6">
+        <v>2.3</v>
+      </c>
+      <c r="R6">
+        <v>2.3</v>
+      </c>
+      <c r="S6">
+        <v>4.75</v>
+      </c>
+      <c r="T6">
+        <v>1.36</v>
+      </c>
+      <c r="U6">
+        <v>3</v>
+      </c>
+      <c r="V6">
+        <v>2.63</v>
+      </c>
+      <c r="W6">
+        <v>1.44</v>
+      </c>
+      <c r="X6">
+        <v>7</v>
+      </c>
+      <c r="Y6">
+        <v>1.1</v>
+      </c>
+      <c r="Z6">
+        <v>1.75</v>
+      </c>
+      <c r="AA6">
+        <v>3.74</v>
+      </c>
+      <c r="AB6">
+        <v>4.33</v>
+      </c>
+      <c r="AC6">
+        <v>1.04</v>
+      </c>
+      <c r="AD6">
+        <v>9</v>
+      </c>
+      <c r="AE6">
+        <v>1.25</v>
+      </c>
+      <c r="AF6">
+        <v>3.7</v>
+      </c>
+      <c r="AG6">
+        <v>1.77</v>
+      </c>
+      <c r="AH6">
+        <v>1.98</v>
+      </c>
+      <c r="AI6">
+        <v>1.75</v>
+      </c>
+      <c r="AJ6">
+        <v>2</v>
+      </c>
+      <c r="AK6">
+        <v>1.23</v>
+      </c>
+      <c r="AL6">
+        <v>1.26</v>
+      </c>
+      <c r="AM6">
+        <v>1.93</v>
+      </c>
+      <c r="AN6">
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <v>3</v>
+      </c>
+      <c r="AQ6">
+        <v>0</v>
+      </c>
+      <c r="AR6">
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <v>7</v>
+      </c>
+      <c r="AV6">
+        <v>4</v>
+      </c>
+      <c r="AW6">
+        <v>12</v>
+      </c>
+      <c r="AX6">
+        <v>6</v>
+      </c>
+      <c r="AY6">
+        <v>25</v>
+      </c>
+      <c r="AZ6">
+        <v>10</v>
+      </c>
+      <c r="BA6">
+        <v>7</v>
+      </c>
+      <c r="BB6">
+        <v>2</v>
+      </c>
+      <c r="BC6">
+        <v>9</v>
+      </c>
+      <c r="BD6">
+        <v>1.49</v>
+      </c>
+      <c r="BE6">
+        <v>9.1</v>
+      </c>
+      <c r="BF6">
+        <v>3.2</v>
+      </c>
+      <c r="BG6">
+        <v>1.21</v>
+      </c>
+      <c r="BH6">
+        <v>3.8</v>
+      </c>
+      <c r="BI6">
+        <v>1.41</v>
+      </c>
+      <c r="BJ6">
+        <v>2.6</v>
+      </c>
+      <c r="BK6">
+        <v>1.72</v>
+      </c>
+      <c r="BL6">
+        <v>1.93</v>
+      </c>
+      <c r="BM6">
+        <v>2.25</v>
+      </c>
+      <c r="BN6">
+        <v>1.53</v>
+      </c>
+      <c r="BO6">
+        <v>3.1</v>
+      </c>
+      <c r="BP6">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:68">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>7811486</v>
+      </c>
+      <c r="C7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D7" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45752.54166666666</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7" t="s">
+        <v>75</v>
+      </c>
+      <c r="H7" t="s">
+        <v>81</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>3</v>
+      </c>
+      <c r="M7">
+        <v>2</v>
+      </c>
+      <c r="N7">
+        <v>5</v>
+      </c>
+      <c r="O7" t="s">
+        <v>86</v>
+      </c>
+      <c r="P7" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q7">
+        <v>3.4</v>
+      </c>
+      <c r="R7">
+        <v>2.2</v>
+      </c>
+      <c r="S7">
+        <v>3.1</v>
+      </c>
+      <c r="T7">
+        <v>1.36</v>
+      </c>
+      <c r="U7">
+        <v>3</v>
+      </c>
+      <c r="V7">
+        <v>2.75</v>
+      </c>
+      <c r="W7">
+        <v>1.4</v>
+      </c>
+      <c r="X7">
+        <v>7</v>
+      </c>
+      <c r="Y7">
+        <v>1.1</v>
+      </c>
+      <c r="Z7">
+        <v>2.51</v>
+      </c>
+      <c r="AA7">
+        <v>3.41</v>
+      </c>
+      <c r="AB7">
+        <v>2.64</v>
+      </c>
+      <c r="AC7">
+        <v>1.05</v>
+      </c>
+      <c r="AD7">
+        <v>8.5</v>
+      </c>
+      <c r="AE7">
+        <v>1.25</v>
+      </c>
+      <c r="AF7">
+        <v>3.6</v>
+      </c>
+      <c r="AG7">
+        <v>1.8</v>
+      </c>
+      <c r="AH7">
+        <v>1.94</v>
+      </c>
+      <c r="AI7">
+        <v>1.67</v>
+      </c>
+      <c r="AJ7">
+        <v>2.1</v>
+      </c>
+      <c r="AK7">
+        <v>1.52</v>
+      </c>
+      <c r="AL7">
+        <v>1.29</v>
+      </c>
+      <c r="AM7">
+        <v>1.44</v>
+      </c>
+      <c r="AN7">
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <v>3</v>
+      </c>
+      <c r="AQ7">
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <v>6</v>
+      </c>
+      <c r="AV7">
+        <v>6</v>
+      </c>
+      <c r="AW7">
+        <v>10</v>
+      </c>
+      <c r="AX7">
+        <v>9</v>
+      </c>
+      <c r="AY7">
+        <v>16</v>
+      </c>
+      <c r="AZ7">
+        <v>15</v>
+      </c>
+      <c r="BA7">
+        <v>4</v>
+      </c>
+      <c r="BB7">
+        <v>11</v>
+      </c>
+      <c r="BC7">
+        <v>15</v>
+      </c>
+      <c r="BD7">
+        <v>1.95</v>
+      </c>
+      <c r="BE7">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="BF7">
+        <v>2.15</v>
+      </c>
+      <c r="BG7">
+        <v>1.21</v>
+      </c>
+      <c r="BH7">
+        <v>3.8</v>
+      </c>
+      <c r="BI7">
+        <v>1.32</v>
+      </c>
+      <c r="BJ7">
+        <v>3</v>
+      </c>
+      <c r="BK7">
+        <v>1.58</v>
+      </c>
+      <c r="BL7">
+        <v>2.15</v>
+      </c>
+      <c r="BM7">
+        <v>2</v>
+      </c>
+      <c r="BN7">
+        <v>1.68</v>
+      </c>
+      <c r="BO7">
+        <v>2.65</v>
+      </c>
+      <c r="BP7">
+        <v>1.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="168">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -382,6 +382,9 @@
     <t>['66', '90+4']</t>
   </si>
   <si>
+    <t>['13']</t>
+  </si>
+  <si>
     <t>['4', '14']</t>
   </si>
   <si>
@@ -512,6 +515,9 @@
   </si>
   <si>
     <t>['61']</t>
+  </si>
+  <si>
+    <t>['54']</t>
   </si>
 </sst>
 </file>
@@ -873,7 +879,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP59"/>
+  <dimension ref="A1:BP60"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1129,7 +1135,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q2">
         <v>3.2</v>
@@ -1335,7 +1341,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Q3">
         <v>3.25</v>
@@ -1413,7 +1419,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AQ3">
         <v>1.6</v>
@@ -1541,7 +1547,7 @@
         <v>84</v>
       </c>
       <c r="P4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q4">
         <v>3.1</v>
@@ -1953,7 +1959,7 @@
         <v>85</v>
       </c>
       <c r="P6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q6">
         <v>2.3</v>
@@ -2159,7 +2165,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q7">
         <v>3.4</v>
@@ -2365,7 +2371,7 @@
         <v>87</v>
       </c>
       <c r="P8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q8">
         <v>4.1</v>
@@ -2777,7 +2783,7 @@
         <v>89</v>
       </c>
       <c r="P10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Q10">
         <v>1.7</v>
@@ -2983,7 +2989,7 @@
         <v>84</v>
       </c>
       <c r="P11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q11">
         <v>2.25</v>
@@ -3267,7 +3273,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AQ12">
         <v>1.4</v>
@@ -3601,7 +3607,7 @@
         <v>84</v>
       </c>
       <c r="P14" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q14">
         <v>3.1</v>
@@ -3807,7 +3813,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q15">
         <v>3.2</v>
@@ -4013,7 +4019,7 @@
         <v>93</v>
       </c>
       <c r="P16" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q16">
         <v>4.79</v>
@@ -4219,7 +4225,7 @@
         <v>84</v>
       </c>
       <c r="P17" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q17">
         <v>4.17</v>
@@ -4631,7 +4637,7 @@
         <v>84</v>
       </c>
       <c r="P19" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q19">
         <v>1.72</v>
@@ -4837,7 +4843,7 @@
         <v>95</v>
       </c>
       <c r="P20" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q20">
         <v>1.91</v>
@@ -5043,7 +5049,7 @@
         <v>96</v>
       </c>
       <c r="P21" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q21">
         <v>2.2</v>
@@ -5249,7 +5255,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q22">
         <v>4.75</v>
@@ -5455,7 +5461,7 @@
         <v>98</v>
       </c>
       <c r="P23" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q23">
         <v>2.3</v>
@@ -5661,7 +5667,7 @@
         <v>99</v>
       </c>
       <c r="P24" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q24">
         <v>2.25</v>
@@ -5867,7 +5873,7 @@
         <v>100</v>
       </c>
       <c r="P25" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q25">
         <v>3.75</v>
@@ -6073,7 +6079,7 @@
         <v>101</v>
       </c>
       <c r="P26" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q26">
         <v>6.5</v>
@@ -6279,7 +6285,7 @@
         <v>102</v>
       </c>
       <c r="P27" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q27">
         <v>1.85</v>
@@ -6360,7 +6366,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ27">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="AR27">
         <v>2.08</v>
@@ -6485,7 +6491,7 @@
         <v>84</v>
       </c>
       <c r="P28" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q28">
         <v>2.5</v>
@@ -6691,7 +6697,7 @@
         <v>103</v>
       </c>
       <c r="P29" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q29">
         <v>2.7</v>
@@ -7515,7 +7521,7 @@
         <v>106</v>
       </c>
       <c r="P33" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q33">
         <v>2.93</v>
@@ -7593,7 +7599,7 @@
         <v>0</v>
       </c>
       <c r="AP33">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AQ33">
         <v>1.4</v>
@@ -7721,7 +7727,7 @@
         <v>107</v>
       </c>
       <c r="P34" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q34">
         <v>2.26</v>
@@ -7802,7 +7808,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ34">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="AR34">
         <v>1.49</v>
@@ -8133,7 +8139,7 @@
         <v>109</v>
       </c>
       <c r="P36" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q36">
         <v>6.4</v>
@@ -8339,7 +8345,7 @@
         <v>110</v>
       </c>
       <c r="P37" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q37">
         <v>3.84</v>
@@ -8545,7 +8551,7 @@
         <v>84</v>
       </c>
       <c r="P38" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q38">
         <v>5.25</v>
@@ -8751,7 +8757,7 @@
         <v>111</v>
       </c>
       <c r="P39" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -8957,7 +8963,7 @@
         <v>112</v>
       </c>
       <c r="P40" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q40">
         <v>2.85</v>
@@ -9163,7 +9169,7 @@
         <v>113</v>
       </c>
       <c r="P41" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q41">
         <v>4.02</v>
@@ -9369,7 +9375,7 @@
         <v>84</v>
       </c>
       <c r="P42" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q42">
         <v>2.1</v>
@@ -9575,7 +9581,7 @@
         <v>114</v>
       </c>
       <c r="P43" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q43">
         <v>2.75</v>
@@ -9653,7 +9659,7 @@
         <v>1</v>
       </c>
       <c r="AP43">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AQ43">
         <v>1.2</v>
@@ -9781,7 +9787,7 @@
         <v>115</v>
       </c>
       <c r="P44" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q44">
         <v>1.68</v>
@@ -10193,7 +10199,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q46">
         <v>1.91</v>
@@ -10686,7 +10692,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ48">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="AR48">
         <v>1.4</v>
@@ -10811,7 +10817,7 @@
         <v>118</v>
       </c>
       <c r="P49" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q49">
         <v>3.45</v>
@@ -11223,7 +11229,7 @@
         <v>84</v>
       </c>
       <c r="P51" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q51">
         <v>6.5</v>
@@ -11429,7 +11435,7 @@
         <v>84</v>
       </c>
       <c r="P52" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q52">
         <v>2.18</v>
@@ -11635,7 +11641,7 @@
         <v>84</v>
       </c>
       <c r="P53" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q53">
         <v>3.85</v>
@@ -11841,7 +11847,7 @@
         <v>119</v>
       </c>
       <c r="P54" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q54">
         <v>2.66</v>
@@ -12047,7 +12053,7 @@
         <v>120</v>
       </c>
       <c r="P55" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q55">
         <v>3</v>
@@ -12253,7 +12259,7 @@
         <v>121</v>
       </c>
       <c r="P56" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q56">
         <v>3.35</v>
@@ -12665,7 +12671,7 @@
         <v>84</v>
       </c>
       <c r="P58" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q58">
         <v>3.3</v>
@@ -12871,7 +12877,7 @@
         <v>84</v>
       </c>
       <c r="P59" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q59">
         <v>5.5</v>
@@ -13028,6 +13034,212 @@
       </c>
       <c r="BP59">
         <v>1.44</v>
+      </c>
+    </row>
+    <row r="60" spans="1:68">
+      <c r="A60" s="1">
+        <v>59</v>
+      </c>
+      <c r="B60">
+        <v>7811535</v>
+      </c>
+      <c r="C60" t="s">
+        <v>68</v>
+      </c>
+      <c r="D60" t="s">
+        <v>69</v>
+      </c>
+      <c r="E60" s="2">
+        <v>45822.33333333334</v>
+      </c>
+      <c r="F60">
+        <v>0</v>
+      </c>
+      <c r="G60" t="s">
+        <v>71</v>
+      </c>
+      <c r="H60" t="s">
+        <v>75</v>
+      </c>
+      <c r="I60">
+        <v>1</v>
+      </c>
+      <c r="J60">
+        <v>0</v>
+      </c>
+      <c r="K60">
+        <v>1</v>
+      </c>
+      <c r="L60">
+        <v>1</v>
+      </c>
+      <c r="M60">
+        <v>1</v>
+      </c>
+      <c r="N60">
+        <v>2</v>
+      </c>
+      <c r="O60" t="s">
+        <v>122</v>
+      </c>
+      <c r="P60" t="s">
+        <v>167</v>
+      </c>
+      <c r="Q60">
+        <v>2.11</v>
+      </c>
+      <c r="R60">
+        <v>2.5</v>
+      </c>
+      <c r="S60">
+        <v>4.8</v>
+      </c>
+      <c r="T60">
+        <v>1.27</v>
+      </c>
+      <c r="U60">
+        <v>3.4</v>
+      </c>
+      <c r="V60">
+        <v>2.34</v>
+      </c>
+      <c r="W60">
+        <v>1.58</v>
+      </c>
+      <c r="X60">
+        <v>5.3</v>
+      </c>
+      <c r="Y60">
+        <v>1.11</v>
+      </c>
+      <c r="Z60">
+        <v>1.5</v>
+      </c>
+      <c r="AA60">
+        <v>4</v>
+      </c>
+      <c r="AB60">
+        <v>6.8</v>
+      </c>
+      <c r="AC60">
+        <v>1.03</v>
+      </c>
+      <c r="AD60">
+        <v>12</v>
+      </c>
+      <c r="AE60">
+        <v>1.19</v>
+      </c>
+      <c r="AF60">
+        <v>4.82</v>
+      </c>
+      <c r="AG60">
+        <v>1.58</v>
+      </c>
+      <c r="AH60">
+        <v>2.27</v>
+      </c>
+      <c r="AI60">
+        <v>1.67</v>
+      </c>
+      <c r="AJ60">
+        <v>2.15</v>
+      </c>
+      <c r="AK60">
+        <v>1.07</v>
+      </c>
+      <c r="AL60">
+        <v>1.22</v>
+      </c>
+      <c r="AM60">
+        <v>2.5</v>
+      </c>
+      <c r="AN60">
+        <v>2</v>
+      </c>
+      <c r="AO60">
+        <v>0.67</v>
+      </c>
+      <c r="AP60">
+        <v>1.8</v>
+      </c>
+      <c r="AQ60">
+        <v>0.75</v>
+      </c>
+      <c r="AR60">
+        <v>1.95</v>
+      </c>
+      <c r="AS60">
+        <v>1.6</v>
+      </c>
+      <c r="AT60">
+        <v>3.55</v>
+      </c>
+      <c r="AU60">
+        <v>5</v>
+      </c>
+      <c r="AV60">
+        <v>5</v>
+      </c>
+      <c r="AW60">
+        <v>12</v>
+      </c>
+      <c r="AX60">
+        <v>6</v>
+      </c>
+      <c r="AY60">
+        <v>17</v>
+      </c>
+      <c r="AZ60">
+        <v>11</v>
+      </c>
+      <c r="BA60">
+        <v>4</v>
+      </c>
+      <c r="BB60">
+        <v>4</v>
+      </c>
+      <c r="BC60">
+        <v>8</v>
+      </c>
+      <c r="BD60">
+        <v>1.25</v>
+      </c>
+      <c r="BE60">
+        <v>8</v>
+      </c>
+      <c r="BF60">
+        <v>4.5</v>
+      </c>
+      <c r="BG60">
+        <v>1.2</v>
+      </c>
+      <c r="BH60">
+        <v>3.9</v>
+      </c>
+      <c r="BI60">
+        <v>1.38</v>
+      </c>
+      <c r="BJ60">
+        <v>2.65</v>
+      </c>
+      <c r="BK60">
+        <v>1.8</v>
+      </c>
+      <c r="BL60">
+        <v>2.1</v>
+      </c>
+      <c r="BM60">
+        <v>2</v>
+      </c>
+      <c r="BN60">
+        <v>1.72</v>
+      </c>
+      <c r="BO60">
+        <v>2.5</v>
+      </c>
+      <c r="BP60">
+        <v>1.47</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="175">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -385,6 +385,15 @@
     <t>['13']</t>
   </si>
   <si>
+    <t>['65', '90+2']</t>
+  </si>
+  <si>
+    <t>['11', '29', '90+4']</t>
+  </si>
+  <si>
+    <t>['72']</t>
+  </si>
+  <si>
     <t>['4', '14']</t>
   </si>
   <si>
@@ -424,9 +433,6 @@
     <t>['59']</t>
   </si>
   <si>
-    <t>['72']</t>
-  </si>
-  <si>
     <t>['38']</t>
   </si>
   <si>
@@ -518,6 +524,21 @@
   </si>
   <si>
     <t>['54']</t>
+  </si>
+  <si>
+    <t>['22', '90+1', '78', '71']</t>
+  </si>
+  <si>
+    <t>['35']</t>
+  </si>
+  <si>
+    <t>['31', '44', '55']</t>
+  </si>
+  <si>
+    <t>['87']</t>
+  </si>
+  <si>
+    <t>['6', '54', '57', '66', '80']</t>
   </si>
 </sst>
 </file>
@@ -879,7 +900,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP60"/>
+  <dimension ref="A1:BP65"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1135,7 +1156,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="Q2">
         <v>3.2</v>
@@ -1216,7 +1237,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ2">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1341,7 +1362,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="Q3">
         <v>3.25</v>
@@ -1547,7 +1568,7 @@
         <v>84</v>
       </c>
       <c r="P4" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="Q4">
         <v>3.1</v>
@@ -1625,10 +1646,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AQ4">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1959,7 +1980,7 @@
         <v>85</v>
       </c>
       <c r="P6" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="Q6">
         <v>2.3</v>
@@ -2165,7 +2186,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="Q7">
         <v>3.4</v>
@@ -2371,7 +2392,7 @@
         <v>87</v>
       </c>
       <c r="P8" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="Q8">
         <v>4.1</v>
@@ -2452,7 +2473,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ8">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AR8">
         <v>1.58</v>
@@ -2655,10 +2676,10 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AQ9">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -2783,7 +2804,7 @@
         <v>89</v>
       </c>
       <c r="P10" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="Q10">
         <v>1.7</v>
@@ -2864,7 +2885,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ10">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AR10">
         <v>1.48</v>
@@ -2989,7 +3010,7 @@
         <v>84</v>
       </c>
       <c r="P11" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="Q11">
         <v>2.25</v>
@@ -3479,7 +3500,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="AQ13">
         <v>0.67</v>
@@ -3607,7 +3628,7 @@
         <v>84</v>
       </c>
       <c r="P14" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="Q14">
         <v>3.1</v>
@@ -3813,7 +3834,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="Q15">
         <v>3.2</v>
@@ -4019,7 +4040,7 @@
         <v>93</v>
       </c>
       <c r="P16" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="Q16">
         <v>4.79</v>
@@ -4097,7 +4118,7 @@
         <v>3</v>
       </c>
       <c r="AP16">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AQ16">
         <v>1.33</v>
@@ -4225,7 +4246,7 @@
         <v>84</v>
       </c>
       <c r="P17" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="Q17">
         <v>4.17</v>
@@ -4306,7 +4327,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ17">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AR17">
         <v>1.59</v>
@@ -4509,10 +4530,10 @@
         <v>1.5</v>
       </c>
       <c r="AP18">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="AQ18">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AR18">
         <v>1.27</v>
@@ -4637,7 +4658,7 @@
         <v>84</v>
       </c>
       <c r="P19" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="Q19">
         <v>1.72</v>
@@ -4843,7 +4864,7 @@
         <v>95</v>
       </c>
       <c r="P20" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="Q20">
         <v>1.91</v>
@@ -4921,7 +4942,7 @@
         <v>3</v>
       </c>
       <c r="AP20">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="AQ20">
         <v>1.4</v>
@@ -5049,7 +5070,7 @@
         <v>96</v>
       </c>
       <c r="P21" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="Q21">
         <v>2.2</v>
@@ -5127,7 +5148,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AQ21">
         <v>0.67</v>
@@ -5255,7 +5276,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="Q22">
         <v>4.75</v>
@@ -5333,7 +5354,7 @@
         <v>3</v>
       </c>
       <c r="AP22">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AQ22">
         <v>2.6</v>
@@ -5461,7 +5482,7 @@
         <v>98</v>
       </c>
       <c r="P23" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="Q23">
         <v>2.3</v>
@@ -5542,7 +5563,7 @@
         <v>0.25</v>
       </c>
       <c r="AQ23">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AR23">
         <v>0</v>
@@ -5667,7 +5688,7 @@
         <v>99</v>
       </c>
       <c r="P24" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="Q24">
         <v>2.25</v>
@@ -5748,7 +5769,7 @@
         <v>2</v>
       </c>
       <c r="AQ24">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AR24">
         <v>1.6</v>
@@ -5873,7 +5894,7 @@
         <v>100</v>
       </c>
       <c r="P25" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="Q25">
         <v>3.75</v>
@@ -5951,7 +5972,7 @@
         <v>1</v>
       </c>
       <c r="AP25">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AQ25">
         <v>1.6</v>
@@ -6079,7 +6100,7 @@
         <v>101</v>
       </c>
       <c r="P26" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="Q26">
         <v>6.5</v>
@@ -6157,10 +6178,10 @@
         <v>3</v>
       </c>
       <c r="AP26">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AQ26">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AR26">
         <v>1.17</v>
@@ -6285,7 +6306,7 @@
         <v>102</v>
       </c>
       <c r="P27" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="Q27">
         <v>1.85</v>
@@ -6363,7 +6384,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AQ27">
         <v>0.75</v>
@@ -6491,7 +6512,7 @@
         <v>84</v>
       </c>
       <c r="P28" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="Q28">
         <v>2.5</v>
@@ -6572,7 +6593,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ28">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AR28">
         <v>1.83</v>
@@ -6697,7 +6718,7 @@
         <v>103</v>
       </c>
       <c r="P29" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="Q29">
         <v>2.7</v>
@@ -6984,7 +7005,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ30">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AR30">
         <v>1.89</v>
@@ -7187,7 +7208,7 @@
         <v>3</v>
       </c>
       <c r="AP31">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="AQ31">
         <v>1.33</v>
@@ -7393,7 +7414,7 @@
         <v>1.5</v>
       </c>
       <c r="AP32">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AQ32">
         <v>1.4</v>
@@ -7521,7 +7542,7 @@
         <v>106</v>
       </c>
       <c r="P33" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="Q33">
         <v>2.93</v>
@@ -7602,7 +7623,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ33">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AR33">
         <v>1.89</v>
@@ -7727,7 +7748,7 @@
         <v>107</v>
       </c>
       <c r="P34" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="Q34">
         <v>2.26</v>
@@ -8011,10 +8032,10 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="AQ35">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AR35">
         <v>1.73</v>
@@ -8139,7 +8160,7 @@
         <v>109</v>
       </c>
       <c r="P36" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="Q36">
         <v>6.4</v>
@@ -8217,7 +8238,7 @@
         <v>3</v>
       </c>
       <c r="AP36">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AQ36">
         <v>2.6</v>
@@ -8345,7 +8366,7 @@
         <v>110</v>
       </c>
       <c r="P37" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="Q37">
         <v>3.84</v>
@@ -8423,7 +8444,7 @@
         <v>1</v>
       </c>
       <c r="AP37">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AQ37">
         <v>1.4</v>
@@ -8551,7 +8572,7 @@
         <v>84</v>
       </c>
       <c r="P38" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="Q38">
         <v>5.25</v>
@@ -8632,7 +8653,7 @@
         <v>0.25</v>
       </c>
       <c r="AQ38">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AR38">
         <v>1.28</v>
@@ -8757,7 +8778,7 @@
         <v>111</v>
       </c>
       <c r="P39" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -8835,10 +8856,10 @@
         <v>0.5</v>
       </c>
       <c r="AP39">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AQ39">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AR39">
         <v>1.9</v>
@@ -8963,7 +8984,7 @@
         <v>112</v>
       </c>
       <c r="P40" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="Q40">
         <v>2.85</v>
@@ -9041,7 +9062,7 @@
         <v>2</v>
       </c>
       <c r="AP40">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AQ40">
         <v>1.33</v>
@@ -9169,7 +9190,7 @@
         <v>113</v>
       </c>
       <c r="P41" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="Q41">
         <v>4.02</v>
@@ -9375,7 +9396,7 @@
         <v>84</v>
       </c>
       <c r="P42" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="Q42">
         <v>2.1</v>
@@ -9453,7 +9474,7 @@
         <v>1</v>
       </c>
       <c r="AP42">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AQ42">
         <v>1.4</v>
@@ -9581,7 +9602,7 @@
         <v>114</v>
       </c>
       <c r="P43" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="Q43">
         <v>2.75</v>
@@ -9662,7 +9683,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ43">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AR43">
         <v>2.09</v>
@@ -9787,7 +9808,7 @@
         <v>115</v>
       </c>
       <c r="P44" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="Q44">
         <v>1.68</v>
@@ -9868,7 +9889,7 @@
         <v>2</v>
       </c>
       <c r="AQ44">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AR44">
         <v>1.82</v>
@@ -10074,7 +10095,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ45">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AR45">
         <v>1.67</v>
@@ -10199,7 +10220,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="Q46">
         <v>1.91</v>
@@ -10817,7 +10838,7 @@
         <v>118</v>
       </c>
       <c r="P49" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Q49">
         <v>3.45</v>
@@ -11229,7 +11250,7 @@
         <v>84</v>
       </c>
       <c r="P51" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q51">
         <v>6.5</v>
@@ -11307,10 +11328,10 @@
         <v>1</v>
       </c>
       <c r="AP51">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AQ51">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AR51">
         <v>1.2</v>
@@ -11435,7 +11456,7 @@
         <v>84</v>
       </c>
       <c r="P52" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="Q52">
         <v>2.18</v>
@@ -11513,10 +11534,10 @@
         <v>1.33</v>
       </c>
       <c r="AP52">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="AQ52">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AR52">
         <v>1.97</v>
@@ -11641,7 +11662,7 @@
         <v>84</v>
       </c>
       <c r="P53" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="Q53">
         <v>3.85</v>
@@ -11719,7 +11740,7 @@
         <v>2.33</v>
       </c>
       <c r="AP53">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AQ53">
         <v>2.6</v>
@@ -11847,7 +11868,7 @@
         <v>119</v>
       </c>
       <c r="P54" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Q54">
         <v>2.66</v>
@@ -12053,7 +12074,7 @@
         <v>120</v>
       </c>
       <c r="P55" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Q55">
         <v>3</v>
@@ -12134,7 +12155,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ55">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AR55">
         <v>1.69</v>
@@ -12259,7 +12280,7 @@
         <v>121</v>
       </c>
       <c r="P56" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q56">
         <v>3.35</v>
@@ -12337,7 +12358,7 @@
         <v>1.4</v>
       </c>
       <c r="AP56">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AQ56">
         <v>1.33</v>
@@ -12671,7 +12692,7 @@
         <v>84</v>
       </c>
       <c r="P58" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q58">
         <v>3.3</v>
@@ -12749,10 +12770,10 @@
         <v>0.75</v>
       </c>
       <c r="AP58">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AQ58">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AR58">
         <v>1.88</v>
@@ -12877,7 +12898,7 @@
         <v>84</v>
       </c>
       <c r="P59" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q59">
         <v>5.5</v>
@@ -13083,7 +13104,7 @@
         <v>122</v>
       </c>
       <c r="P60" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q60">
         <v>2.11</v>
@@ -13182,25 +13203,25 @@
         <v>5</v>
       </c>
       <c r="AW60">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="AX60">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AY60">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="AZ60">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BA60">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BB60">
         <v>4</v>
       </c>
       <c r="BC60">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BD60">
         <v>1.25</v>
@@ -13240,6 +13261,1036 @@
       </c>
       <c r="BP60">
         <v>1.47</v>
+      </c>
+    </row>
+    <row r="61" spans="1:68">
+      <c r="A61" s="1">
+        <v>60</v>
+      </c>
+      <c r="B61">
+        <v>7811536</v>
+      </c>
+      <c r="C61" t="s">
+        <v>68</v>
+      </c>
+      <c r="D61" t="s">
+        <v>69</v>
+      </c>
+      <c r="E61" s="2">
+        <v>45822.45833333334</v>
+      </c>
+      <c r="F61">
+        <v>0</v>
+      </c>
+      <c r="G61" t="s">
+        <v>79</v>
+      </c>
+      <c r="H61" t="s">
+        <v>78</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>1</v>
+      </c>
+      <c r="K61">
+        <v>1</v>
+      </c>
+      <c r="L61">
+        <v>0</v>
+      </c>
+      <c r="M61">
+        <v>4</v>
+      </c>
+      <c r="N61">
+        <v>4</v>
+      </c>
+      <c r="O61" t="s">
+        <v>84</v>
+      </c>
+      <c r="P61" t="s">
+        <v>170</v>
+      </c>
+      <c r="Q61">
+        <v>4.5</v>
+      </c>
+      <c r="R61">
+        <v>2.27</v>
+      </c>
+      <c r="S61">
+        <v>2.1</v>
+      </c>
+      <c r="T61">
+        <v>1.34</v>
+      </c>
+      <c r="U61">
+        <v>3.3</v>
+      </c>
+      <c r="V61">
+        <v>2.35</v>
+      </c>
+      <c r="W61">
+        <v>1.49</v>
+      </c>
+      <c r="X61">
+        <v>5.6</v>
+      </c>
+      <c r="Y61">
+        <v>1.11</v>
+      </c>
+      <c r="Z61">
+        <v>5.1</v>
+      </c>
+      <c r="AA61">
+        <v>3.91</v>
+      </c>
+      <c r="AB61">
+        <v>1.5</v>
+      </c>
+      <c r="AC61">
+        <v>1.04</v>
+      </c>
+      <c r="AD61">
+        <v>11</v>
+      </c>
+      <c r="AE61">
+        <v>1.21</v>
+      </c>
+      <c r="AF61">
+        <v>4.19</v>
+      </c>
+      <c r="AG61">
+        <v>1.76</v>
+      </c>
+      <c r="AH61">
+        <v>1.94</v>
+      </c>
+      <c r="AI61">
+        <v>1.62</v>
+      </c>
+      <c r="AJ61">
+        <v>2.1</v>
+      </c>
+      <c r="AK61">
+        <v>2.1</v>
+      </c>
+      <c r="AL61">
+        <v>1.22</v>
+      </c>
+      <c r="AM61">
+        <v>1.2</v>
+      </c>
+      <c r="AN61">
+        <v>0.25</v>
+      </c>
+      <c r="AO61">
+        <v>1.4</v>
+      </c>
+      <c r="AP61">
+        <v>0.2</v>
+      </c>
+      <c r="AQ61">
+        <v>1.67</v>
+      </c>
+      <c r="AR61">
+        <v>1.48</v>
+      </c>
+      <c r="AS61">
+        <v>1.85</v>
+      </c>
+      <c r="AT61">
+        <v>3.33</v>
+      </c>
+      <c r="AU61">
+        <v>2</v>
+      </c>
+      <c r="AV61">
+        <v>8</v>
+      </c>
+      <c r="AW61">
+        <v>3</v>
+      </c>
+      <c r="AX61">
+        <v>8</v>
+      </c>
+      <c r="AY61">
+        <v>5</v>
+      </c>
+      <c r="AZ61">
+        <v>16</v>
+      </c>
+      <c r="BA61">
+        <v>2</v>
+      </c>
+      <c r="BB61">
+        <v>13</v>
+      </c>
+      <c r="BC61">
+        <v>15</v>
+      </c>
+      <c r="BD61">
+        <v>2.76</v>
+      </c>
+      <c r="BE61">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF61">
+        <v>1.65</v>
+      </c>
+      <c r="BG61">
+        <v>1.24</v>
+      </c>
+      <c r="BH61">
+        <v>3.5</v>
+      </c>
+      <c r="BI61">
+        <v>1.5</v>
+      </c>
+      <c r="BJ61">
+        <v>2.4</v>
+      </c>
+      <c r="BK61">
+        <v>1.77</v>
+      </c>
+      <c r="BL61">
+        <v>1.95</v>
+      </c>
+      <c r="BM61">
+        <v>2.2</v>
+      </c>
+      <c r="BN61">
+        <v>1.6</v>
+      </c>
+      <c r="BO61">
+        <v>2.75</v>
+      </c>
+      <c r="BP61">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="62" spans="1:68">
+      <c r="A62" s="1">
+        <v>61</v>
+      </c>
+      <c r="B62">
+        <v>7811538</v>
+      </c>
+      <c r="C62" t="s">
+        <v>68</v>
+      </c>
+      <c r="D62" t="s">
+        <v>69</v>
+      </c>
+      <c r="E62" s="2">
+        <v>45822.54166666666</v>
+      </c>
+      <c r="F62">
+        <v>0</v>
+      </c>
+      <c r="G62" t="s">
+        <v>81</v>
+      </c>
+      <c r="H62" t="s">
+        <v>73</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>1</v>
+      </c>
+      <c r="K62">
+        <v>1</v>
+      </c>
+      <c r="L62">
+        <v>2</v>
+      </c>
+      <c r="M62">
+        <v>1</v>
+      </c>
+      <c r="N62">
+        <v>3</v>
+      </c>
+      <c r="O62" t="s">
+        <v>123</v>
+      </c>
+      <c r="P62" t="s">
+        <v>171</v>
+      </c>
+      <c r="Q62">
+        <v>2.26</v>
+      </c>
+      <c r="R62">
+        <v>2.43</v>
+      </c>
+      <c r="S62">
+        <v>4.05</v>
+      </c>
+      <c r="T62">
+        <v>1.24</v>
+      </c>
+      <c r="U62">
+        <v>3.5</v>
+      </c>
+      <c r="V62">
+        <v>2.33</v>
+      </c>
+      <c r="W62">
+        <v>1.65</v>
+      </c>
+      <c r="X62">
+        <v>5</v>
+      </c>
+      <c r="Y62">
+        <v>1.16</v>
+      </c>
+      <c r="Z62">
+        <v>1.71</v>
+      </c>
+      <c r="AA62">
+        <v>4.18</v>
+      </c>
+      <c r="AB62">
+        <v>4.1</v>
+      </c>
+      <c r="AC62">
+        <v>1</v>
+      </c>
+      <c r="AD62">
+        <v>17</v>
+      </c>
+      <c r="AE62">
+        <v>1.09</v>
+      </c>
+      <c r="AF62">
+        <v>4.75</v>
+      </c>
+      <c r="AG62">
+        <v>1.53</v>
+      </c>
+      <c r="AH62">
+        <v>2.4</v>
+      </c>
+      <c r="AI62">
+        <v>1.57</v>
+      </c>
+      <c r="AJ62">
+        <v>2.3</v>
+      </c>
+      <c r="AK62">
+        <v>1.24</v>
+      </c>
+      <c r="AL62">
+        <v>1.22</v>
+      </c>
+      <c r="AM62">
+        <v>2.18</v>
+      </c>
+      <c r="AN62">
+        <v>1</v>
+      </c>
+      <c r="AO62">
+        <v>1</v>
+      </c>
+      <c r="AP62">
+        <v>1.4</v>
+      </c>
+      <c r="AQ62">
+        <v>0.75</v>
+      </c>
+      <c r="AR62">
+        <v>1.67</v>
+      </c>
+      <c r="AS62">
+        <v>1.22</v>
+      </c>
+      <c r="AT62">
+        <v>2.89</v>
+      </c>
+      <c r="AU62">
+        <v>7</v>
+      </c>
+      <c r="AV62">
+        <v>7</v>
+      </c>
+      <c r="AW62">
+        <v>10</v>
+      </c>
+      <c r="AX62">
+        <v>6</v>
+      </c>
+      <c r="AY62">
+        <v>17</v>
+      </c>
+      <c r="AZ62">
+        <v>13</v>
+      </c>
+      <c r="BA62">
+        <v>8</v>
+      </c>
+      <c r="BB62">
+        <v>2</v>
+      </c>
+      <c r="BC62">
+        <v>10</v>
+      </c>
+      <c r="BD62">
+        <v>1.57</v>
+      </c>
+      <c r="BE62">
+        <v>6.75</v>
+      </c>
+      <c r="BF62">
+        <v>3.02</v>
+      </c>
+      <c r="BG62">
+        <v>1.21</v>
+      </c>
+      <c r="BH62">
+        <v>3.8</v>
+      </c>
+      <c r="BI62">
+        <v>1.3</v>
+      </c>
+      <c r="BJ62">
+        <v>2.88</v>
+      </c>
+      <c r="BK62">
+        <v>1.6</v>
+      </c>
+      <c r="BL62">
+        <v>2.14</v>
+      </c>
+      <c r="BM62">
+        <v>1.9</v>
+      </c>
+      <c r="BN62">
+        <v>1.8</v>
+      </c>
+      <c r="BO62">
+        <v>2.4</v>
+      </c>
+      <c r="BP62">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="63" spans="1:68">
+      <c r="A63" s="1">
+        <v>62</v>
+      </c>
+      <c r="B63">
+        <v>7811539</v>
+      </c>
+      <c r="C63" t="s">
+        <v>68</v>
+      </c>
+      <c r="D63" t="s">
+        <v>69</v>
+      </c>
+      <c r="E63" s="2">
+        <v>45822.54166666666</v>
+      </c>
+      <c r="F63">
+        <v>0</v>
+      </c>
+      <c r="G63" t="s">
+        <v>77</v>
+      </c>
+      <c r="H63" t="s">
+        <v>70</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>2</v>
+      </c>
+      <c r="K63">
+        <v>2</v>
+      </c>
+      <c r="L63">
+        <v>0</v>
+      </c>
+      <c r="M63">
+        <v>3</v>
+      </c>
+      <c r="N63">
+        <v>3</v>
+      </c>
+      <c r="O63" t="s">
+        <v>84</v>
+      </c>
+      <c r="P63" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q63">
+        <v>2.87</v>
+      </c>
+      <c r="R63">
+        <v>2.15</v>
+      </c>
+      <c r="S63">
+        <v>3.2</v>
+      </c>
+      <c r="T63">
+        <v>1.32</v>
+      </c>
+      <c r="U63">
+        <v>3.1</v>
+      </c>
+      <c r="V63">
+        <v>2.65</v>
+      </c>
+      <c r="W63">
+        <v>1.45</v>
+      </c>
+      <c r="X63">
+        <v>6.1</v>
+      </c>
+      <c r="Y63">
+        <v>1.11</v>
+      </c>
+      <c r="Z63">
+        <v>2.3</v>
+      </c>
+      <c r="AA63">
+        <v>3.25</v>
+      </c>
+      <c r="AB63">
+        <v>2.62</v>
+      </c>
+      <c r="AC63">
+        <v>1.04</v>
+      </c>
+      <c r="AD63">
+        <v>12</v>
+      </c>
+      <c r="AE63">
+        <v>1.22</v>
+      </c>
+      <c r="AF63">
+        <v>4</v>
+      </c>
+      <c r="AG63">
+        <v>1.76</v>
+      </c>
+      <c r="AH63">
+        <v>2</v>
+      </c>
+      <c r="AI63">
+        <v>1.64</v>
+      </c>
+      <c r="AJ63">
+        <v>2.15</v>
+      </c>
+      <c r="AK63">
+        <v>1.33</v>
+      </c>
+      <c r="AL63">
+        <v>1.33</v>
+      </c>
+      <c r="AM63">
+        <v>1.6</v>
+      </c>
+      <c r="AN63">
+        <v>2.5</v>
+      </c>
+      <c r="AO63">
+        <v>1.2</v>
+      </c>
+      <c r="AP63">
+        <v>2.14</v>
+      </c>
+      <c r="AQ63">
+        <v>1.5</v>
+      </c>
+      <c r="AR63">
+        <v>2.11</v>
+      </c>
+      <c r="AS63">
+        <v>2.17</v>
+      </c>
+      <c r="AT63">
+        <v>4.28</v>
+      </c>
+      <c r="AU63">
+        <v>3</v>
+      </c>
+      <c r="AV63">
+        <v>7</v>
+      </c>
+      <c r="AW63">
+        <v>8</v>
+      </c>
+      <c r="AX63">
+        <v>11</v>
+      </c>
+      <c r="AY63">
+        <v>11</v>
+      </c>
+      <c r="AZ63">
+        <v>18</v>
+      </c>
+      <c r="BA63">
+        <v>5</v>
+      </c>
+      <c r="BB63">
+        <v>5</v>
+      </c>
+      <c r="BC63">
+        <v>10</v>
+      </c>
+      <c r="BD63">
+        <v>1.9</v>
+      </c>
+      <c r="BE63">
+        <v>8.5</v>
+      </c>
+      <c r="BF63">
+        <v>2.15</v>
+      </c>
+      <c r="BG63">
+        <v>1.23</v>
+      </c>
+      <c r="BH63">
+        <v>3.6</v>
+      </c>
+      <c r="BI63">
+        <v>1.42</v>
+      </c>
+      <c r="BJ63">
+        <v>2.45</v>
+      </c>
+      <c r="BK63">
+        <v>1.81</v>
+      </c>
+      <c r="BL63">
+        <v>2</v>
+      </c>
+      <c r="BM63">
+        <v>2.28</v>
+      </c>
+      <c r="BN63">
+        <v>1.59</v>
+      </c>
+      <c r="BO63">
+        <v>3.2</v>
+      </c>
+      <c r="BP63">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="64" spans="1:68">
+      <c r="A64" s="1">
+        <v>63</v>
+      </c>
+      <c r="B64">
+        <v>7811540</v>
+      </c>
+      <c r="C64" t="s">
+        <v>68</v>
+      </c>
+      <c r="D64" t="s">
+        <v>69</v>
+      </c>
+      <c r="E64" s="2">
+        <v>45822.54166666666</v>
+      </c>
+      <c r="F64">
+        <v>0</v>
+      </c>
+      <c r="G64" t="s">
+        <v>76</v>
+      </c>
+      <c r="H64" t="s">
+        <v>80</v>
+      </c>
+      <c r="I64">
+        <v>2</v>
+      </c>
+      <c r="J64">
+        <v>0</v>
+      </c>
+      <c r="K64">
+        <v>2</v>
+      </c>
+      <c r="L64">
+        <v>3</v>
+      </c>
+      <c r="M64">
+        <v>1</v>
+      </c>
+      <c r="N64">
+        <v>4</v>
+      </c>
+      <c r="O64" t="s">
+        <v>124</v>
+      </c>
+      <c r="P64" t="s">
+        <v>173</v>
+      </c>
+      <c r="Q64">
+        <v>1.85</v>
+      </c>
+      <c r="R64">
+        <v>2.53</v>
+      </c>
+      <c r="S64">
+        <v>6.03</v>
+      </c>
+      <c r="T64">
+        <v>1.25</v>
+      </c>
+      <c r="U64">
+        <v>3.65</v>
+      </c>
+      <c r="V64">
+        <v>2.15</v>
+      </c>
+      <c r="W64">
+        <v>1.62</v>
+      </c>
+      <c r="X64">
+        <v>4.9</v>
+      </c>
+      <c r="Y64">
+        <v>1.16</v>
+      </c>
+      <c r="Z64">
+        <v>1.36</v>
+      </c>
+      <c r="AA64">
+        <v>4.33</v>
+      </c>
+      <c r="AB64">
+        <v>5.6</v>
+      </c>
+      <c r="AC64">
+        <v>1.03</v>
+      </c>
+      <c r="AD64">
+        <v>17</v>
+      </c>
+      <c r="AE64">
+        <v>1.17</v>
+      </c>
+      <c r="AF64">
+        <v>5.4</v>
+      </c>
+      <c r="AG64">
+        <v>1.5</v>
+      </c>
+      <c r="AH64">
+        <v>2.58</v>
+      </c>
+      <c r="AI64">
+        <v>1.7</v>
+      </c>
+      <c r="AJ64">
+        <v>2.22</v>
+      </c>
+      <c r="AK64">
+        <v>1.21</v>
+      </c>
+      <c r="AL64">
+        <v>1.25</v>
+      </c>
+      <c r="AM64">
+        <v>2.94</v>
+      </c>
+      <c r="AN64">
+        <v>1.4</v>
+      </c>
+      <c r="AO64">
+        <v>1.4</v>
+      </c>
+      <c r="AP64">
+        <v>1.67</v>
+      </c>
+      <c r="AQ64">
+        <v>1.17</v>
+      </c>
+      <c r="AR64">
+        <v>1.77</v>
+      </c>
+      <c r="AS64">
+        <v>1.13</v>
+      </c>
+      <c r="AT64">
+        <v>2.9</v>
+      </c>
+      <c r="AU64">
+        <v>7</v>
+      </c>
+      <c r="AV64">
+        <v>3</v>
+      </c>
+      <c r="AW64">
+        <v>11</v>
+      </c>
+      <c r="AX64">
+        <v>2</v>
+      </c>
+      <c r="AY64">
+        <v>18</v>
+      </c>
+      <c r="AZ64">
+        <v>5</v>
+      </c>
+      <c r="BA64">
+        <v>9</v>
+      </c>
+      <c r="BB64">
+        <v>0</v>
+      </c>
+      <c r="BC64">
+        <v>9</v>
+      </c>
+      <c r="BD64">
+        <v>1.4</v>
+      </c>
+      <c r="BE64">
+        <v>9.5</v>
+      </c>
+      <c r="BF64">
+        <v>3.8</v>
+      </c>
+      <c r="BG64">
+        <v>1.2</v>
+      </c>
+      <c r="BH64">
+        <v>3.9</v>
+      </c>
+      <c r="BI64">
+        <v>1.39</v>
+      </c>
+      <c r="BJ64">
+        <v>3.1</v>
+      </c>
+      <c r="BK64">
+        <v>1.55</v>
+      </c>
+      <c r="BL64">
+        <v>2.2</v>
+      </c>
+      <c r="BM64">
+        <v>2.05</v>
+      </c>
+      <c r="BN64">
+        <v>1.7</v>
+      </c>
+      <c r="BO64">
+        <v>2.55</v>
+      </c>
+      <c r="BP64">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="65" spans="1:68">
+      <c r="A65" s="1">
+        <v>64</v>
+      </c>
+      <c r="B65">
+        <v>7811537</v>
+      </c>
+      <c r="C65" t="s">
+        <v>68</v>
+      </c>
+      <c r="D65" t="s">
+        <v>69</v>
+      </c>
+      <c r="E65" s="2">
+        <v>45822.54166666666</v>
+      </c>
+      <c r="F65">
+        <v>0</v>
+      </c>
+      <c r="G65" t="s">
+        <v>72</v>
+      </c>
+      <c r="H65" t="s">
+        <v>74</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>1</v>
+      </c>
+      <c r="K65">
+        <v>1</v>
+      </c>
+      <c r="L65">
+        <v>1</v>
+      </c>
+      <c r="M65">
+        <v>5</v>
+      </c>
+      <c r="N65">
+        <v>6</v>
+      </c>
+      <c r="O65" t="s">
+        <v>125</v>
+      </c>
+      <c r="P65" t="s">
+        <v>174</v>
+      </c>
+      <c r="Q65">
+        <v>4.28</v>
+      </c>
+      <c r="R65">
+        <v>2.2</v>
+      </c>
+      <c r="S65">
+        <v>2.61</v>
+      </c>
+      <c r="T65">
+        <v>1.32</v>
+      </c>
+      <c r="U65">
+        <v>3.1</v>
+      </c>
+      <c r="V65">
+        <v>2.72</v>
+      </c>
+      <c r="W65">
+        <v>1.45</v>
+      </c>
+      <c r="X65">
+        <v>5.8</v>
+      </c>
+      <c r="Y65">
+        <v>1.1</v>
+      </c>
+      <c r="Z65">
+        <v>3.64</v>
+      </c>
+      <c r="AA65">
+        <v>3.65</v>
+      </c>
+      <c r="AB65">
+        <v>1.99</v>
+      </c>
+      <c r="AC65">
+        <v>1.05</v>
+      </c>
+      <c r="AD65">
+        <v>10.5</v>
+      </c>
+      <c r="AE65">
+        <v>1.2</v>
+      </c>
+      <c r="AF65">
+        <v>3.8</v>
+      </c>
+      <c r="AG65">
+        <v>1.75</v>
+      </c>
+      <c r="AH65">
+        <v>1.95</v>
+      </c>
+      <c r="AI65">
+        <v>1.71</v>
+      </c>
+      <c r="AJ65">
+        <v>2.15</v>
+      </c>
+      <c r="AK65">
+        <v>1.25</v>
+      </c>
+      <c r="AL65">
+        <v>1.29</v>
+      </c>
+      <c r="AM65">
+        <v>1.28</v>
+      </c>
+      <c r="AN65">
+        <v>0.8</v>
+      </c>
+      <c r="AO65">
+        <v>1.4</v>
+      </c>
+      <c r="AP65">
+        <v>0.67</v>
+      </c>
+      <c r="AQ65">
+        <v>1.67</v>
+      </c>
+      <c r="AR65">
+        <v>1.16</v>
+      </c>
+      <c r="AS65">
+        <v>1.21</v>
+      </c>
+      <c r="AT65">
+        <v>2.37</v>
+      </c>
+      <c r="AU65">
+        <v>4</v>
+      </c>
+      <c r="AV65">
+        <v>7</v>
+      </c>
+      <c r="AW65">
+        <v>13</v>
+      </c>
+      <c r="AX65">
+        <v>4</v>
+      </c>
+      <c r="AY65">
+        <v>17</v>
+      </c>
+      <c r="AZ65">
+        <v>11</v>
+      </c>
+      <c r="BA65">
+        <v>9</v>
+      </c>
+      <c r="BB65">
+        <v>2</v>
+      </c>
+      <c r="BC65">
+        <v>11</v>
+      </c>
+      <c r="BD65">
+        <v>2.43</v>
+      </c>
+      <c r="BE65">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF65">
+        <v>1.67</v>
+      </c>
+      <c r="BG65">
+        <v>1.22</v>
+      </c>
+      <c r="BH65">
+        <v>3.5</v>
+      </c>
+      <c r="BI65">
+        <v>1.47</v>
+      </c>
+      <c r="BJ65">
+        <v>2.55</v>
+      </c>
+      <c r="BK65">
+        <v>1.73</v>
+      </c>
+      <c r="BL65">
+        <v>1.93</v>
+      </c>
+      <c r="BM65">
+        <v>2.25</v>
+      </c>
+      <c r="BN65">
+        <v>1.54</v>
+      </c>
+      <c r="BO65">
+        <v>3.1</v>
+      </c>
+      <c r="BP65">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
@@ -13197,22 +13197,22 @@
         <v>3.55</v>
       </c>
       <c r="AU60">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV60">
         <v>5</v>
       </c>
       <c r="AW60">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="AX60">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AY60">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="AZ60">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BA60">
         <v>7</v>
@@ -13406,19 +13406,19 @@
         <v>2</v>
       </c>
       <c r="AV61">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AW61">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX61">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="AY61">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AZ61">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="BA61">
         <v>2</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="182">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -394,6 +394,18 @@
     <t>['72']</t>
   </si>
   <si>
+    <t>['61', '90+3']</t>
+  </si>
+  <si>
+    <t>['79']</t>
+  </si>
+  <si>
+    <t>['71', '88']</t>
+  </si>
+  <si>
+    <t>['23', '12', '58']</t>
+  </si>
+  <si>
     <t>['4', '14']</t>
   </si>
   <si>
@@ -539,6 +551,15 @@
   </si>
   <si>
     <t>['6', '54', '57', '66', '80']</t>
+  </si>
+  <si>
+    <t>['45+2', '69', '90']</t>
+  </si>
+  <si>
+    <t>['49']</t>
+  </si>
+  <si>
+    <t>['26']</t>
   </si>
 </sst>
 </file>
@@ -900,7 +921,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP65"/>
+  <dimension ref="A1:BP70"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1156,7 +1177,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="Q2">
         <v>3.2</v>
@@ -1234,7 +1255,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
       <c r="AQ2">
         <v>1.67</v>
@@ -1362,7 +1383,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="Q3">
         <v>3.25</v>
@@ -1443,7 +1464,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ3">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1568,7 +1589,7 @@
         <v>84</v>
       </c>
       <c r="P4" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="Q4">
         <v>3.1</v>
@@ -1646,7 +1667,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AQ4">
         <v>1.17</v>
@@ -1855,7 +1876,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ5">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -1980,7 +2001,7 @@
         <v>85</v>
       </c>
       <c r="P6" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="Q6">
         <v>2.3</v>
@@ -2058,10 +2079,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AQ6">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2186,7 +2207,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="Q7">
         <v>3.4</v>
@@ -2267,7 +2288,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ7">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2392,7 +2413,7 @@
         <v>87</v>
       </c>
       <c r="P8" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="Q8">
         <v>4.1</v>
@@ -2804,7 +2825,7 @@
         <v>89</v>
       </c>
       <c r="P10" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="Q10">
         <v>1.7</v>
@@ -2882,7 +2903,7 @@
         <v>3</v>
       </c>
       <c r="AP10">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
       <c r="AQ10">
         <v>1.17</v>
@@ -3010,7 +3031,7 @@
         <v>84</v>
       </c>
       <c r="P11" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="Q11">
         <v>2.25</v>
@@ -3297,7 +3318,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ12">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AR12">
         <v>1.71</v>
@@ -3503,7 +3524,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ13">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3628,7 +3649,7 @@
         <v>84</v>
       </c>
       <c r="P14" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="Q14">
         <v>3.1</v>
@@ -3706,7 +3727,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AQ14">
         <v>2.6</v>
@@ -3834,7 +3855,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="Q15">
         <v>3.2</v>
@@ -3915,7 +3936,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ15">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AR15">
         <v>1.98</v>
@@ -4040,7 +4061,7 @@
         <v>93</v>
       </c>
       <c r="P16" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="Q16">
         <v>4.79</v>
@@ -4118,10 +4139,10 @@
         <v>3</v>
       </c>
       <c r="AP16">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AQ16">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AR16">
         <v>1.59</v>
@@ -4246,7 +4267,7 @@
         <v>84</v>
       </c>
       <c r="P17" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="Q17">
         <v>4.17</v>
@@ -4658,7 +4679,7 @@
         <v>84</v>
       </c>
       <c r="P19" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="Q19">
         <v>1.72</v>
@@ -4736,10 +4757,10 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AQ19">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5070,7 +5091,7 @@
         <v>96</v>
       </c>
       <c r="P21" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="Q21">
         <v>2.2</v>
@@ -5151,7 +5172,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ21">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AR21">
         <v>2.05</v>
@@ -5276,7 +5297,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="Q22">
         <v>4.75</v>
@@ -5482,7 +5503,7 @@
         <v>98</v>
       </c>
       <c r="P23" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="Q23">
         <v>2.3</v>
@@ -5560,7 +5581,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>0.25</v>
+        <v>0.8</v>
       </c>
       <c r="AQ23">
         <v>0.75</v>
@@ -5688,7 +5709,7 @@
         <v>99</v>
       </c>
       <c r="P24" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="Q24">
         <v>2.25</v>
@@ -5766,7 +5787,7 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AQ24">
         <v>1.67</v>
@@ -5894,7 +5915,7 @@
         <v>100</v>
       </c>
       <c r="P25" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="Q25">
         <v>3.75</v>
@@ -5975,7 +5996,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ25">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AR25">
         <v>0</v>
@@ -6100,7 +6121,7 @@
         <v>101</v>
       </c>
       <c r="P26" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="Q26">
         <v>6.5</v>
@@ -6178,7 +6199,7 @@
         <v>3</v>
       </c>
       <c r="AP26">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AQ26">
         <v>1.5</v>
@@ -6306,7 +6327,7 @@
         <v>102</v>
       </c>
       <c r="P27" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="Q27">
         <v>1.85</v>
@@ -6387,7 +6408,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ27">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AR27">
         <v>2.08</v>
@@ -6512,7 +6533,7 @@
         <v>84</v>
       </c>
       <c r="P28" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="Q28">
         <v>2.5</v>
@@ -6718,7 +6739,7 @@
         <v>103</v>
       </c>
       <c r="P29" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="Q29">
         <v>2.7</v>
@@ -6799,7 +6820,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ29">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AR29">
         <v>1.44</v>
@@ -7002,7 +7023,7 @@
         <v>1.5</v>
       </c>
       <c r="AP30">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AQ30">
         <v>1.5</v>
@@ -7211,7 +7232,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ31">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AR31">
         <v>1.87</v>
@@ -7542,7 +7563,7 @@
         <v>106</v>
       </c>
       <c r="P33" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="Q33">
         <v>2.93</v>
@@ -7748,7 +7769,7 @@
         <v>107</v>
       </c>
       <c r="P34" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="Q34">
         <v>2.26</v>
@@ -7826,10 +7847,10 @@
         <v>1</v>
       </c>
       <c r="AP34">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
       <c r="AQ34">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AR34">
         <v>1.49</v>
@@ -8160,7 +8181,7 @@
         <v>109</v>
       </c>
       <c r="P36" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="Q36">
         <v>6.4</v>
@@ -8238,7 +8259,7 @@
         <v>3</v>
       </c>
       <c r="AP36">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AQ36">
         <v>2.6</v>
@@ -8366,7 +8387,7 @@
         <v>110</v>
       </c>
       <c r="P37" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="Q37">
         <v>3.84</v>
@@ -8447,7 +8468,7 @@
         <v>0.2</v>
       </c>
       <c r="AQ37">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AR37">
         <v>1.04</v>
@@ -8572,7 +8593,7 @@
         <v>84</v>
       </c>
       <c r="P38" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="Q38">
         <v>5.25</v>
@@ -8650,7 +8671,7 @@
         <v>0.33</v>
       </c>
       <c r="AP38">
-        <v>0.25</v>
+        <v>0.8</v>
       </c>
       <c r="AQ38">
         <v>1.67</v>
@@ -8778,7 +8799,7 @@
         <v>111</v>
       </c>
       <c r="P39" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -8984,7 +9005,7 @@
         <v>112</v>
       </c>
       <c r="P40" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="Q40">
         <v>2.85</v>
@@ -9065,7 +9086,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ40">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AR40">
         <v>2.02</v>
@@ -9190,7 +9211,7 @@
         <v>113</v>
       </c>
       <c r="P41" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="Q41">
         <v>4.02</v>
@@ -9271,7 +9292,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ41">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AR41">
         <v>1.76</v>
@@ -9396,7 +9417,7 @@
         <v>84</v>
       </c>
       <c r="P42" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="Q42">
         <v>2.1</v>
@@ -9602,7 +9623,7 @@
         <v>114</v>
       </c>
       <c r="P43" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="Q43">
         <v>2.75</v>
@@ -9808,7 +9829,7 @@
         <v>115</v>
       </c>
       <c r="P44" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="Q44">
         <v>1.68</v>
@@ -9886,7 +9907,7 @@
         <v>1.5</v>
       </c>
       <c r="AP44">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AQ44">
         <v>0.75</v>
@@ -10092,7 +10113,7 @@
         <v>1.5</v>
       </c>
       <c r="AP45">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AQ45">
         <v>1.17</v>
@@ -10220,7 +10241,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="Q46">
         <v>1.91</v>
@@ -10298,10 +10319,10 @@
         <v>1.75</v>
       </c>
       <c r="AP46">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AQ46">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AR46">
         <v>2.31</v>
@@ -10504,10 +10525,10 @@
         <v>2.33</v>
       </c>
       <c r="AP47">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
       <c r="AQ47">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AR47">
         <v>1.71</v>
@@ -10713,7 +10734,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ48">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AR48">
         <v>1.4</v>
@@ -10838,7 +10859,7 @@
         <v>118</v>
       </c>
       <c r="P49" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="Q49">
         <v>3.45</v>
@@ -10916,10 +10937,10 @@
         <v>1.5</v>
       </c>
       <c r="AP49">
-        <v>0.25</v>
+        <v>0.8</v>
       </c>
       <c r="AQ49">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AR49">
         <v>0.93</v>
@@ -11122,10 +11143,10 @@
         <v>0.6</v>
       </c>
       <c r="AP50">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
       <c r="AQ50">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AR50">
         <v>1.72</v>
@@ -11250,7 +11271,7 @@
         <v>84</v>
       </c>
       <c r="P51" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="Q51">
         <v>6.5</v>
@@ -11328,7 +11349,7 @@
         <v>1</v>
       </c>
       <c r="AP51">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AQ51">
         <v>1.67</v>
@@ -11456,7 +11477,7 @@
         <v>84</v>
       </c>
       <c r="P52" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="Q52">
         <v>2.18</v>
@@ -11662,7 +11683,7 @@
         <v>84</v>
       </c>
       <c r="P53" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="Q53">
         <v>3.85</v>
@@ -11868,7 +11889,7 @@
         <v>119</v>
       </c>
       <c r="P54" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="Q54">
         <v>2.66</v>
@@ -12074,7 +12095,7 @@
         <v>120</v>
       </c>
       <c r="P55" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="Q55">
         <v>3</v>
@@ -12280,7 +12301,7 @@
         <v>121</v>
       </c>
       <c r="P56" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="Q56">
         <v>3.35</v>
@@ -12361,7 +12382,7 @@
         <v>0.2</v>
       </c>
       <c r="AQ56">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AR56">
         <v>1.46</v>
@@ -12564,10 +12585,10 @@
         <v>1.75</v>
       </c>
       <c r="AP57">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AQ57">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AR57">
         <v>2.2</v>
@@ -12692,7 +12713,7 @@
         <v>84</v>
       </c>
       <c r="P58" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="Q58">
         <v>3.3</v>
@@ -12898,7 +12919,7 @@
         <v>84</v>
       </c>
       <c r="P59" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="Q59">
         <v>5.5</v>
@@ -12976,7 +12997,7 @@
         <v>2.5</v>
       </c>
       <c r="AP59">
-        <v>0.25</v>
+        <v>0.8</v>
       </c>
       <c r="AQ59">
         <v>2.6</v>
@@ -13104,7 +13125,7 @@
         <v>122</v>
       </c>
       <c r="P60" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="Q60">
         <v>2.11</v>
@@ -13185,7 +13206,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ60">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AR60">
         <v>1.95</v>
@@ -13310,7 +13331,7 @@
         <v>84</v>
       </c>
       <c r="P61" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="Q61">
         <v>4.5</v>
@@ -13516,7 +13537,7 @@
         <v>123</v>
       </c>
       <c r="P62" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="Q62">
         <v>2.26</v>
@@ -13722,7 +13743,7 @@
         <v>84</v>
       </c>
       <c r="P63" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="Q63">
         <v>2.87</v>
@@ -13928,7 +13949,7 @@
         <v>124</v>
       </c>
       <c r="P64" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="Q64">
         <v>1.85</v>
@@ -14134,7 +14155,7 @@
         <v>125</v>
       </c>
       <c r="P65" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="Q65">
         <v>4.28</v>
@@ -14212,7 +14233,7 @@
         <v>1.4</v>
       </c>
       <c r="AP65">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AQ65">
         <v>1.67</v>
@@ -14291,6 +14312,1036 @@
       </c>
       <c r="BP65">
         <v>1.3</v>
+      </c>
+    </row>
+    <row r="66" spans="1:68">
+      <c r="A66" s="1">
+        <v>65</v>
+      </c>
+      <c r="B66">
+        <v>7811541</v>
+      </c>
+      <c r="C66" t="s">
+        <v>68</v>
+      </c>
+      <c r="D66" t="s">
+        <v>69</v>
+      </c>
+      <c r="E66" s="2">
+        <v>45826.45833333334</v>
+      </c>
+      <c r="F66">
+        <v>0</v>
+      </c>
+      <c r="G66" t="s">
+        <v>70</v>
+      </c>
+      <c r="H66" t="s">
+        <v>76</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>1</v>
+      </c>
+      <c r="K66">
+        <v>1</v>
+      </c>
+      <c r="L66">
+        <v>2</v>
+      </c>
+      <c r="M66">
+        <v>3</v>
+      </c>
+      <c r="N66">
+        <v>5</v>
+      </c>
+      <c r="O66" t="s">
+        <v>126</v>
+      </c>
+      <c r="P66" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q66">
+        <v>2.19</v>
+      </c>
+      <c r="R66">
+        <v>2.57</v>
+      </c>
+      <c r="S66">
+        <v>3.95</v>
+      </c>
+      <c r="T66">
+        <v>1.2</v>
+      </c>
+      <c r="U66">
+        <v>3.9</v>
+      </c>
+      <c r="V66">
+        <v>2.02</v>
+      </c>
+      <c r="W66">
+        <v>1.88</v>
+      </c>
+      <c r="X66">
+        <v>3.9</v>
+      </c>
+      <c r="Y66">
+        <v>1.2</v>
+      </c>
+      <c r="Z66">
+        <v>1.55</v>
+      </c>
+      <c r="AA66">
+        <v>4.2</v>
+      </c>
+      <c r="AB66">
+        <v>4.2</v>
+      </c>
+      <c r="AC66">
+        <v>1.01</v>
+      </c>
+      <c r="AD66">
+        <v>23</v>
+      </c>
+      <c r="AE66">
+        <v>1.11</v>
+      </c>
+      <c r="AF66">
+        <v>6.5</v>
+      </c>
+      <c r="AG66">
+        <v>1.46</v>
+      </c>
+      <c r="AH66">
+        <v>2.52</v>
+      </c>
+      <c r="AI66">
+        <v>1.4</v>
+      </c>
+      <c r="AJ66">
+        <v>2.75</v>
+      </c>
+      <c r="AK66">
+        <v>1.22</v>
+      </c>
+      <c r="AL66">
+        <v>1.21</v>
+      </c>
+      <c r="AM66">
+        <v>2.1</v>
+      </c>
+      <c r="AN66">
+        <v>2.6</v>
+      </c>
+      <c r="AO66">
+        <v>1.33</v>
+      </c>
+      <c r="AP66">
+        <v>2.17</v>
+      </c>
+      <c r="AQ66">
+        <v>1.57</v>
+      </c>
+      <c r="AR66">
+        <v>1.76</v>
+      </c>
+      <c r="AS66">
+        <v>1.84</v>
+      </c>
+      <c r="AT66">
+        <v>3.6</v>
+      </c>
+      <c r="AU66">
+        <v>6</v>
+      </c>
+      <c r="AV66">
+        <v>6</v>
+      </c>
+      <c r="AW66">
+        <v>6</v>
+      </c>
+      <c r="AX66">
+        <v>4</v>
+      </c>
+      <c r="AY66">
+        <v>12</v>
+      </c>
+      <c r="AZ66">
+        <v>10</v>
+      </c>
+      <c r="BA66">
+        <v>11</v>
+      </c>
+      <c r="BB66">
+        <v>3</v>
+      </c>
+      <c r="BC66">
+        <v>14</v>
+      </c>
+      <c r="BD66">
+        <v>1.53</v>
+      </c>
+      <c r="BE66">
+        <v>9.5</v>
+      </c>
+      <c r="BF66">
+        <v>3.8</v>
+      </c>
+      <c r="BG66">
+        <v>1.18</v>
+      </c>
+      <c r="BH66">
+        <v>4.1</v>
+      </c>
+      <c r="BI66">
+        <v>1.32</v>
+      </c>
+      <c r="BJ66">
+        <v>2.7</v>
+      </c>
+      <c r="BK66">
+        <v>1.56</v>
+      </c>
+      <c r="BL66">
+        <v>2.2</v>
+      </c>
+      <c r="BM66">
+        <v>1.9</v>
+      </c>
+      <c r="BN66">
+        <v>1.8</v>
+      </c>
+      <c r="BO66">
+        <v>2.42</v>
+      </c>
+      <c r="BP66">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="67" spans="1:68">
+      <c r="A67" s="1">
+        <v>66</v>
+      </c>
+      <c r="B67">
+        <v>7811543</v>
+      </c>
+      <c r="C67" t="s">
+        <v>68</v>
+      </c>
+      <c r="D67" t="s">
+        <v>69</v>
+      </c>
+      <c r="E67" s="2">
+        <v>45826.45833333334</v>
+      </c>
+      <c r="F67">
+        <v>0</v>
+      </c>
+      <c r="G67" t="s">
+        <v>72</v>
+      </c>
+      <c r="H67" t="s">
+        <v>77</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>0</v>
+      </c>
+      <c r="K67">
+        <v>0</v>
+      </c>
+      <c r="L67">
+        <v>1</v>
+      </c>
+      <c r="M67">
+        <v>0</v>
+      </c>
+      <c r="N67">
+        <v>1</v>
+      </c>
+      <c r="O67" t="s">
+        <v>127</v>
+      </c>
+      <c r="P67" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q67">
+        <v>5.49</v>
+      </c>
+      <c r="R67">
+        <v>2.4</v>
+      </c>
+      <c r="S67">
+        <v>2.12</v>
+      </c>
+      <c r="T67">
+        <v>1.32</v>
+      </c>
+      <c r="U67">
+        <v>3.38</v>
+      </c>
+      <c r="V67">
+        <v>2.51</v>
+      </c>
+      <c r="W67">
+        <v>1.56</v>
+      </c>
+      <c r="X67">
+        <v>5.3</v>
+      </c>
+      <c r="Y67">
+        <v>1.11</v>
+      </c>
+      <c r="Z67">
+        <v>6</v>
+      </c>
+      <c r="AA67">
+        <v>4.2</v>
+      </c>
+      <c r="AB67">
+        <v>1.4</v>
+      </c>
+      <c r="AC67">
+        <v>1.04</v>
+      </c>
+      <c r="AD67">
+        <v>12</v>
+      </c>
+      <c r="AE67">
+        <v>1.16</v>
+      </c>
+      <c r="AF67">
+        <v>4.2</v>
+      </c>
+      <c r="AG67">
+        <v>1.61</v>
+      </c>
+      <c r="AH67">
+        <v>2.17</v>
+      </c>
+      <c r="AI67">
+        <v>1.73</v>
+      </c>
+      <c r="AJ67">
+        <v>2.1</v>
+      </c>
+      <c r="AK67">
+        <v>1.25</v>
+      </c>
+      <c r="AL67">
+        <v>1.2</v>
+      </c>
+      <c r="AM67">
+        <v>1.15</v>
+      </c>
+      <c r="AN67">
+        <v>0.67</v>
+      </c>
+      <c r="AO67">
+        <v>1.6</v>
+      </c>
+      <c r="AP67">
+        <v>1</v>
+      </c>
+      <c r="AQ67">
+        <v>1.33</v>
+      </c>
+      <c r="AR67">
+        <v>1.26</v>
+      </c>
+      <c r="AS67">
+        <v>1.36</v>
+      </c>
+      <c r="AT67">
+        <v>2.62</v>
+      </c>
+      <c r="AU67">
+        <v>3</v>
+      </c>
+      <c r="AV67">
+        <v>6</v>
+      </c>
+      <c r="AW67">
+        <v>9</v>
+      </c>
+      <c r="AX67">
+        <v>19</v>
+      </c>
+      <c r="AY67">
+        <v>12</v>
+      </c>
+      <c r="AZ67">
+        <v>25</v>
+      </c>
+      <c r="BA67">
+        <v>2</v>
+      </c>
+      <c r="BB67">
+        <v>10</v>
+      </c>
+      <c r="BC67">
+        <v>12</v>
+      </c>
+      <c r="BD67">
+        <v>3.45</v>
+      </c>
+      <c r="BE67">
+        <v>10</v>
+      </c>
+      <c r="BF67">
+        <v>1.34</v>
+      </c>
+      <c r="BG67">
+        <v>1.19</v>
+      </c>
+      <c r="BH67">
+        <v>3.45</v>
+      </c>
+      <c r="BI67">
+        <v>1.45</v>
+      </c>
+      <c r="BJ67">
+        <v>2.64</v>
+      </c>
+      <c r="BK67">
+        <v>1.77</v>
+      </c>
+      <c r="BL67">
+        <v>1.97</v>
+      </c>
+      <c r="BM67">
+        <v>2.1</v>
+      </c>
+      <c r="BN67">
+        <v>1.65</v>
+      </c>
+      <c r="BO67">
+        <v>2.55</v>
+      </c>
+      <c r="BP67">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="68" spans="1:68">
+      <c r="A68" s="1">
+        <v>67</v>
+      </c>
+      <c r="B68">
+        <v>7811546</v>
+      </c>
+      <c r="C68" t="s">
+        <v>68</v>
+      </c>
+      <c r="D68" t="s">
+        <v>69</v>
+      </c>
+      <c r="E68" s="2">
+        <v>45826.625</v>
+      </c>
+      <c r="F68">
+        <v>0</v>
+      </c>
+      <c r="G68" t="s">
+        <v>80</v>
+      </c>
+      <c r="H68" t="s">
+        <v>79</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>0</v>
+      </c>
+      <c r="K68">
+        <v>0</v>
+      </c>
+      <c r="L68">
+        <v>2</v>
+      </c>
+      <c r="M68">
+        <v>1</v>
+      </c>
+      <c r="N68">
+        <v>3</v>
+      </c>
+      <c r="O68" t="s">
+        <v>128</v>
+      </c>
+      <c r="P68" t="s">
+        <v>180</v>
+      </c>
+      <c r="Q68">
+        <v>3.3</v>
+      </c>
+      <c r="R68">
+        <v>2.05</v>
+      </c>
+      <c r="S68">
+        <v>2.9</v>
+      </c>
+      <c r="T68">
+        <v>1.4</v>
+      </c>
+      <c r="U68">
+        <v>2.9</v>
+      </c>
+      <c r="V68">
+        <v>2.8</v>
+      </c>
+      <c r="W68">
+        <v>1.38</v>
+      </c>
+      <c r="X68">
+        <v>7.25</v>
+      </c>
+      <c r="Y68">
+        <v>1.07</v>
+      </c>
+      <c r="Z68">
+        <v>2.7</v>
+      </c>
+      <c r="AA68">
+        <v>3.32</v>
+      </c>
+      <c r="AB68">
+        <v>2.7</v>
+      </c>
+      <c r="AC68">
+        <v>1.06</v>
+      </c>
+      <c r="AD68">
+        <v>9</v>
+      </c>
+      <c r="AE68">
+        <v>1.32</v>
+      </c>
+      <c r="AF68">
+        <v>3.2</v>
+      </c>
+      <c r="AG68">
+        <v>2.06</v>
+      </c>
+      <c r="AH68">
+        <v>1.84</v>
+      </c>
+      <c r="AI68">
+        <v>1.78</v>
+      </c>
+      <c r="AJ68">
+        <v>2.1</v>
+      </c>
+      <c r="AK68">
+        <v>1.28</v>
+      </c>
+      <c r="AL68">
+        <v>1.32</v>
+      </c>
+      <c r="AM68">
+        <v>1.4</v>
+      </c>
+      <c r="AN68">
+        <v>0.25</v>
+      </c>
+      <c r="AO68">
+        <v>0.67</v>
+      </c>
+      <c r="AP68">
+        <v>0.8</v>
+      </c>
+      <c r="AQ68">
+        <v>0.57</v>
+      </c>
+      <c r="AR68">
+        <v>0.97</v>
+      </c>
+      <c r="AS68">
+        <v>1.22</v>
+      </c>
+      <c r="AT68">
+        <v>2.19</v>
+      </c>
+      <c r="AU68">
+        <v>8</v>
+      </c>
+      <c r="AV68">
+        <v>2</v>
+      </c>
+      <c r="AW68">
+        <v>5</v>
+      </c>
+      <c r="AX68">
+        <v>3</v>
+      </c>
+      <c r="AY68">
+        <v>13</v>
+      </c>
+      <c r="AZ68">
+        <v>5</v>
+      </c>
+      <c r="BA68">
+        <v>8</v>
+      </c>
+      <c r="BB68">
+        <v>4</v>
+      </c>
+      <c r="BC68">
+        <v>12</v>
+      </c>
+      <c r="BD68">
+        <v>2.2</v>
+      </c>
+      <c r="BE68">
+        <v>8</v>
+      </c>
+      <c r="BF68">
+        <v>1.9</v>
+      </c>
+      <c r="BG68">
+        <v>1.28</v>
+      </c>
+      <c r="BH68">
+        <v>3.02</v>
+      </c>
+      <c r="BI68">
+        <v>1.49</v>
+      </c>
+      <c r="BJ68">
+        <v>2.23</v>
+      </c>
+      <c r="BK68">
+        <v>2.04</v>
+      </c>
+      <c r="BL68">
+        <v>1.75</v>
+      </c>
+      <c r="BM68">
+        <v>2.48</v>
+      </c>
+      <c r="BN68">
+        <v>1.49</v>
+      </c>
+      <c r="BO68">
+        <v>3.25</v>
+      </c>
+      <c r="BP68">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="69" spans="1:68">
+      <c r="A69" s="1">
+        <v>68</v>
+      </c>
+      <c r="B69">
+        <v>7811542</v>
+      </c>
+      <c r="C69" t="s">
+        <v>68</v>
+      </c>
+      <c r="D69" t="s">
+        <v>69</v>
+      </c>
+      <c r="E69" s="2">
+        <v>45826.625</v>
+      </c>
+      <c r="F69">
+        <v>0</v>
+      </c>
+      <c r="G69" t="s">
+        <v>78</v>
+      </c>
+      <c r="H69" t="s">
+        <v>75</v>
+      </c>
+      <c r="I69">
+        <v>2</v>
+      </c>
+      <c r="J69">
+        <v>1</v>
+      </c>
+      <c r="K69">
+        <v>3</v>
+      </c>
+      <c r="L69">
+        <v>3</v>
+      </c>
+      <c r="M69">
+        <v>1</v>
+      </c>
+      <c r="N69">
+        <v>4</v>
+      </c>
+      <c r="O69" t="s">
+        <v>129</v>
+      </c>
+      <c r="P69" t="s">
+        <v>181</v>
+      </c>
+      <c r="Q69">
+        <v>2.03</v>
+      </c>
+      <c r="R69">
+        <v>2.49</v>
+      </c>
+      <c r="S69">
+        <v>4.69</v>
+      </c>
+      <c r="T69">
+        <v>1.25</v>
+      </c>
+      <c r="U69">
+        <v>3.6</v>
+      </c>
+      <c r="V69">
+        <v>2.15</v>
+      </c>
+      <c r="W69">
+        <v>1.56</v>
+      </c>
+      <c r="X69">
+        <v>5.3</v>
+      </c>
+      <c r="Y69">
+        <v>1.15</v>
+      </c>
+      <c r="Z69">
+        <v>1.53</v>
+      </c>
+      <c r="AA69">
+        <v>4.4</v>
+      </c>
+      <c r="AB69">
+        <v>6.6</v>
+      </c>
+      <c r="AC69">
+        <v>1.03</v>
+      </c>
+      <c r="AD69">
+        <v>10</v>
+      </c>
+      <c r="AE69">
+        <v>1.11</v>
+      </c>
+      <c r="AF69">
+        <v>4.6</v>
+      </c>
+      <c r="AG69">
+        <v>1.53</v>
+      </c>
+      <c r="AH69">
+        <v>2.4</v>
+      </c>
+      <c r="AI69">
+        <v>1.63</v>
+      </c>
+      <c r="AJ69">
+        <v>2.23</v>
+      </c>
+      <c r="AK69">
+        <v>1.22</v>
+      </c>
+      <c r="AL69">
+        <v>1.17</v>
+      </c>
+      <c r="AM69">
+        <v>2.5</v>
+      </c>
+      <c r="AN69">
+        <v>2</v>
+      </c>
+      <c r="AO69">
+        <v>0.75</v>
+      </c>
+      <c r="AP69">
+        <v>2.17</v>
+      </c>
+      <c r="AQ69">
+        <v>0.6</v>
+      </c>
+      <c r="AR69">
+        <v>1.98</v>
+      </c>
+      <c r="AS69">
+        <v>1.52</v>
+      </c>
+      <c r="AT69">
+        <v>3.5</v>
+      </c>
+      <c r="AU69">
+        <v>11</v>
+      </c>
+      <c r="AV69">
+        <v>5</v>
+      </c>
+      <c r="AW69">
+        <v>5</v>
+      </c>
+      <c r="AX69">
+        <v>7</v>
+      </c>
+      <c r="AY69">
+        <v>16</v>
+      </c>
+      <c r="AZ69">
+        <v>12</v>
+      </c>
+      <c r="BA69">
+        <v>5</v>
+      </c>
+      <c r="BB69">
+        <v>5</v>
+      </c>
+      <c r="BC69">
+        <v>10</v>
+      </c>
+      <c r="BD69">
+        <v>1.22</v>
+      </c>
+      <c r="BE69">
+        <v>7.5</v>
+      </c>
+      <c r="BF69">
+        <v>3.15</v>
+      </c>
+      <c r="BG69">
+        <v>1.13</v>
+      </c>
+      <c r="BH69">
+        <v>4.2</v>
+      </c>
+      <c r="BI69">
+        <v>1.28</v>
+      </c>
+      <c r="BJ69">
+        <v>3.02</v>
+      </c>
+      <c r="BK69">
+        <v>1.71</v>
+      </c>
+      <c r="BL69">
+        <v>2.31</v>
+      </c>
+      <c r="BM69">
+        <v>1.92</v>
+      </c>
+      <c r="BN69">
+        <v>1.82</v>
+      </c>
+      <c r="BO69">
+        <v>2.42</v>
+      </c>
+      <c r="BP69">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="70" spans="1:68">
+      <c r="A70" s="1">
+        <v>69</v>
+      </c>
+      <c r="B70">
+        <v>7811544</v>
+      </c>
+      <c r="C70" t="s">
+        <v>68</v>
+      </c>
+      <c r="D70" t="s">
+        <v>69</v>
+      </c>
+      <c r="E70" s="2">
+        <v>45826.625</v>
+      </c>
+      <c r="F70">
+        <v>0</v>
+      </c>
+      <c r="G70" t="s">
+        <v>74</v>
+      </c>
+      <c r="H70" t="s">
+        <v>81</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>0</v>
+      </c>
+      <c r="K70">
+        <v>0</v>
+      </c>
+      <c r="L70">
+        <v>0</v>
+      </c>
+      <c r="M70">
+        <v>0</v>
+      </c>
+      <c r="N70">
+        <v>0</v>
+      </c>
+      <c r="O70" t="s">
+        <v>84</v>
+      </c>
+      <c r="P70" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q70">
+        <v>2.4</v>
+      </c>
+      <c r="R70">
+        <v>2.3</v>
+      </c>
+      <c r="S70">
+        <v>3.74</v>
+      </c>
+      <c r="T70">
+        <v>1.36</v>
+      </c>
+      <c r="U70">
+        <v>2.9</v>
+      </c>
+      <c r="V70">
+        <v>2.5</v>
+      </c>
+      <c r="W70">
+        <v>1.49</v>
+      </c>
+      <c r="X70">
+        <v>5.8</v>
+      </c>
+      <c r="Y70">
+        <v>1.09</v>
+      </c>
+      <c r="Z70">
+        <v>2.05</v>
+      </c>
+      <c r="AA70">
+        <v>3.6</v>
+      </c>
+      <c r="AB70">
+        <v>3.1</v>
+      </c>
+      <c r="AC70">
+        <v>1.02</v>
+      </c>
+      <c r="AD70">
+        <v>10</v>
+      </c>
+      <c r="AE70">
+        <v>1.25</v>
+      </c>
+      <c r="AF70">
+        <v>3.65</v>
+      </c>
+      <c r="AG70">
+        <v>1.85</v>
+      </c>
+      <c r="AH70">
+        <v>1.95</v>
+      </c>
+      <c r="AI70">
+        <v>1.68</v>
+      </c>
+      <c r="AJ70">
+        <v>2.25</v>
+      </c>
+      <c r="AK70">
+        <v>1.34</v>
+      </c>
+      <c r="AL70">
+        <v>1.27</v>
+      </c>
+      <c r="AM70">
+        <v>1.7</v>
+      </c>
+      <c r="AN70">
+        <v>1.75</v>
+      </c>
+      <c r="AO70">
+        <v>1.4</v>
+      </c>
+      <c r="AP70">
+        <v>1.6</v>
+      </c>
+      <c r="AQ70">
+        <v>1.33</v>
+      </c>
+      <c r="AR70">
+        <v>1.74</v>
+      </c>
+      <c r="AS70">
+        <v>1.35</v>
+      </c>
+      <c r="AT70">
+        <v>3.09</v>
+      </c>
+      <c r="AU70">
+        <v>6</v>
+      </c>
+      <c r="AV70">
+        <v>4</v>
+      </c>
+      <c r="AW70">
+        <v>6</v>
+      </c>
+      <c r="AX70">
+        <v>6</v>
+      </c>
+      <c r="AY70">
+        <v>12</v>
+      </c>
+      <c r="AZ70">
+        <v>10</v>
+      </c>
+      <c r="BA70">
+        <v>10</v>
+      </c>
+      <c r="BB70">
+        <v>4</v>
+      </c>
+      <c r="BC70">
+        <v>14</v>
+      </c>
+      <c r="BD70">
+        <v>1.8</v>
+      </c>
+      <c r="BE70">
+        <v>8.5</v>
+      </c>
+      <c r="BF70">
+        <v>2.51</v>
+      </c>
+      <c r="BG70">
+        <v>1.16</v>
+      </c>
+      <c r="BH70">
+        <v>4.15</v>
+      </c>
+      <c r="BI70">
+        <v>1.36</v>
+      </c>
+      <c r="BJ70">
+        <v>2.65</v>
+      </c>
+      <c r="BK70">
+        <v>1.62</v>
+      </c>
+      <c r="BL70">
+        <v>2.15</v>
+      </c>
+      <c r="BM70">
+        <v>2.02</v>
+      </c>
+      <c r="BN70">
+        <v>1.76</v>
+      </c>
+      <c r="BO70">
+        <v>2.8</v>
+      </c>
+      <c r="BP70">
+        <v>1.36</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
@@ -15075,13 +15075,13 @@
         <v>11</v>
       </c>
       <c r="AV69">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW69">
         <v>5</v>
       </c>
       <c r="AX69">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY69">
         <v>16</v>
@@ -15278,22 +15278,22 @@
         <v>3.09</v>
       </c>
       <c r="AU70">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV70">
         <v>4</v>
       </c>
       <c r="AW70">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX70">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AY70">
         <v>12</v>
       </c>
       <c r="AZ70">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BA70">
         <v>10</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="183">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -403,7 +403,10 @@
     <t>['71', '88']</t>
   </si>
   <si>
-    <t>['23', '12', '58']</t>
+    <t>['23', '13', '58']</t>
+  </si>
+  <si>
+    <t>['18', '44', '82', '61', '90+2']</t>
   </si>
   <si>
     <t>['4', '14']</t>
@@ -921,7 +924,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP70"/>
+  <dimension ref="A1:BP71"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1177,7 +1180,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q2">
         <v>3.2</v>
@@ -1383,7 +1386,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q3">
         <v>3.25</v>
@@ -1461,7 +1464,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AQ3">
         <v>1.33</v>
@@ -1589,7 +1592,7 @@
         <v>84</v>
       </c>
       <c r="P4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q4">
         <v>3.1</v>
@@ -2001,7 +2004,7 @@
         <v>85</v>
       </c>
       <c r="P6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q6">
         <v>2.3</v>
@@ -2207,7 +2210,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q7">
         <v>3.4</v>
@@ -2413,7 +2416,7 @@
         <v>87</v>
       </c>
       <c r="P8" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q8">
         <v>4.1</v>
@@ -2825,7 +2828,7 @@
         <v>89</v>
       </c>
       <c r="P10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q10">
         <v>1.7</v>
@@ -3031,7 +3034,7 @@
         <v>84</v>
       </c>
       <c r="P11" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q11">
         <v>2.25</v>
@@ -3315,7 +3318,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AQ12">
         <v>1.33</v>
@@ -3649,7 +3652,7 @@
         <v>84</v>
       </c>
       <c r="P14" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q14">
         <v>3.1</v>
@@ -3855,7 +3858,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q15">
         <v>3.2</v>
@@ -4061,7 +4064,7 @@
         <v>93</v>
       </c>
       <c r="P16" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q16">
         <v>4.79</v>
@@ -4267,7 +4270,7 @@
         <v>84</v>
       </c>
       <c r="P17" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q17">
         <v>4.17</v>
@@ -4679,7 +4682,7 @@
         <v>84</v>
       </c>
       <c r="P19" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q19">
         <v>1.72</v>
@@ -5091,7 +5094,7 @@
         <v>96</v>
       </c>
       <c r="P21" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q21">
         <v>2.2</v>
@@ -5297,7 +5300,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q22">
         <v>4.75</v>
@@ -5503,7 +5506,7 @@
         <v>98</v>
       </c>
       <c r="P23" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q23">
         <v>2.3</v>
@@ -5584,7 +5587,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ23">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AR23">
         <v>0</v>
@@ -5709,7 +5712,7 @@
         <v>99</v>
       </c>
       <c r="P24" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q24">
         <v>2.25</v>
@@ -5915,7 +5918,7 @@
         <v>100</v>
       </c>
       <c r="P25" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q25">
         <v>3.75</v>
@@ -6121,7 +6124,7 @@
         <v>101</v>
       </c>
       <c r="P26" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q26">
         <v>6.5</v>
@@ -6327,7 +6330,7 @@
         <v>102</v>
       </c>
       <c r="P27" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q27">
         <v>1.85</v>
@@ -6533,7 +6536,7 @@
         <v>84</v>
       </c>
       <c r="P28" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q28">
         <v>2.5</v>
@@ -6739,7 +6742,7 @@
         <v>103</v>
       </c>
       <c r="P29" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q29">
         <v>2.7</v>
@@ -7563,7 +7566,7 @@
         <v>106</v>
       </c>
       <c r="P33" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q33">
         <v>2.93</v>
@@ -7641,7 +7644,7 @@
         <v>0</v>
       </c>
       <c r="AP33">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AQ33">
         <v>1.67</v>
@@ -7769,7 +7772,7 @@
         <v>107</v>
       </c>
       <c r="P34" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q34">
         <v>2.26</v>
@@ -8056,7 +8059,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ35">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AR35">
         <v>1.73</v>
@@ -8181,7 +8184,7 @@
         <v>109</v>
       </c>
       <c r="P36" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q36">
         <v>6.4</v>
@@ -8387,7 +8390,7 @@
         <v>110</v>
       </c>
       <c r="P37" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q37">
         <v>3.84</v>
@@ -8593,7 +8596,7 @@
         <v>84</v>
       </c>
       <c r="P38" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q38">
         <v>5.25</v>
@@ -8799,7 +8802,7 @@
         <v>111</v>
       </c>
       <c r="P39" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -9005,7 +9008,7 @@
         <v>112</v>
       </c>
       <c r="P40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q40">
         <v>2.85</v>
@@ -9211,7 +9214,7 @@
         <v>113</v>
       </c>
       <c r="P41" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q41">
         <v>4.02</v>
@@ -9417,7 +9420,7 @@
         <v>84</v>
       </c>
       <c r="P42" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q42">
         <v>2.1</v>
@@ -9623,7 +9626,7 @@
         <v>114</v>
       </c>
       <c r="P43" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q43">
         <v>2.75</v>
@@ -9701,7 +9704,7 @@
         <v>1</v>
       </c>
       <c r="AP43">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AQ43">
         <v>1.5</v>
@@ -9829,7 +9832,7 @@
         <v>115</v>
       </c>
       <c r="P44" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q44">
         <v>1.68</v>
@@ -9910,7 +9913,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ44">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AR44">
         <v>1.82</v>
@@ -10241,7 +10244,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q46">
         <v>1.91</v>
@@ -10859,7 +10862,7 @@
         <v>118</v>
       </c>
       <c r="P49" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q49">
         <v>3.45</v>
@@ -11271,7 +11274,7 @@
         <v>84</v>
       </c>
       <c r="P51" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q51">
         <v>6.5</v>
@@ -11477,7 +11480,7 @@
         <v>84</v>
       </c>
       <c r="P52" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q52">
         <v>2.18</v>
@@ -11683,7 +11686,7 @@
         <v>84</v>
       </c>
       <c r="P53" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q53">
         <v>3.85</v>
@@ -11889,7 +11892,7 @@
         <v>119</v>
       </c>
       <c r="P54" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q54">
         <v>2.66</v>
@@ -12095,7 +12098,7 @@
         <v>120</v>
       </c>
       <c r="P55" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q55">
         <v>3</v>
@@ -12301,7 +12304,7 @@
         <v>121</v>
       </c>
       <c r="P56" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q56">
         <v>3.35</v>
@@ -12713,7 +12716,7 @@
         <v>84</v>
       </c>
       <c r="P58" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q58">
         <v>3.3</v>
@@ -12919,7 +12922,7 @@
         <v>84</v>
       </c>
       <c r="P59" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q59">
         <v>5.5</v>
@@ -13125,7 +13128,7 @@
         <v>122</v>
       </c>
       <c r="P60" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q60">
         <v>2.11</v>
@@ -13203,7 +13206,7 @@
         <v>0.67</v>
       </c>
       <c r="AP60">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AQ60">
         <v>0.6</v>
@@ -13331,7 +13334,7 @@
         <v>84</v>
       </c>
       <c r="P61" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q61">
         <v>4.5</v>
@@ -13537,7 +13540,7 @@
         <v>123</v>
       </c>
       <c r="P62" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q62">
         <v>2.26</v>
@@ -13618,7 +13621,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ62">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AR62">
         <v>1.67</v>
@@ -13743,7 +13746,7 @@
         <v>84</v>
       </c>
       <c r="P63" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q63">
         <v>2.87</v>
@@ -13949,7 +13952,7 @@
         <v>124</v>
       </c>
       <c r="P64" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q64">
         <v>1.85</v>
@@ -14155,7 +14158,7 @@
         <v>125</v>
       </c>
       <c r="P65" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q65">
         <v>4.28</v>
@@ -14361,7 +14364,7 @@
         <v>126</v>
       </c>
       <c r="P66" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q66">
         <v>2.19</v>
@@ -14773,7 +14776,7 @@
         <v>128</v>
       </c>
       <c r="P68" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q68">
         <v>3.3</v>
@@ -14979,7 +14982,7 @@
         <v>129</v>
       </c>
       <c r="P69" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q69">
         <v>2.03</v>
@@ -15342,6 +15345,212 @@
       </c>
       <c r="BP70">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="71" spans="1:68">
+      <c r="A71" s="1">
+        <v>70</v>
+      </c>
+      <c r="B71">
+        <v>7811545</v>
+      </c>
+      <c r="C71" t="s">
+        <v>68</v>
+      </c>
+      <c r="D71" t="s">
+        <v>69</v>
+      </c>
+      <c r="E71" s="2">
+        <v>45827.5</v>
+      </c>
+      <c r="F71">
+        <v>0</v>
+      </c>
+      <c r="G71" t="s">
+        <v>71</v>
+      </c>
+      <c r="H71" t="s">
+        <v>73</v>
+      </c>
+      <c r="I71">
+        <v>2</v>
+      </c>
+      <c r="J71">
+        <v>0</v>
+      </c>
+      <c r="K71">
+        <v>2</v>
+      </c>
+      <c r="L71">
+        <v>5</v>
+      </c>
+      <c r="M71">
+        <v>0</v>
+      </c>
+      <c r="N71">
+        <v>5</v>
+      </c>
+      <c r="O71" t="s">
+        <v>130</v>
+      </c>
+      <c r="P71" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q71">
+        <v>1.67</v>
+      </c>
+      <c r="R71">
+        <v>2.92</v>
+      </c>
+      <c r="S71">
+        <v>7.5</v>
+      </c>
+      <c r="T71">
+        <v>1.18</v>
+      </c>
+      <c r="U71">
+        <v>4.2</v>
+      </c>
+      <c r="V71">
+        <v>1.9</v>
+      </c>
+      <c r="W71">
+        <v>1.8</v>
+      </c>
+      <c r="X71">
+        <v>3.7</v>
+      </c>
+      <c r="Y71">
+        <v>1.22</v>
+      </c>
+      <c r="Z71">
+        <v>1.27</v>
+      </c>
+      <c r="AA71">
+        <v>6.5</v>
+      </c>
+      <c r="AB71">
+        <v>11</v>
+      </c>
+      <c r="AC71">
+        <v>1.01</v>
+      </c>
+      <c r="AD71">
+        <v>23</v>
+      </c>
+      <c r="AE71">
+        <v>1.11</v>
+      </c>
+      <c r="AF71">
+        <v>6.5</v>
+      </c>
+      <c r="AG71">
+        <v>1.36</v>
+      </c>
+      <c r="AH71">
+        <v>3.17</v>
+      </c>
+      <c r="AI71">
+        <v>1.75</v>
+      </c>
+      <c r="AJ71">
+        <v>1.9</v>
+      </c>
+      <c r="AK71">
+        <v>1.11</v>
+      </c>
+      <c r="AL71">
+        <v>1.12</v>
+      </c>
+      <c r="AM71">
+        <v>4.2</v>
+      </c>
+      <c r="AN71">
+        <v>1.8</v>
+      </c>
+      <c r="AO71">
+        <v>0.75</v>
+      </c>
+      <c r="AP71">
+        <v>2</v>
+      </c>
+      <c r="AQ71">
+        <v>0.6</v>
+      </c>
+      <c r="AR71">
+        <v>1.89</v>
+      </c>
+      <c r="AS71">
+        <v>1.31</v>
+      </c>
+      <c r="AT71">
+        <v>3.2</v>
+      </c>
+      <c r="AU71">
+        <v>11</v>
+      </c>
+      <c r="AV71">
+        <v>5</v>
+      </c>
+      <c r="AW71">
+        <v>12</v>
+      </c>
+      <c r="AX71">
+        <v>6</v>
+      </c>
+      <c r="AY71">
+        <v>23</v>
+      </c>
+      <c r="AZ71">
+        <v>11</v>
+      </c>
+      <c r="BA71">
+        <v>5</v>
+      </c>
+      <c r="BB71">
+        <v>1</v>
+      </c>
+      <c r="BC71">
+        <v>6</v>
+      </c>
+      <c r="BD71">
+        <v>1.13</v>
+      </c>
+      <c r="BE71">
+        <v>12</v>
+      </c>
+      <c r="BF71">
+        <v>7</v>
+      </c>
+      <c r="BG71">
+        <v>1.19</v>
+      </c>
+      <c r="BH71">
+        <v>4.3</v>
+      </c>
+      <c r="BI71">
+        <v>1.38</v>
+      </c>
+      <c r="BJ71">
+        <v>3.05</v>
+      </c>
+      <c r="BK71">
+        <v>1.65</v>
+      </c>
+      <c r="BL71">
+        <v>2.1</v>
+      </c>
+      <c r="BM71">
+        <v>2</v>
+      </c>
+      <c r="BN71">
+        <v>1.7</v>
+      </c>
+      <c r="BO71">
+        <v>2.55</v>
+      </c>
+      <c r="BP71">
+        <v>1.45</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="186">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -409,6 +409,12 @@
     <t>['18', '44', '82', '61', '90+2']</t>
   </si>
   <si>
+    <t>['12', '26']</t>
+  </si>
+  <si>
+    <t>['2', '8', '71']</t>
+  </si>
+  <si>
     <t>['4', '14']</t>
   </si>
   <si>
@@ -563,6 +569,9 @@
   </si>
   <si>
     <t>['26']</t>
+  </si>
+  <si>
+    <t>['45', '90+2']</t>
   </si>
 </sst>
 </file>
@@ -924,7 +933,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP71"/>
+  <dimension ref="A1:BP73"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1180,7 +1189,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="Q2">
         <v>3.2</v>
@@ -1261,7 +1270,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ2">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1386,7 +1395,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="Q3">
         <v>3.25</v>
@@ -1592,7 +1601,7 @@
         <v>84</v>
       </c>
       <c r="P4" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="Q4">
         <v>3.1</v>
@@ -2004,7 +2013,7 @@
         <v>85</v>
       </c>
       <c r="P6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="Q6">
         <v>2.3</v>
@@ -2210,7 +2219,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="Q7">
         <v>3.4</v>
@@ -2416,7 +2425,7 @@
         <v>87</v>
       </c>
       <c r="P8" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="Q8">
         <v>4.1</v>
@@ -2703,7 +2712,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ9">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -2828,7 +2837,7 @@
         <v>89</v>
       </c>
       <c r="P10" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="Q10">
         <v>1.7</v>
@@ -3034,7 +3043,7 @@
         <v>84</v>
       </c>
       <c r="P11" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="Q11">
         <v>2.25</v>
@@ -3524,7 +3533,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AQ13">
         <v>0.57</v>
@@ -3652,7 +3661,7 @@
         <v>84</v>
       </c>
       <c r="P14" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="Q14">
         <v>3.1</v>
@@ -3733,7 +3742,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ14">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="AR14">
         <v>2.17</v>
@@ -3858,7 +3867,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="Q15">
         <v>3.2</v>
@@ -4064,7 +4073,7 @@
         <v>93</v>
       </c>
       <c r="P16" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="Q16">
         <v>4.79</v>
@@ -4270,7 +4279,7 @@
         <v>84</v>
       </c>
       <c r="P17" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="Q17">
         <v>4.17</v>
@@ -4554,7 +4563,7 @@
         <v>1.5</v>
       </c>
       <c r="AP18">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AQ18">
         <v>1.17</v>
@@ -4682,7 +4691,7 @@
         <v>84</v>
       </c>
       <c r="P19" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="Q19">
         <v>1.72</v>
@@ -4966,7 +4975,7 @@
         <v>3</v>
       </c>
       <c r="AP20">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AQ20">
         <v>1.4</v>
@@ -5094,7 +5103,7 @@
         <v>96</v>
       </c>
       <c r="P21" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="Q21">
         <v>2.2</v>
@@ -5300,7 +5309,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="Q22">
         <v>4.75</v>
@@ -5381,7 +5390,7 @@
         <v>0.2</v>
       </c>
       <c r="AQ22">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="AR22">
         <v>0</v>
@@ -5506,7 +5515,7 @@
         <v>98</v>
       </c>
       <c r="P23" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="Q23">
         <v>2.3</v>
@@ -5712,7 +5721,7 @@
         <v>99</v>
       </c>
       <c r="P24" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="Q24">
         <v>2.25</v>
@@ -5918,7 +5927,7 @@
         <v>100</v>
       </c>
       <c r="P25" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="Q25">
         <v>3.75</v>
@@ -5996,7 +6005,7 @@
         <v>1</v>
       </c>
       <c r="AP25">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AQ25">
         <v>1.33</v>
@@ -6124,7 +6133,7 @@
         <v>101</v>
       </c>
       <c r="P26" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="Q26">
         <v>6.5</v>
@@ -6330,7 +6339,7 @@
         <v>102</v>
       </c>
       <c r="P27" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="Q27">
         <v>1.85</v>
@@ -6536,7 +6545,7 @@
         <v>84</v>
       </c>
       <c r="P28" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="Q28">
         <v>2.5</v>
@@ -6742,7 +6751,7 @@
         <v>103</v>
       </c>
       <c r="P29" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="Q29">
         <v>2.7</v>
@@ -7232,7 +7241,7 @@
         <v>3</v>
       </c>
       <c r="AP31">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AQ31">
         <v>1.57</v>
@@ -7438,7 +7447,7 @@
         <v>1.5</v>
       </c>
       <c r="AP32">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AQ32">
         <v>1.4</v>
@@ -7566,7 +7575,7 @@
         <v>106</v>
       </c>
       <c r="P33" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="Q33">
         <v>2.93</v>
@@ -7647,7 +7656,7 @@
         <v>2</v>
       </c>
       <c r="AQ33">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AR33">
         <v>1.89</v>
@@ -7772,7 +7781,7 @@
         <v>107</v>
       </c>
       <c r="P34" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="Q34">
         <v>2.26</v>
@@ -8056,7 +8065,7 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AQ35">
         <v>0.6</v>
@@ -8184,7 +8193,7 @@
         <v>109</v>
       </c>
       <c r="P36" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="Q36">
         <v>6.4</v>
@@ -8265,7 +8274,7 @@
         <v>1</v>
       </c>
       <c r="AQ36">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="AR36">
         <v>1.26</v>
@@ -8390,7 +8399,7 @@
         <v>110</v>
       </c>
       <c r="P37" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="Q37">
         <v>3.84</v>
@@ -8596,7 +8605,7 @@
         <v>84</v>
       </c>
       <c r="P38" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="Q38">
         <v>5.25</v>
@@ -8677,7 +8686,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ38">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AR38">
         <v>1.28</v>
@@ -8802,7 +8811,7 @@
         <v>111</v>
       </c>
       <c r="P39" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -9008,7 +9017,7 @@
         <v>112</v>
       </c>
       <c r="P40" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q40">
         <v>2.85</v>
@@ -9086,7 +9095,7 @@
         <v>2</v>
       </c>
       <c r="AP40">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AQ40">
         <v>1.57</v>
@@ -9214,7 +9223,7 @@
         <v>113</v>
       </c>
       <c r="P41" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="Q41">
         <v>4.02</v>
@@ -9420,7 +9429,7 @@
         <v>84</v>
       </c>
       <c r="P42" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="Q42">
         <v>2.1</v>
@@ -9626,7 +9635,7 @@
         <v>114</v>
       </c>
       <c r="P43" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Q43">
         <v>2.75</v>
@@ -9832,7 +9841,7 @@
         <v>115</v>
       </c>
       <c r="P44" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Q44">
         <v>1.68</v>
@@ -10244,7 +10253,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q46">
         <v>1.91</v>
@@ -10862,7 +10871,7 @@
         <v>118</v>
       </c>
       <c r="P49" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q49">
         <v>3.45</v>
@@ -11274,7 +11283,7 @@
         <v>84</v>
       </c>
       <c r="P51" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q51">
         <v>6.5</v>
@@ -11355,7 +11364,7 @@
         <v>1</v>
       </c>
       <c r="AQ51">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AR51">
         <v>1.2</v>
@@ -11480,7 +11489,7 @@
         <v>84</v>
       </c>
       <c r="P52" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q52">
         <v>2.18</v>
@@ -11558,7 +11567,7 @@
         <v>1.33</v>
       </c>
       <c r="AP52">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AQ52">
         <v>1.67</v>
@@ -11686,7 +11695,7 @@
         <v>84</v>
       </c>
       <c r="P53" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q53">
         <v>3.85</v>
@@ -11767,7 +11776,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ53">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="AR53">
         <v>1.88</v>
@@ -11892,7 +11901,7 @@
         <v>119</v>
       </c>
       <c r="P54" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q54">
         <v>2.66</v>
@@ -12098,7 +12107,7 @@
         <v>120</v>
       </c>
       <c r="P55" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q55">
         <v>3</v>
@@ -12304,7 +12313,7 @@
         <v>121</v>
       </c>
       <c r="P56" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q56">
         <v>3.35</v>
@@ -12716,7 +12725,7 @@
         <v>84</v>
       </c>
       <c r="P58" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q58">
         <v>3.3</v>
@@ -12794,7 +12803,7 @@
         <v>0.75</v>
       </c>
       <c r="AP58">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AQ58">
         <v>1.5</v>
@@ -12922,7 +12931,7 @@
         <v>84</v>
       </c>
       <c r="P59" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q59">
         <v>5.5</v>
@@ -13003,7 +13012,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ59">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="AR59">
         <v>0.99</v>
@@ -13128,7 +13137,7 @@
         <v>122</v>
       </c>
       <c r="P60" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q60">
         <v>2.11</v>
@@ -13334,7 +13343,7 @@
         <v>84</v>
       </c>
       <c r="P61" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q61">
         <v>4.5</v>
@@ -13415,7 +13424,7 @@
         <v>0.2</v>
       </c>
       <c r="AQ61">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AR61">
         <v>1.48</v>
@@ -13540,7 +13549,7 @@
         <v>123</v>
       </c>
       <c r="P62" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q62">
         <v>2.26</v>
@@ -13618,7 +13627,7 @@
         <v>1</v>
       </c>
       <c r="AP62">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AQ62">
         <v>0.6</v>
@@ -13746,7 +13755,7 @@
         <v>84</v>
       </c>
       <c r="P63" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q63">
         <v>2.87</v>
@@ -13824,7 +13833,7 @@
         <v>1.2</v>
       </c>
       <c r="AP63">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AQ63">
         <v>1.5</v>
@@ -13952,7 +13961,7 @@
         <v>124</v>
       </c>
       <c r="P64" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q64">
         <v>1.85</v>
@@ -14158,7 +14167,7 @@
         <v>125</v>
       </c>
       <c r="P65" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q65">
         <v>4.28</v>
@@ -14364,7 +14373,7 @@
         <v>126</v>
       </c>
       <c r="P66" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q66">
         <v>2.19</v>
@@ -14776,7 +14785,7 @@
         <v>128</v>
       </c>
       <c r="P68" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q68">
         <v>3.3</v>
@@ -14982,7 +14991,7 @@
         <v>129</v>
       </c>
       <c r="P69" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q69">
         <v>2.03</v>
@@ -15551,6 +15560,418 @@
       </c>
       <c r="BP71">
         <v>1.45</v>
+      </c>
+    </row>
+    <row r="72" spans="1:68">
+      <c r="A72" s="1">
+        <v>71</v>
+      </c>
+      <c r="B72">
+        <v>7811547</v>
+      </c>
+      <c r="C72" t="s">
+        <v>68</v>
+      </c>
+      <c r="D72" t="s">
+        <v>69</v>
+      </c>
+      <c r="E72" s="2">
+        <v>45835.5</v>
+      </c>
+      <c r="F72">
+        <v>0</v>
+      </c>
+      <c r="G72" t="s">
+        <v>81</v>
+      </c>
+      <c r="H72" t="s">
+        <v>71</v>
+      </c>
+      <c r="I72">
+        <v>2</v>
+      </c>
+      <c r="J72">
+        <v>1</v>
+      </c>
+      <c r="K72">
+        <v>3</v>
+      </c>
+      <c r="L72">
+        <v>2</v>
+      </c>
+      <c r="M72">
+        <v>2</v>
+      </c>
+      <c r="N72">
+        <v>4</v>
+      </c>
+      <c r="O72" t="s">
+        <v>131</v>
+      </c>
+      <c r="P72" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q72">
+        <v>4.6</v>
+      </c>
+      <c r="R72">
+        <v>2.35</v>
+      </c>
+      <c r="S72">
+        <v>2.23</v>
+      </c>
+      <c r="T72">
+        <v>1.27</v>
+      </c>
+      <c r="U72">
+        <v>3.4</v>
+      </c>
+      <c r="V72">
+        <v>2.3</v>
+      </c>
+      <c r="W72">
+        <v>1.55</v>
+      </c>
+      <c r="X72">
+        <v>5.2</v>
+      </c>
+      <c r="Y72">
+        <v>1.12</v>
+      </c>
+      <c r="Z72">
+        <v>4</v>
+      </c>
+      <c r="AA72">
+        <v>3.5</v>
+      </c>
+      <c r="AB72">
+        <v>1.71</v>
+      </c>
+      <c r="AC72">
+        <v>1.01</v>
+      </c>
+      <c r="AD72">
+        <v>12</v>
+      </c>
+      <c r="AE72">
+        <v>1.16</v>
+      </c>
+      <c r="AF72">
+        <v>4.4</v>
+      </c>
+      <c r="AG72">
+        <v>1.66</v>
+      </c>
+      <c r="AH72">
+        <v>2.31</v>
+      </c>
+      <c r="AI72">
+        <v>1.62</v>
+      </c>
+      <c r="AJ72">
+        <v>2.11</v>
+      </c>
+      <c r="AK72">
+        <v>1.25</v>
+      </c>
+      <c r="AL72">
+        <v>1.29</v>
+      </c>
+      <c r="AM72">
+        <v>1.2</v>
+      </c>
+      <c r="AN72">
+        <v>1.4</v>
+      </c>
+      <c r="AO72">
+        <v>2.6</v>
+      </c>
+      <c r="AP72">
+        <v>1.33</v>
+      </c>
+      <c r="AQ72">
+        <v>2.33</v>
+      </c>
+      <c r="AR72">
+        <v>1.7</v>
+      </c>
+      <c r="AS72">
+        <v>1.95</v>
+      </c>
+      <c r="AT72">
+        <v>3.65</v>
+      </c>
+      <c r="AU72">
+        <v>9</v>
+      </c>
+      <c r="AV72">
+        <v>7</v>
+      </c>
+      <c r="AW72">
+        <v>6</v>
+      </c>
+      <c r="AX72">
+        <v>9</v>
+      </c>
+      <c r="AY72">
+        <v>15</v>
+      </c>
+      <c r="AZ72">
+        <v>16</v>
+      </c>
+      <c r="BA72">
+        <v>2</v>
+      </c>
+      <c r="BB72">
+        <v>12</v>
+      </c>
+      <c r="BC72">
+        <v>14</v>
+      </c>
+      <c r="BD72">
+        <v>2.9</v>
+      </c>
+      <c r="BE72">
+        <v>9</v>
+      </c>
+      <c r="BF72">
+        <v>1.57</v>
+      </c>
+      <c r="BG72">
+        <v>1.17</v>
+      </c>
+      <c r="BH72">
+        <v>4.2</v>
+      </c>
+      <c r="BI72">
+        <v>1.33</v>
+      </c>
+      <c r="BJ72">
+        <v>3.05</v>
+      </c>
+      <c r="BK72">
+        <v>1.52</v>
+      </c>
+      <c r="BL72">
+        <v>2.3</v>
+      </c>
+      <c r="BM72">
+        <v>1.91</v>
+      </c>
+      <c r="BN72">
+        <v>1.83</v>
+      </c>
+      <c r="BO72">
+        <v>2.37</v>
+      </c>
+      <c r="BP72">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="73" spans="1:68">
+      <c r="A73" s="1">
+        <v>72</v>
+      </c>
+      <c r="B73">
+        <v>7811548</v>
+      </c>
+      <c r="C73" t="s">
+        <v>68</v>
+      </c>
+      <c r="D73" t="s">
+        <v>69</v>
+      </c>
+      <c r="E73" s="2">
+        <v>45835.58333333334</v>
+      </c>
+      <c r="F73">
+        <v>0</v>
+      </c>
+      <c r="G73" t="s">
+        <v>77</v>
+      </c>
+      <c r="H73" t="s">
+        <v>78</v>
+      </c>
+      <c r="I73">
+        <v>2</v>
+      </c>
+      <c r="J73">
+        <v>0</v>
+      </c>
+      <c r="K73">
+        <v>2</v>
+      </c>
+      <c r="L73">
+        <v>3</v>
+      </c>
+      <c r="M73">
+        <v>0</v>
+      </c>
+      <c r="N73">
+        <v>3</v>
+      </c>
+      <c r="O73" t="s">
+        <v>132</v>
+      </c>
+      <c r="P73" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q73">
+        <v>2.98</v>
+      </c>
+      <c r="R73">
+        <v>2.25</v>
+      </c>
+      <c r="S73">
+        <v>2.93</v>
+      </c>
+      <c r="T73">
+        <v>1.27</v>
+      </c>
+      <c r="U73">
+        <v>3.4</v>
+      </c>
+      <c r="V73">
+        <v>2.44</v>
+      </c>
+      <c r="W73">
+        <v>1.6</v>
+      </c>
+      <c r="X73">
+        <v>5.1</v>
+      </c>
+      <c r="Y73">
+        <v>1.13</v>
+      </c>
+      <c r="Z73">
+        <v>2.59</v>
+      </c>
+      <c r="AA73">
+        <v>3.58</v>
+      </c>
+      <c r="AB73">
+        <v>2.57</v>
+      </c>
+      <c r="AC73">
+        <v>1.03</v>
+      </c>
+      <c r="AD73">
+        <v>13</v>
+      </c>
+      <c r="AE73">
+        <v>1.15</v>
+      </c>
+      <c r="AF73">
+        <v>4.5</v>
+      </c>
+      <c r="AG73">
+        <v>1.63</v>
+      </c>
+      <c r="AH73">
+        <v>2.2</v>
+      </c>
+      <c r="AI73">
+        <v>1.53</v>
+      </c>
+      <c r="AJ73">
+        <v>2.4</v>
+      </c>
+      <c r="AK73">
+        <v>1.5</v>
+      </c>
+      <c r="AL73">
+        <v>1.3</v>
+      </c>
+      <c r="AM73">
+        <v>1.53</v>
+      </c>
+      <c r="AN73">
+        <v>2.14</v>
+      </c>
+      <c r="AO73">
+        <v>1.67</v>
+      </c>
+      <c r="AP73">
+        <v>2.25</v>
+      </c>
+      <c r="AQ73">
+        <v>1.43</v>
+      </c>
+      <c r="AR73">
+        <v>2</v>
+      </c>
+      <c r="AS73">
+        <v>1.99</v>
+      </c>
+      <c r="AT73">
+        <v>3.99</v>
+      </c>
+      <c r="AU73">
+        <v>7</v>
+      </c>
+      <c r="AV73">
+        <v>9</v>
+      </c>
+      <c r="AW73">
+        <v>3</v>
+      </c>
+      <c r="AX73">
+        <v>5</v>
+      </c>
+      <c r="AY73">
+        <v>10</v>
+      </c>
+      <c r="AZ73">
+        <v>14</v>
+      </c>
+      <c r="BA73">
+        <v>7</v>
+      </c>
+      <c r="BB73">
+        <v>3</v>
+      </c>
+      <c r="BC73">
+        <v>10</v>
+      </c>
+      <c r="BD73">
+        <v>2.1</v>
+      </c>
+      <c r="BE73">
+        <v>6.55</v>
+      </c>
+      <c r="BF73">
+        <v>1.93</v>
+      </c>
+      <c r="BG73">
+        <v>1.21</v>
+      </c>
+      <c r="BH73">
+        <v>3.7</v>
+      </c>
+      <c r="BI73">
+        <v>1.4</v>
+      </c>
+      <c r="BJ73">
+        <v>2.65</v>
+      </c>
+      <c r="BK73">
+        <v>1.7</v>
+      </c>
+      <c r="BL73">
+        <v>2</v>
+      </c>
+      <c r="BM73">
+        <v>2.1</v>
+      </c>
+      <c r="BN73">
+        <v>1.71</v>
+      </c>
+      <c r="BO73">
+        <v>2.7</v>
+      </c>
+      <c r="BP73">
+        <v>1.44</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="187">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -413,6 +413,9 @@
   </si>
   <si>
     <t>['2', '8', '71']</t>
+  </si>
+  <si>
+    <t>['18', '6', '16', '64']</t>
   </si>
   <si>
     <t>['4', '14']</t>
@@ -933,7 +936,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP73"/>
+  <dimension ref="A1:BP75"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1189,7 +1192,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q2">
         <v>3.2</v>
@@ -1395,7 +1398,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q3">
         <v>3.25</v>
@@ -1601,7 +1604,7 @@
         <v>84</v>
       </c>
       <c r="P4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q4">
         <v>3.1</v>
@@ -2013,7 +2016,7 @@
         <v>85</v>
       </c>
       <c r="P6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q6">
         <v>2.3</v>
@@ -2219,7 +2222,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q7">
         <v>3.4</v>
@@ -2425,7 +2428,7 @@
         <v>87</v>
       </c>
       <c r="P8" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q8">
         <v>4.1</v>
@@ -2709,7 +2712,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ9">
         <v>1.43</v>
@@ -2837,7 +2840,7 @@
         <v>89</v>
       </c>
       <c r="P10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q10">
         <v>1.7</v>
@@ -3043,7 +3046,7 @@
         <v>84</v>
       </c>
       <c r="P11" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q11">
         <v>2.25</v>
@@ -3124,7 +3127,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ11">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="AR11">
         <v>1.83</v>
@@ -3661,7 +3664,7 @@
         <v>84</v>
       </c>
       <c r="P14" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q14">
         <v>3.1</v>
@@ -3867,7 +3870,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q15">
         <v>3.2</v>
@@ -4073,7 +4076,7 @@
         <v>93</v>
       </c>
       <c r="P16" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q16">
         <v>4.79</v>
@@ -4279,7 +4282,7 @@
         <v>84</v>
       </c>
       <c r="P17" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q17">
         <v>4.17</v>
@@ -4691,7 +4694,7 @@
         <v>84</v>
       </c>
       <c r="P19" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q19">
         <v>1.72</v>
@@ -4769,7 +4772,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AQ19">
         <v>1.33</v>
@@ -4978,7 +4981,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ20">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="AR20">
         <v>1.66</v>
@@ -5103,7 +5106,7 @@
         <v>96</v>
       </c>
       <c r="P21" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q21">
         <v>2.2</v>
@@ -5181,7 +5184,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ21">
         <v>0.57</v>
@@ -5309,7 +5312,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q22">
         <v>4.75</v>
@@ -5515,7 +5518,7 @@
         <v>98</v>
       </c>
       <c r="P23" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q23">
         <v>2.3</v>
@@ -5721,7 +5724,7 @@
         <v>99</v>
       </c>
       <c r="P24" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q24">
         <v>2.25</v>
@@ -5799,7 +5802,7 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AQ24">
         <v>1.67</v>
@@ -5927,7 +5930,7 @@
         <v>100</v>
       </c>
       <c r="P25" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q25">
         <v>3.75</v>
@@ -6133,7 +6136,7 @@
         <v>101</v>
       </c>
       <c r="P26" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q26">
         <v>6.5</v>
@@ -6339,7 +6342,7 @@
         <v>102</v>
       </c>
       <c r="P27" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q27">
         <v>1.85</v>
@@ -6417,7 +6420,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ27">
         <v>0.6</v>
@@ -6545,7 +6548,7 @@
         <v>84</v>
       </c>
       <c r="P28" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q28">
         <v>2.5</v>
@@ -6751,7 +6754,7 @@
         <v>103</v>
       </c>
       <c r="P29" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q29">
         <v>2.7</v>
@@ -7450,7 +7453,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ32">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="AR32">
         <v>1.86</v>
@@ -7575,7 +7578,7 @@
         <v>106</v>
       </c>
       <c r="P33" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q33">
         <v>2.93</v>
@@ -7781,7 +7784,7 @@
         <v>107</v>
       </c>
       <c r="P34" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q34">
         <v>2.26</v>
@@ -8193,7 +8196,7 @@
         <v>109</v>
       </c>
       <c r="P36" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q36">
         <v>6.4</v>
@@ -8399,7 +8402,7 @@
         <v>110</v>
       </c>
       <c r="P37" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q37">
         <v>3.84</v>
@@ -8605,7 +8608,7 @@
         <v>84</v>
       </c>
       <c r="P38" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q38">
         <v>5.25</v>
@@ -8811,7 +8814,7 @@
         <v>111</v>
       </c>
       <c r="P39" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -8889,7 +8892,7 @@
         <v>0.5</v>
       </c>
       <c r="AP39">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ39">
         <v>1.67</v>
@@ -9017,7 +9020,7 @@
         <v>112</v>
       </c>
       <c r="P40" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q40">
         <v>2.85</v>
@@ -9223,7 +9226,7 @@
         <v>113</v>
       </c>
       <c r="P41" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q41">
         <v>4.02</v>
@@ -9429,7 +9432,7 @@
         <v>84</v>
       </c>
       <c r="P42" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q42">
         <v>2.1</v>
@@ -9510,7 +9513,7 @@
         <v>0.2</v>
       </c>
       <c r="AQ42">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="AR42">
         <v>1.2</v>
@@ -9635,7 +9638,7 @@
         <v>114</v>
       </c>
       <c r="P43" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q43">
         <v>2.75</v>
@@ -9841,7 +9844,7 @@
         <v>115</v>
       </c>
       <c r="P44" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q44">
         <v>1.68</v>
@@ -9919,7 +9922,7 @@
         <v>1.5</v>
       </c>
       <c r="AP44">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AQ44">
         <v>0.6</v>
@@ -10253,7 +10256,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q46">
         <v>1.91</v>
@@ -10331,7 +10334,7 @@
         <v>1.75</v>
       </c>
       <c r="AP46">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AQ46">
         <v>1.57</v>
@@ -10871,7 +10874,7 @@
         <v>118</v>
       </c>
       <c r="P49" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q49">
         <v>3.45</v>
@@ -11283,7 +11286,7 @@
         <v>84</v>
       </c>
       <c r="P51" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q51">
         <v>6.5</v>
@@ -11489,7 +11492,7 @@
         <v>84</v>
       </c>
       <c r="P52" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q52">
         <v>2.18</v>
@@ -11695,7 +11698,7 @@
         <v>84</v>
       </c>
       <c r="P53" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q53">
         <v>3.85</v>
@@ -11773,7 +11776,7 @@
         <v>2.33</v>
       </c>
       <c r="AP53">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ53">
         <v>2.33</v>
@@ -11901,7 +11904,7 @@
         <v>119</v>
       </c>
       <c r="P54" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q54">
         <v>2.66</v>
@@ -11982,7 +11985,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ54">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="AR54">
         <v>1.43</v>
@@ -12107,7 +12110,7 @@
         <v>120</v>
       </c>
       <c r="P55" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q55">
         <v>3</v>
@@ -12313,7 +12316,7 @@
         <v>121</v>
       </c>
       <c r="P56" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q56">
         <v>3.35</v>
@@ -12597,7 +12600,7 @@
         <v>1.75</v>
       </c>
       <c r="AP57">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AQ57">
         <v>1.33</v>
@@ -12725,7 +12728,7 @@
         <v>84</v>
       </c>
       <c r="P58" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q58">
         <v>3.3</v>
@@ -12931,7 +12934,7 @@
         <v>84</v>
       </c>
       <c r="P59" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q59">
         <v>5.5</v>
@@ -13137,7 +13140,7 @@
         <v>122</v>
       </c>
       <c r="P60" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q60">
         <v>2.11</v>
@@ -13343,7 +13346,7 @@
         <v>84</v>
       </c>
       <c r="P61" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q61">
         <v>4.5</v>
@@ -13549,7 +13552,7 @@
         <v>123</v>
       </c>
       <c r="P62" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q62">
         <v>2.26</v>
@@ -13755,7 +13758,7 @@
         <v>84</v>
       </c>
       <c r="P63" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q63">
         <v>2.87</v>
@@ -13961,7 +13964,7 @@
         <v>124</v>
       </c>
       <c r="P64" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q64">
         <v>1.85</v>
@@ -14039,7 +14042,7 @@
         <v>1.4</v>
       </c>
       <c r="AP64">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ64">
         <v>1.17</v>
@@ -14167,7 +14170,7 @@
         <v>125</v>
       </c>
       <c r="P65" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q65">
         <v>4.28</v>
@@ -14373,7 +14376,7 @@
         <v>126</v>
       </c>
       <c r="P66" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q66">
         <v>2.19</v>
@@ -14785,7 +14788,7 @@
         <v>128</v>
       </c>
       <c r="P68" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q68">
         <v>3.3</v>
@@ -14991,7 +14994,7 @@
         <v>129</v>
       </c>
       <c r="P69" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q69">
         <v>2.03</v>
@@ -15069,7 +15072,7 @@
         <v>0.75</v>
       </c>
       <c r="AP69">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AQ69">
         <v>0.6</v>
@@ -15609,7 +15612,7 @@
         <v>131</v>
       </c>
       <c r="P72" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q72">
         <v>4.6</v>
@@ -15702,22 +15705,22 @@
         <v>3.65</v>
       </c>
       <c r="AU72">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV72">
+        <v>8</v>
+      </c>
+      <c r="AW72">
         <v>7</v>
       </c>
-      <c r="AW72">
-        <v>6</v>
-      </c>
       <c r="AX72">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AY72">
         <v>15</v>
       </c>
       <c r="AZ72">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="BA72">
         <v>2</v>
@@ -15972,6 +15975,418 @@
       </c>
       <c r="BP73">
         <v>1.44</v>
+      </c>
+    </row>
+    <row r="74" spans="1:68">
+      <c r="A74" s="1">
+        <v>73</v>
+      </c>
+      <c r="B74">
+        <v>7811617</v>
+      </c>
+      <c r="C74" t="s">
+        <v>68</v>
+      </c>
+      <c r="D74" t="s">
+        <v>69</v>
+      </c>
+      <c r="E74" s="2">
+        <v>45836.25</v>
+      </c>
+      <c r="F74">
+        <v>0</v>
+      </c>
+      <c r="G74" t="s">
+        <v>78</v>
+      </c>
+      <c r="H74" t="s">
+        <v>72</v>
+      </c>
+      <c r="I74">
+        <v>3</v>
+      </c>
+      <c r="J74">
+        <v>0</v>
+      </c>
+      <c r="K74">
+        <v>3</v>
+      </c>
+      <c r="L74">
+        <v>4</v>
+      </c>
+      <c r="M74">
+        <v>1</v>
+      </c>
+      <c r="N74">
+        <v>5</v>
+      </c>
+      <c r="O74" t="s">
+        <v>133</v>
+      </c>
+      <c r="P74" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q74">
+        <v>0</v>
+      </c>
+      <c r="R74">
+        <v>0</v>
+      </c>
+      <c r="S74">
+        <v>0</v>
+      </c>
+      <c r="T74">
+        <v>0</v>
+      </c>
+      <c r="U74">
+        <v>0</v>
+      </c>
+      <c r="V74">
+        <v>0</v>
+      </c>
+      <c r="W74">
+        <v>0</v>
+      </c>
+      <c r="X74">
+        <v>0</v>
+      </c>
+      <c r="Y74">
+        <v>0</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+      <c r="AA74">
+        <v>0</v>
+      </c>
+      <c r="AB74">
+        <v>0</v>
+      </c>
+      <c r="AC74">
+        <v>0</v>
+      </c>
+      <c r="AD74">
+        <v>0</v>
+      </c>
+      <c r="AE74">
+        <v>0</v>
+      </c>
+      <c r="AF74">
+        <v>0</v>
+      </c>
+      <c r="AG74">
+        <v>0</v>
+      </c>
+      <c r="AH74">
+        <v>0</v>
+      </c>
+      <c r="AI74">
+        <v>0</v>
+      </c>
+      <c r="AJ74">
+        <v>0</v>
+      </c>
+      <c r="AK74">
+        <v>0</v>
+      </c>
+      <c r="AL74">
+        <v>0</v>
+      </c>
+      <c r="AM74">
+        <v>0</v>
+      </c>
+      <c r="AN74">
+        <v>2.17</v>
+      </c>
+      <c r="AO74">
+        <v>1.4</v>
+      </c>
+      <c r="AP74">
+        <v>2.29</v>
+      </c>
+      <c r="AQ74">
+        <v>1</v>
+      </c>
+      <c r="AR74">
+        <v>2.02</v>
+      </c>
+      <c r="AS74">
+        <v>1.2</v>
+      </c>
+      <c r="AT74">
+        <v>3.22</v>
+      </c>
+      <c r="AU74">
+        <v>-1</v>
+      </c>
+      <c r="AV74">
+        <v>-1</v>
+      </c>
+      <c r="AW74">
+        <v>-1</v>
+      </c>
+      <c r="AX74">
+        <v>-1</v>
+      </c>
+      <c r="AY74">
+        <v>-1</v>
+      </c>
+      <c r="AZ74">
+        <v>-1</v>
+      </c>
+      <c r="BA74">
+        <v>-1</v>
+      </c>
+      <c r="BB74">
+        <v>-1</v>
+      </c>
+      <c r="BC74">
+        <v>-1</v>
+      </c>
+      <c r="BD74">
+        <v>0</v>
+      </c>
+      <c r="BE74">
+        <v>0</v>
+      </c>
+      <c r="BF74">
+        <v>0</v>
+      </c>
+      <c r="BG74">
+        <v>0</v>
+      </c>
+      <c r="BH74">
+        <v>0</v>
+      </c>
+      <c r="BI74">
+        <v>0</v>
+      </c>
+      <c r="BJ74">
+        <v>0</v>
+      </c>
+      <c r="BK74">
+        <v>0</v>
+      </c>
+      <c r="BL74">
+        <v>0</v>
+      </c>
+      <c r="BM74">
+        <v>0</v>
+      </c>
+      <c r="BN74">
+        <v>0</v>
+      </c>
+      <c r="BO74">
+        <v>0</v>
+      </c>
+      <c r="BP74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:68">
+      <c r="A75" s="1">
+        <v>74</v>
+      </c>
+      <c r="B75">
+        <v>7811549</v>
+      </c>
+      <c r="C75" t="s">
+        <v>68</v>
+      </c>
+      <c r="D75" t="s">
+        <v>69</v>
+      </c>
+      <c r="E75" s="2">
+        <v>45836.25</v>
+      </c>
+      <c r="F75">
+        <v>0</v>
+      </c>
+      <c r="G75" t="s">
+        <v>76</v>
+      </c>
+      <c r="H75" t="s">
+        <v>72</v>
+      </c>
+      <c r="I75">
+        <v>3</v>
+      </c>
+      <c r="J75">
+        <v>0</v>
+      </c>
+      <c r="K75">
+        <v>3</v>
+      </c>
+      <c r="L75">
+        <v>4</v>
+      </c>
+      <c r="M75">
+        <v>1</v>
+      </c>
+      <c r="N75">
+        <v>5</v>
+      </c>
+      <c r="O75" t="s">
+        <v>133</v>
+      </c>
+      <c r="P75" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q75">
+        <v>1.77</v>
+      </c>
+      <c r="R75">
+        <v>2.8</v>
+      </c>
+      <c r="S75">
+        <v>6.2</v>
+      </c>
+      <c r="T75">
+        <v>1.2</v>
+      </c>
+      <c r="U75">
+        <v>4.2</v>
+      </c>
+      <c r="V75">
+        <v>1.91</v>
+      </c>
+      <c r="W75">
+        <v>1.75</v>
+      </c>
+      <c r="X75">
+        <v>4.1</v>
+      </c>
+      <c r="Y75">
+        <v>1.22</v>
+      </c>
+      <c r="Z75">
+        <v>1.35</v>
+      </c>
+      <c r="AA75">
+        <v>4.8</v>
+      </c>
+      <c r="AB75">
+        <v>6</v>
+      </c>
+      <c r="AC75">
+        <v>1.01</v>
+      </c>
+      <c r="AD75">
+        <v>19</v>
+      </c>
+      <c r="AE75">
+        <v>1.09</v>
+      </c>
+      <c r="AF75">
+        <v>6.25</v>
+      </c>
+      <c r="AG75">
+        <v>1.33</v>
+      </c>
+      <c r="AH75">
+        <v>2.9</v>
+      </c>
+      <c r="AI75">
+        <v>1.66</v>
+      </c>
+      <c r="AJ75">
+        <v>2.25</v>
+      </c>
+      <c r="AK75">
+        <v>1.11</v>
+      </c>
+      <c r="AL75">
+        <v>1.15</v>
+      </c>
+      <c r="AM75">
+        <v>2.95</v>
+      </c>
+      <c r="AN75">
+        <v>1.67</v>
+      </c>
+      <c r="AO75">
+        <v>1.4</v>
+      </c>
+      <c r="AP75">
+        <v>1.86</v>
+      </c>
+      <c r="AQ75">
+        <v>1</v>
+      </c>
+      <c r="AR75">
+        <v>1.83</v>
+      </c>
+      <c r="AS75">
+        <v>1.2</v>
+      </c>
+      <c r="AT75">
+        <v>3.03</v>
+      </c>
+      <c r="AU75">
+        <v>7</v>
+      </c>
+      <c r="AV75">
+        <v>2</v>
+      </c>
+      <c r="AW75">
+        <v>7</v>
+      </c>
+      <c r="AX75">
+        <v>3</v>
+      </c>
+      <c r="AY75">
+        <v>14</v>
+      </c>
+      <c r="AZ75">
+        <v>5</v>
+      </c>
+      <c r="BA75">
+        <v>11</v>
+      </c>
+      <c r="BB75">
+        <v>3</v>
+      </c>
+      <c r="BC75">
+        <v>14</v>
+      </c>
+      <c r="BD75">
+        <v>1.25</v>
+      </c>
+      <c r="BE75">
+        <v>9.6</v>
+      </c>
+      <c r="BF75">
+        <v>3.7</v>
+      </c>
+      <c r="BG75">
+        <v>1.14</v>
+      </c>
+      <c r="BH75">
+        <v>4.15</v>
+      </c>
+      <c r="BI75">
+        <v>1.34</v>
+      </c>
+      <c r="BJ75">
+        <v>2.9</v>
+      </c>
+      <c r="BK75">
+        <v>1.57</v>
+      </c>
+      <c r="BL75">
+        <v>2.2</v>
+      </c>
+      <c r="BM75">
+        <v>1.97</v>
+      </c>
+      <c r="BN75">
+        <v>1.75</v>
+      </c>
+      <c r="BO75">
+        <v>2.4</v>
+      </c>
+      <c r="BP75">
+        <v>1.51</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="188">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -575,6 +575,9 @@
   </si>
   <si>
     <t>['45', '90+2']</t>
+  </si>
+  <si>
+    <t>['21', '49', '90+3', '88']</t>
   </si>
 </sst>
 </file>
@@ -936,7 +939,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP75"/>
+  <dimension ref="A1:BP76"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2300,7 +2303,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AQ7">
         <v>1.33</v>
@@ -3124,7 +3127,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AQ11">
         <v>1</v>
@@ -3948,7 +3951,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AQ15">
         <v>0.57</v>
@@ -4363,7 +4366,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ17">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AR17">
         <v>1.59</v>
@@ -6217,7 +6220,7 @@
         <v>1</v>
       </c>
       <c r="AQ26">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AR26">
         <v>1.17</v>
@@ -6626,7 +6629,7 @@
         <v>1</v>
       </c>
       <c r="AP28">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AQ28">
         <v>1.17</v>
@@ -7041,7 +7044,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ30">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AR30">
         <v>1.89</v>
@@ -9304,7 +9307,7 @@
         <v>2</v>
       </c>
       <c r="AP41">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AQ41">
         <v>1.33</v>
@@ -9719,7 +9722,7 @@
         <v>2</v>
       </c>
       <c r="AQ43">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AR43">
         <v>2.09</v>
@@ -12188,7 +12191,7 @@
         <v>1.75</v>
       </c>
       <c r="AP55">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AQ55">
         <v>1.67</v>
@@ -12809,7 +12812,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ58">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AR58">
         <v>1.88</v>
@@ -13839,7 +13842,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ63">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AR63">
         <v>2.11</v>
@@ -16326,19 +16329,19 @@
         <v>7</v>
       </c>
       <c r="AV75">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW75">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX75">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY75">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ75">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA75">
         <v>11</v>
@@ -16387,6 +16390,212 @@
       </c>
       <c r="BP75">
         <v>1.51</v>
+      </c>
+    </row>
+    <row r="76" spans="1:68">
+      <c r="A76" s="1">
+        <v>75</v>
+      </c>
+      <c r="B76">
+        <v>7811550</v>
+      </c>
+      <c r="C76" t="s">
+        <v>68</v>
+      </c>
+      <c r="D76" t="s">
+        <v>69</v>
+      </c>
+      <c r="E76" s="2">
+        <v>45836.5</v>
+      </c>
+      <c r="F76">
+        <v>0</v>
+      </c>
+      <c r="G76" t="s">
+        <v>75</v>
+      </c>
+      <c r="H76" t="s">
+        <v>70</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>1</v>
+      </c>
+      <c r="K76">
+        <v>1</v>
+      </c>
+      <c r="L76">
+        <v>0</v>
+      </c>
+      <c r="M76">
+        <v>4</v>
+      </c>
+      <c r="N76">
+        <v>4</v>
+      </c>
+      <c r="O76" t="s">
+        <v>84</v>
+      </c>
+      <c r="P76" t="s">
+        <v>187</v>
+      </c>
+      <c r="Q76">
+        <v>4</v>
+      </c>
+      <c r="R76">
+        <v>2.4</v>
+      </c>
+      <c r="S76">
+        <v>2.25</v>
+      </c>
+      <c r="T76">
+        <v>1.25</v>
+      </c>
+      <c r="U76">
+        <v>3.5</v>
+      </c>
+      <c r="V76">
+        <v>2.15</v>
+      </c>
+      <c r="W76">
+        <v>1.65</v>
+      </c>
+      <c r="X76">
+        <v>4.5</v>
+      </c>
+      <c r="Y76">
+        <v>1.13</v>
+      </c>
+      <c r="Z76">
+        <v>4.1</v>
+      </c>
+      <c r="AA76">
+        <v>3.8</v>
+      </c>
+      <c r="AB76">
+        <v>1.75</v>
+      </c>
+      <c r="AC76">
+        <v>1</v>
+      </c>
+      <c r="AD76">
+        <v>12</v>
+      </c>
+      <c r="AE76">
+        <v>1.11</v>
+      </c>
+      <c r="AF76">
+        <v>5.3</v>
+      </c>
+      <c r="AG76">
+        <v>1.46</v>
+      </c>
+      <c r="AH76">
+        <v>2.63</v>
+      </c>
+      <c r="AI76">
+        <v>1.51</v>
+      </c>
+      <c r="AJ76">
+        <v>2.5</v>
+      </c>
+      <c r="AK76">
+        <v>1.25</v>
+      </c>
+      <c r="AL76">
+        <v>1.26</v>
+      </c>
+      <c r="AM76">
+        <v>1.22</v>
+      </c>
+      <c r="AN76">
+        <v>1.5</v>
+      </c>
+      <c r="AO76">
+        <v>1.5</v>
+      </c>
+      <c r="AP76">
+        <v>1.29</v>
+      </c>
+      <c r="AQ76">
+        <v>1.71</v>
+      </c>
+      <c r="AR76">
+        <v>1.69</v>
+      </c>
+      <c r="AS76">
+        <v>2.12</v>
+      </c>
+      <c r="AT76">
+        <v>3.81</v>
+      </c>
+      <c r="AU76">
+        <v>5</v>
+      </c>
+      <c r="AV76">
+        <v>12</v>
+      </c>
+      <c r="AW76">
+        <v>5</v>
+      </c>
+      <c r="AX76">
+        <v>9</v>
+      </c>
+      <c r="AY76">
+        <v>10</v>
+      </c>
+      <c r="AZ76">
+        <v>21</v>
+      </c>
+      <c r="BA76">
+        <v>3</v>
+      </c>
+      <c r="BB76">
+        <v>9</v>
+      </c>
+      <c r="BC76">
+        <v>12</v>
+      </c>
+      <c r="BD76">
+        <v>2.9</v>
+      </c>
+      <c r="BE76">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF76">
+        <v>1.49</v>
+      </c>
+      <c r="BG76">
+        <v>1.2</v>
+      </c>
+      <c r="BH76">
+        <v>3.95</v>
+      </c>
+      <c r="BI76">
+        <v>1.38</v>
+      </c>
+      <c r="BJ76">
+        <v>2.82</v>
+      </c>
+      <c r="BK76">
+        <v>1.81</v>
+      </c>
+      <c r="BL76">
+        <v>2.21</v>
+      </c>
+      <c r="BM76">
+        <v>2</v>
+      </c>
+      <c r="BN76">
+        <v>1.76</v>
+      </c>
+      <c r="BO76">
+        <v>2.4</v>
+      </c>
+      <c r="BP76">
+        <v>1.47</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="190">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -418,6 +418,9 @@
     <t>['18', '6', '16', '64']</t>
   </si>
   <si>
+    <t>['34', '43', '49']</t>
+  </si>
+  <si>
     <t>['4', '14']</t>
   </si>
   <si>
@@ -578,6 +581,9 @@
   </si>
   <si>
     <t>['21', '49', '90+3', '88']</t>
+  </si>
+  <si>
+    <t>['21', '90+4']</t>
   </si>
 </sst>
 </file>
@@ -939,7 +945,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP76"/>
+  <dimension ref="A1:BP77"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1195,7 +1201,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q2">
         <v>3.2</v>
@@ -1401,7 +1407,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q3">
         <v>3.25</v>
@@ -1607,7 +1613,7 @@
         <v>84</v>
       </c>
       <c r="P4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q4">
         <v>3.1</v>
@@ -1688,7 +1694,7 @@
         <v>1</v>
       </c>
       <c r="AQ4">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1891,7 +1897,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="AQ5">
         <v>1.57</v>
@@ -2019,7 +2025,7 @@
         <v>85</v>
       </c>
       <c r="P6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q6">
         <v>2.3</v>
@@ -2225,7 +2231,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q7">
         <v>3.4</v>
@@ -2431,7 +2437,7 @@
         <v>87</v>
       </c>
       <c r="P8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q8">
         <v>4.1</v>
@@ -2509,7 +2515,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="AQ8">
         <v>1.67</v>
@@ -2843,7 +2849,7 @@
         <v>89</v>
       </c>
       <c r="P10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q10">
         <v>1.7</v>
@@ -2924,7 +2930,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ10">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AR10">
         <v>1.48</v>
@@ -3049,7 +3055,7 @@
         <v>84</v>
       </c>
       <c r="P11" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q11">
         <v>2.25</v>
@@ -3667,7 +3673,7 @@
         <v>84</v>
       </c>
       <c r="P14" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q14">
         <v>3.1</v>
@@ -3873,7 +3879,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q15">
         <v>3.2</v>
@@ -4079,7 +4085,7 @@
         <v>93</v>
       </c>
       <c r="P16" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q16">
         <v>4.79</v>
@@ -4285,7 +4291,7 @@
         <v>84</v>
       </c>
       <c r="P17" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q17">
         <v>4.17</v>
@@ -4363,7 +4369,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="AQ17">
         <v>1.71</v>
@@ -4572,7 +4578,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ18">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AR18">
         <v>1.27</v>
@@ -4697,7 +4703,7 @@
         <v>84</v>
       </c>
       <c r="P19" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q19">
         <v>1.72</v>
@@ -5109,7 +5115,7 @@
         <v>96</v>
       </c>
       <c r="P21" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q21">
         <v>2.2</v>
@@ -5315,7 +5321,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q22">
         <v>4.75</v>
@@ -5521,7 +5527,7 @@
         <v>98</v>
       </c>
       <c r="P23" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q23">
         <v>2.3</v>
@@ -5727,7 +5733,7 @@
         <v>99</v>
       </c>
       <c r="P24" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q24">
         <v>2.25</v>
@@ -5933,7 +5939,7 @@
         <v>100</v>
       </c>
       <c r="P25" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q25">
         <v>3.75</v>
@@ -6139,7 +6145,7 @@
         <v>101</v>
       </c>
       <c r="P26" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q26">
         <v>6.5</v>
@@ -6345,7 +6351,7 @@
         <v>102</v>
       </c>
       <c r="P27" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q27">
         <v>1.85</v>
@@ -6551,7 +6557,7 @@
         <v>84</v>
       </c>
       <c r="P28" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q28">
         <v>2.5</v>
@@ -6632,7 +6638,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ28">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AR28">
         <v>1.83</v>
@@ -6757,7 +6763,7 @@
         <v>103</v>
       </c>
       <c r="P29" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q29">
         <v>2.7</v>
@@ -6835,7 +6841,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="AQ29">
         <v>0.57</v>
@@ -7581,7 +7587,7 @@
         <v>106</v>
       </c>
       <c r="P33" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q33">
         <v>2.93</v>
@@ -7787,7 +7793,7 @@
         <v>107</v>
       </c>
       <c r="P34" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q34">
         <v>2.26</v>
@@ -8199,7 +8205,7 @@
         <v>109</v>
       </c>
       <c r="P36" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q36">
         <v>6.4</v>
@@ -8405,7 +8411,7 @@
         <v>110</v>
       </c>
       <c r="P37" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q37">
         <v>3.84</v>
@@ -8611,7 +8617,7 @@
         <v>84</v>
       </c>
       <c r="P38" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q38">
         <v>5.25</v>
@@ -8817,7 +8823,7 @@
         <v>111</v>
       </c>
       <c r="P39" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -9023,7 +9029,7 @@
         <v>112</v>
       </c>
       <c r="P40" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q40">
         <v>2.85</v>
@@ -9229,7 +9235,7 @@
         <v>113</v>
       </c>
       <c r="P41" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q41">
         <v>4.02</v>
@@ -9435,7 +9441,7 @@
         <v>84</v>
       </c>
       <c r="P42" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q42">
         <v>2.1</v>
@@ -9641,7 +9647,7 @@
         <v>114</v>
       </c>
       <c r="P43" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q43">
         <v>2.75</v>
@@ -9847,7 +9853,7 @@
         <v>115</v>
       </c>
       <c r="P44" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q44">
         <v>1.68</v>
@@ -10134,7 +10140,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ45">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AR45">
         <v>1.67</v>
@@ -10259,7 +10265,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q46">
         <v>1.91</v>
@@ -10749,7 +10755,7 @@
         <v>0.5</v>
       </c>
       <c r="AP48">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="AQ48">
         <v>0.6</v>
@@ -10877,7 +10883,7 @@
         <v>118</v>
       </c>
       <c r="P49" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q49">
         <v>3.45</v>
@@ -11289,7 +11295,7 @@
         <v>84</v>
       </c>
       <c r="P51" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q51">
         <v>6.5</v>
@@ -11495,7 +11501,7 @@
         <v>84</v>
       </c>
       <c r="P52" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q52">
         <v>2.18</v>
@@ -11701,7 +11707,7 @@
         <v>84</v>
       </c>
       <c r="P53" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q53">
         <v>3.85</v>
@@ -11907,7 +11913,7 @@
         <v>119</v>
       </c>
       <c r="P54" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q54">
         <v>2.66</v>
@@ -11985,7 +11991,7 @@
         <v>1.5</v>
       </c>
       <c r="AP54">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="AQ54">
         <v>1</v>
@@ -12113,7 +12119,7 @@
         <v>120</v>
       </c>
       <c r="P55" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q55">
         <v>3</v>
@@ -12319,7 +12325,7 @@
         <v>121</v>
       </c>
       <c r="P56" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q56">
         <v>3.35</v>
@@ -12731,7 +12737,7 @@
         <v>84</v>
       </c>
       <c r="P58" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q58">
         <v>3.3</v>
@@ -12937,7 +12943,7 @@
         <v>84</v>
       </c>
       <c r="P59" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q59">
         <v>5.5</v>
@@ -13143,7 +13149,7 @@
         <v>122</v>
       </c>
       <c r="P60" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q60">
         <v>2.11</v>
@@ -13349,7 +13355,7 @@
         <v>84</v>
       </c>
       <c r="P61" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q61">
         <v>4.5</v>
@@ -13555,7 +13561,7 @@
         <v>123</v>
       </c>
       <c r="P62" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q62">
         <v>2.26</v>
@@ -13761,7 +13767,7 @@
         <v>84</v>
       </c>
       <c r="P63" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q63">
         <v>2.87</v>
@@ -13967,7 +13973,7 @@
         <v>124</v>
       </c>
       <c r="P64" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q64">
         <v>1.85</v>
@@ -14048,7 +14054,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ64">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AR64">
         <v>1.77</v>
@@ -14173,7 +14179,7 @@
         <v>125</v>
       </c>
       <c r="P65" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q65">
         <v>4.28</v>
@@ -14379,7 +14385,7 @@
         <v>126</v>
       </c>
       <c r="P66" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q66">
         <v>2.19</v>
@@ -14791,7 +14797,7 @@
         <v>128</v>
       </c>
       <c r="P68" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q68">
         <v>3.3</v>
@@ -14997,7 +15003,7 @@
         <v>129</v>
       </c>
       <c r="P69" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q69">
         <v>2.03</v>
@@ -15615,7 +15621,7 @@
         <v>131</v>
       </c>
       <c r="P72" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q72">
         <v>4.6</v>
@@ -16439,7 +16445,7 @@
         <v>84</v>
       </c>
       <c r="P76" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -16596,6 +16602,212 @@
       </c>
       <c r="BP76">
         <v>1.47</v>
+      </c>
+    </row>
+    <row r="77" spans="1:68">
+      <c r="A77" s="1">
+        <v>76</v>
+      </c>
+      <c r="B77">
+        <v>7811551</v>
+      </c>
+      <c r="C77" t="s">
+        <v>68</v>
+      </c>
+      <c r="D77" t="s">
+        <v>69</v>
+      </c>
+      <c r="E77" s="2">
+        <v>45836.58333333334</v>
+      </c>
+      <c r="F77">
+        <v>0</v>
+      </c>
+      <c r="G77" t="s">
+        <v>73</v>
+      </c>
+      <c r="H77" t="s">
+        <v>80</v>
+      </c>
+      <c r="I77">
+        <v>2</v>
+      </c>
+      <c r="J77">
+        <v>1</v>
+      </c>
+      <c r="K77">
+        <v>3</v>
+      </c>
+      <c r="L77">
+        <v>3</v>
+      </c>
+      <c r="M77">
+        <v>2</v>
+      </c>
+      <c r="N77">
+        <v>5</v>
+      </c>
+      <c r="O77" t="s">
+        <v>134</v>
+      </c>
+      <c r="P77" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q77">
+        <v>3.28</v>
+      </c>
+      <c r="R77">
+        <v>2.35</v>
+      </c>
+      <c r="S77">
+        <v>3.24</v>
+      </c>
+      <c r="T77">
+        <v>1.35</v>
+      </c>
+      <c r="U77">
+        <v>3.31</v>
+      </c>
+      <c r="V77">
+        <v>2.54</v>
+      </c>
+      <c r="W77">
+        <v>1.5</v>
+      </c>
+      <c r="X77">
+        <v>5.5</v>
+      </c>
+      <c r="Y77">
+        <v>1.09</v>
+      </c>
+      <c r="Z77">
+        <v>2.65</v>
+      </c>
+      <c r="AA77">
+        <v>3.25</v>
+      </c>
+      <c r="AB77">
+        <v>2.73</v>
+      </c>
+      <c r="AC77">
+        <v>1.05</v>
+      </c>
+      <c r="AD77">
+        <v>10</v>
+      </c>
+      <c r="AE77">
+        <v>1.24</v>
+      </c>
+      <c r="AF77">
+        <v>3.74</v>
+      </c>
+      <c r="AG77">
+        <v>1.85</v>
+      </c>
+      <c r="AH77">
+        <v>1.97</v>
+      </c>
+      <c r="AI77">
+        <v>1.57</v>
+      </c>
+      <c r="AJ77">
+        <v>2.25</v>
+      </c>
+      <c r="AK77">
+        <v>1.3</v>
+      </c>
+      <c r="AL77">
+        <v>1.28</v>
+      </c>
+      <c r="AM77">
+        <v>1.44</v>
+      </c>
+      <c r="AN77">
+        <v>0.5</v>
+      </c>
+      <c r="AO77">
+        <v>1.17</v>
+      </c>
+      <c r="AP77">
+        <v>0.86</v>
+      </c>
+      <c r="AQ77">
+        <v>1</v>
+      </c>
+      <c r="AR77">
+        <v>1.66</v>
+      </c>
+      <c r="AS77">
+        <v>1.08</v>
+      </c>
+      <c r="AT77">
+        <v>2.74</v>
+      </c>
+      <c r="AU77">
+        <v>6</v>
+      </c>
+      <c r="AV77">
+        <v>9</v>
+      </c>
+      <c r="AW77">
+        <v>5</v>
+      </c>
+      <c r="AX77">
+        <v>11</v>
+      </c>
+      <c r="AY77">
+        <v>11</v>
+      </c>
+      <c r="AZ77">
+        <v>20</v>
+      </c>
+      <c r="BA77">
+        <v>5</v>
+      </c>
+      <c r="BB77">
+        <v>8</v>
+      </c>
+      <c r="BC77">
+        <v>13</v>
+      </c>
+      <c r="BD77">
+        <v>1.96</v>
+      </c>
+      <c r="BE77">
+        <v>7.4</v>
+      </c>
+      <c r="BF77">
+        <v>2.07</v>
+      </c>
+      <c r="BG77">
+        <v>1.22</v>
+      </c>
+      <c r="BH77">
+        <v>3.35</v>
+      </c>
+      <c r="BI77">
+        <v>1.48</v>
+      </c>
+      <c r="BJ77">
+        <v>2.46</v>
+      </c>
+      <c r="BK77">
+        <v>2.09</v>
+      </c>
+      <c r="BL77">
+        <v>1.94</v>
+      </c>
+      <c r="BM77">
+        <v>2.26</v>
+      </c>
+      <c r="BN77">
+        <v>1.59</v>
+      </c>
+      <c r="BO77">
+        <v>2.9</v>
+      </c>
+      <c r="BP77">
+        <v>1.34</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="192">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -421,6 +421,9 @@
     <t>['34', '43', '49']</t>
   </si>
   <si>
+    <t>['43', '56']</t>
+  </si>
+  <si>
     <t>['4', '14']</t>
   </si>
   <si>
@@ -584,6 +587,9 @@
   </si>
   <si>
     <t>['21', '90+4']</t>
+  </si>
+  <si>
+    <t>['33']</t>
   </si>
 </sst>
 </file>
@@ -945,7 +951,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP77"/>
+  <dimension ref="A1:BP78"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1201,7 +1207,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q2">
         <v>3.2</v>
@@ -1407,7 +1413,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q3">
         <v>3.25</v>
@@ -1613,7 +1619,7 @@
         <v>84</v>
       </c>
       <c r="P4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q4">
         <v>3.1</v>
@@ -2025,7 +2031,7 @@
         <v>85</v>
       </c>
       <c r="P6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q6">
         <v>2.3</v>
@@ -2231,7 +2237,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q7">
         <v>3.4</v>
@@ -2437,7 +2443,7 @@
         <v>87</v>
       </c>
       <c r="P8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q8">
         <v>4.1</v>
@@ -2518,7 +2524,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ8">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AR8">
         <v>1.58</v>
@@ -2849,7 +2855,7 @@
         <v>89</v>
       </c>
       <c r="P10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q10">
         <v>1.7</v>
@@ -3055,7 +3061,7 @@
         <v>84</v>
       </c>
       <c r="P11" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q11">
         <v>2.25</v>
@@ -3673,7 +3679,7 @@
         <v>84</v>
       </c>
       <c r="P14" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q14">
         <v>3.1</v>
@@ -3879,7 +3885,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q15">
         <v>3.2</v>
@@ -4085,7 +4091,7 @@
         <v>93</v>
       </c>
       <c r="P16" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q16">
         <v>4.79</v>
@@ -4291,7 +4297,7 @@
         <v>84</v>
       </c>
       <c r="P17" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q17">
         <v>4.17</v>
@@ -4703,7 +4709,7 @@
         <v>84</v>
       </c>
       <c r="P19" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q19">
         <v>1.72</v>
@@ -5115,7 +5121,7 @@
         <v>96</v>
       </c>
       <c r="P21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q21">
         <v>2.2</v>
@@ -5321,7 +5327,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q22">
         <v>4.75</v>
@@ -5399,7 +5405,7 @@
         <v>3</v>
       </c>
       <c r="AP22">
-        <v>0.2</v>
+        <v>0.67</v>
       </c>
       <c r="AQ22">
         <v>2.33</v>
@@ -5527,7 +5533,7 @@
         <v>98</v>
       </c>
       <c r="P23" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q23">
         <v>2.3</v>
@@ -5733,7 +5739,7 @@
         <v>99</v>
       </c>
       <c r="P24" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q24">
         <v>2.25</v>
@@ -5814,7 +5820,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ24">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AR24">
         <v>1.6</v>
@@ -5939,7 +5945,7 @@
         <v>100</v>
       </c>
       <c r="P25" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q25">
         <v>3.75</v>
@@ -6145,7 +6151,7 @@
         <v>101</v>
       </c>
       <c r="P26" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q26">
         <v>6.5</v>
@@ -6351,7 +6357,7 @@
         <v>102</v>
       </c>
       <c r="P27" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q27">
         <v>1.85</v>
@@ -6557,7 +6563,7 @@
         <v>84</v>
       </c>
       <c r="P28" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q28">
         <v>2.5</v>
@@ -6763,7 +6769,7 @@
         <v>103</v>
       </c>
       <c r="P29" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q29">
         <v>2.7</v>
@@ -7587,7 +7593,7 @@
         <v>106</v>
       </c>
       <c r="P33" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q33">
         <v>2.93</v>
@@ -7793,7 +7799,7 @@
         <v>107</v>
       </c>
       <c r="P34" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q34">
         <v>2.26</v>
@@ -8205,7 +8211,7 @@
         <v>109</v>
       </c>
       <c r="P36" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q36">
         <v>6.4</v>
@@ -8411,7 +8417,7 @@
         <v>110</v>
       </c>
       <c r="P37" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q37">
         <v>3.84</v>
@@ -8489,7 +8495,7 @@
         <v>1</v>
       </c>
       <c r="AP37">
-        <v>0.2</v>
+        <v>0.67</v>
       </c>
       <c r="AQ37">
         <v>1.33</v>
@@ -8617,7 +8623,7 @@
         <v>84</v>
       </c>
       <c r="P38" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q38">
         <v>5.25</v>
@@ -8823,7 +8829,7 @@
         <v>111</v>
       </c>
       <c r="P39" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -8904,7 +8910,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ39">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AR39">
         <v>1.9</v>
@@ -9029,7 +9035,7 @@
         <v>112</v>
       </c>
       <c r="P40" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q40">
         <v>2.85</v>
@@ -9235,7 +9241,7 @@
         <v>113</v>
       </c>
       <c r="P41" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q41">
         <v>4.02</v>
@@ -9441,7 +9447,7 @@
         <v>84</v>
       </c>
       <c r="P42" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q42">
         <v>2.1</v>
@@ -9519,7 +9525,7 @@
         <v>1</v>
       </c>
       <c r="AP42">
-        <v>0.2</v>
+        <v>0.67</v>
       </c>
       <c r="AQ42">
         <v>1</v>
@@ -9647,7 +9653,7 @@
         <v>114</v>
       </c>
       <c r="P43" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q43">
         <v>2.75</v>
@@ -9853,7 +9859,7 @@
         <v>115</v>
       </c>
       <c r="P44" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q44">
         <v>1.68</v>
@@ -10265,7 +10271,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q46">
         <v>1.91</v>
@@ -10883,7 +10889,7 @@
         <v>118</v>
       </c>
       <c r="P49" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q49">
         <v>3.45</v>
@@ -11295,7 +11301,7 @@
         <v>84</v>
       </c>
       <c r="P51" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q51">
         <v>6.5</v>
@@ -11501,7 +11507,7 @@
         <v>84</v>
       </c>
       <c r="P52" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q52">
         <v>2.18</v>
@@ -11582,7 +11588,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ52">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AR52">
         <v>1.97</v>
@@ -11707,7 +11713,7 @@
         <v>84</v>
       </c>
       <c r="P53" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q53">
         <v>3.85</v>
@@ -11913,7 +11919,7 @@
         <v>119</v>
       </c>
       <c r="P54" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q54">
         <v>2.66</v>
@@ -12119,7 +12125,7 @@
         <v>120</v>
       </c>
       <c r="P55" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q55">
         <v>3</v>
@@ -12200,7 +12206,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ55">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AR55">
         <v>1.69</v>
@@ -12325,7 +12331,7 @@
         <v>121</v>
       </c>
       <c r="P56" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q56">
         <v>3.35</v>
@@ -12403,7 +12409,7 @@
         <v>1.4</v>
       </c>
       <c r="AP56">
-        <v>0.2</v>
+        <v>0.67</v>
       </c>
       <c r="AQ56">
         <v>1.57</v>
@@ -12737,7 +12743,7 @@
         <v>84</v>
       </c>
       <c r="P58" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q58">
         <v>3.3</v>
@@ -12943,7 +12949,7 @@
         <v>84</v>
       </c>
       <c r="P59" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q59">
         <v>5.5</v>
@@ -13149,7 +13155,7 @@
         <v>122</v>
       </c>
       <c r="P60" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q60">
         <v>2.11</v>
@@ -13355,7 +13361,7 @@
         <v>84</v>
       </c>
       <c r="P61" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q61">
         <v>4.5</v>
@@ -13433,7 +13439,7 @@
         <v>1.4</v>
       </c>
       <c r="AP61">
-        <v>0.2</v>
+        <v>0.67</v>
       </c>
       <c r="AQ61">
         <v>1.43</v>
@@ -13561,7 +13567,7 @@
         <v>123</v>
       </c>
       <c r="P62" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q62">
         <v>2.26</v>
@@ -13767,7 +13773,7 @@
         <v>84</v>
       </c>
       <c r="P63" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q63">
         <v>2.87</v>
@@ -13973,7 +13979,7 @@
         <v>124</v>
       </c>
       <c r="P64" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q64">
         <v>1.85</v>
@@ -14179,7 +14185,7 @@
         <v>125</v>
       </c>
       <c r="P65" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q65">
         <v>4.28</v>
@@ -14260,7 +14266,7 @@
         <v>1</v>
       </c>
       <c r="AQ65">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AR65">
         <v>1.16</v>
@@ -14385,7 +14391,7 @@
         <v>126</v>
       </c>
       <c r="P66" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q66">
         <v>2.19</v>
@@ -14797,7 +14803,7 @@
         <v>128</v>
       </c>
       <c r="P68" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q68">
         <v>3.3</v>
@@ -15003,7 +15009,7 @@
         <v>129</v>
       </c>
       <c r="P69" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q69">
         <v>2.03</v>
@@ -15621,7 +15627,7 @@
         <v>131</v>
       </c>
       <c r="P72" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q72">
         <v>4.6</v>
@@ -16445,7 +16451,7 @@
         <v>84</v>
       </c>
       <c r="P76" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -16651,7 +16657,7 @@
         <v>134</v>
       </c>
       <c r="P77" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q77">
         <v>3.28</v>
@@ -16765,10 +16771,10 @@
         <v>5</v>
       </c>
       <c r="BB77">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BC77">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD77">
         <v>1.96</v>
@@ -16808,6 +16814,212 @@
       </c>
       <c r="BP77">
         <v>1.34</v>
+      </c>
+    </row>
+    <row r="78" spans="1:68">
+      <c r="A78" s="1">
+        <v>77</v>
+      </c>
+      <c r="B78">
+        <v>7811552</v>
+      </c>
+      <c r="C78" t="s">
+        <v>68</v>
+      </c>
+      <c r="D78" t="s">
+        <v>69</v>
+      </c>
+      <c r="E78" s="2">
+        <v>45836.70833333334</v>
+      </c>
+      <c r="F78">
+        <v>0</v>
+      </c>
+      <c r="G78" t="s">
+        <v>79</v>
+      </c>
+      <c r="H78" t="s">
+        <v>74</v>
+      </c>
+      <c r="I78">
+        <v>1</v>
+      </c>
+      <c r="J78">
+        <v>1</v>
+      </c>
+      <c r="K78">
+        <v>2</v>
+      </c>
+      <c r="L78">
+        <v>2</v>
+      </c>
+      <c r="M78">
+        <v>1</v>
+      </c>
+      <c r="N78">
+        <v>3</v>
+      </c>
+      <c r="O78" t="s">
+        <v>135</v>
+      </c>
+      <c r="P78" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q78">
+        <v>3.6</v>
+      </c>
+      <c r="R78">
+        <v>2.07</v>
+      </c>
+      <c r="S78">
+        <v>2.85</v>
+      </c>
+      <c r="T78">
+        <v>1.42</v>
+      </c>
+      <c r="U78">
+        <v>2.8</v>
+      </c>
+      <c r="V78">
+        <v>2.96</v>
+      </c>
+      <c r="W78">
+        <v>1.4</v>
+      </c>
+      <c r="X78">
+        <v>7.3</v>
+      </c>
+      <c r="Y78">
+        <v>1.1</v>
+      </c>
+      <c r="Z78">
+        <v>2.73</v>
+      </c>
+      <c r="AA78">
+        <v>3.23</v>
+      </c>
+      <c r="AB78">
+        <v>2.25</v>
+      </c>
+      <c r="AC78">
+        <v>1.01</v>
+      </c>
+      <c r="AD78">
+        <v>9.65</v>
+      </c>
+      <c r="AE78">
+        <v>1.31</v>
+      </c>
+      <c r="AF78">
+        <v>3.6</v>
+      </c>
+      <c r="AG78">
+        <v>1.88</v>
+      </c>
+      <c r="AH78">
+        <v>1.82</v>
+      </c>
+      <c r="AI78">
+        <v>1.73</v>
+      </c>
+      <c r="AJ78">
+        <v>2.07</v>
+      </c>
+      <c r="AK78">
+        <v>1.33</v>
+      </c>
+      <c r="AL78">
+        <v>1.32</v>
+      </c>
+      <c r="AM78">
+        <v>1.39</v>
+      </c>
+      <c r="AN78">
+        <v>0.2</v>
+      </c>
+      <c r="AO78">
+        <v>1.67</v>
+      </c>
+      <c r="AP78">
+        <v>0.67</v>
+      </c>
+      <c r="AQ78">
+        <v>1.43</v>
+      </c>
+      <c r="AR78">
+        <v>1.34</v>
+      </c>
+      <c r="AS78">
+        <v>1.26</v>
+      </c>
+      <c r="AT78">
+        <v>2.6</v>
+      </c>
+      <c r="AU78">
+        <v>8</v>
+      </c>
+      <c r="AV78">
+        <v>6</v>
+      </c>
+      <c r="AW78">
+        <v>5</v>
+      </c>
+      <c r="AX78">
+        <v>2</v>
+      </c>
+      <c r="AY78">
+        <v>13</v>
+      </c>
+      <c r="AZ78">
+        <v>8</v>
+      </c>
+      <c r="BA78">
+        <v>5</v>
+      </c>
+      <c r="BB78">
+        <v>5</v>
+      </c>
+      <c r="BC78">
+        <v>10</v>
+      </c>
+      <c r="BD78">
+        <v>2.05</v>
+      </c>
+      <c r="BE78">
+        <v>6.5</v>
+      </c>
+      <c r="BF78">
+        <v>2.1</v>
+      </c>
+      <c r="BG78">
+        <v>1.28</v>
+      </c>
+      <c r="BH78">
+        <v>3.22</v>
+      </c>
+      <c r="BI78">
+        <v>1.52</v>
+      </c>
+      <c r="BJ78">
+        <v>2.42</v>
+      </c>
+      <c r="BK78">
+        <v>2.15</v>
+      </c>
+      <c r="BL78">
+        <v>1.88</v>
+      </c>
+      <c r="BM78">
+        <v>2.38</v>
+      </c>
+      <c r="BN78">
+        <v>1.53</v>
+      </c>
+      <c r="BO78">
+        <v>3.05</v>
+      </c>
+      <c r="BP78">
+        <v>1.33</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
@@ -16750,19 +16750,19 @@
         <v>2.74</v>
       </c>
       <c r="AU77">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV77">
+        <v>11</v>
+      </c>
+      <c r="AW77">
+        <v>2</v>
+      </c>
+      <c r="AX77">
         <v>9</v>
       </c>
-      <c r="AW77">
-        <v>5</v>
-      </c>
-      <c r="AX77">
-        <v>11</v>
-      </c>
       <c r="AY77">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ77">
         <v>20</v>
@@ -16956,22 +16956,22 @@
         <v>2.6</v>
       </c>
       <c r="AU78">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV78">
         <v>6</v>
       </c>
       <c r="AW78">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AX78">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY78">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ78">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA78">
         <v>5</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
@@ -16132,31 +16132,31 @@
         <v>3.22</v>
       </c>
       <c r="AU74">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AV74">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AW74">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AX74">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AY74">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AZ74">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BA74">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="BB74">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BC74">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="BD74">
         <v>0</v>
@@ -16341,19 +16341,19 @@
         <v>7</v>
       </c>
       <c r="AV75">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW75">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX75">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY75">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ75">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BA75">
         <v>11</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
@@ -16341,19 +16341,19 @@
         <v>7</v>
       </c>
       <c r="AV75">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW75">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX75">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY75">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ75">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA75">
         <v>11</v>
@@ -16750,22 +16750,22 @@
         <v>2.74</v>
       </c>
       <c r="AU77">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV77">
         <v>11</v>
       </c>
       <c r="AW77">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX77">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY77">
         <v>9</v>
       </c>
       <c r="AZ77">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA77">
         <v>5</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
@@ -16956,22 +16956,22 @@
         <v>2.6</v>
       </c>
       <c r="AU78">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV78">
         <v>6</v>
       </c>
       <c r="AW78">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AX78">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY78">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ78">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA78">
         <v>5</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
@@ -16750,22 +16750,22 @@
         <v>2.74</v>
       </c>
       <c r="AU77">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV77">
         <v>11</v>
       </c>
       <c r="AW77">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AX77">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AY77">
         <v>9</v>
       </c>
       <c r="AZ77">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA77">
         <v>5</v>
@@ -16956,22 +16956,22 @@
         <v>2.6</v>
       </c>
       <c r="AU78">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV78">
         <v>6</v>
       </c>
       <c r="AW78">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AX78">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY78">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ78">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA78">
         <v>5</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="194">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -424,6 +424,9 @@
     <t>['43', '56']</t>
   </si>
   <si>
+    <t>['41', '37', '45+1', '51', '80', '64']</t>
+  </si>
+  <si>
     <t>['4', '14']</t>
   </si>
   <si>
@@ -590,6 +593,9 @@
   </si>
   <si>
     <t>['33']</t>
+  </si>
+  <si>
+    <t>['16', '47']</t>
   </si>
 </sst>
 </file>
@@ -951,7 +957,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP78"/>
+  <dimension ref="A1:BP79"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1207,7 +1213,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q2">
         <v>3.2</v>
@@ -1413,7 +1419,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q3">
         <v>3.25</v>
@@ -1619,7 +1625,7 @@
         <v>84</v>
       </c>
       <c r="P4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q4">
         <v>3.1</v>
@@ -2031,7 +2037,7 @@
         <v>85</v>
       </c>
       <c r="P6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q6">
         <v>2.3</v>
@@ -2237,7 +2243,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q7">
         <v>3.4</v>
@@ -2318,7 +2324,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ7">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2443,7 +2449,7 @@
         <v>87</v>
       </c>
       <c r="P8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q8">
         <v>4.1</v>
@@ -2855,7 +2861,7 @@
         <v>89</v>
       </c>
       <c r="P10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q10">
         <v>1.7</v>
@@ -3061,7 +3067,7 @@
         <v>84</v>
       </c>
       <c r="P11" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q11">
         <v>2.25</v>
@@ -3348,7 +3354,7 @@
         <v>2</v>
       </c>
       <c r="AQ12">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR12">
         <v>1.71</v>
@@ -3551,7 +3557,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AQ13">
         <v>0.57</v>
@@ -3679,7 +3685,7 @@
         <v>84</v>
       </c>
       <c r="P14" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q14">
         <v>3.1</v>
@@ -3885,7 +3891,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q15">
         <v>3.2</v>
@@ -4091,7 +4097,7 @@
         <v>93</v>
       </c>
       <c r="P16" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q16">
         <v>4.79</v>
@@ -4297,7 +4303,7 @@
         <v>84</v>
       </c>
       <c r="P17" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q17">
         <v>4.17</v>
@@ -4581,7 +4587,7 @@
         <v>1.5</v>
       </c>
       <c r="AP18">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AQ18">
         <v>1</v>
@@ -4709,7 +4715,7 @@
         <v>84</v>
       </c>
       <c r="P19" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q19">
         <v>1.72</v>
@@ -4790,7 +4796,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ19">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -4993,7 +4999,7 @@
         <v>3</v>
       </c>
       <c r="AP20">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AQ20">
         <v>1</v>
@@ -5121,7 +5127,7 @@
         <v>96</v>
       </c>
       <c r="P21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q21">
         <v>2.2</v>
@@ -5327,7 +5333,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q22">
         <v>4.75</v>
@@ -5533,7 +5539,7 @@
         <v>98</v>
       </c>
       <c r="P23" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q23">
         <v>2.3</v>
@@ -5739,7 +5745,7 @@
         <v>99</v>
       </c>
       <c r="P24" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q24">
         <v>2.25</v>
@@ -5945,7 +5951,7 @@
         <v>100</v>
       </c>
       <c r="P25" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q25">
         <v>3.75</v>
@@ -6151,7 +6157,7 @@
         <v>101</v>
       </c>
       <c r="P26" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q26">
         <v>6.5</v>
@@ -6357,7 +6363,7 @@
         <v>102</v>
       </c>
       <c r="P27" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q27">
         <v>1.85</v>
@@ -6563,7 +6569,7 @@
         <v>84</v>
       </c>
       <c r="P28" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q28">
         <v>2.5</v>
@@ -6769,7 +6775,7 @@
         <v>103</v>
       </c>
       <c r="P29" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q29">
         <v>2.7</v>
@@ -7259,7 +7265,7 @@
         <v>3</v>
       </c>
       <c r="AP31">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AQ31">
         <v>1.57</v>
@@ -7593,7 +7599,7 @@
         <v>106</v>
       </c>
       <c r="P33" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q33">
         <v>2.93</v>
@@ -7799,7 +7805,7 @@
         <v>107</v>
       </c>
       <c r="P34" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q34">
         <v>2.26</v>
@@ -8083,7 +8089,7 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AQ35">
         <v>0.6</v>
@@ -8211,7 +8217,7 @@
         <v>109</v>
       </c>
       <c r="P36" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q36">
         <v>6.4</v>
@@ -8417,7 +8423,7 @@
         <v>110</v>
       </c>
       <c r="P37" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q37">
         <v>3.84</v>
@@ -8498,7 +8504,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ37">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR37">
         <v>1.04</v>
@@ -8623,7 +8629,7 @@
         <v>84</v>
       </c>
       <c r="P38" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q38">
         <v>5.25</v>
@@ -8829,7 +8835,7 @@
         <v>111</v>
       </c>
       <c r="P39" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -9035,7 +9041,7 @@
         <v>112</v>
       </c>
       <c r="P40" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q40">
         <v>2.85</v>
@@ -9241,7 +9247,7 @@
         <v>113</v>
       </c>
       <c r="P41" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q41">
         <v>4.02</v>
@@ -9447,7 +9453,7 @@
         <v>84</v>
       </c>
       <c r="P42" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q42">
         <v>2.1</v>
@@ -9653,7 +9659,7 @@
         <v>114</v>
       </c>
       <c r="P43" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q43">
         <v>2.75</v>
@@ -9859,7 +9865,7 @@
         <v>115</v>
       </c>
       <c r="P44" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q44">
         <v>1.68</v>
@@ -10271,7 +10277,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q46">
         <v>1.91</v>
@@ -10889,7 +10895,7 @@
         <v>118</v>
       </c>
       <c r="P49" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q49">
         <v>3.45</v>
@@ -10970,7 +10976,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ49">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR49">
         <v>0.93</v>
@@ -11301,7 +11307,7 @@
         <v>84</v>
       </c>
       <c r="P51" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q51">
         <v>6.5</v>
@@ -11507,7 +11513,7 @@
         <v>84</v>
       </c>
       <c r="P52" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q52">
         <v>2.18</v>
@@ -11585,7 +11591,7 @@
         <v>1.33</v>
       </c>
       <c r="AP52">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AQ52">
         <v>1.43</v>
@@ -11713,7 +11719,7 @@
         <v>84</v>
       </c>
       <c r="P53" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q53">
         <v>3.85</v>
@@ -11919,7 +11925,7 @@
         <v>119</v>
       </c>
       <c r="P54" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q54">
         <v>2.66</v>
@@ -12125,7 +12131,7 @@
         <v>120</v>
       </c>
       <c r="P55" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q55">
         <v>3</v>
@@ -12331,7 +12337,7 @@
         <v>121</v>
       </c>
       <c r="P56" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q56">
         <v>3.35</v>
@@ -12743,7 +12749,7 @@
         <v>84</v>
       </c>
       <c r="P58" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q58">
         <v>3.3</v>
@@ -12949,7 +12955,7 @@
         <v>84</v>
       </c>
       <c r="P59" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q59">
         <v>5.5</v>
@@ -13155,7 +13161,7 @@
         <v>122</v>
       </c>
       <c r="P60" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q60">
         <v>2.11</v>
@@ -13361,7 +13367,7 @@
         <v>84</v>
       </c>
       <c r="P61" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q61">
         <v>4.5</v>
@@ -13567,7 +13573,7 @@
         <v>123</v>
       </c>
       <c r="P62" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q62">
         <v>2.26</v>
@@ -13773,7 +13779,7 @@
         <v>84</v>
       </c>
       <c r="P63" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q63">
         <v>2.87</v>
@@ -13851,7 +13857,7 @@
         <v>1.2</v>
       </c>
       <c r="AP63">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AQ63">
         <v>1.71</v>
@@ -13979,7 +13985,7 @@
         <v>124</v>
       </c>
       <c r="P64" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q64">
         <v>1.85</v>
@@ -14185,7 +14191,7 @@
         <v>125</v>
       </c>
       <c r="P65" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q65">
         <v>4.28</v>
@@ -14391,7 +14397,7 @@
         <v>126</v>
       </c>
       <c r="P66" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q66">
         <v>2.19</v>
@@ -14803,7 +14809,7 @@
         <v>128</v>
       </c>
       <c r="P68" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q68">
         <v>3.3</v>
@@ -15009,7 +15015,7 @@
         <v>129</v>
       </c>
       <c r="P69" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q69">
         <v>2.03</v>
@@ -15296,7 +15302,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ70">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR70">
         <v>1.74</v>
@@ -15627,7 +15633,7 @@
         <v>131</v>
       </c>
       <c r="P72" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q72">
         <v>4.6</v>
@@ -15911,7 +15917,7 @@
         <v>1.67</v>
       </c>
       <c r="AP73">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AQ73">
         <v>1.43</v>
@@ -16451,7 +16457,7 @@
         <v>84</v>
       </c>
       <c r="P76" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -16657,7 +16663,7 @@
         <v>134</v>
       </c>
       <c r="P77" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q77">
         <v>3.28</v>
@@ -16863,7 +16869,7 @@
         <v>135</v>
       </c>
       <c r="P78" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q78">
         <v>3.6</v>
@@ -17020,6 +17026,212 @@
       </c>
       <c r="BP78">
         <v>1.33</v>
+      </c>
+    </row>
+    <row r="79" spans="1:68">
+      <c r="A79" s="1">
+        <v>78</v>
+      </c>
+      <c r="B79">
+        <v>7811554</v>
+      </c>
+      <c r="C79" t="s">
+        <v>68</v>
+      </c>
+      <c r="D79" t="s">
+        <v>69</v>
+      </c>
+      <c r="E79" s="2">
+        <v>45839.5</v>
+      </c>
+      <c r="F79">
+        <v>0</v>
+      </c>
+      <c r="G79" t="s">
+        <v>77</v>
+      </c>
+      <c r="H79" t="s">
+        <v>81</v>
+      </c>
+      <c r="I79">
+        <v>3</v>
+      </c>
+      <c r="J79">
+        <v>1</v>
+      </c>
+      <c r="K79">
+        <v>4</v>
+      </c>
+      <c r="L79">
+        <v>6</v>
+      </c>
+      <c r="M79">
+        <v>2</v>
+      </c>
+      <c r="N79">
+        <v>8</v>
+      </c>
+      <c r="O79" t="s">
+        <v>136</v>
+      </c>
+      <c r="P79" t="s">
+        <v>193</v>
+      </c>
+      <c r="Q79">
+        <v>2.17</v>
+      </c>
+      <c r="R79">
+        <v>2.45</v>
+      </c>
+      <c r="S79">
+        <v>4.35</v>
+      </c>
+      <c r="T79">
+        <v>1.25</v>
+      </c>
+      <c r="U79">
+        <v>3.5</v>
+      </c>
+      <c r="V79">
+        <v>2.31</v>
+      </c>
+      <c r="W79">
+        <v>1.66</v>
+      </c>
+      <c r="X79">
+        <v>4.9</v>
+      </c>
+      <c r="Y79">
+        <v>1.14</v>
+      </c>
+      <c r="Z79">
+        <v>1.6</v>
+      </c>
+      <c r="AA79">
+        <v>3.9</v>
+      </c>
+      <c r="AB79">
+        <v>5.11</v>
+      </c>
+      <c r="AC79">
+        <v>1.03</v>
+      </c>
+      <c r="AD79">
+        <v>14.3</v>
+      </c>
+      <c r="AE79">
+        <v>1.15</v>
+      </c>
+      <c r="AF79">
+        <v>5</v>
+      </c>
+      <c r="AG79">
+        <v>1.53</v>
+      </c>
+      <c r="AH79">
+        <v>2.4</v>
+      </c>
+      <c r="AI79">
+        <v>1.62</v>
+      </c>
+      <c r="AJ79">
+        <v>2.25</v>
+      </c>
+      <c r="AK79">
+        <v>1.25</v>
+      </c>
+      <c r="AL79">
+        <v>1.23</v>
+      </c>
+      <c r="AM79">
+        <v>2.25</v>
+      </c>
+      <c r="AN79">
+        <v>2.25</v>
+      </c>
+      <c r="AO79">
+        <v>1.33</v>
+      </c>
+      <c r="AP79">
+        <v>2.33</v>
+      </c>
+      <c r="AQ79">
+        <v>1.14</v>
+      </c>
+      <c r="AR79">
+        <v>1.93</v>
+      </c>
+      <c r="AS79">
+        <v>1.35</v>
+      </c>
+      <c r="AT79">
+        <v>3.28</v>
+      </c>
+      <c r="AU79">
+        <v>9</v>
+      </c>
+      <c r="AV79">
+        <v>8</v>
+      </c>
+      <c r="AW79">
+        <v>8</v>
+      </c>
+      <c r="AX79">
+        <v>3</v>
+      </c>
+      <c r="AY79">
+        <v>17</v>
+      </c>
+      <c r="AZ79">
+        <v>11</v>
+      </c>
+      <c r="BA79">
+        <v>7</v>
+      </c>
+      <c r="BB79">
+        <v>2</v>
+      </c>
+      <c r="BC79">
+        <v>9</v>
+      </c>
+      <c r="BD79">
+        <v>1.45</v>
+      </c>
+      <c r="BE79">
+        <v>8.5</v>
+      </c>
+      <c r="BF79">
+        <v>3.52</v>
+      </c>
+      <c r="BG79">
+        <v>1.18</v>
+      </c>
+      <c r="BH79">
+        <v>4.1</v>
+      </c>
+      <c r="BI79">
+        <v>1.25</v>
+      </c>
+      <c r="BJ79">
+        <v>3.05</v>
+      </c>
+      <c r="BK79">
+        <v>1.6</v>
+      </c>
+      <c r="BL79">
+        <v>2.44</v>
+      </c>
+      <c r="BM79">
+        <v>1.83</v>
+      </c>
+      <c r="BN79">
+        <v>1.85</v>
+      </c>
+      <c r="BO79">
+        <v>2.23</v>
+      </c>
+      <c r="BP79">
+        <v>1.56</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
@@ -17168,31 +17168,31 @@
         <v>3.28</v>
       </c>
       <c r="AU79">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AV79">
+        <v>3</v>
+      </c>
+      <c r="AW79">
+        <v>0</v>
+      </c>
+      <c r="AX79">
+        <v>0</v>
+      </c>
+      <c r="AY79">
+        <v>7</v>
+      </c>
+      <c r="AZ79">
+        <v>3</v>
+      </c>
+      <c r="BA79">
         <v>8</v>
       </c>
-      <c r="AW79">
-        <v>8</v>
-      </c>
-      <c r="AX79">
+      <c r="BB79">
         <v>3</v>
       </c>
-      <c r="AY79">
-        <v>17</v>
-      </c>
-      <c r="AZ79">
+      <c r="BC79">
         <v>11</v>
-      </c>
-      <c r="BA79">
-        <v>7</v>
-      </c>
-      <c r="BB79">
-        <v>2</v>
-      </c>
-      <c r="BC79">
-        <v>9</v>
       </c>
       <c r="BD79">
         <v>1.45</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="200">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -427,6 +427,15 @@
     <t>['41', '37', '45+1', '51', '80', '64']</t>
   </si>
   <si>
+    <t>['15', '54']</t>
+  </si>
+  <si>
+    <t>['14', '46']</t>
+  </si>
+  <si>
+    <t>['6']</t>
+  </si>
+  <si>
     <t>['4', '14']</t>
   </si>
   <si>
@@ -596,6 +605,15 @@
   </si>
   <si>
     <t>['16', '47']</t>
+  </si>
+  <si>
+    <t>['61', '56', '90+6']</t>
+  </si>
+  <si>
+    <t>['85']</t>
+  </si>
+  <si>
+    <t>['13', '33']</t>
   </si>
 </sst>
 </file>
@@ -957,7 +975,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP79"/>
+  <dimension ref="A1:BP83"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1213,7 +1231,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="Q2">
         <v>3.2</v>
@@ -1291,7 +1309,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AQ2">
         <v>1.43</v>
@@ -1419,7 +1437,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="Q3">
         <v>3.25</v>
@@ -1497,7 +1515,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ3">
         <v>1.33</v>
@@ -1625,7 +1643,7 @@
         <v>84</v>
       </c>
       <c r="P4" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="Q4">
         <v>3.1</v>
@@ -1706,7 +1724,7 @@
         <v>1</v>
       </c>
       <c r="AQ4">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2037,7 +2055,7 @@
         <v>85</v>
       </c>
       <c r="P6" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="Q6">
         <v>2.3</v>
@@ -2115,7 +2133,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AQ6">
         <v>0.57</v>
@@ -2243,7 +2261,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="Q7">
         <v>3.4</v>
@@ -2449,7 +2467,7 @@
         <v>87</v>
       </c>
       <c r="P8" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="Q8">
         <v>4.1</v>
@@ -2861,7 +2879,7 @@
         <v>89</v>
       </c>
       <c r="P10" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="Q10">
         <v>1.7</v>
@@ -2939,10 +2957,10 @@
         <v>3</v>
       </c>
       <c r="AP10">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AQ10">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AR10">
         <v>1.48</v>
@@ -3067,7 +3085,7 @@
         <v>84</v>
       </c>
       <c r="P11" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="Q11">
         <v>2.25</v>
@@ -3351,7 +3369,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ12">
         <v>1.14</v>
@@ -3685,7 +3703,7 @@
         <v>84</v>
       </c>
       <c r="P14" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="Q14">
         <v>3.1</v>
@@ -3763,7 +3781,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AQ14">
         <v>2.33</v>
@@ -3891,7 +3909,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="Q15">
         <v>3.2</v>
@@ -4097,7 +4115,7 @@
         <v>93</v>
       </c>
       <c r="P16" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="Q16">
         <v>4.79</v>
@@ -4303,7 +4321,7 @@
         <v>84</v>
       </c>
       <c r="P17" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="Q17">
         <v>4.17</v>
@@ -4590,7 +4608,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ18">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AR18">
         <v>1.27</v>
@@ -4715,7 +4733,7 @@
         <v>84</v>
       </c>
       <c r="P19" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="Q19">
         <v>1.72</v>
@@ -4793,7 +4811,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AQ19">
         <v>1.14</v>
@@ -5127,7 +5145,7 @@
         <v>96</v>
       </c>
       <c r="P21" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="Q21">
         <v>2.2</v>
@@ -5333,7 +5351,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="Q22">
         <v>4.75</v>
@@ -5539,7 +5557,7 @@
         <v>98</v>
       </c>
       <c r="P23" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="Q23">
         <v>2.3</v>
@@ -5620,7 +5638,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ23">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AR23">
         <v>0</v>
@@ -5745,7 +5763,7 @@
         <v>99</v>
       </c>
       <c r="P24" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="Q24">
         <v>2.25</v>
@@ -5823,7 +5841,7 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AQ24">
         <v>1.43</v>
@@ -5951,7 +5969,7 @@
         <v>100</v>
       </c>
       <c r="P25" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="Q25">
         <v>3.75</v>
@@ -6157,7 +6175,7 @@
         <v>101</v>
       </c>
       <c r="P26" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="Q26">
         <v>6.5</v>
@@ -6363,7 +6381,7 @@
         <v>102</v>
       </c>
       <c r="P27" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="Q27">
         <v>1.85</v>
@@ -6444,7 +6462,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ27">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AR27">
         <v>2.08</v>
@@ -6569,7 +6587,7 @@
         <v>84</v>
       </c>
       <c r="P28" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="Q28">
         <v>2.5</v>
@@ -6650,7 +6668,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ28">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AR28">
         <v>1.83</v>
@@ -6775,7 +6793,7 @@
         <v>103</v>
       </c>
       <c r="P29" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="Q29">
         <v>2.7</v>
@@ -7059,7 +7077,7 @@
         <v>1.5</v>
       </c>
       <c r="AP30">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AQ30">
         <v>1.71</v>
@@ -7599,7 +7617,7 @@
         <v>106</v>
       </c>
       <c r="P33" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="Q33">
         <v>2.93</v>
@@ -7677,7 +7695,7 @@
         <v>0</v>
       </c>
       <c r="AP33">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ33">
         <v>1.43</v>
@@ -7805,7 +7823,7 @@
         <v>107</v>
       </c>
       <c r="P34" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="Q34">
         <v>2.26</v>
@@ -7883,10 +7901,10 @@
         <v>1</v>
       </c>
       <c r="AP34">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AQ34">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AR34">
         <v>1.49</v>
@@ -8092,7 +8110,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ35">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AR35">
         <v>1.73</v>
@@ -8217,7 +8235,7 @@
         <v>109</v>
       </c>
       <c r="P36" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="Q36">
         <v>6.4</v>
@@ -8423,7 +8441,7 @@
         <v>110</v>
       </c>
       <c r="P37" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="Q37">
         <v>3.84</v>
@@ -8629,7 +8647,7 @@
         <v>84</v>
       </c>
       <c r="P38" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="Q38">
         <v>5.25</v>
@@ -8835,7 +8853,7 @@
         <v>111</v>
       </c>
       <c r="P39" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -9041,7 +9059,7 @@
         <v>112</v>
       </c>
       <c r="P40" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="Q40">
         <v>2.85</v>
@@ -9247,7 +9265,7 @@
         <v>113</v>
       </c>
       <c r="P41" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="Q41">
         <v>4.02</v>
@@ -9453,7 +9471,7 @@
         <v>84</v>
       </c>
       <c r="P42" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="Q42">
         <v>2.1</v>
@@ -9659,7 +9677,7 @@
         <v>114</v>
       </c>
       <c r="P43" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="Q43">
         <v>2.75</v>
@@ -9737,7 +9755,7 @@
         <v>1</v>
       </c>
       <c r="AP43">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ43">
         <v>1.71</v>
@@ -9865,7 +9883,7 @@
         <v>115</v>
       </c>
       <c r="P44" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="Q44">
         <v>1.68</v>
@@ -9943,10 +9961,10 @@
         <v>1.5</v>
       </c>
       <c r="AP44">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AQ44">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AR44">
         <v>1.82</v>
@@ -10149,10 +10167,10 @@
         <v>1.5</v>
       </c>
       <c r="AP45">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AQ45">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AR45">
         <v>1.67</v>
@@ -10277,7 +10295,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="Q46">
         <v>1.91</v>
@@ -10355,7 +10373,7 @@
         <v>1.75</v>
       </c>
       <c r="AP46">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AQ46">
         <v>1.57</v>
@@ -10561,7 +10579,7 @@
         <v>2.33</v>
       </c>
       <c r="AP47">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AQ47">
         <v>1.33</v>
@@ -10770,7 +10788,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ48">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AR48">
         <v>1.4</v>
@@ -10895,7 +10913,7 @@
         <v>118</v>
       </c>
       <c r="P49" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="Q49">
         <v>3.45</v>
@@ -11179,7 +11197,7 @@
         <v>0.6</v>
       </c>
       <c r="AP50">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AQ50">
         <v>0.57</v>
@@ -11307,7 +11325,7 @@
         <v>84</v>
       </c>
       <c r="P51" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="Q51">
         <v>6.5</v>
@@ -11513,7 +11531,7 @@
         <v>84</v>
       </c>
       <c r="P52" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="Q52">
         <v>2.18</v>
@@ -11719,7 +11737,7 @@
         <v>84</v>
       </c>
       <c r="P53" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="Q53">
         <v>3.85</v>
@@ -11925,7 +11943,7 @@
         <v>119</v>
       </c>
       <c r="P54" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="Q54">
         <v>2.66</v>
@@ -12131,7 +12149,7 @@
         <v>120</v>
       </c>
       <c r="P55" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="Q55">
         <v>3</v>
@@ -12337,7 +12355,7 @@
         <v>121</v>
       </c>
       <c r="P56" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="Q56">
         <v>3.35</v>
@@ -12621,7 +12639,7 @@
         <v>1.75</v>
       </c>
       <c r="AP57">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AQ57">
         <v>1.33</v>
@@ -12749,7 +12767,7 @@
         <v>84</v>
       </c>
       <c r="P58" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="Q58">
         <v>3.3</v>
@@ -12955,7 +12973,7 @@
         <v>84</v>
       </c>
       <c r="P59" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="Q59">
         <v>5.5</v>
@@ -13161,7 +13179,7 @@
         <v>122</v>
       </c>
       <c r="P60" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="Q60">
         <v>2.11</v>
@@ -13239,10 +13257,10 @@
         <v>0.67</v>
       </c>
       <c r="AP60">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ60">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AR60">
         <v>1.95</v>
@@ -13367,7 +13385,7 @@
         <v>84</v>
       </c>
       <c r="P61" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="Q61">
         <v>4.5</v>
@@ -13573,7 +13591,7 @@
         <v>123</v>
       </c>
       <c r="P62" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="Q62">
         <v>2.26</v>
@@ -13654,7 +13672,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ62">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AR62">
         <v>1.67</v>
@@ -13779,7 +13797,7 @@
         <v>84</v>
       </c>
       <c r="P63" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="Q63">
         <v>2.87</v>
@@ -13985,7 +14003,7 @@
         <v>124</v>
       </c>
       <c r="P64" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="Q64">
         <v>1.85</v>
@@ -14066,7 +14084,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ64">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AR64">
         <v>1.77</v>
@@ -14191,7 +14209,7 @@
         <v>125</v>
       </c>
       <c r="P65" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="Q65">
         <v>4.28</v>
@@ -14397,7 +14415,7 @@
         <v>126</v>
       </c>
       <c r="P66" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="Q66">
         <v>2.19</v>
@@ -14475,7 +14493,7 @@
         <v>1.33</v>
       </c>
       <c r="AP66">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AQ66">
         <v>1.57</v>
@@ -14809,7 +14827,7 @@
         <v>128</v>
       </c>
       <c r="P68" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="Q68">
         <v>3.3</v>
@@ -15015,7 +15033,7 @@
         <v>129</v>
       </c>
       <c r="P69" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="Q69">
         <v>2.03</v>
@@ -15093,10 +15111,10 @@
         <v>0.75</v>
       </c>
       <c r="AP69">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AQ69">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AR69">
         <v>1.98</v>
@@ -15299,7 +15317,7 @@
         <v>1.4</v>
       </c>
       <c r="AP70">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AQ70">
         <v>1.14</v>
@@ -15505,10 +15523,10 @@
         <v>0.75</v>
       </c>
       <c r="AP71">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ71">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AR71">
         <v>1.89</v>
@@ -15633,7 +15651,7 @@
         <v>131</v>
       </c>
       <c r="P72" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="Q72">
         <v>4.6</v>
@@ -16123,7 +16141,7 @@
         <v>1.4</v>
       </c>
       <c r="AP74">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AQ74">
         <v>1</v>
@@ -16457,7 +16475,7 @@
         <v>84</v>
       </c>
       <c r="P76" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -16663,7 +16681,7 @@
         <v>134</v>
       </c>
       <c r="P77" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="Q77">
         <v>3.28</v>
@@ -16744,7 +16762,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ77">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AR77">
         <v>1.66</v>
@@ -16869,7 +16887,7 @@
         <v>135</v>
       </c>
       <c r="P78" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="Q78">
         <v>3.6</v>
@@ -17075,7 +17093,7 @@
         <v>136</v>
       </c>
       <c r="P79" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Q79">
         <v>2.17</v>
@@ -17232,6 +17250,830 @@
       </c>
       <c r="BP79">
         <v>1.56</v>
+      </c>
+    </row>
+    <row r="80" spans="1:68">
+      <c r="A80" s="1">
+        <v>79</v>
+      </c>
+      <c r="B80">
+        <v>7811556</v>
+      </c>
+      <c r="C80" t="s">
+        <v>68</v>
+      </c>
+      <c r="D80" t="s">
+        <v>69</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45840.5</v>
+      </c>
+      <c r="F80">
+        <v>0</v>
+      </c>
+      <c r="G80" t="s">
+        <v>78</v>
+      </c>
+      <c r="H80" t="s">
+        <v>80</v>
+      </c>
+      <c r="I80">
+        <v>1</v>
+      </c>
+      <c r="J80">
+        <v>0</v>
+      </c>
+      <c r="K80">
+        <v>1</v>
+      </c>
+      <c r="L80">
+        <v>2</v>
+      </c>
+      <c r="M80">
+        <v>3</v>
+      </c>
+      <c r="N80">
+        <v>5</v>
+      </c>
+      <c r="O80" t="s">
+        <v>137</v>
+      </c>
+      <c r="P80" t="s">
+        <v>197</v>
+      </c>
+      <c r="Q80">
+        <v>1.68</v>
+      </c>
+      <c r="R80">
+        <v>2.75</v>
+      </c>
+      <c r="S80">
+        <v>7</v>
+      </c>
+      <c r="T80">
+        <v>1.22</v>
+      </c>
+      <c r="U80">
+        <v>3.7</v>
+      </c>
+      <c r="V80">
+        <v>2.1</v>
+      </c>
+      <c r="W80">
+        <v>1.63</v>
+      </c>
+      <c r="X80">
+        <v>4.1</v>
+      </c>
+      <c r="Y80">
+        <v>1.17</v>
+      </c>
+      <c r="Z80">
+        <v>1.26</v>
+      </c>
+      <c r="AA80">
+        <v>5.9</v>
+      </c>
+      <c r="AB80">
+        <v>8</v>
+      </c>
+      <c r="AC80">
+        <v>1.01</v>
+      </c>
+      <c r="AD80">
+        <v>16.5</v>
+      </c>
+      <c r="AE80">
+        <v>1.13</v>
+      </c>
+      <c r="AF80">
+        <v>5.8</v>
+      </c>
+      <c r="AG80">
+        <v>1.4</v>
+      </c>
+      <c r="AH80">
+        <v>2.62</v>
+      </c>
+      <c r="AI80">
+        <v>1.81</v>
+      </c>
+      <c r="AJ80">
+        <v>1.99</v>
+      </c>
+      <c r="AK80">
+        <v>1.1</v>
+      </c>
+      <c r="AL80">
+        <v>1.12</v>
+      </c>
+      <c r="AM80">
+        <v>3.47</v>
+      </c>
+      <c r="AN80">
+        <v>2.29</v>
+      </c>
+      <c r="AO80">
+        <v>1</v>
+      </c>
+      <c r="AP80">
+        <v>2</v>
+      </c>
+      <c r="AQ80">
+        <v>1.25</v>
+      </c>
+      <c r="AR80">
+        <v>2.02</v>
+      </c>
+      <c r="AS80">
+        <v>1.29</v>
+      </c>
+      <c r="AT80">
+        <v>3.31</v>
+      </c>
+      <c r="AU80">
+        <v>8</v>
+      </c>
+      <c r="AV80">
+        <v>8</v>
+      </c>
+      <c r="AW80">
+        <v>6</v>
+      </c>
+      <c r="AX80">
+        <v>4</v>
+      </c>
+      <c r="AY80">
+        <v>14</v>
+      </c>
+      <c r="AZ80">
+        <v>12</v>
+      </c>
+      <c r="BA80">
+        <v>6</v>
+      </c>
+      <c r="BB80">
+        <v>7</v>
+      </c>
+      <c r="BC80">
+        <v>13</v>
+      </c>
+      <c r="BD80">
+        <v>1.21</v>
+      </c>
+      <c r="BE80">
+        <v>12</v>
+      </c>
+      <c r="BF80">
+        <v>4.4</v>
+      </c>
+      <c r="BG80">
+        <v>1.21</v>
+      </c>
+      <c r="BH80">
+        <v>4.35</v>
+      </c>
+      <c r="BI80">
+        <v>1.3</v>
+      </c>
+      <c r="BJ80">
+        <v>2.9</v>
+      </c>
+      <c r="BK80">
+        <v>1.54</v>
+      </c>
+      <c r="BL80">
+        <v>2.33</v>
+      </c>
+      <c r="BM80">
+        <v>1.85</v>
+      </c>
+      <c r="BN80">
+        <v>1.79</v>
+      </c>
+      <c r="BO80">
+        <v>2.34</v>
+      </c>
+      <c r="BP80">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="81" spans="1:68">
+      <c r="A81" s="1">
+        <v>80</v>
+      </c>
+      <c r="B81">
+        <v>7811557</v>
+      </c>
+      <c r="C81" t="s">
+        <v>68</v>
+      </c>
+      <c r="D81" t="s">
+        <v>69</v>
+      </c>
+      <c r="E81" s="2">
+        <v>45840.5</v>
+      </c>
+      <c r="F81">
+        <v>0</v>
+      </c>
+      <c r="G81" t="s">
+        <v>70</v>
+      </c>
+      <c r="H81" t="s">
+        <v>73</v>
+      </c>
+      <c r="I81">
+        <v>1</v>
+      </c>
+      <c r="J81">
+        <v>0</v>
+      </c>
+      <c r="K81">
+        <v>1</v>
+      </c>
+      <c r="L81">
+        <v>2</v>
+      </c>
+      <c r="M81">
+        <v>1</v>
+      </c>
+      <c r="N81">
+        <v>3</v>
+      </c>
+      <c r="O81" t="s">
+        <v>138</v>
+      </c>
+      <c r="P81" t="s">
+        <v>198</v>
+      </c>
+      <c r="Q81">
+        <v>1.52</v>
+      </c>
+      <c r="R81">
+        <v>3.55</v>
+      </c>
+      <c r="S81">
+        <v>8.5</v>
+      </c>
+      <c r="T81">
+        <v>1.17</v>
+      </c>
+      <c r="U81">
+        <v>5.2</v>
+      </c>
+      <c r="V81">
+        <v>1.66</v>
+      </c>
+      <c r="W81">
+        <v>2</v>
+      </c>
+      <c r="X81">
+        <v>3.05</v>
+      </c>
+      <c r="Y81">
+        <v>1.33</v>
+      </c>
+      <c r="Z81">
+        <v>1.22</v>
+      </c>
+      <c r="AA81">
+        <v>9.4</v>
+      </c>
+      <c r="AB81">
+        <v>14</v>
+      </c>
+      <c r="AC81">
+        <v>1</v>
+      </c>
+      <c r="AD81">
+        <v>29</v>
+      </c>
+      <c r="AE81">
+        <v>1.06</v>
+      </c>
+      <c r="AF81">
+        <v>10</v>
+      </c>
+      <c r="AG81">
+        <v>1.18</v>
+      </c>
+      <c r="AH81">
+        <v>3.9</v>
+      </c>
+      <c r="AI81">
+        <v>1.7</v>
+      </c>
+      <c r="AJ81">
+        <v>2.05</v>
+      </c>
+      <c r="AK81">
+        <v>1.08</v>
+      </c>
+      <c r="AL81">
+        <v>1.12</v>
+      </c>
+      <c r="AM81">
+        <v>4.75</v>
+      </c>
+      <c r="AN81">
+        <v>2.17</v>
+      </c>
+      <c r="AO81">
+        <v>0.6</v>
+      </c>
+      <c r="AP81">
+        <v>2.29</v>
+      </c>
+      <c r="AQ81">
+        <v>0.5</v>
+      </c>
+      <c r="AR81">
+        <v>1.74</v>
+      </c>
+      <c r="AS81">
+        <v>1.3</v>
+      </c>
+      <c r="AT81">
+        <v>3.04</v>
+      </c>
+      <c r="AU81">
+        <v>6</v>
+      </c>
+      <c r="AV81">
+        <v>4</v>
+      </c>
+      <c r="AW81">
+        <v>19</v>
+      </c>
+      <c r="AX81">
+        <v>6</v>
+      </c>
+      <c r="AY81">
+        <v>25</v>
+      </c>
+      <c r="AZ81">
+        <v>10</v>
+      </c>
+      <c r="BA81">
+        <v>4</v>
+      </c>
+      <c r="BB81">
+        <v>2</v>
+      </c>
+      <c r="BC81">
+        <v>6</v>
+      </c>
+      <c r="BD81">
+        <v>1.13</v>
+      </c>
+      <c r="BE81">
+        <v>10</v>
+      </c>
+      <c r="BF81">
+        <v>8.1</v>
+      </c>
+      <c r="BG81">
+        <v>1.17</v>
+      </c>
+      <c r="BH81">
+        <v>3.8</v>
+      </c>
+      <c r="BI81">
+        <v>1.36</v>
+      </c>
+      <c r="BJ81">
+        <v>2.55</v>
+      </c>
+      <c r="BK81">
+        <v>1.68</v>
+      </c>
+      <c r="BL81">
+        <v>2</v>
+      </c>
+      <c r="BM81">
+        <v>1.91</v>
+      </c>
+      <c r="BN81">
+        <v>1.84</v>
+      </c>
+      <c r="BO81">
+        <v>2.36</v>
+      </c>
+      <c r="BP81">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="82" spans="1:68">
+      <c r="A82" s="1">
+        <v>81</v>
+      </c>
+      <c r="B82">
+        <v>7811558</v>
+      </c>
+      <c r="C82" t="s">
+        <v>68</v>
+      </c>
+      <c r="D82" t="s">
+        <v>69</v>
+      </c>
+      <c r="E82" s="2">
+        <v>45840.5</v>
+      </c>
+      <c r="F82">
+        <v>0</v>
+      </c>
+      <c r="G82" t="s">
+        <v>74</v>
+      </c>
+      <c r="H82" t="s">
+        <v>75</v>
+      </c>
+      <c r="I82">
+        <v>1</v>
+      </c>
+      <c r="J82">
+        <v>2</v>
+      </c>
+      <c r="K82">
+        <v>3</v>
+      </c>
+      <c r="L82">
+        <v>1</v>
+      </c>
+      <c r="M82">
+        <v>2</v>
+      </c>
+      <c r="N82">
+        <v>3</v>
+      </c>
+      <c r="O82" t="s">
+        <v>139</v>
+      </c>
+      <c r="P82" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q82">
+        <v>2.38</v>
+      </c>
+      <c r="R82">
+        <v>2.39</v>
+      </c>
+      <c r="S82">
+        <v>4</v>
+      </c>
+      <c r="T82">
+        <v>1.29</v>
+      </c>
+      <c r="U82">
+        <v>3.3</v>
+      </c>
+      <c r="V82">
+        <v>2.29</v>
+      </c>
+      <c r="W82">
+        <v>1.6</v>
+      </c>
+      <c r="X82">
+        <v>5</v>
+      </c>
+      <c r="Y82">
+        <v>1.15</v>
+      </c>
+      <c r="Z82">
+        <v>1.92</v>
+      </c>
+      <c r="AA82">
+        <v>3.75</v>
+      </c>
+      <c r="AB82">
+        <v>3.5</v>
+      </c>
+      <c r="AC82">
+        <v>1.03</v>
+      </c>
+      <c r="AD82">
+        <v>10</v>
+      </c>
+      <c r="AE82">
+        <v>1.14</v>
+      </c>
+      <c r="AF82">
+        <v>4.5</v>
+      </c>
+      <c r="AG82">
+        <v>1.6</v>
+      </c>
+      <c r="AH82">
+        <v>2.25</v>
+      </c>
+      <c r="AI82">
+        <v>1.5</v>
+      </c>
+      <c r="AJ82">
+        <v>2.43</v>
+      </c>
+      <c r="AK82">
+        <v>1.25</v>
+      </c>
+      <c r="AL82">
+        <v>1.3</v>
+      </c>
+      <c r="AM82">
+        <v>1.8</v>
+      </c>
+      <c r="AN82">
+        <v>1.6</v>
+      </c>
+      <c r="AO82">
+        <v>0.6</v>
+      </c>
+      <c r="AP82">
+        <v>1.33</v>
+      </c>
+      <c r="AQ82">
+        <v>1</v>
+      </c>
+      <c r="AR82">
+        <v>1.73</v>
+      </c>
+      <c r="AS82">
+        <v>1.49</v>
+      </c>
+      <c r="AT82">
+        <v>3.22</v>
+      </c>
+      <c r="AU82">
+        <v>5</v>
+      </c>
+      <c r="AV82">
+        <v>6</v>
+      </c>
+      <c r="AW82">
+        <v>9</v>
+      </c>
+      <c r="AX82">
+        <v>12</v>
+      </c>
+      <c r="AY82">
+        <v>14</v>
+      </c>
+      <c r="AZ82">
+        <v>18</v>
+      </c>
+      <c r="BA82">
+        <v>8</v>
+      </c>
+      <c r="BB82">
+        <v>9</v>
+      </c>
+      <c r="BC82">
+        <v>17</v>
+      </c>
+      <c r="BD82">
+        <v>1.55</v>
+      </c>
+      <c r="BE82">
+        <v>8</v>
+      </c>
+      <c r="BF82">
+        <v>2.95</v>
+      </c>
+      <c r="BG82">
+        <v>1.12</v>
+      </c>
+      <c r="BH82">
+        <v>4.75</v>
+      </c>
+      <c r="BI82">
+        <v>1.3</v>
+      </c>
+      <c r="BJ82">
+        <v>3.15</v>
+      </c>
+      <c r="BK82">
+        <v>1.6</v>
+      </c>
+      <c r="BL82">
+        <v>2.2</v>
+      </c>
+      <c r="BM82">
+        <v>1.91</v>
+      </c>
+      <c r="BN82">
+        <v>1.8</v>
+      </c>
+      <c r="BO82">
+        <v>2.32</v>
+      </c>
+      <c r="BP82">
+        <v>1.58</v>
+      </c>
+    </row>
+    <row r="83" spans="1:68">
+      <c r="A83" s="1">
+        <v>82</v>
+      </c>
+      <c r="B83">
+        <v>7811555</v>
+      </c>
+      <c r="C83" t="s">
+        <v>68</v>
+      </c>
+      <c r="D83" t="s">
+        <v>69</v>
+      </c>
+      <c r="E83" s="2">
+        <v>45840.5</v>
+      </c>
+      <c r="F83">
+        <v>0</v>
+      </c>
+      <c r="G83" t="s">
+        <v>71</v>
+      </c>
+      <c r="H83" t="s">
+        <v>72</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>0</v>
+      </c>
+      <c r="K83">
+        <v>0</v>
+      </c>
+      <c r="L83">
+        <v>0</v>
+      </c>
+      <c r="M83">
+        <v>0</v>
+      </c>
+      <c r="N83">
+        <v>0</v>
+      </c>
+      <c r="O83" t="s">
+        <v>84</v>
+      </c>
+      <c r="P83" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q83">
+        <v>1.68</v>
+      </c>
+      <c r="R83">
+        <v>2.9</v>
+      </c>
+      <c r="S83">
+        <v>7.5</v>
+      </c>
+      <c r="T83">
+        <v>1.15</v>
+      </c>
+      <c r="U83">
+        <v>4.33</v>
+      </c>
+      <c r="V83">
+        <v>2</v>
+      </c>
+      <c r="W83">
+        <v>1.66</v>
+      </c>
+      <c r="X83">
+        <v>4.4</v>
+      </c>
+      <c r="Y83">
+        <v>1.18</v>
+      </c>
+      <c r="Z83">
+        <v>1.2</v>
+      </c>
+      <c r="AA83">
+        <v>7.5</v>
+      </c>
+      <c r="AB83">
+        <v>13</v>
+      </c>
+      <c r="AC83">
+        <v>1.01</v>
+      </c>
+      <c r="AD83">
+        <v>26</v>
+      </c>
+      <c r="AE83">
+        <v>1.09</v>
+      </c>
+      <c r="AF83">
+        <v>6.75</v>
+      </c>
+      <c r="AG83">
+        <v>1.36</v>
+      </c>
+      <c r="AH83">
+        <v>2.95</v>
+      </c>
+      <c r="AI83">
+        <v>1.89</v>
+      </c>
+      <c r="AJ83">
+        <v>1.87</v>
+      </c>
+      <c r="AK83">
+        <v>1.02</v>
+      </c>
+      <c r="AL83">
+        <v>1.1</v>
+      </c>
+      <c r="AM83">
+        <v>4.75</v>
+      </c>
+      <c r="AN83">
+        <v>2</v>
+      </c>
+      <c r="AO83">
+        <v>1</v>
+      </c>
+      <c r="AP83">
+        <v>1.86</v>
+      </c>
+      <c r="AQ83">
+        <v>1</v>
+      </c>
+      <c r="AR83">
+        <v>2</v>
+      </c>
+      <c r="AS83">
+        <v>1.08</v>
+      </c>
+      <c r="AT83">
+        <v>3.08</v>
+      </c>
+      <c r="AU83">
+        <v>3</v>
+      </c>
+      <c r="AV83">
+        <v>3</v>
+      </c>
+      <c r="AW83">
+        <v>18</v>
+      </c>
+      <c r="AX83">
+        <v>6</v>
+      </c>
+      <c r="AY83">
+        <v>21</v>
+      </c>
+      <c r="AZ83">
+        <v>9</v>
+      </c>
+      <c r="BA83">
+        <v>12</v>
+      </c>
+      <c r="BB83">
+        <v>3</v>
+      </c>
+      <c r="BC83">
+        <v>15</v>
+      </c>
+      <c r="BD83">
+        <v>1.08</v>
+      </c>
+      <c r="BE83">
+        <v>15.5</v>
+      </c>
+      <c r="BF83">
+        <v>5.6</v>
+      </c>
+      <c r="BG83">
+        <v>1.22</v>
+      </c>
+      <c r="BH83">
+        <v>3.92</v>
+      </c>
+      <c r="BI83">
+        <v>1.38</v>
+      </c>
+      <c r="BJ83">
+        <v>2.8</v>
+      </c>
+      <c r="BK83">
+        <v>1.79</v>
+      </c>
+      <c r="BL83">
+        <v>2.15</v>
+      </c>
+      <c r="BM83">
+        <v>1.85</v>
+      </c>
+      <c r="BN83">
+        <v>1.68</v>
+      </c>
+      <c r="BO83">
+        <v>2.3</v>
+      </c>
+      <c r="BP83">
+        <v>1.55</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="202">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -436,6 +436,9 @@
     <t>['6']</t>
   </si>
   <si>
+    <t>['78', '4']</t>
+  </si>
+  <si>
     <t>['4', '14']</t>
   </si>
   <si>
@@ -614,6 +617,9 @@
   </si>
   <si>
     <t>['13', '33']</t>
+  </si>
+  <si>
+    <t>['65', '52']</t>
   </si>
 </sst>
 </file>
@@ -975,7 +981,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP83"/>
+  <dimension ref="A1:BP84"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1231,7 +1237,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q2">
         <v>3.2</v>
@@ -1437,7 +1443,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q3">
         <v>3.25</v>
@@ -1518,7 +1524,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ3">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1643,7 +1649,7 @@
         <v>84</v>
       </c>
       <c r="P4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q4">
         <v>3.1</v>
@@ -2055,7 +2061,7 @@
         <v>85</v>
       </c>
       <c r="P6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q6">
         <v>2.3</v>
@@ -2261,7 +2267,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q7">
         <v>3.4</v>
@@ -2467,7 +2473,7 @@
         <v>87</v>
       </c>
       <c r="P8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q8">
         <v>4.1</v>
@@ -2879,7 +2885,7 @@
         <v>89</v>
       </c>
       <c r="P10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q10">
         <v>1.7</v>
@@ -3085,7 +3091,7 @@
         <v>84</v>
       </c>
       <c r="P11" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q11">
         <v>2.25</v>
@@ -3703,7 +3709,7 @@
         <v>84</v>
       </c>
       <c r="P14" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q14">
         <v>3.1</v>
@@ -3909,7 +3915,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q15">
         <v>3.2</v>
@@ -4115,7 +4121,7 @@
         <v>93</v>
       </c>
       <c r="P16" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q16">
         <v>4.79</v>
@@ -4321,7 +4327,7 @@
         <v>84</v>
       </c>
       <c r="P17" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q17">
         <v>4.17</v>
@@ -4733,7 +4739,7 @@
         <v>84</v>
       </c>
       <c r="P19" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q19">
         <v>1.72</v>
@@ -5145,7 +5151,7 @@
         <v>96</v>
       </c>
       <c r="P21" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q21">
         <v>2.2</v>
@@ -5351,7 +5357,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q22">
         <v>4.75</v>
@@ -5429,7 +5435,7 @@
         <v>3</v>
       </c>
       <c r="AP22">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="AQ22">
         <v>2.33</v>
@@ -5557,7 +5563,7 @@
         <v>98</v>
       </c>
       <c r="P23" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q23">
         <v>2.3</v>
@@ -5763,7 +5769,7 @@
         <v>99</v>
       </c>
       <c r="P24" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q24">
         <v>2.25</v>
@@ -5969,7 +5975,7 @@
         <v>100</v>
       </c>
       <c r="P25" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q25">
         <v>3.75</v>
@@ -6050,7 +6056,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ25">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AR25">
         <v>0</v>
@@ -6175,7 +6181,7 @@
         <v>101</v>
       </c>
       <c r="P26" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q26">
         <v>6.5</v>
@@ -6381,7 +6387,7 @@
         <v>102</v>
       </c>
       <c r="P27" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q27">
         <v>1.85</v>
@@ -6587,7 +6593,7 @@
         <v>84</v>
       </c>
       <c r="P28" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q28">
         <v>2.5</v>
@@ -6793,7 +6799,7 @@
         <v>103</v>
       </c>
       <c r="P29" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q29">
         <v>2.7</v>
@@ -7617,7 +7623,7 @@
         <v>106</v>
       </c>
       <c r="P33" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q33">
         <v>2.93</v>
@@ -7823,7 +7829,7 @@
         <v>107</v>
       </c>
       <c r="P34" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q34">
         <v>2.26</v>
@@ -8235,7 +8241,7 @@
         <v>109</v>
       </c>
       <c r="P36" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q36">
         <v>6.4</v>
@@ -8441,7 +8447,7 @@
         <v>110</v>
       </c>
       <c r="P37" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q37">
         <v>3.84</v>
@@ -8519,7 +8525,7 @@
         <v>1</v>
       </c>
       <c r="AP37">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="AQ37">
         <v>1.14</v>
@@ -8647,7 +8653,7 @@
         <v>84</v>
       </c>
       <c r="P38" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q38">
         <v>5.25</v>
@@ -8853,7 +8859,7 @@
         <v>111</v>
       </c>
       <c r="P39" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -9059,7 +9065,7 @@
         <v>112</v>
       </c>
       <c r="P40" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q40">
         <v>2.85</v>
@@ -9265,7 +9271,7 @@
         <v>113</v>
       </c>
       <c r="P41" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q41">
         <v>4.02</v>
@@ -9346,7 +9352,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ41">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AR41">
         <v>1.76</v>
@@ -9471,7 +9477,7 @@
         <v>84</v>
       </c>
       <c r="P42" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q42">
         <v>2.1</v>
@@ -9549,7 +9555,7 @@
         <v>1</v>
       </c>
       <c r="AP42">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="AQ42">
         <v>1</v>
@@ -9677,7 +9683,7 @@
         <v>114</v>
       </c>
       <c r="P43" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q43">
         <v>2.75</v>
@@ -9883,7 +9889,7 @@
         <v>115</v>
       </c>
       <c r="P44" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q44">
         <v>1.68</v>
@@ -10295,7 +10301,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q46">
         <v>1.91</v>
@@ -10582,7 +10588,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ47">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AR47">
         <v>1.71</v>
@@ -10913,7 +10919,7 @@
         <v>118</v>
       </c>
       <c r="P49" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q49">
         <v>3.45</v>
@@ -11325,7 +11331,7 @@
         <v>84</v>
       </c>
       <c r="P51" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q51">
         <v>6.5</v>
@@ -11531,7 +11537,7 @@
         <v>84</v>
       </c>
       <c r="P52" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q52">
         <v>2.18</v>
@@ -11737,7 +11743,7 @@
         <v>84</v>
       </c>
       <c r="P53" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q53">
         <v>3.85</v>
@@ -11943,7 +11949,7 @@
         <v>119</v>
       </c>
       <c r="P54" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q54">
         <v>2.66</v>
@@ -12149,7 +12155,7 @@
         <v>120</v>
       </c>
       <c r="P55" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q55">
         <v>3</v>
@@ -12355,7 +12361,7 @@
         <v>121</v>
       </c>
       <c r="P56" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q56">
         <v>3.35</v>
@@ -12433,7 +12439,7 @@
         <v>1.4</v>
       </c>
       <c r="AP56">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="AQ56">
         <v>1.57</v>
@@ -12642,7 +12648,7 @@
         <v>2</v>
       </c>
       <c r="AQ57">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AR57">
         <v>2.2</v>
@@ -12767,7 +12773,7 @@
         <v>84</v>
       </c>
       <c r="P58" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q58">
         <v>3.3</v>
@@ -12973,7 +12979,7 @@
         <v>84</v>
       </c>
       <c r="P59" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q59">
         <v>5.5</v>
@@ -13179,7 +13185,7 @@
         <v>122</v>
       </c>
       <c r="P60" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q60">
         <v>2.11</v>
@@ -13385,7 +13391,7 @@
         <v>84</v>
       </c>
       <c r="P61" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q61">
         <v>4.5</v>
@@ -13463,7 +13469,7 @@
         <v>1.4</v>
       </c>
       <c r="AP61">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="AQ61">
         <v>1.43</v>
@@ -13591,7 +13597,7 @@
         <v>123</v>
       </c>
       <c r="P62" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q62">
         <v>2.26</v>
@@ -13797,7 +13803,7 @@
         <v>84</v>
       </c>
       <c r="P63" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q63">
         <v>2.87</v>
@@ -14003,7 +14009,7 @@
         <v>124</v>
       </c>
       <c r="P64" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q64">
         <v>1.85</v>
@@ -14209,7 +14215,7 @@
         <v>125</v>
       </c>
       <c r="P65" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q65">
         <v>4.28</v>
@@ -14415,7 +14421,7 @@
         <v>126</v>
       </c>
       <c r="P66" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q66">
         <v>2.19</v>
@@ -14702,7 +14708,7 @@
         <v>1</v>
       </c>
       <c r="AQ67">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AR67">
         <v>1.26</v>
@@ -14827,7 +14833,7 @@
         <v>128</v>
       </c>
       <c r="P68" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q68">
         <v>3.3</v>
@@ -15033,7 +15039,7 @@
         <v>129</v>
       </c>
       <c r="P69" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q69">
         <v>2.03</v>
@@ -15651,7 +15657,7 @@
         <v>131</v>
       </c>
       <c r="P72" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q72">
         <v>4.6</v>
@@ -16475,7 +16481,7 @@
         <v>84</v>
       </c>
       <c r="P76" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -16681,7 +16687,7 @@
         <v>134</v>
       </c>
       <c r="P77" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q77">
         <v>3.28</v>
@@ -16887,7 +16893,7 @@
         <v>135</v>
       </c>
       <c r="P78" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q78">
         <v>3.6</v>
@@ -16965,7 +16971,7 @@
         <v>1.67</v>
       </c>
       <c r="AP78">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="AQ78">
         <v>1.43</v>
@@ -17093,7 +17099,7 @@
         <v>136</v>
       </c>
       <c r="P79" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q79">
         <v>2.17</v>
@@ -17299,7 +17305,7 @@
         <v>137</v>
       </c>
       <c r="P80" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q80">
         <v>1.68</v>
@@ -17505,7 +17511,7 @@
         <v>138</v>
       </c>
       <c r="P81" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q81">
         <v>1.52</v>
@@ -17711,7 +17717,7 @@
         <v>139</v>
       </c>
       <c r="P82" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q82">
         <v>2.38</v>
@@ -18074,6 +18080,212 @@
       </c>
       <c r="BP83">
         <v>1.55</v>
+      </c>
+    </row>
+    <row r="84" spans="1:68">
+      <c r="A84" s="1">
+        <v>83</v>
+      </c>
+      <c r="B84">
+        <v>7811559</v>
+      </c>
+      <c r="C84" t="s">
+        <v>68</v>
+      </c>
+      <c r="D84" t="s">
+        <v>69</v>
+      </c>
+      <c r="E84" s="2">
+        <v>45842.5</v>
+      </c>
+      <c r="F84">
+        <v>0</v>
+      </c>
+      <c r="G84" t="s">
+        <v>79</v>
+      </c>
+      <c r="H84" t="s">
+        <v>77</v>
+      </c>
+      <c r="I84">
+        <v>1</v>
+      </c>
+      <c r="J84">
+        <v>0</v>
+      </c>
+      <c r="K84">
+        <v>1</v>
+      </c>
+      <c r="L84">
+        <v>2</v>
+      </c>
+      <c r="M84">
+        <v>2</v>
+      </c>
+      <c r="N84">
+        <v>4</v>
+      </c>
+      <c r="O84" t="s">
+        <v>140</v>
+      </c>
+      <c r="P84" t="s">
+        <v>201</v>
+      </c>
+      <c r="Q84">
+        <v>3.6</v>
+      </c>
+      <c r="R84">
+        <v>2.2</v>
+      </c>
+      <c r="S84">
+        <v>2.5</v>
+      </c>
+      <c r="T84">
+        <v>1.32</v>
+      </c>
+      <c r="U84">
+        <v>3.1</v>
+      </c>
+      <c r="V84">
+        <v>2.5</v>
+      </c>
+      <c r="W84">
+        <v>1.45</v>
+      </c>
+      <c r="X84">
+        <v>5.75</v>
+      </c>
+      <c r="Y84">
+        <v>1.1</v>
+      </c>
+      <c r="Z84">
+        <v>4.05</v>
+      </c>
+      <c r="AA84">
+        <v>3.7</v>
+      </c>
+      <c r="AB84">
+        <v>2.29</v>
+      </c>
+      <c r="AC84">
+        <v>1.05</v>
+      </c>
+      <c r="AD84">
+        <v>11</v>
+      </c>
+      <c r="AE84">
+        <v>1.2</v>
+      </c>
+      <c r="AF84">
+        <v>3.75</v>
+      </c>
+      <c r="AG84">
+        <v>1.75</v>
+      </c>
+      <c r="AH84">
+        <v>2.02</v>
+      </c>
+      <c r="AI84">
+        <v>1.6</v>
+      </c>
+      <c r="AJ84">
+        <v>2</v>
+      </c>
+      <c r="AK84">
+        <v>1.3</v>
+      </c>
+      <c r="AL84">
+        <v>1.25</v>
+      </c>
+      <c r="AM84">
+        <v>1.36</v>
+      </c>
+      <c r="AN84">
+        <v>0.67</v>
+      </c>
+      <c r="AO84">
+        <v>1.33</v>
+      </c>
+      <c r="AP84">
+        <v>0.71</v>
+      </c>
+      <c r="AQ84">
+        <v>1.29</v>
+      </c>
+      <c r="AR84">
+        <v>1.4</v>
+      </c>
+      <c r="AS84">
+        <v>1.58</v>
+      </c>
+      <c r="AT84">
+        <v>2.98</v>
+      </c>
+      <c r="AU84">
+        <v>3</v>
+      </c>
+      <c r="AV84">
+        <v>5</v>
+      </c>
+      <c r="AW84">
+        <v>1</v>
+      </c>
+      <c r="AX84">
+        <v>7</v>
+      </c>
+      <c r="AY84">
+        <v>4</v>
+      </c>
+      <c r="AZ84">
+        <v>12</v>
+      </c>
+      <c r="BA84">
+        <v>2</v>
+      </c>
+      <c r="BB84">
+        <v>7</v>
+      </c>
+      <c r="BC84">
+        <v>9</v>
+      </c>
+      <c r="BD84">
+        <v>3.1</v>
+      </c>
+      <c r="BE84">
+        <v>8</v>
+      </c>
+      <c r="BF84">
+        <v>1.48</v>
+      </c>
+      <c r="BG84">
+        <v>1.2</v>
+      </c>
+      <c r="BH84">
+        <v>3.72</v>
+      </c>
+      <c r="BI84">
+        <v>1.42</v>
+      </c>
+      <c r="BJ84">
+        <v>2.65</v>
+      </c>
+      <c r="BK84">
+        <v>1.73</v>
+      </c>
+      <c r="BL84">
+        <v>2.05</v>
+      </c>
+      <c r="BM84">
+        <v>2.17</v>
+      </c>
+      <c r="BN84">
+        <v>1.58</v>
+      </c>
+      <c r="BO84">
+        <v>2.83</v>
+      </c>
+      <c r="BP84">
+        <v>1.33</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="204">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -439,6 +439,9 @@
     <t>['78', '4']</t>
   </si>
   <si>
+    <t>['14']</t>
+  </si>
+  <si>
     <t>['4', '14']</t>
   </si>
   <si>
@@ -620,6 +623,9 @@
   </si>
   <si>
     <t>['65', '52']</t>
+  </si>
+  <si>
+    <t>['64']</t>
   </si>
 </sst>
 </file>
@@ -981,7 +987,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP84"/>
+  <dimension ref="A1:BP85"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1237,7 +1243,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q2">
         <v>3.2</v>
@@ -1443,7 +1449,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q3">
         <v>3.25</v>
@@ -1649,7 +1655,7 @@
         <v>84</v>
       </c>
       <c r="P4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q4">
         <v>3.1</v>
@@ -2061,7 +2067,7 @@
         <v>85</v>
       </c>
       <c r="P6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q6">
         <v>2.3</v>
@@ -2267,7 +2273,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q7">
         <v>3.4</v>
@@ -2473,7 +2479,7 @@
         <v>87</v>
       </c>
       <c r="P8" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q8">
         <v>4.1</v>
@@ -2757,7 +2763,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AQ9">
         <v>1.43</v>
@@ -2885,7 +2891,7 @@
         <v>89</v>
       </c>
       <c r="P10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q10">
         <v>1.7</v>
@@ -3091,7 +3097,7 @@
         <v>84</v>
       </c>
       <c r="P11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q11">
         <v>2.25</v>
@@ -3709,7 +3715,7 @@
         <v>84</v>
       </c>
       <c r="P14" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q14">
         <v>3.1</v>
@@ -3915,7 +3921,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q15">
         <v>3.2</v>
@@ -4121,7 +4127,7 @@
         <v>93</v>
       </c>
       <c r="P16" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q16">
         <v>4.79</v>
@@ -4327,7 +4333,7 @@
         <v>84</v>
       </c>
       <c r="P17" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q17">
         <v>4.17</v>
@@ -4408,7 +4414,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ17">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AR17">
         <v>1.59</v>
@@ -4739,7 +4745,7 @@
         <v>84</v>
       </c>
       <c r="P19" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q19">
         <v>1.72</v>
@@ -5151,7 +5157,7 @@
         <v>96</v>
       </c>
       <c r="P21" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q21">
         <v>2.2</v>
@@ -5229,7 +5235,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AQ21">
         <v>0.57</v>
@@ -5357,7 +5363,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q22">
         <v>4.75</v>
@@ -5563,7 +5569,7 @@
         <v>98</v>
       </c>
       <c r="P23" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q23">
         <v>2.3</v>
@@ -5769,7 +5775,7 @@
         <v>99</v>
       </c>
       <c r="P24" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q24">
         <v>2.25</v>
@@ -5975,7 +5981,7 @@
         <v>100</v>
       </c>
       <c r="P25" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q25">
         <v>3.75</v>
@@ -6181,7 +6187,7 @@
         <v>101</v>
       </c>
       <c r="P26" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q26">
         <v>6.5</v>
@@ -6262,7 +6268,7 @@
         <v>1</v>
       </c>
       <c r="AQ26">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AR26">
         <v>1.17</v>
@@ -6387,7 +6393,7 @@
         <v>102</v>
       </c>
       <c r="P27" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q27">
         <v>1.85</v>
@@ -6465,7 +6471,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AQ27">
         <v>1</v>
@@ -6593,7 +6599,7 @@
         <v>84</v>
       </c>
       <c r="P28" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q28">
         <v>2.5</v>
@@ -6799,7 +6805,7 @@
         <v>103</v>
       </c>
       <c r="P29" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q29">
         <v>2.7</v>
@@ -7086,7 +7092,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ30">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AR30">
         <v>1.89</v>
@@ -7623,7 +7629,7 @@
         <v>106</v>
       </c>
       <c r="P33" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q33">
         <v>2.93</v>
@@ -7829,7 +7835,7 @@
         <v>107</v>
       </c>
       <c r="P34" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q34">
         <v>2.26</v>
@@ -8241,7 +8247,7 @@
         <v>109</v>
       </c>
       <c r="P36" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q36">
         <v>6.4</v>
@@ -8447,7 +8453,7 @@
         <v>110</v>
       </c>
       <c r="P37" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q37">
         <v>3.84</v>
@@ -8653,7 +8659,7 @@
         <v>84</v>
       </c>
       <c r="P38" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q38">
         <v>5.25</v>
@@ -8859,7 +8865,7 @@
         <v>111</v>
       </c>
       <c r="P39" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -8937,7 +8943,7 @@
         <v>0.5</v>
       </c>
       <c r="AP39">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AQ39">
         <v>1.43</v>
@@ -9065,7 +9071,7 @@
         <v>112</v>
       </c>
       <c r="P40" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q40">
         <v>2.85</v>
@@ -9271,7 +9277,7 @@
         <v>113</v>
       </c>
       <c r="P41" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q41">
         <v>4.02</v>
@@ -9477,7 +9483,7 @@
         <v>84</v>
       </c>
       <c r="P42" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q42">
         <v>2.1</v>
@@ -9683,7 +9689,7 @@
         <v>114</v>
       </c>
       <c r="P43" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q43">
         <v>2.75</v>
@@ -9764,7 +9770,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ43">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AR43">
         <v>2.09</v>
@@ -9889,7 +9895,7 @@
         <v>115</v>
       </c>
       <c r="P44" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q44">
         <v>1.68</v>
@@ -10301,7 +10307,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q46">
         <v>1.91</v>
@@ -10919,7 +10925,7 @@
         <v>118</v>
       </c>
       <c r="P49" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q49">
         <v>3.45</v>
@@ -11331,7 +11337,7 @@
         <v>84</v>
       </c>
       <c r="P51" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q51">
         <v>6.5</v>
@@ -11537,7 +11543,7 @@
         <v>84</v>
       </c>
       <c r="P52" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q52">
         <v>2.18</v>
@@ -11743,7 +11749,7 @@
         <v>84</v>
       </c>
       <c r="P53" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q53">
         <v>3.85</v>
@@ -11821,7 +11827,7 @@
         <v>2.33</v>
       </c>
       <c r="AP53">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AQ53">
         <v>2.33</v>
@@ -11949,7 +11955,7 @@
         <v>119</v>
       </c>
       <c r="P54" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q54">
         <v>2.66</v>
@@ -12155,7 +12161,7 @@
         <v>120</v>
       </c>
       <c r="P55" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q55">
         <v>3</v>
@@ -12361,7 +12367,7 @@
         <v>121</v>
       </c>
       <c r="P56" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q56">
         <v>3.35</v>
@@ -12773,7 +12779,7 @@
         <v>84</v>
       </c>
       <c r="P58" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q58">
         <v>3.3</v>
@@ -12854,7 +12860,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ58">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AR58">
         <v>1.88</v>
@@ -12979,7 +12985,7 @@
         <v>84</v>
       </c>
       <c r="P59" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q59">
         <v>5.5</v>
@@ -13185,7 +13191,7 @@
         <v>122</v>
       </c>
       <c r="P60" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q60">
         <v>2.11</v>
@@ -13391,7 +13397,7 @@
         <v>84</v>
       </c>
       <c r="P61" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q61">
         <v>4.5</v>
@@ -13597,7 +13603,7 @@
         <v>123</v>
       </c>
       <c r="P62" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q62">
         <v>2.26</v>
@@ -13803,7 +13809,7 @@
         <v>84</v>
       </c>
       <c r="P63" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q63">
         <v>2.87</v>
@@ -13884,7 +13890,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ63">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AR63">
         <v>2.11</v>
@@ -14009,7 +14015,7 @@
         <v>124</v>
       </c>
       <c r="P64" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q64">
         <v>1.85</v>
@@ -14087,7 +14093,7 @@
         <v>1.4</v>
       </c>
       <c r="AP64">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AQ64">
         <v>1.25</v>
@@ -14215,7 +14221,7 @@
         <v>125</v>
       </c>
       <c r="P65" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q65">
         <v>4.28</v>
@@ -14421,7 +14427,7 @@
         <v>126</v>
       </c>
       <c r="P66" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q66">
         <v>2.19</v>
@@ -14833,7 +14839,7 @@
         <v>128</v>
       </c>
       <c r="P68" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q68">
         <v>3.3</v>
@@ -15039,7 +15045,7 @@
         <v>129</v>
       </c>
       <c r="P69" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q69">
         <v>2.03</v>
@@ -15657,7 +15663,7 @@
         <v>131</v>
       </c>
       <c r="P72" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q72">
         <v>4.6</v>
@@ -16353,7 +16359,7 @@
         <v>1.4</v>
       </c>
       <c r="AP75">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AQ75">
         <v>1</v>
@@ -16481,7 +16487,7 @@
         <v>84</v>
       </c>
       <c r="P76" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -16562,7 +16568,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ76">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AR76">
         <v>1.69</v>
@@ -16687,7 +16693,7 @@
         <v>134</v>
       </c>
       <c r="P77" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q77">
         <v>3.28</v>
@@ -16893,7 +16899,7 @@
         <v>135</v>
       </c>
       <c r="P78" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q78">
         <v>3.6</v>
@@ -17099,7 +17105,7 @@
         <v>136</v>
       </c>
       <c r="P79" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q79">
         <v>2.17</v>
@@ -17305,7 +17311,7 @@
         <v>137</v>
       </c>
       <c r="P80" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q80">
         <v>1.68</v>
@@ -17511,7 +17517,7 @@
         <v>138</v>
       </c>
       <c r="P81" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q81">
         <v>1.52</v>
@@ -17717,7 +17723,7 @@
         <v>139</v>
       </c>
       <c r="P82" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q82">
         <v>2.38</v>
@@ -18129,7 +18135,7 @@
         <v>140</v>
       </c>
       <c r="P84" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q84">
         <v>3.6</v>
@@ -18286,6 +18292,212 @@
       </c>
       <c r="BP84">
         <v>1.33</v>
+      </c>
+    </row>
+    <row r="85" spans="1:68">
+      <c r="A85" s="1">
+        <v>84</v>
+      </c>
+      <c r="B85">
+        <v>7811560</v>
+      </c>
+      <c r="C85" t="s">
+        <v>68</v>
+      </c>
+      <c r="D85" t="s">
+        <v>69</v>
+      </c>
+      <c r="E85" s="2">
+        <v>45843.45833333334</v>
+      </c>
+      <c r="F85">
+        <v>0</v>
+      </c>
+      <c r="G85" t="s">
+        <v>76</v>
+      </c>
+      <c r="H85" t="s">
+        <v>70</v>
+      </c>
+      <c r="I85">
+        <v>1</v>
+      </c>
+      <c r="J85">
+        <v>0</v>
+      </c>
+      <c r="K85">
+        <v>1</v>
+      </c>
+      <c r="L85">
+        <v>1</v>
+      </c>
+      <c r="M85">
+        <v>1</v>
+      </c>
+      <c r="N85">
+        <v>2</v>
+      </c>
+      <c r="O85" t="s">
+        <v>141</v>
+      </c>
+      <c r="P85" t="s">
+        <v>203</v>
+      </c>
+      <c r="Q85">
+        <v>3.27</v>
+      </c>
+      <c r="R85">
+        <v>2.4</v>
+      </c>
+      <c r="S85">
+        <v>2.7</v>
+      </c>
+      <c r="T85">
+        <v>1.2</v>
+      </c>
+      <c r="U85">
+        <v>4</v>
+      </c>
+      <c r="V85">
+        <v>2.07</v>
+      </c>
+      <c r="W85">
+        <v>1.83</v>
+      </c>
+      <c r="X85">
+        <v>3.8</v>
+      </c>
+      <c r="Y85">
+        <v>1.22</v>
+      </c>
+      <c r="Z85">
+        <v>3.2</v>
+      </c>
+      <c r="AA85">
+        <v>3.4</v>
+      </c>
+      <c r="AB85">
+        <v>1.95</v>
+      </c>
+      <c r="AC85">
+        <v>1.01</v>
+      </c>
+      <c r="AD85">
+        <v>19</v>
+      </c>
+      <c r="AE85">
+        <v>1.11</v>
+      </c>
+      <c r="AF85">
+        <v>7</v>
+      </c>
+      <c r="AG85">
+        <v>1.45</v>
+      </c>
+      <c r="AH85">
+        <v>2.56</v>
+      </c>
+      <c r="AI85">
+        <v>1.35</v>
+      </c>
+      <c r="AJ85">
+        <v>3.1</v>
+      </c>
+      <c r="AK85">
+        <v>1.25</v>
+      </c>
+      <c r="AL85">
+        <v>1.25</v>
+      </c>
+      <c r="AM85">
+        <v>1.44</v>
+      </c>
+      <c r="AN85">
+        <v>1.86</v>
+      </c>
+      <c r="AO85">
+        <v>1.71</v>
+      </c>
+      <c r="AP85">
+        <v>1.75</v>
+      </c>
+      <c r="AQ85">
+        <v>1.63</v>
+      </c>
+      <c r="AR85">
+        <v>1.81</v>
+      </c>
+      <c r="AS85">
+        <v>2.21</v>
+      </c>
+      <c r="AT85">
+        <v>4.02</v>
+      </c>
+      <c r="AU85">
+        <v>3</v>
+      </c>
+      <c r="AV85">
+        <v>7</v>
+      </c>
+      <c r="AW85">
+        <v>5</v>
+      </c>
+      <c r="AX85">
+        <v>9</v>
+      </c>
+      <c r="AY85">
+        <v>8</v>
+      </c>
+      <c r="AZ85">
+        <v>16</v>
+      </c>
+      <c r="BA85">
+        <v>4</v>
+      </c>
+      <c r="BB85">
+        <v>9</v>
+      </c>
+      <c r="BC85">
+        <v>13</v>
+      </c>
+      <c r="BD85">
+        <v>2.4</v>
+      </c>
+      <c r="BE85">
+        <v>9</v>
+      </c>
+      <c r="BF85">
+        <v>1.72</v>
+      </c>
+      <c r="BG85">
+        <v>1.14</v>
+      </c>
+      <c r="BH85">
+        <v>4.1</v>
+      </c>
+      <c r="BI85">
+        <v>1.38</v>
+      </c>
+      <c r="BJ85">
+        <v>2.8</v>
+      </c>
+      <c r="BK85">
+        <v>1.74</v>
+      </c>
+      <c r="BL85">
+        <v>2.26</v>
+      </c>
+      <c r="BM85">
+        <v>1.97</v>
+      </c>
+      <c r="BN85">
+        <v>1.73</v>
+      </c>
+      <c r="BO85">
+        <v>2.4</v>
+      </c>
+      <c r="BP85">
+        <v>1.42</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="205">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -626,6 +626,9 @@
   </si>
   <si>
     <t>['64']</t>
+  </si>
+  <si>
+    <t>['54', '70']</t>
   </si>
 </sst>
 </file>
@@ -987,7 +990,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP85"/>
+  <dimension ref="A1:BP86"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1324,7 +1327,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ2">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -2145,7 +2148,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AQ6">
         <v>0.57</v>
@@ -2766,7 +2769,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ9">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3793,7 +3796,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AQ14">
         <v>2.33</v>
@@ -7089,7 +7092,7 @@
         <v>1.5</v>
       </c>
       <c r="AP30">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AQ30">
         <v>1.63</v>
@@ -7710,7 +7713,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ33">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AR33">
         <v>1.89</v>
@@ -8740,7 +8743,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ38">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AR38">
         <v>1.28</v>
@@ -10179,7 +10182,7 @@
         <v>1.5</v>
       </c>
       <c r="AP45">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AQ45">
         <v>1.25</v>
@@ -11418,7 +11421,7 @@
         <v>1</v>
       </c>
       <c r="AQ51">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AR51">
         <v>1.2</v>
@@ -13478,7 +13481,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ61">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AR61">
         <v>1.48</v>
@@ -15329,7 +15332,7 @@
         <v>1.4</v>
       </c>
       <c r="AP70">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AQ70">
         <v>1.14</v>
@@ -15950,7 +15953,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ73">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AR73">
         <v>2</v>
@@ -17801,7 +17804,7 @@
         <v>0.6</v>
       </c>
       <c r="AP82">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AQ82">
         <v>1</v>
@@ -18498,6 +18501,212 @@
       </c>
       <c r="BP85">
         <v>1.42</v>
+      </c>
+    </row>
+    <row r="86" spans="1:68">
+      <c r="A86" s="1">
+        <v>85</v>
+      </c>
+      <c r="B86">
+        <v>7811561</v>
+      </c>
+      <c r="C86" t="s">
+        <v>68</v>
+      </c>
+      <c r="D86" t="s">
+        <v>69</v>
+      </c>
+      <c r="E86" s="2">
+        <v>45843.54166666666</v>
+      </c>
+      <c r="F86">
+        <v>0</v>
+      </c>
+      <c r="G86" t="s">
+        <v>74</v>
+      </c>
+      <c r="H86" t="s">
+        <v>78</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>0</v>
+      </c>
+      <c r="K86">
+        <v>0</v>
+      </c>
+      <c r="L86">
+        <v>0</v>
+      </c>
+      <c r="M86">
+        <v>2</v>
+      </c>
+      <c r="N86">
+        <v>2</v>
+      </c>
+      <c r="O86" t="s">
+        <v>84</v>
+      </c>
+      <c r="P86" t="s">
+        <v>204</v>
+      </c>
+      <c r="Q86">
+        <v>3.9</v>
+      </c>
+      <c r="R86">
+        <v>2.34</v>
+      </c>
+      <c r="S86">
+        <v>2.32</v>
+      </c>
+      <c r="T86">
+        <v>1.25</v>
+      </c>
+      <c r="U86">
+        <v>3.42</v>
+      </c>
+      <c r="V86">
+        <v>2.2</v>
+      </c>
+      <c r="W86">
+        <v>1.62</v>
+      </c>
+      <c r="X86">
+        <v>4.8</v>
+      </c>
+      <c r="Y86">
+        <v>1.17</v>
+      </c>
+      <c r="Z86">
+        <v>3.75</v>
+      </c>
+      <c r="AA86">
+        <v>4.1</v>
+      </c>
+      <c r="AB86">
+        <v>1.81</v>
+      </c>
+      <c r="AC86">
+        <v>1.03</v>
+      </c>
+      <c r="AD86">
+        <v>10</v>
+      </c>
+      <c r="AE86">
+        <v>1.17</v>
+      </c>
+      <c r="AF86">
+        <v>4.95</v>
+      </c>
+      <c r="AG86">
+        <v>1.51</v>
+      </c>
+      <c r="AH86">
+        <v>2.37</v>
+      </c>
+      <c r="AI86">
+        <v>1.5</v>
+      </c>
+      <c r="AJ86">
+        <v>2.54</v>
+      </c>
+      <c r="AK86">
+        <v>1.29</v>
+      </c>
+      <c r="AL86">
+        <v>1.26</v>
+      </c>
+      <c r="AM86">
+        <v>1.25</v>
+      </c>
+      <c r="AN86">
+        <v>1.33</v>
+      </c>
+      <c r="AO86">
+        <v>1.43</v>
+      </c>
+      <c r="AP86">
+        <v>1.14</v>
+      </c>
+      <c r="AQ86">
+        <v>1.63</v>
+      </c>
+      <c r="AR86">
+        <v>1.73</v>
+      </c>
+      <c r="AS86">
+        <v>1.99</v>
+      </c>
+      <c r="AT86">
+        <v>3.72</v>
+      </c>
+      <c r="AU86">
+        <v>4</v>
+      </c>
+      <c r="AV86">
+        <v>3</v>
+      </c>
+      <c r="AW86">
+        <v>9</v>
+      </c>
+      <c r="AX86">
+        <v>4</v>
+      </c>
+      <c r="AY86">
+        <v>13</v>
+      </c>
+      <c r="AZ86">
+        <v>7</v>
+      </c>
+      <c r="BA86">
+        <v>9</v>
+      </c>
+      <c r="BB86">
+        <v>3</v>
+      </c>
+      <c r="BC86">
+        <v>12</v>
+      </c>
+      <c r="BD86">
+        <v>2.69</v>
+      </c>
+      <c r="BE86">
+        <v>8.6</v>
+      </c>
+      <c r="BF86">
+        <v>1.62</v>
+      </c>
+      <c r="BG86">
+        <v>1.18</v>
+      </c>
+      <c r="BH86">
+        <v>4.05</v>
+      </c>
+      <c r="BI86">
+        <v>1.32</v>
+      </c>
+      <c r="BJ86">
+        <v>3.2</v>
+      </c>
+      <c r="BK86">
+        <v>1.74</v>
+      </c>
+      <c r="BL86">
+        <v>2.1</v>
+      </c>
+      <c r="BM86">
+        <v>1.96</v>
+      </c>
+      <c r="BN86">
+        <v>1.79</v>
+      </c>
+      <c r="BO86">
+        <v>2.43</v>
+      </c>
+      <c r="BP86">
+        <v>1.49</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="206">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -442,6 +442,9 @@
     <t>['14']</t>
   </si>
   <si>
+    <t>['35']</t>
+  </si>
+  <si>
     <t>['4', '14']</t>
   </si>
   <si>
@@ -577,9 +580,6 @@
     <t>['22', '90+1', '78', '71']</t>
   </si>
   <si>
-    <t>['35']</t>
-  </si>
-  <si>
     <t>['31', '44', '55']</t>
   </si>
   <si>
@@ -629,6 +629,9 @@
   </si>
   <si>
     <t>['54', '70']</t>
+  </si>
+  <si>
+    <t>['50']</t>
   </si>
 </sst>
 </file>
@@ -990,7 +993,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP86"/>
+  <dimension ref="A1:BP88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1246,7 +1249,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q2">
         <v>3.2</v>
@@ -1452,7 +1455,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q3">
         <v>3.25</v>
@@ -1658,7 +1661,7 @@
         <v>84</v>
       </c>
       <c r="P4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q4">
         <v>3.1</v>
@@ -2070,7 +2073,7 @@
         <v>85</v>
       </c>
       <c r="P6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q6">
         <v>2.3</v>
@@ -2276,7 +2279,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q7">
         <v>3.4</v>
@@ -2354,7 +2357,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ7">
         <v>1.14</v>
@@ -2482,7 +2485,7 @@
         <v>87</v>
       </c>
       <c r="P8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q8">
         <v>4.1</v>
@@ -2894,7 +2897,7 @@
         <v>89</v>
       </c>
       <c r="P10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q10">
         <v>1.7</v>
@@ -3100,7 +3103,7 @@
         <v>84</v>
       </c>
       <c r="P11" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q11">
         <v>2.25</v>
@@ -3178,7 +3181,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ11">
         <v>1</v>
@@ -3718,7 +3721,7 @@
         <v>84</v>
       </c>
       <c r="P14" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q14">
         <v>3.1</v>
@@ -3799,7 +3802,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ14">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AR14">
         <v>2.17</v>
@@ -3924,7 +3927,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q15">
         <v>3.2</v>
@@ -4002,7 +4005,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ15">
         <v>0.57</v>
@@ -4130,7 +4133,7 @@
         <v>93</v>
       </c>
       <c r="P16" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q16">
         <v>4.79</v>
@@ -4336,7 +4339,7 @@
         <v>84</v>
       </c>
       <c r="P17" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q17">
         <v>4.17</v>
@@ -4748,7 +4751,7 @@
         <v>84</v>
       </c>
       <c r="P19" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q19">
         <v>1.72</v>
@@ -5160,7 +5163,7 @@
         <v>96</v>
       </c>
       <c r="P21" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q21">
         <v>2.2</v>
@@ -5366,7 +5369,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q22">
         <v>4.75</v>
@@ -5447,7 +5450,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ22">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AR22">
         <v>0</v>
@@ -5572,7 +5575,7 @@
         <v>98</v>
       </c>
       <c r="P23" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q23">
         <v>2.3</v>
@@ -5650,7 +5653,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AQ23">
         <v>0.5</v>
@@ -5778,7 +5781,7 @@
         <v>99</v>
       </c>
       <c r="P24" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q24">
         <v>2.25</v>
@@ -5984,7 +5987,7 @@
         <v>100</v>
       </c>
       <c r="P25" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q25">
         <v>3.75</v>
@@ -6190,7 +6193,7 @@
         <v>101</v>
       </c>
       <c r="P26" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q26">
         <v>6.5</v>
@@ -6396,7 +6399,7 @@
         <v>102</v>
       </c>
       <c r="P27" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q27">
         <v>1.85</v>
@@ -6602,7 +6605,7 @@
         <v>84</v>
       </c>
       <c r="P28" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q28">
         <v>2.5</v>
@@ -6680,7 +6683,7 @@
         <v>1</v>
       </c>
       <c r="AP28">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ28">
         <v>1.25</v>
@@ -6808,7 +6811,7 @@
         <v>103</v>
       </c>
       <c r="P29" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q29">
         <v>2.7</v>
@@ -7632,7 +7635,7 @@
         <v>106</v>
       </c>
       <c r="P33" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q33">
         <v>2.93</v>
@@ -7838,7 +7841,7 @@
         <v>107</v>
       </c>
       <c r="P34" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q34">
         <v>2.26</v>
@@ -8250,7 +8253,7 @@
         <v>109</v>
       </c>
       <c r="P36" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q36">
         <v>6.4</v>
@@ -8331,7 +8334,7 @@
         <v>1</v>
       </c>
       <c r="AQ36">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AR36">
         <v>1.26</v>
@@ -8456,7 +8459,7 @@
         <v>110</v>
       </c>
       <c r="P37" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q37">
         <v>3.84</v>
@@ -8662,7 +8665,7 @@
         <v>84</v>
       </c>
       <c r="P38" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q38">
         <v>5.25</v>
@@ -8740,7 +8743,7 @@
         <v>0.33</v>
       </c>
       <c r="AP38">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AQ38">
         <v>1.63</v>
@@ -8868,7 +8871,7 @@
         <v>111</v>
       </c>
       <c r="P39" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -9074,7 +9077,7 @@
         <v>112</v>
       </c>
       <c r="P40" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q40">
         <v>2.85</v>
@@ -9280,7 +9283,7 @@
         <v>113</v>
       </c>
       <c r="P41" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q41">
         <v>4.02</v>
@@ -9358,7 +9361,7 @@
         <v>2</v>
       </c>
       <c r="AP41">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ41">
         <v>1.29</v>
@@ -9486,7 +9489,7 @@
         <v>84</v>
       </c>
       <c r="P42" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q42">
         <v>2.1</v>
@@ -9692,7 +9695,7 @@
         <v>114</v>
       </c>
       <c r="P43" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q43">
         <v>2.75</v>
@@ -9898,7 +9901,7 @@
         <v>115</v>
       </c>
       <c r="P44" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q44">
         <v>1.68</v>
@@ -10310,7 +10313,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q46">
         <v>1.91</v>
@@ -10928,7 +10931,7 @@
         <v>118</v>
       </c>
       <c r="P49" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q49">
         <v>3.45</v>
@@ -11006,7 +11009,7 @@
         <v>1.5</v>
       </c>
       <c r="AP49">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AQ49">
         <v>1.14</v>
@@ -11340,7 +11343,7 @@
         <v>84</v>
       </c>
       <c r="P51" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q51">
         <v>6.5</v>
@@ -11546,7 +11549,7 @@
         <v>84</v>
       </c>
       <c r="P52" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q52">
         <v>2.18</v>
@@ -11752,7 +11755,7 @@
         <v>84</v>
       </c>
       <c r="P53" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q53">
         <v>3.85</v>
@@ -11833,7 +11836,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ53">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AR53">
         <v>1.88</v>
@@ -11958,7 +11961,7 @@
         <v>119</v>
       </c>
       <c r="P54" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q54">
         <v>2.66</v>
@@ -12164,7 +12167,7 @@
         <v>120</v>
       </c>
       <c r="P55" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q55">
         <v>3</v>
@@ -12242,7 +12245,7 @@
         <v>1.75</v>
       </c>
       <c r="AP55">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ55">
         <v>1.43</v>
@@ -12370,7 +12373,7 @@
         <v>121</v>
       </c>
       <c r="P56" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q56">
         <v>3.35</v>
@@ -12782,7 +12785,7 @@
         <v>84</v>
       </c>
       <c r="P58" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q58">
         <v>3.3</v>
@@ -12988,7 +12991,7 @@
         <v>84</v>
       </c>
       <c r="P59" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q59">
         <v>5.5</v>
@@ -13066,10 +13069,10 @@
         <v>2.5</v>
       </c>
       <c r="AP59">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AQ59">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AR59">
         <v>0.99</v>
@@ -13194,7 +13197,7 @@
         <v>122</v>
       </c>
       <c r="P60" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q60">
         <v>2.11</v>
@@ -13400,7 +13403,7 @@
         <v>84</v>
       </c>
       <c r="P61" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q61">
         <v>4.5</v>
@@ -13606,7 +13609,7 @@
         <v>123</v>
       </c>
       <c r="P62" t="s">
-        <v>187</v>
+        <v>142</v>
       </c>
       <c r="Q62">
         <v>2.26</v>
@@ -14920,7 +14923,7 @@
         <v>0.67</v>
       </c>
       <c r="AP68">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AQ68">
         <v>0.57</v>
@@ -15747,7 +15750,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ72">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AR72">
         <v>1.7</v>
@@ -16568,7 +16571,7 @@
         <v>1.5</v>
       </c>
       <c r="AP76">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ76">
         <v>1.63</v>
@@ -18707,6 +18710,418 @@
       </c>
       <c r="BP86">
         <v>1.49</v>
+      </c>
+    </row>
+    <row r="87" spans="1:68">
+      <c r="A87" s="1">
+        <v>86</v>
+      </c>
+      <c r="B87">
+        <v>7811562</v>
+      </c>
+      <c r="C87" t="s">
+        <v>68</v>
+      </c>
+      <c r="D87" t="s">
+        <v>69</v>
+      </c>
+      <c r="E87" s="2">
+        <v>45844.41666666666</v>
+      </c>
+      <c r="F87">
+        <v>0</v>
+      </c>
+      <c r="G87" t="s">
+        <v>80</v>
+      </c>
+      <c r="H87" t="s">
+        <v>72</v>
+      </c>
+      <c r="I87">
+        <v>1</v>
+      </c>
+      <c r="J87">
+        <v>0</v>
+      </c>
+      <c r="K87">
+        <v>1</v>
+      </c>
+      <c r="L87">
+        <v>1</v>
+      </c>
+      <c r="M87">
+        <v>1</v>
+      </c>
+      <c r="N87">
+        <v>2</v>
+      </c>
+      <c r="O87" t="s">
+        <v>142</v>
+      </c>
+      <c r="P87" t="s">
+        <v>205</v>
+      </c>
+      <c r="Q87">
+        <v>2.53</v>
+      </c>
+      <c r="R87">
+        <v>2.1</v>
+      </c>
+      <c r="S87">
+        <v>4.8</v>
+      </c>
+      <c r="T87">
+        <v>1.37</v>
+      </c>
+      <c r="U87">
+        <v>2.75</v>
+      </c>
+      <c r="V87">
+        <v>2.75</v>
+      </c>
+      <c r="W87">
+        <v>1.36</v>
+      </c>
+      <c r="X87">
+        <v>6.5</v>
+      </c>
+      <c r="Y87">
+        <v>1.05</v>
+      </c>
+      <c r="Z87">
+        <v>1.8</v>
+      </c>
+      <c r="AA87">
+        <v>3.7</v>
+      </c>
+      <c r="AB87">
+        <v>4.2</v>
+      </c>
+      <c r="AC87">
+        <v>1.01</v>
+      </c>
+      <c r="AD87">
+        <v>9.5</v>
+      </c>
+      <c r="AE87">
+        <v>1.3</v>
+      </c>
+      <c r="AF87">
+        <v>3.5</v>
+      </c>
+      <c r="AG87">
+        <v>1.95</v>
+      </c>
+      <c r="AH87">
+        <v>1.8</v>
+      </c>
+      <c r="AI87">
+        <v>1.83</v>
+      </c>
+      <c r="AJ87">
+        <v>1.91</v>
+      </c>
+      <c r="AK87">
+        <v>1.29</v>
+      </c>
+      <c r="AL87">
+        <v>1.3</v>
+      </c>
+      <c r="AM87">
+        <v>1.91</v>
+      </c>
+      <c r="AN87">
+        <v>0.8</v>
+      </c>
+      <c r="AO87">
+        <v>1</v>
+      </c>
+      <c r="AP87">
+        <v>0.83</v>
+      </c>
+      <c r="AQ87">
+        <v>1</v>
+      </c>
+      <c r="AR87">
+        <v>1.14</v>
+      </c>
+      <c r="AS87">
+        <v>1.06</v>
+      </c>
+      <c r="AT87">
+        <v>2.2</v>
+      </c>
+      <c r="AU87">
+        <v>7</v>
+      </c>
+      <c r="AV87">
+        <v>9</v>
+      </c>
+      <c r="AW87">
+        <v>10</v>
+      </c>
+      <c r="AX87">
+        <v>8</v>
+      </c>
+      <c r="AY87">
+        <v>17</v>
+      </c>
+      <c r="AZ87">
+        <v>17</v>
+      </c>
+      <c r="BA87">
+        <v>7</v>
+      </c>
+      <c r="BB87">
+        <v>4</v>
+      </c>
+      <c r="BC87">
+        <v>11</v>
+      </c>
+      <c r="BD87">
+        <v>1.62</v>
+      </c>
+      <c r="BE87">
+        <v>8.1</v>
+      </c>
+      <c r="BF87">
+        <v>2.86</v>
+      </c>
+      <c r="BG87">
+        <v>1.27</v>
+      </c>
+      <c r="BH87">
+        <v>3.8</v>
+      </c>
+      <c r="BI87">
+        <v>1.39</v>
+      </c>
+      <c r="BJ87">
+        <v>2.67</v>
+      </c>
+      <c r="BK87">
+        <v>1.73</v>
+      </c>
+      <c r="BL87">
+        <v>2</v>
+      </c>
+      <c r="BM87">
+        <v>2.1</v>
+      </c>
+      <c r="BN87">
+        <v>1.65</v>
+      </c>
+      <c r="BO87">
+        <v>3</v>
+      </c>
+      <c r="BP87">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="88" spans="1:68">
+      <c r="A88" s="1">
+        <v>87</v>
+      </c>
+      <c r="B88">
+        <v>7811563</v>
+      </c>
+      <c r="C88" t="s">
+        <v>68</v>
+      </c>
+      <c r="D88" t="s">
+        <v>69</v>
+      </c>
+      <c r="E88" s="2">
+        <v>45844.52083333334</v>
+      </c>
+      <c r="F88">
+        <v>0</v>
+      </c>
+      <c r="G88" t="s">
+        <v>75</v>
+      </c>
+      <c r="H88" t="s">
+        <v>71</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>1</v>
+      </c>
+      <c r="K88">
+        <v>1</v>
+      </c>
+      <c r="L88">
+        <v>0</v>
+      </c>
+      <c r="M88">
+        <v>1</v>
+      </c>
+      <c r="N88">
+        <v>1</v>
+      </c>
+      <c r="O88" t="s">
+        <v>84</v>
+      </c>
+      <c r="P88" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q88">
+        <v>3.95</v>
+      </c>
+      <c r="R88">
+        <v>2.37</v>
+      </c>
+      <c r="S88">
+        <v>2.35</v>
+      </c>
+      <c r="T88">
+        <v>1.2</v>
+      </c>
+      <c r="U88">
+        <v>3.72</v>
+      </c>
+      <c r="V88">
+        <v>2.26</v>
+      </c>
+      <c r="W88">
+        <v>1.65</v>
+      </c>
+      <c r="X88">
+        <v>5</v>
+      </c>
+      <c r="Y88">
+        <v>1.1</v>
+      </c>
+      <c r="Z88">
+        <v>4.09</v>
+      </c>
+      <c r="AA88">
+        <v>4</v>
+      </c>
+      <c r="AB88">
+        <v>1.8</v>
+      </c>
+      <c r="AC88">
+        <v>1.03</v>
+      </c>
+      <c r="AD88">
+        <v>15</v>
+      </c>
+      <c r="AE88">
+        <v>1.11</v>
+      </c>
+      <c r="AF88">
+        <v>5.43</v>
+      </c>
+      <c r="AG88">
+        <v>1.45</v>
+      </c>
+      <c r="AH88">
+        <v>2.45</v>
+      </c>
+      <c r="AI88">
+        <v>1.44</v>
+      </c>
+      <c r="AJ88">
+        <v>2.5</v>
+      </c>
+      <c r="AK88">
+        <v>1.25</v>
+      </c>
+      <c r="AL88">
+        <v>1.23</v>
+      </c>
+      <c r="AM88">
+        <v>1.25</v>
+      </c>
+      <c r="AN88">
+        <v>1.29</v>
+      </c>
+      <c r="AO88">
+        <v>2.33</v>
+      </c>
+      <c r="AP88">
+        <v>1.13</v>
+      </c>
+      <c r="AQ88">
+        <v>2.43</v>
+      </c>
+      <c r="AR88">
+        <v>1.61</v>
+      </c>
+      <c r="AS88">
+        <v>2.01</v>
+      </c>
+      <c r="AT88">
+        <v>3.62</v>
+      </c>
+      <c r="AU88">
+        <v>5</v>
+      </c>
+      <c r="AV88">
+        <v>5</v>
+      </c>
+      <c r="AW88">
+        <v>7</v>
+      </c>
+      <c r="AX88">
+        <v>7</v>
+      </c>
+      <c r="AY88">
+        <v>12</v>
+      </c>
+      <c r="AZ88">
+        <v>12</v>
+      </c>
+      <c r="BA88">
+        <v>8</v>
+      </c>
+      <c r="BB88">
+        <v>6</v>
+      </c>
+      <c r="BC88">
+        <v>14</v>
+      </c>
+      <c r="BD88">
+        <v>3.08</v>
+      </c>
+      <c r="BE88">
+        <v>9</v>
+      </c>
+      <c r="BF88">
+        <v>1.53</v>
+      </c>
+      <c r="BG88">
+        <v>1.13</v>
+      </c>
+      <c r="BH88">
+        <v>4.9</v>
+      </c>
+      <c r="BI88">
+        <v>1.25</v>
+      </c>
+      <c r="BJ88">
+        <v>3.45</v>
+      </c>
+      <c r="BK88">
+        <v>1.56</v>
+      </c>
+      <c r="BL88">
+        <v>2.55</v>
+      </c>
+      <c r="BM88">
+        <v>1.85</v>
+      </c>
+      <c r="BN88">
+        <v>1.85</v>
+      </c>
+      <c r="BO88">
+        <v>2.16</v>
+      </c>
+      <c r="BP88">
+        <v>1.55</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
@@ -19061,19 +19061,19 @@
         <v>5</v>
       </c>
       <c r="AV88">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AW88">
         <v>7</v>
       </c>
       <c r="AX88">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY88">
         <v>12</v>
       </c>
       <c r="AZ88">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BA88">
         <v>8</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="206">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -993,7 +993,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP88"/>
+  <dimension ref="A1:BP89"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1945,7 +1945,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AQ5">
         <v>1.57</v>
@@ -2360,7 +2360,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ7">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2563,7 +2563,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AQ8">
         <v>1.43</v>
@@ -3390,7 +3390,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ12">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR12">
         <v>1.71</v>
@@ -4417,7 +4417,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AQ17">
         <v>1.63</v>
@@ -4832,7 +4832,7 @@
         <v>2</v>
       </c>
       <c r="AQ19">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -6889,7 +6889,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AQ29">
         <v>0.57</v>
@@ -8540,7 +8540,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ37">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR37">
         <v>1.04</v>
@@ -10803,7 +10803,7 @@
         <v>0.5</v>
       </c>
       <c r="AP48">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AQ48">
         <v>1</v>
@@ -11012,7 +11012,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ49">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR49">
         <v>0.93</v>
@@ -12039,7 +12039,7 @@
         <v>1.5</v>
       </c>
       <c r="AP54">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AQ54">
         <v>1</v>
@@ -15338,7 +15338,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ70">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR70">
         <v>1.74</v>
@@ -16777,7 +16777,7 @@
         <v>1.17</v>
       </c>
       <c r="AP77">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AQ77">
         <v>1.25</v>
@@ -17192,7 +17192,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ79">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR79">
         <v>1.93</v>
@@ -19122,6 +19122,212 @@
       </c>
       <c r="BP88">
         <v>1.55</v>
+      </c>
+    </row>
+    <row r="89" spans="1:68">
+      <c r="A89" s="1">
+        <v>88</v>
+      </c>
+      <c r="B89">
+        <v>7811576</v>
+      </c>
+      <c r="C89" t="s">
+        <v>68</v>
+      </c>
+      <c r="D89" t="s">
+        <v>69</v>
+      </c>
+      <c r="E89" s="2">
+        <v>45845.5</v>
+      </c>
+      <c r="F89">
+        <v>0</v>
+      </c>
+      <c r="G89" t="s">
+        <v>73</v>
+      </c>
+      <c r="H89" t="s">
+        <v>81</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>0</v>
+      </c>
+      <c r="K89">
+        <v>0</v>
+      </c>
+      <c r="L89">
+        <v>0</v>
+      </c>
+      <c r="M89">
+        <v>0</v>
+      </c>
+      <c r="N89">
+        <v>0</v>
+      </c>
+      <c r="O89" t="s">
+        <v>84</v>
+      </c>
+      <c r="P89" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q89">
+        <v>3.43</v>
+      </c>
+      <c r="R89">
+        <v>2.42</v>
+      </c>
+      <c r="S89">
+        <v>2.3</v>
+      </c>
+      <c r="T89">
+        <v>1.22</v>
+      </c>
+      <c r="U89">
+        <v>3.65</v>
+      </c>
+      <c r="V89">
+        <v>2.1</v>
+      </c>
+      <c r="W89">
+        <v>1.65</v>
+      </c>
+      <c r="X89">
+        <v>4.4</v>
+      </c>
+      <c r="Y89">
+        <v>1.16</v>
+      </c>
+      <c r="Z89">
+        <v>3.09</v>
+      </c>
+      <c r="AA89">
+        <v>3.39</v>
+      </c>
+      <c r="AB89">
+        <v>2</v>
+      </c>
+      <c r="AC89">
+        <v>1.01</v>
+      </c>
+      <c r="AD89">
+        <v>10</v>
+      </c>
+      <c r="AE89">
+        <v>1.14</v>
+      </c>
+      <c r="AF89">
+        <v>5.4</v>
+      </c>
+      <c r="AG89">
+        <v>1.65</v>
+      </c>
+      <c r="AH89">
+        <v>2</v>
+      </c>
+      <c r="AI89">
+        <v>1.4</v>
+      </c>
+      <c r="AJ89">
+        <v>2.62</v>
+      </c>
+      <c r="AK89">
+        <v>1.88</v>
+      </c>
+      <c r="AL89">
+        <v>1.28</v>
+      </c>
+      <c r="AM89">
+        <v>1.3</v>
+      </c>
+      <c r="AN89">
+        <v>0.86</v>
+      </c>
+      <c r="AO89">
+        <v>1.14</v>
+      </c>
+      <c r="AP89">
+        <v>0.88</v>
+      </c>
+      <c r="AQ89">
+        <v>1.13</v>
+      </c>
+      <c r="AR89">
+        <v>1.62</v>
+      </c>
+      <c r="AS89">
+        <v>1.35</v>
+      </c>
+      <c r="AT89">
+        <v>2.97</v>
+      </c>
+      <c r="AU89">
+        <v>3</v>
+      </c>
+      <c r="AV89">
+        <v>5</v>
+      </c>
+      <c r="AW89">
+        <v>13</v>
+      </c>
+      <c r="AX89">
+        <v>3</v>
+      </c>
+      <c r="AY89">
+        <v>16</v>
+      </c>
+      <c r="AZ89">
+        <v>8</v>
+      </c>
+      <c r="BA89">
+        <v>9</v>
+      </c>
+      <c r="BB89">
+        <v>2</v>
+      </c>
+      <c r="BC89">
+        <v>11</v>
+      </c>
+      <c r="BD89">
+        <v>2.46</v>
+      </c>
+      <c r="BE89">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF89">
+        <v>1.72</v>
+      </c>
+      <c r="BG89">
+        <v>1.17</v>
+      </c>
+      <c r="BH89">
+        <v>4.2</v>
+      </c>
+      <c r="BI89">
+        <v>1.33</v>
+      </c>
+      <c r="BJ89">
+        <v>3.05</v>
+      </c>
+      <c r="BK89">
+        <v>1.6</v>
+      </c>
+      <c r="BL89">
+        <v>2.3</v>
+      </c>
+      <c r="BM89">
+        <v>1.91</v>
+      </c>
+      <c r="BN89">
+        <v>1.83</v>
+      </c>
+      <c r="BO89">
+        <v>2.36</v>
+      </c>
+      <c r="BP89">
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="206">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -427,15 +427,15 @@
     <t>['41', '37', '45+1', '51', '80', '64']</t>
   </si>
   <si>
+    <t>['14', '46']</t>
+  </si>
+  <si>
+    <t>['6']</t>
+  </si>
+  <si>
     <t>['15', '54']</t>
   </si>
   <si>
-    <t>['14', '46']</t>
-  </si>
-  <si>
-    <t>['6']</t>
-  </si>
-  <si>
     <t>['78', '4']</t>
   </si>
   <si>
@@ -613,13 +613,13 @@
     <t>['16', '47']</t>
   </si>
   <si>
+    <t>['85']</t>
+  </si>
+  <si>
+    <t>['13', '33']</t>
+  </si>
+  <si>
     <t>['61', '56', '90+6']</t>
-  </si>
-  <si>
-    <t>['85']</t>
-  </si>
-  <si>
-    <t>['13', '33']</t>
   </si>
   <si>
     <t>['65', '52']</t>
@@ -993,7 +993,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP89"/>
+  <dimension ref="A1:BP88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -3184,7 +3184,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ11">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR11">
         <v>1.83</v>
@@ -4829,7 +4829,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ19">
         <v>1.13</v>
@@ -5038,7 +5038,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ20">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR20">
         <v>1.66</v>
@@ -5859,7 +5859,7 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ24">
         <v>1.43</v>
@@ -7510,7 +7510,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ32">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR32">
         <v>1.86</v>
@@ -9570,7 +9570,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ42">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR42">
         <v>1.2</v>
@@ -9979,7 +9979,7 @@
         <v>1.5</v>
       </c>
       <c r="AP44">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ44">
         <v>0.5</v>
@@ -10391,7 +10391,7 @@
         <v>1.75</v>
       </c>
       <c r="AP46">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ46">
         <v>1.57</v>
@@ -12042,7 +12042,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ54">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR54">
         <v>1.43</v>
@@ -12657,7 +12657,7 @@
         <v>1.75</v>
       </c>
       <c r="AP57">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ57">
         <v>1.29</v>
@@ -15129,7 +15129,7 @@
         <v>0.75</v>
       </c>
       <c r="AP69">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ69">
         <v>1</v>
@@ -16039,7 +16039,7 @@
         <v>73</v>
       </c>
       <c r="B74">
-        <v>7811617</v>
+        <v>7811549</v>
       </c>
       <c r="C74" t="s">
         <v>68</v>
@@ -16054,7 +16054,7 @@
         <v>0</v>
       </c>
       <c r="G74" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="H74" t="s">
         <v>72</v>
@@ -16084,109 +16084,109 @@
         <v>103</v>
       </c>
       <c r="Q74">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="R74">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S74">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="T74">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="U74">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="V74">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="W74">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="X74">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Y74">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z74">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AA74">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AB74">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AC74">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AD74">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AE74">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF74">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AG74">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH74">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AI74">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AJ74">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AK74">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AL74">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AM74">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AN74">
-        <v>2.17</v>
+        <v>1.67</v>
       </c>
       <c r="AO74">
         <v>1.4</v>
       </c>
       <c r="AP74">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AQ74">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR74">
-        <v>2.02</v>
+        <v>1.83</v>
       </c>
       <c r="AS74">
         <v>1.2</v>
       </c>
       <c r="AT74">
-        <v>3.22</v>
+        <v>3.03</v>
       </c>
       <c r="AU74">
         <v>7</v>
       </c>
       <c r="AV74">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW74">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AX74">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AY74">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AZ74">
         <v>4</v>
@@ -16201,43 +16201,43 @@
         <v>14</v>
       </c>
       <c r="BD74">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BE74">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BF74">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BG74">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BH74">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="BI74">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="BJ74">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="BK74">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BL74">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BM74">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BN74">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BO74">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BP74">
-        <v>0</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="75" spans="1:68">
@@ -16245,7 +16245,7 @@
         <v>74</v>
       </c>
       <c r="B75">
-        <v>7811549</v>
+        <v>7811550</v>
       </c>
       <c r="C75" t="s">
         <v>68</v>
@@ -16254,196 +16254,196 @@
         <v>69</v>
       </c>
       <c r="E75" s="2">
-        <v>45836.25</v>
+        <v>45836.5</v>
       </c>
       <c r="F75">
         <v>0</v>
       </c>
       <c r="G75" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H75" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>1</v>
+      </c>
+      <c r="K75">
+        <v>1</v>
+      </c>
+      <c r="L75">
+        <v>0</v>
+      </c>
+      <c r="M75">
+        <v>4</v>
+      </c>
+      <c r="N75">
+        <v>4</v>
+      </c>
+      <c r="O75" t="s">
+        <v>84</v>
+      </c>
+      <c r="P75" t="s">
+        <v>195</v>
+      </c>
+      <c r="Q75">
+        <v>4</v>
+      </c>
+      <c r="R75">
+        <v>2.4</v>
+      </c>
+      <c r="S75">
+        <v>2.25</v>
+      </c>
+      <c r="T75">
+        <v>1.25</v>
+      </c>
+      <c r="U75">
+        <v>3.5</v>
+      </c>
+      <c r="V75">
+        <v>2.15</v>
+      </c>
+      <c r="W75">
+        <v>1.65</v>
+      </c>
+      <c r="X75">
+        <v>4.5</v>
+      </c>
+      <c r="Y75">
+        <v>1.13</v>
+      </c>
+      <c r="Z75">
+        <v>4.1</v>
+      </c>
+      <c r="AA75">
+        <v>3.8</v>
+      </c>
+      <c r="AB75">
+        <v>1.75</v>
+      </c>
+      <c r="AC75">
+        <v>1</v>
+      </c>
+      <c r="AD75">
+        <v>12</v>
+      </c>
+      <c r="AE75">
+        <v>1.11</v>
+      </c>
+      <c r="AF75">
+        <v>5.3</v>
+      </c>
+      <c r="AG75">
+        <v>1.46</v>
+      </c>
+      <c r="AH75">
+        <v>2.63</v>
+      </c>
+      <c r="AI75">
+        <v>1.51</v>
+      </c>
+      <c r="AJ75">
+        <v>2.5</v>
+      </c>
+      <c r="AK75">
+        <v>1.25</v>
+      </c>
+      <c r="AL75">
+        <v>1.26</v>
+      </c>
+      <c r="AM75">
+        <v>1.22</v>
+      </c>
+      <c r="AN75">
+        <v>1.5</v>
+      </c>
+      <c r="AO75">
+        <v>1.5</v>
+      </c>
+      <c r="AP75">
+        <v>1.13</v>
+      </c>
+      <c r="AQ75">
+        <v>1.63</v>
+      </c>
+      <c r="AR75">
+        <v>1.69</v>
+      </c>
+      <c r="AS75">
+        <v>2.12</v>
+      </c>
+      <c r="AT75">
+        <v>3.81</v>
+      </c>
+      <c r="AU75">
+        <v>5</v>
+      </c>
+      <c r="AV75">
+        <v>12</v>
+      </c>
+      <c r="AW75">
+        <v>5</v>
+      </c>
+      <c r="AX75">
+        <v>9</v>
+      </c>
+      <c r="AY75">
+        <v>10</v>
+      </c>
+      <c r="AZ75">
+        <v>21</v>
+      </c>
+      <c r="BA75">
         <v>3</v>
       </c>
-      <c r="J75">
-        <v>0</v>
-      </c>
-      <c r="K75">
-        <v>3</v>
-      </c>
-      <c r="L75">
-        <v>4</v>
-      </c>
-      <c r="M75">
-        <v>1</v>
-      </c>
-      <c r="N75">
-        <v>5</v>
-      </c>
-      <c r="O75" t="s">
-        <v>133</v>
-      </c>
-      <c r="P75" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q75">
-        <v>1.77</v>
-      </c>
-      <c r="R75">
-        <v>2.8</v>
-      </c>
-      <c r="S75">
-        <v>6.2</v>
-      </c>
-      <c r="T75">
+      <c r="BB75">
+        <v>9</v>
+      </c>
+      <c r="BC75">
+        <v>12</v>
+      </c>
+      <c r="BD75">
+        <v>2.9</v>
+      </c>
+      <c r="BE75">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF75">
+        <v>1.49</v>
+      </c>
+      <c r="BG75">
         <v>1.2</v>
       </c>
-      <c r="U75">
-        <v>4.2</v>
-      </c>
-      <c r="V75">
-        <v>1.91</v>
-      </c>
-      <c r="W75">
-        <v>1.75</v>
-      </c>
-      <c r="X75">
-        <v>4.1</v>
-      </c>
-      <c r="Y75">
-        <v>1.22</v>
-      </c>
-      <c r="Z75">
-        <v>1.35</v>
-      </c>
-      <c r="AA75">
-        <v>4.8</v>
-      </c>
-      <c r="AB75">
-        <v>6</v>
-      </c>
-      <c r="AC75">
-        <v>1.01</v>
-      </c>
-      <c r="AD75">
-        <v>19</v>
-      </c>
-      <c r="AE75">
-        <v>1.09</v>
-      </c>
-      <c r="AF75">
-        <v>6.25</v>
-      </c>
-      <c r="AG75">
-        <v>1.33</v>
-      </c>
-      <c r="AH75">
-        <v>2.9</v>
-      </c>
-      <c r="AI75">
-        <v>1.66</v>
-      </c>
-      <c r="AJ75">
-        <v>2.25</v>
-      </c>
-      <c r="AK75">
-        <v>1.11</v>
-      </c>
-      <c r="AL75">
-        <v>1.15</v>
-      </c>
-      <c r="AM75">
-        <v>2.95</v>
-      </c>
-      <c r="AN75">
-        <v>1.67</v>
-      </c>
-      <c r="AO75">
-        <v>1.4</v>
-      </c>
-      <c r="AP75">
-        <v>1.75</v>
-      </c>
-      <c r="AQ75">
-        <v>1</v>
-      </c>
-      <c r="AR75">
-        <v>1.83</v>
-      </c>
-      <c r="AS75">
-        <v>1.2</v>
-      </c>
-      <c r="AT75">
-        <v>3.03</v>
-      </c>
-      <c r="AU75">
-        <v>7</v>
-      </c>
-      <c r="AV75">
-        <v>0</v>
-      </c>
-      <c r="AW75">
-        <v>6</v>
-      </c>
-      <c r="AX75">
-        <v>4</v>
-      </c>
-      <c r="AY75">
-        <v>13</v>
-      </c>
-      <c r="AZ75">
-        <v>4</v>
-      </c>
-      <c r="BA75">
-        <v>11</v>
-      </c>
-      <c r="BB75">
-        <v>3</v>
-      </c>
-      <c r="BC75">
-        <v>14</v>
-      </c>
-      <c r="BD75">
-        <v>1.25</v>
-      </c>
-      <c r="BE75">
-        <v>9.6</v>
-      </c>
-      <c r="BF75">
-        <v>3.7</v>
-      </c>
-      <c r="BG75">
-        <v>1.14</v>
-      </c>
       <c r="BH75">
-        <v>4.15</v>
+        <v>3.95</v>
       </c>
       <c r="BI75">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="BJ75">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="BK75">
-        <v>1.57</v>
+        <v>1.81</v>
       </c>
       <c r="BL75">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="BM75">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="BN75">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="BO75">
         <v>2.4</v>
       </c>
       <c r="BP75">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="76" spans="1:68">
@@ -16451,7 +16451,7 @@
         <v>75</v>
       </c>
       <c r="B76">
-        <v>7811550</v>
+        <v>7811551</v>
       </c>
       <c r="C76" t="s">
         <v>68</v>
@@ -16460,196 +16460,196 @@
         <v>69</v>
       </c>
       <c r="E76" s="2">
-        <v>45836.5</v>
+        <v>45836.58333333334</v>
       </c>
       <c r="F76">
         <v>0</v>
       </c>
       <c r="G76" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H76" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="I76">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J76">
         <v>1</v>
       </c>
       <c r="K76">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L76">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M76">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N76">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O76" t="s">
-        <v>84</v>
+        <v>134</v>
       </c>
       <c r="P76" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q76">
-        <v>4</v>
+        <v>3.28</v>
       </c>
       <c r="R76">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="S76">
+        <v>3.24</v>
+      </c>
+      <c r="T76">
+        <v>1.35</v>
+      </c>
+      <c r="U76">
+        <v>3.31</v>
+      </c>
+      <c r="V76">
+        <v>2.54</v>
+      </c>
+      <c r="W76">
+        <v>1.5</v>
+      </c>
+      <c r="X76">
+        <v>5.5</v>
+      </c>
+      <c r="Y76">
+        <v>1.09</v>
+      </c>
+      <c r="Z76">
+        <v>2.65</v>
+      </c>
+      <c r="AA76">
+        <v>3.25</v>
+      </c>
+      <c r="AB76">
+        <v>2.73</v>
+      </c>
+      <c r="AC76">
+        <v>1.05</v>
+      </c>
+      <c r="AD76">
+        <v>10</v>
+      </c>
+      <c r="AE76">
+        <v>1.24</v>
+      </c>
+      <c r="AF76">
+        <v>3.74</v>
+      </c>
+      <c r="AG76">
+        <v>1.85</v>
+      </c>
+      <c r="AH76">
+        <v>1.97</v>
+      </c>
+      <c r="AI76">
+        <v>1.57</v>
+      </c>
+      <c r="AJ76">
         <v>2.25</v>
       </c>
-      <c r="T76">
+      <c r="AK76">
+        <v>1.3</v>
+      </c>
+      <c r="AL76">
+        <v>1.28</v>
+      </c>
+      <c r="AM76">
+        <v>1.44</v>
+      </c>
+      <c r="AN76">
+        <v>0.5</v>
+      </c>
+      <c r="AO76">
+        <v>1.17</v>
+      </c>
+      <c r="AP76">
+        <v>0.88</v>
+      </c>
+      <c r="AQ76">
         <v>1.25</v>
       </c>
-      <c r="U76">
-        <v>3.5</v>
-      </c>
-      <c r="V76">
-        <v>2.15</v>
-      </c>
-      <c r="W76">
-        <v>1.65</v>
-      </c>
-      <c r="X76">
-        <v>4.5</v>
-      </c>
-      <c r="Y76">
-        <v>1.13</v>
-      </c>
-      <c r="Z76">
-        <v>4.1</v>
-      </c>
-      <c r="AA76">
-        <v>3.8</v>
-      </c>
-      <c r="AB76">
-        <v>1.75</v>
-      </c>
-      <c r="AC76">
-        <v>1</v>
-      </c>
-      <c r="AD76">
-        <v>12</v>
-      </c>
-      <c r="AE76">
-        <v>1.11</v>
-      </c>
-      <c r="AF76">
-        <v>5.3</v>
-      </c>
-      <c r="AG76">
-        <v>1.46</v>
-      </c>
-      <c r="AH76">
-        <v>2.63</v>
-      </c>
-      <c r="AI76">
-        <v>1.51</v>
-      </c>
-      <c r="AJ76">
-        <v>2.5</v>
-      </c>
-      <c r="AK76">
-        <v>1.25</v>
-      </c>
-      <c r="AL76">
-        <v>1.26</v>
-      </c>
-      <c r="AM76">
-        <v>1.22</v>
-      </c>
-      <c r="AN76">
-        <v>1.5</v>
-      </c>
-      <c r="AO76">
-        <v>1.5</v>
-      </c>
-      <c r="AP76">
-        <v>1.13</v>
-      </c>
-      <c r="AQ76">
-        <v>1.63</v>
-      </c>
       <c r="AR76">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="AS76">
-        <v>2.12</v>
+        <v>1.08</v>
       </c>
       <c r="AT76">
-        <v>3.81</v>
+        <v>2.74</v>
       </c>
       <c r="AU76">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AV76">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AW76">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AX76">
         <v>9</v>
       </c>
       <c r="AY76">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ76">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA76">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BB76">
         <v>9</v>
       </c>
       <c r="BC76">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BD76">
+        <v>1.96</v>
+      </c>
+      <c r="BE76">
+        <v>7.4</v>
+      </c>
+      <c r="BF76">
+        <v>2.07</v>
+      </c>
+      <c r="BG76">
+        <v>1.22</v>
+      </c>
+      <c r="BH76">
+        <v>3.35</v>
+      </c>
+      <c r="BI76">
+        <v>1.48</v>
+      </c>
+      <c r="BJ76">
+        <v>2.46</v>
+      </c>
+      <c r="BK76">
+        <v>2.09</v>
+      </c>
+      <c r="BL76">
+        <v>1.94</v>
+      </c>
+      <c r="BM76">
+        <v>2.26</v>
+      </c>
+      <c r="BN76">
+        <v>1.59</v>
+      </c>
+      <c r="BO76">
         <v>2.9</v>
       </c>
-      <c r="BE76">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF76">
-        <v>1.49</v>
-      </c>
-      <c r="BG76">
-        <v>1.2</v>
-      </c>
-      <c r="BH76">
-        <v>3.95</v>
-      </c>
-      <c r="BI76">
-        <v>1.38</v>
-      </c>
-      <c r="BJ76">
-        <v>2.82</v>
-      </c>
-      <c r="BK76">
-        <v>1.81</v>
-      </c>
-      <c r="BL76">
-        <v>2.21</v>
-      </c>
-      <c r="BM76">
-        <v>2</v>
-      </c>
-      <c r="BN76">
-        <v>1.76</v>
-      </c>
-      <c r="BO76">
-        <v>2.4</v>
-      </c>
       <c r="BP76">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="77" spans="1:68">
@@ -16657,7 +16657,7 @@
         <v>76</v>
       </c>
       <c r="B77">
-        <v>7811551</v>
+        <v>7811552</v>
       </c>
       <c r="C77" t="s">
         <v>68</v>
@@ -16666,196 +16666,196 @@
         <v>69</v>
       </c>
       <c r="E77" s="2">
-        <v>45836.58333333334</v>
+        <v>45836.70833333334</v>
       </c>
       <c r="F77">
         <v>0</v>
       </c>
       <c r="G77" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="H77" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="I77">
+        <v>1</v>
+      </c>
+      <c r="J77">
+        <v>1</v>
+      </c>
+      <c r="K77">
         <v>2</v>
       </c>
-      <c r="J77">
-        <v>1</v>
-      </c>
-      <c r="K77">
+      <c r="L77">
+        <v>2</v>
+      </c>
+      <c r="M77">
+        <v>1</v>
+      </c>
+      <c r="N77">
         <v>3</v>
       </c>
-      <c r="L77">
-        <v>3</v>
-      </c>
-      <c r="M77">
-        <v>2</v>
-      </c>
-      <c r="N77">
-        <v>5</v>
-      </c>
       <c r="O77" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P77" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q77">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="R77">
-        <v>2.35</v>
+        <v>2.07</v>
       </c>
       <c r="S77">
-        <v>3.24</v>
+        <v>2.85</v>
       </c>
       <c r="T77">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="U77">
-        <v>3.31</v>
+        <v>2.8</v>
       </c>
       <c r="V77">
-        <v>2.54</v>
+        <v>2.96</v>
       </c>
       <c r="W77">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="X77">
-        <v>5.5</v>
+        <v>7.3</v>
       </c>
       <c r="Y77">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z77">
-        <v>2.65</v>
+        <v>2.73</v>
       </c>
       <c r="AA77">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="AB77">
-        <v>2.73</v>
+        <v>2.25</v>
       </c>
       <c r="AC77">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AD77">
-        <v>10</v>
+        <v>9.65</v>
       </c>
       <c r="AE77">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="AF77">
-        <v>3.74</v>
+        <v>3.6</v>
       </c>
       <c r="AG77">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AH77">
-        <v>1.97</v>
+        <v>1.82</v>
       </c>
       <c r="AI77">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AJ77">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="AK77">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AL77">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AM77">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AN77">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="AO77">
-        <v>1.17</v>
+        <v>1.67</v>
       </c>
       <c r="AP77">
-        <v>0.88</v>
+        <v>0.71</v>
       </c>
       <c r="AQ77">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="AR77">
-        <v>1.66</v>
+        <v>1.34</v>
       </c>
       <c r="AS77">
-        <v>1.08</v>
+        <v>1.26</v>
       </c>
       <c r="AT77">
-        <v>2.74</v>
+        <v>2.6</v>
       </c>
       <c r="AU77">
         <v>7</v>
       </c>
       <c r="AV77">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AW77">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AX77">
+        <v>3</v>
+      </c>
+      <c r="AY77">
+        <v>14</v>
+      </c>
+      <c r="AZ77">
         <v>9</v>
-      </c>
-      <c r="AY77">
-        <v>9</v>
-      </c>
-      <c r="AZ77">
-        <v>20</v>
       </c>
       <c r="BA77">
         <v>5</v>
       </c>
       <c r="BB77">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="BC77">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="BD77">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="BE77">
-        <v>7.4</v>
+        <v>6.5</v>
       </c>
       <c r="BF77">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="BG77">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="BH77">
-        <v>3.35</v>
+        <v>3.22</v>
       </c>
       <c r="BI77">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="BJ77">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="BK77">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="BL77">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="BM77">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="BN77">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="BO77">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="BP77">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="78" spans="1:68">
@@ -16863,7 +16863,7 @@
         <v>77</v>
       </c>
       <c r="B78">
-        <v>7811552</v>
+        <v>7811554</v>
       </c>
       <c r="C78" t="s">
         <v>68</v>
@@ -16872,196 +16872,196 @@
         <v>69</v>
       </c>
       <c r="E78" s="2">
-        <v>45836.70833333334</v>
+        <v>45839.5</v>
       </c>
       <c r="F78">
         <v>0</v>
       </c>
       <c r="G78" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H78" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="I78">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J78">
         <v>1</v>
       </c>
       <c r="K78">
+        <v>4</v>
+      </c>
+      <c r="L78">
+        <v>6</v>
+      </c>
+      <c r="M78">
         <v>2</v>
       </c>
-      <c r="L78">
-        <v>2</v>
-      </c>
-      <c r="M78">
-        <v>1</v>
-      </c>
       <c r="N78">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="O78" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P78" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q78">
-        <v>3.6</v>
+        <v>2.17</v>
       </c>
       <c r="R78">
-        <v>2.07</v>
+        <v>2.45</v>
       </c>
       <c r="S78">
-        <v>2.85</v>
+        <v>4.35</v>
       </c>
       <c r="T78">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="U78">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="V78">
-        <v>2.96</v>
+        <v>2.31</v>
       </c>
       <c r="W78">
-        <v>1.4</v>
+        <v>1.66</v>
       </c>
       <c r="X78">
-        <v>7.3</v>
+        <v>4.9</v>
       </c>
       <c r="Y78">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z78">
-        <v>2.73</v>
+        <v>1.6</v>
       </c>
       <c r="AA78">
-        <v>3.23</v>
+        <v>3.9</v>
       </c>
       <c r="AB78">
+        <v>5.11</v>
+      </c>
+      <c r="AC78">
+        <v>1.03</v>
+      </c>
+      <c r="AD78">
+        <v>14.3</v>
+      </c>
+      <c r="AE78">
+        <v>1.15</v>
+      </c>
+      <c r="AF78">
+        <v>5</v>
+      </c>
+      <c r="AG78">
+        <v>1.53</v>
+      </c>
+      <c r="AH78">
+        <v>2.4</v>
+      </c>
+      <c r="AI78">
+        <v>1.62</v>
+      </c>
+      <c r="AJ78">
         <v>2.25</v>
       </c>
-      <c r="AC78">
-        <v>1.01</v>
-      </c>
-      <c r="AD78">
-        <v>9.65</v>
-      </c>
-      <c r="AE78">
-        <v>1.31</v>
-      </c>
-      <c r="AF78">
-        <v>3.6</v>
-      </c>
-      <c r="AG78">
-        <v>1.88</v>
-      </c>
-      <c r="AH78">
-        <v>1.82</v>
-      </c>
-      <c r="AI78">
-        <v>1.73</v>
-      </c>
-      <c r="AJ78">
-        <v>2.07</v>
-      </c>
       <c r="AK78">
+        <v>1.25</v>
+      </c>
+      <c r="AL78">
+        <v>1.23</v>
+      </c>
+      <c r="AM78">
+        <v>2.25</v>
+      </c>
+      <c r="AN78">
+        <v>2.25</v>
+      </c>
+      <c r="AO78">
         <v>1.33</v>
       </c>
-      <c r="AL78">
-        <v>1.32</v>
-      </c>
-      <c r="AM78">
-        <v>1.39</v>
-      </c>
-      <c r="AN78">
-        <v>0.2</v>
-      </c>
-      <c r="AO78">
-        <v>1.67</v>
-      </c>
       <c r="AP78">
-        <v>0.71</v>
+        <v>2.33</v>
       </c>
       <c r="AQ78">
-        <v>1.43</v>
+        <v>1.13</v>
       </c>
       <c r="AR78">
-        <v>1.34</v>
+        <v>1.93</v>
       </c>
       <c r="AS78">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="AT78">
-        <v>2.6</v>
+        <v>3.28</v>
       </c>
       <c r="AU78">
         <v>7</v>
       </c>
       <c r="AV78">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AW78">
+        <v>0</v>
+      </c>
+      <c r="AX78">
+        <v>0</v>
+      </c>
+      <c r="AY78">
         <v>7</v>
       </c>
-      <c r="AX78">
+      <c r="AZ78">
         <v>3</v>
       </c>
-      <c r="AY78">
-        <v>14</v>
-      </c>
-      <c r="AZ78">
-        <v>9</v>
-      </c>
       <c r="BA78">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BB78">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BC78">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BD78">
-        <v>2.05</v>
+        <v>1.45</v>
       </c>
       <c r="BE78">
-        <v>6.5</v>
+        <v>8.5</v>
       </c>
       <c r="BF78">
-        <v>2.1</v>
+        <v>3.52</v>
       </c>
       <c r="BG78">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="BH78">
-        <v>3.22</v>
+        <v>4.1</v>
       </c>
       <c r="BI78">
-        <v>1.52</v>
+        <v>1.25</v>
       </c>
       <c r="BJ78">
-        <v>2.42</v>
+        <v>3.05</v>
       </c>
       <c r="BK78">
-        <v>2.15</v>
+        <v>1.6</v>
       </c>
       <c r="BL78">
-        <v>1.88</v>
+        <v>2.44</v>
       </c>
       <c r="BM78">
-        <v>2.38</v>
+        <v>1.83</v>
       </c>
       <c r="BN78">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="BO78">
-        <v>3.05</v>
+        <v>2.23</v>
       </c>
       <c r="BP78">
-        <v>1.33</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="79" spans="1:68">
@@ -17069,7 +17069,7 @@
         <v>78</v>
       </c>
       <c r="B79">
-        <v>7811554</v>
+        <v>7811555</v>
       </c>
       <c r="C79" t="s">
         <v>68</v>
@@ -17078,196 +17078,196 @@
         <v>69</v>
       </c>
       <c r="E79" s="2">
-        <v>45839.5</v>
+        <v>45840.5</v>
       </c>
       <c r="F79">
         <v>0</v>
       </c>
       <c r="G79" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H79" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="I79">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J79">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K79">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L79">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M79">
+        <v>0</v>
+      </c>
+      <c r="N79">
+        <v>0</v>
+      </c>
+      <c r="O79" t="s">
+        <v>84</v>
+      </c>
+      <c r="P79" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q79">
+        <v>1.68</v>
+      </c>
+      <c r="R79">
+        <v>2.9</v>
+      </c>
+      <c r="S79">
+        <v>7.5</v>
+      </c>
+      <c r="T79">
+        <v>1.15</v>
+      </c>
+      <c r="U79">
+        <v>4.33</v>
+      </c>
+      <c r="V79">
         <v>2</v>
-      </c>
-      <c r="N79">
-        <v>8</v>
-      </c>
-      <c r="O79" t="s">
-        <v>136</v>
-      </c>
-      <c r="P79" t="s">
-        <v>198</v>
-      </c>
-      <c r="Q79">
-        <v>2.17</v>
-      </c>
-      <c r="R79">
-        <v>2.45</v>
-      </c>
-      <c r="S79">
-        <v>4.35</v>
-      </c>
-      <c r="T79">
-        <v>1.25</v>
-      </c>
-      <c r="U79">
-        <v>3.5</v>
-      </c>
-      <c r="V79">
-        <v>2.31</v>
       </c>
       <c r="W79">
         <v>1.66</v>
       </c>
       <c r="X79">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="Y79">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z79">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="AA79">
-        <v>3.9</v>
+        <v>7.5</v>
       </c>
       <c r="AB79">
-        <v>5.11</v>
+        <v>13</v>
       </c>
       <c r="AC79">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AD79">
-        <v>14.3</v>
+        <v>26</v>
       </c>
       <c r="AE79">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="AF79">
-        <v>5</v>
+        <v>6.75</v>
       </c>
       <c r="AG79">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AH79">
-        <v>2.4</v>
+        <v>2.95</v>
       </c>
       <c r="AI79">
-        <v>1.62</v>
+        <v>1.89</v>
       </c>
       <c r="AJ79">
-        <v>2.25</v>
+        <v>1.87</v>
       </c>
       <c r="AK79">
-        <v>1.25</v>
+        <v>1.02</v>
       </c>
       <c r="AL79">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="AM79">
-        <v>2.25</v>
+        <v>4.75</v>
       </c>
       <c r="AN79">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AO79">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AP79">
-        <v>2.33</v>
+        <v>1.86</v>
       </c>
       <c r="AQ79">
         <v>1.13</v>
       </c>
       <c r="AR79">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AS79">
-        <v>1.35</v>
+        <v>1.08</v>
       </c>
       <c r="AT79">
-        <v>3.28</v>
+        <v>3.08</v>
       </c>
       <c r="AU79">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AV79">
         <v>3</v>
       </c>
       <c r="AW79">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AX79">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AY79">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="AZ79">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="BA79">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="BB79">
         <v>3</v>
       </c>
       <c r="BC79">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="BD79">
-        <v>1.45</v>
+        <v>1.08</v>
       </c>
       <c r="BE79">
-        <v>8.5</v>
+        <v>15.5</v>
       </c>
       <c r="BF79">
-        <v>3.52</v>
+        <v>5.6</v>
       </c>
       <c r="BG79">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="BH79">
-        <v>4.1</v>
+        <v>3.92</v>
       </c>
       <c r="BI79">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="BJ79">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="BK79">
-        <v>1.6</v>
+        <v>1.79</v>
       </c>
       <c r="BL79">
-        <v>2.44</v>
+        <v>2.15</v>
       </c>
       <c r="BM79">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="BN79">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="BO79">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="BP79">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="80" spans="1:68">
@@ -17275,7 +17275,7 @@
         <v>79</v>
       </c>
       <c r="B80">
-        <v>7811556</v>
+        <v>7811557</v>
       </c>
       <c r="C80" t="s">
         <v>68</v>
@@ -17290,10 +17290,10 @@
         <v>0</v>
       </c>
       <c r="G80" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="H80" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="I80">
         <v>1</v>
@@ -17308,10 +17308,10 @@
         <v>2</v>
       </c>
       <c r="M80">
+        <v>1</v>
+      </c>
+      <c r="N80">
         <v>3</v>
-      </c>
-      <c r="N80">
-        <v>5</v>
       </c>
       <c r="O80" t="s">
         <v>137</v>
@@ -17320,160 +17320,160 @@
         <v>199</v>
       </c>
       <c r="Q80">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
       <c r="R80">
-        <v>2.75</v>
+        <v>3.55</v>
       </c>
       <c r="S80">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="T80">
+        <v>1.17</v>
+      </c>
+      <c r="U80">
+        <v>5.2</v>
+      </c>
+      <c r="V80">
+        <v>1.66</v>
+      </c>
+      <c r="W80">
+        <v>2</v>
+      </c>
+      <c r="X80">
+        <v>3.05</v>
+      </c>
+      <c r="Y80">
+        <v>1.33</v>
+      </c>
+      <c r="Z80">
         <v>1.22</v>
       </c>
-      <c r="U80">
-        <v>3.7</v>
-      </c>
-      <c r="V80">
-        <v>2.1</v>
-      </c>
-      <c r="W80">
-        <v>1.63</v>
-      </c>
-      <c r="X80">
-        <v>4.1</v>
-      </c>
-      <c r="Y80">
-        <v>1.17</v>
-      </c>
-      <c r="Z80">
-        <v>1.26</v>
-      </c>
       <c r="AA80">
-        <v>5.9</v>
+        <v>9.4</v>
       </c>
       <c r="AB80">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AC80">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AD80">
-        <v>16.5</v>
+        <v>29</v>
       </c>
       <c r="AE80">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AF80">
-        <v>5.8</v>
+        <v>10</v>
       </c>
       <c r="AG80">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="AH80">
-        <v>2.62</v>
+        <v>3.9</v>
       </c>
       <c r="AI80">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="AJ80">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="AK80">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AL80">
         <v>1.12</v>
       </c>
       <c r="AM80">
-        <v>3.47</v>
+        <v>4.75</v>
       </c>
       <c r="AN80">
+        <v>2.17</v>
+      </c>
+      <c r="AO80">
+        <v>0.6</v>
+      </c>
+      <c r="AP80">
         <v>2.29</v>
       </c>
-      <c r="AO80">
-        <v>1</v>
-      </c>
-      <c r="AP80">
+      <c r="AQ80">
+        <v>0.5</v>
+      </c>
+      <c r="AR80">
+        <v>1.74</v>
+      </c>
+      <c r="AS80">
+        <v>1.3</v>
+      </c>
+      <c r="AT80">
+        <v>3.04</v>
+      </c>
+      <c r="AU80">
+        <v>6</v>
+      </c>
+      <c r="AV80">
+        <v>4</v>
+      </c>
+      <c r="AW80">
+        <v>19</v>
+      </c>
+      <c r="AX80">
+        <v>6</v>
+      </c>
+      <c r="AY80">
+        <v>25</v>
+      </c>
+      <c r="AZ80">
+        <v>10</v>
+      </c>
+      <c r="BA80">
+        <v>4</v>
+      </c>
+      <c r="BB80">
         <v>2</v>
       </c>
-      <c r="AQ80">
-        <v>1.25</v>
-      </c>
-      <c r="AR80">
-        <v>2.02</v>
-      </c>
-      <c r="AS80">
-        <v>1.29</v>
-      </c>
-      <c r="AT80">
-        <v>3.31</v>
-      </c>
-      <c r="AU80">
-        <v>8</v>
-      </c>
-      <c r="AV80">
-        <v>8</v>
-      </c>
-      <c r="AW80">
+      <c r="BC80">
         <v>6</v>
       </c>
-      <c r="AX80">
-        <v>4</v>
-      </c>
-      <c r="AY80">
-        <v>14</v>
-      </c>
-      <c r="AZ80">
-        <v>12</v>
-      </c>
-      <c r="BA80">
-        <v>6</v>
-      </c>
-      <c r="BB80">
-        <v>7</v>
-      </c>
-      <c r="BC80">
-        <v>13</v>
-      </c>
       <c r="BD80">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="BE80">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BF80">
-        <v>4.4</v>
+        <v>8.1</v>
       </c>
       <c r="BG80">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="BH80">
-        <v>4.35</v>
+        <v>3.8</v>
       </c>
       <c r="BI80">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="BJ80">
-        <v>2.9</v>
+        <v>2.55</v>
       </c>
       <c r="BK80">
-        <v>1.54</v>
+        <v>1.68</v>
       </c>
       <c r="BL80">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="BM80">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="BN80">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="BO80">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="BP80">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="81" spans="1:68">
@@ -17481,7 +17481,7 @@
         <v>80</v>
       </c>
       <c r="B81">
-        <v>7811557</v>
+        <v>7811558</v>
       </c>
       <c r="C81" t="s">
         <v>68</v>
@@ -17496,25 +17496,25 @@
         <v>0</v>
       </c>
       <c r="G81" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H81" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I81">
         <v>1</v>
       </c>
       <c r="J81">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K81">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L81">
+        <v>1</v>
+      </c>
+      <c r="M81">
         <v>2</v>
-      </c>
-      <c r="M81">
-        <v>1</v>
       </c>
       <c r="N81">
         <v>3</v>
@@ -17526,160 +17526,160 @@
         <v>200</v>
       </c>
       <c r="Q81">
-        <v>1.52</v>
+        <v>2.38</v>
       </c>
       <c r="R81">
-        <v>3.55</v>
+        <v>2.39</v>
       </c>
       <c r="S81">
-        <v>8.5</v>
+        <v>4</v>
       </c>
       <c r="T81">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="U81">
-        <v>5.2</v>
+        <v>3.3</v>
       </c>
       <c r="V81">
-        <v>1.66</v>
+        <v>2.29</v>
       </c>
       <c r="W81">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="X81">
-        <v>3.05</v>
+        <v>5</v>
       </c>
       <c r="Y81">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="Z81">
-        <v>1.22</v>
+        <v>1.92</v>
       </c>
       <c r="AA81">
-        <v>9.4</v>
+        <v>3.75</v>
       </c>
       <c r="AB81">
-        <v>14</v>
+        <v>3.5</v>
       </c>
       <c r="AC81">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AD81">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="AE81">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AF81">
-        <v>10</v>
+        <v>4.5</v>
       </c>
       <c r="AG81">
-        <v>1.18</v>
+        <v>1.6</v>
       </c>
       <c r="AH81">
-        <v>3.9</v>
+        <v>2.25</v>
       </c>
       <c r="AI81">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AJ81">
-        <v>2.05</v>
+        <v>2.43</v>
       </c>
       <c r="AK81">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="AL81">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="AM81">
-        <v>4.75</v>
+        <v>1.8</v>
       </c>
       <c r="AN81">
-        <v>2.17</v>
+        <v>1.6</v>
       </c>
       <c r="AO81">
         <v>0.6</v>
       </c>
       <c r="AP81">
-        <v>2.29</v>
+        <v>1.14</v>
       </c>
       <c r="AQ81">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AR81">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AS81">
+        <v>1.49</v>
+      </c>
+      <c r="AT81">
+        <v>3.22</v>
+      </c>
+      <c r="AU81">
+        <v>5</v>
+      </c>
+      <c r="AV81">
+        <v>6</v>
+      </c>
+      <c r="AW81">
+        <v>9</v>
+      </c>
+      <c r="AX81">
+        <v>12</v>
+      </c>
+      <c r="AY81">
+        <v>14</v>
+      </c>
+      <c r="AZ81">
+        <v>18</v>
+      </c>
+      <c r="BA81">
+        <v>8</v>
+      </c>
+      <c r="BB81">
+        <v>9</v>
+      </c>
+      <c r="BC81">
+        <v>17</v>
+      </c>
+      <c r="BD81">
+        <v>1.55</v>
+      </c>
+      <c r="BE81">
+        <v>8</v>
+      </c>
+      <c r="BF81">
+        <v>2.95</v>
+      </c>
+      <c r="BG81">
+        <v>1.12</v>
+      </c>
+      <c r="BH81">
+        <v>4.75</v>
+      </c>
+      <c r="BI81">
         <v>1.3</v>
       </c>
-      <c r="AT81">
-        <v>3.04</v>
-      </c>
-      <c r="AU81">
-        <v>6</v>
-      </c>
-      <c r="AV81">
-        <v>4</v>
-      </c>
-      <c r="AW81">
-        <v>19</v>
-      </c>
-      <c r="AX81">
-        <v>6</v>
-      </c>
-      <c r="AY81">
-        <v>25</v>
-      </c>
-      <c r="AZ81">
-        <v>10</v>
-      </c>
-      <c r="BA81">
-        <v>4</v>
-      </c>
-      <c r="BB81">
-        <v>2</v>
-      </c>
-      <c r="BC81">
-        <v>6</v>
-      </c>
-      <c r="BD81">
-        <v>1.13</v>
-      </c>
-      <c r="BE81">
-        <v>10</v>
-      </c>
-      <c r="BF81">
-        <v>8.1</v>
-      </c>
-      <c r="BG81">
-        <v>1.17</v>
-      </c>
-      <c r="BH81">
-        <v>3.8</v>
-      </c>
-      <c r="BI81">
-        <v>1.36</v>
-      </c>
       <c r="BJ81">
-        <v>2.55</v>
+        <v>3.15</v>
       </c>
       <c r="BK81">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="BL81">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="BM81">
         <v>1.91</v>
       </c>
       <c r="BN81">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="BO81">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="BP81">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="82" spans="1:68">
@@ -17687,7 +17687,7 @@
         <v>81</v>
       </c>
       <c r="B82">
-        <v>7811558</v>
+        <v>7811556</v>
       </c>
       <c r="C82" t="s">
         <v>68</v>
@@ -17702,28 +17702,28 @@
         <v>0</v>
       </c>
       <c r="G82" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H82" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="I82">
         <v>1</v>
       </c>
       <c r="J82">
+        <v>0</v>
+      </c>
+      <c r="K82">
+        <v>1</v>
+      </c>
+      <c r="L82">
         <v>2</v>
       </c>
-      <c r="K82">
+      <c r="M82">
         <v>3</v>
       </c>
-      <c r="L82">
-        <v>1</v>
-      </c>
-      <c r="M82">
-        <v>2</v>
-      </c>
       <c r="N82">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O82" t="s">
         <v>139</v>
@@ -17732,160 +17732,160 @@
         <v>201</v>
       </c>
       <c r="Q82">
-        <v>2.38</v>
+        <v>1.68</v>
       </c>
       <c r="R82">
-        <v>2.39</v>
+        <v>2.75</v>
       </c>
       <c r="S82">
+        <v>7</v>
+      </c>
+      <c r="T82">
+        <v>1.22</v>
+      </c>
+      <c r="U82">
+        <v>3.7</v>
+      </c>
+      <c r="V82">
+        <v>2.1</v>
+      </c>
+      <c r="W82">
+        <v>1.63</v>
+      </c>
+      <c r="X82">
+        <v>4.1</v>
+      </c>
+      <c r="Y82">
+        <v>1.17</v>
+      </c>
+      <c r="Z82">
+        <v>1.26</v>
+      </c>
+      <c r="AA82">
+        <v>5.9</v>
+      </c>
+      <c r="AB82">
+        <v>8</v>
+      </c>
+      <c r="AC82">
+        <v>1.01</v>
+      </c>
+      <c r="AD82">
+        <v>16.5</v>
+      </c>
+      <c r="AE82">
+        <v>1.13</v>
+      </c>
+      <c r="AF82">
+        <v>5.8</v>
+      </c>
+      <c r="AG82">
+        <v>1.4</v>
+      </c>
+      <c r="AH82">
+        <v>2.62</v>
+      </c>
+      <c r="AI82">
+        <v>1.81</v>
+      </c>
+      <c r="AJ82">
+        <v>1.99</v>
+      </c>
+      <c r="AK82">
+        <v>1.1</v>
+      </c>
+      <c r="AL82">
+        <v>1.12</v>
+      </c>
+      <c r="AM82">
+        <v>3.47</v>
+      </c>
+      <c r="AN82">
+        <v>2.17</v>
+      </c>
+      <c r="AO82">
+        <v>1</v>
+      </c>
+      <c r="AP82">
+        <v>1.86</v>
+      </c>
+      <c r="AQ82">
+        <v>1.25</v>
+      </c>
+      <c r="AR82">
+        <v>2.02</v>
+      </c>
+      <c r="AS82">
+        <v>1.29</v>
+      </c>
+      <c r="AT82">
+        <v>3.31</v>
+      </c>
+      <c r="AU82">
+        <v>8</v>
+      </c>
+      <c r="AV82">
+        <v>8</v>
+      </c>
+      <c r="AW82">
+        <v>6</v>
+      </c>
+      <c r="AX82">
         <v>4</v>
-      </c>
-      <c r="T82">
-        <v>1.29</v>
-      </c>
-      <c r="U82">
-        <v>3.3</v>
-      </c>
-      <c r="V82">
-        <v>2.29</v>
-      </c>
-      <c r="W82">
-        <v>1.6</v>
-      </c>
-      <c r="X82">
-        <v>5</v>
-      </c>
-      <c r="Y82">
-        <v>1.15</v>
-      </c>
-      <c r="Z82">
-        <v>1.92</v>
-      </c>
-      <c r="AA82">
-        <v>3.75</v>
-      </c>
-      <c r="AB82">
-        <v>3.5</v>
-      </c>
-      <c r="AC82">
-        <v>1.03</v>
-      </c>
-      <c r="AD82">
-        <v>10</v>
-      </c>
-      <c r="AE82">
-        <v>1.14</v>
-      </c>
-      <c r="AF82">
-        <v>4.5</v>
-      </c>
-      <c r="AG82">
-        <v>1.6</v>
-      </c>
-      <c r="AH82">
-        <v>2.25</v>
-      </c>
-      <c r="AI82">
-        <v>1.5</v>
-      </c>
-      <c r="AJ82">
-        <v>2.43</v>
-      </c>
-      <c r="AK82">
-        <v>1.25</v>
-      </c>
-      <c r="AL82">
-        <v>1.3</v>
-      </c>
-      <c r="AM82">
-        <v>1.8</v>
-      </c>
-      <c r="AN82">
-        <v>1.6</v>
-      </c>
-      <c r="AO82">
-        <v>0.6</v>
-      </c>
-      <c r="AP82">
-        <v>1.14</v>
-      </c>
-      <c r="AQ82">
-        <v>1</v>
-      </c>
-      <c r="AR82">
-        <v>1.73</v>
-      </c>
-      <c r="AS82">
-        <v>1.49</v>
-      </c>
-      <c r="AT82">
-        <v>3.22</v>
-      </c>
-      <c r="AU82">
-        <v>5</v>
-      </c>
-      <c r="AV82">
-        <v>6</v>
-      </c>
-      <c r="AW82">
-        <v>9</v>
-      </c>
-      <c r="AX82">
-        <v>12</v>
       </c>
       <c r="AY82">
         <v>14</v>
       </c>
       <c r="AZ82">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="BA82">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BB82">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BC82">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="BD82">
-        <v>1.55</v>
+        <v>1.21</v>
       </c>
       <c r="BE82">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="BF82">
-        <v>2.95</v>
+        <v>4.4</v>
       </c>
       <c r="BG82">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="BH82">
-        <v>4.75</v>
+        <v>4.35</v>
       </c>
       <c r="BI82">
         <v>1.3</v>
       </c>
       <c r="BJ82">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="BK82">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="BL82">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="BM82">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="BN82">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="BO82">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="BP82">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="83" spans="1:68">
@@ -17893,7 +17893,7 @@
         <v>82</v>
       </c>
       <c r="B83">
-        <v>7811555</v>
+        <v>7811559</v>
       </c>
       <c r="C83" t="s">
         <v>68</v>
@@ -17902,196 +17902,196 @@
         <v>69</v>
       </c>
       <c r="E83" s="2">
-        <v>45840.5</v>
+        <v>45842.5</v>
       </c>
       <c r="F83">
         <v>0</v>
       </c>
       <c r="G83" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="H83" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="I83">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J83">
         <v>0</v>
       </c>
       <c r="K83">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L83">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M83">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N83">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O83" t="s">
-        <v>84</v>
+        <v>140</v>
       </c>
       <c r="P83" t="s">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="Q83">
-        <v>1.68</v>
+        <v>3.6</v>
       </c>
       <c r="R83">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="S83">
-        <v>7.5</v>
+        <v>2.5</v>
       </c>
       <c r="T83">
-        <v>1.15</v>
+        <v>1.32</v>
       </c>
       <c r="U83">
-        <v>4.33</v>
+        <v>3.1</v>
       </c>
       <c r="V83">
+        <v>2.5</v>
+      </c>
+      <c r="W83">
+        <v>1.45</v>
+      </c>
+      <c r="X83">
+        <v>5.75</v>
+      </c>
+      <c r="Y83">
+        <v>1.1</v>
+      </c>
+      <c r="Z83">
+        <v>4.05</v>
+      </c>
+      <c r="AA83">
+        <v>3.7</v>
+      </c>
+      <c r="AB83">
+        <v>2.29</v>
+      </c>
+      <c r="AC83">
+        <v>1.05</v>
+      </c>
+      <c r="AD83">
+        <v>11</v>
+      </c>
+      <c r="AE83">
+        <v>1.2</v>
+      </c>
+      <c r="AF83">
+        <v>3.75</v>
+      </c>
+      <c r="AG83">
+        <v>1.75</v>
+      </c>
+      <c r="AH83">
+        <v>2.02</v>
+      </c>
+      <c r="AI83">
+        <v>1.6</v>
+      </c>
+      <c r="AJ83">
         <v>2</v>
       </c>
-      <c r="W83">
-        <v>1.66</v>
-      </c>
-      <c r="X83">
-        <v>4.4</v>
-      </c>
-      <c r="Y83">
-        <v>1.18</v>
-      </c>
-      <c r="Z83">
-        <v>1.2</v>
-      </c>
-      <c r="AA83">
-        <v>7.5</v>
-      </c>
-      <c r="AB83">
-        <v>13</v>
-      </c>
-      <c r="AC83">
-        <v>1.01</v>
-      </c>
-      <c r="AD83">
-        <v>26</v>
-      </c>
-      <c r="AE83">
-        <v>1.09</v>
-      </c>
-      <c r="AF83">
-        <v>6.75</v>
-      </c>
-      <c r="AG83">
+      <c r="AK83">
+        <v>1.3</v>
+      </c>
+      <c r="AL83">
+        <v>1.25</v>
+      </c>
+      <c r="AM83">
         <v>1.36</v>
       </c>
-      <c r="AH83">
-        <v>2.95</v>
-      </c>
-      <c r="AI83">
-        <v>1.89</v>
-      </c>
-      <c r="AJ83">
-        <v>1.87</v>
-      </c>
-      <c r="AK83">
-        <v>1.02</v>
-      </c>
-      <c r="AL83">
-        <v>1.1</v>
-      </c>
-      <c r="AM83">
-        <v>4.75</v>
-      </c>
       <c r="AN83">
-        <v>2</v>
+        <v>0.67</v>
       </c>
       <c r="AO83">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AP83">
-        <v>1.86</v>
+        <v>0.71</v>
       </c>
       <c r="AQ83">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AR83">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AS83">
-        <v>1.08</v>
+        <v>1.58</v>
       </c>
       <c r="AT83">
-        <v>3.08</v>
+        <v>2.98</v>
       </c>
       <c r="AU83">
         <v>3</v>
       </c>
       <c r="AV83">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AW83">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="AX83">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY83">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="AZ83">
+        <v>12</v>
+      </c>
+      <c r="BA83">
+        <v>2</v>
+      </c>
+      <c r="BB83">
+        <v>7</v>
+      </c>
+      <c r="BC83">
         <v>9</v>
       </c>
-      <c r="BA83">
-        <v>12</v>
-      </c>
-      <c r="BB83">
-        <v>3</v>
-      </c>
-      <c r="BC83">
-        <v>15</v>
-      </c>
       <c r="BD83">
-        <v>1.08</v>
+        <v>3.1</v>
       </c>
       <c r="BE83">
-        <v>15.5</v>
+        <v>8</v>
       </c>
       <c r="BF83">
-        <v>5.6</v>
+        <v>1.48</v>
       </c>
       <c r="BG83">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="BH83">
-        <v>3.92</v>
+        <v>3.72</v>
       </c>
       <c r="BI83">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="BJ83">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="BK83">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="BL83">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="BM83">
-        <v>1.85</v>
+        <v>2.17</v>
       </c>
       <c r="BN83">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="BO83">
-        <v>2.3</v>
+        <v>2.83</v>
       </c>
       <c r="BP83">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="84" spans="1:68">
@@ -18099,7 +18099,7 @@
         <v>83</v>
       </c>
       <c r="B84">
-        <v>7811559</v>
+        <v>7811560</v>
       </c>
       <c r="C84" t="s">
         <v>68</v>
@@ -18108,16 +18108,16 @@
         <v>69</v>
       </c>
       <c r="E84" s="2">
-        <v>45842.5</v>
+        <v>45843.45833333334</v>
       </c>
       <c r="F84">
         <v>0</v>
       </c>
       <c r="G84" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H84" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="I84">
         <v>1</v>
@@ -18129,175 +18129,175 @@
         <v>1</v>
       </c>
       <c r="L84">
+        <v>1</v>
+      </c>
+      <c r="M84">
+        <v>1</v>
+      </c>
+      <c r="N84">
         <v>2</v>
       </c>
-      <c r="M84">
-        <v>2</v>
-      </c>
-      <c r="N84">
+      <c r="O84" t="s">
+        <v>141</v>
+      </c>
+      <c r="P84" t="s">
+        <v>203</v>
+      </c>
+      <c r="Q84">
+        <v>3.27</v>
+      </c>
+      <c r="R84">
+        <v>2.4</v>
+      </c>
+      <c r="S84">
+        <v>2.7</v>
+      </c>
+      <c r="T84">
+        <v>1.2</v>
+      </c>
+      <c r="U84">
         <v>4</v>
       </c>
-      <c r="O84" t="s">
-        <v>140</v>
-      </c>
-      <c r="P84" t="s">
-        <v>202</v>
-      </c>
-      <c r="Q84">
-        <v>3.6</v>
-      </c>
-      <c r="R84">
-        <v>2.2</v>
-      </c>
-      <c r="S84">
-        <v>2.5</v>
-      </c>
-      <c r="T84">
-        <v>1.32</v>
-      </c>
-      <c r="U84">
+      <c r="V84">
+        <v>2.07</v>
+      </c>
+      <c r="W84">
+        <v>1.83</v>
+      </c>
+      <c r="X84">
+        <v>3.8</v>
+      </c>
+      <c r="Y84">
+        <v>1.22</v>
+      </c>
+      <c r="Z84">
+        <v>3.2</v>
+      </c>
+      <c r="AA84">
+        <v>3.4</v>
+      </c>
+      <c r="AB84">
+        <v>1.95</v>
+      </c>
+      <c r="AC84">
+        <v>1.01</v>
+      </c>
+      <c r="AD84">
+        <v>19</v>
+      </c>
+      <c r="AE84">
+        <v>1.11</v>
+      </c>
+      <c r="AF84">
+        <v>7</v>
+      </c>
+      <c r="AG84">
+        <v>1.45</v>
+      </c>
+      <c r="AH84">
+        <v>2.56</v>
+      </c>
+      <c r="AI84">
+        <v>1.35</v>
+      </c>
+      <c r="AJ84">
         <v>3.1</v>
       </c>
-      <c r="V84">
-        <v>2.5</v>
-      </c>
-      <c r="W84">
-        <v>1.45</v>
-      </c>
-      <c r="X84">
-        <v>5.75</v>
-      </c>
-      <c r="Y84">
-        <v>1.1</v>
-      </c>
-      <c r="Z84">
-        <v>4.05</v>
-      </c>
-      <c r="AA84">
-        <v>3.7</v>
-      </c>
-      <c r="AB84">
-        <v>2.29</v>
-      </c>
-      <c r="AC84">
-        <v>1.05</v>
-      </c>
-      <c r="AD84">
-        <v>11</v>
-      </c>
-      <c r="AE84">
-        <v>1.2</v>
-      </c>
-      <c r="AF84">
-        <v>3.75</v>
-      </c>
-      <c r="AG84">
-        <v>1.75</v>
-      </c>
-      <c r="AH84">
-        <v>2.02</v>
-      </c>
-      <c r="AI84">
-        <v>1.6</v>
-      </c>
-      <c r="AJ84">
-        <v>2</v>
-      </c>
       <c r="AK84">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AL84">
         <v>1.25</v>
       </c>
       <c r="AM84">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AN84">
-        <v>0.67</v>
+        <v>1.86</v>
       </c>
       <c r="AO84">
-        <v>1.33</v>
+        <v>1.71</v>
       </c>
       <c r="AP84">
-        <v>0.71</v>
+        <v>1.75</v>
       </c>
       <c r="AQ84">
-        <v>1.29</v>
+        <v>1.63</v>
       </c>
       <c r="AR84">
-        <v>1.4</v>
+        <v>1.81</v>
       </c>
       <c r="AS84">
-        <v>1.58</v>
+        <v>2.21</v>
       </c>
       <c r="AT84">
-        <v>2.98</v>
+        <v>4.02</v>
       </c>
       <c r="AU84">
         <v>3</v>
       </c>
       <c r="AV84">
+        <v>7</v>
+      </c>
+      <c r="AW84">
         <v>5</v>
       </c>
-      <c r="AW84">
-        <v>1</v>
-      </c>
       <c r="AX84">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AY84">
+        <v>8</v>
+      </c>
+      <c r="AZ84">
+        <v>16</v>
+      </c>
+      <c r="BA84">
         <v>4</v>
       </c>
-      <c r="AZ84">
-        <v>12</v>
-      </c>
-      <c r="BA84">
-        <v>2</v>
-      </c>
       <c r="BB84">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BC84">
+        <v>13</v>
+      </c>
+      <c r="BD84">
+        <v>2.4</v>
+      </c>
+      <c r="BE84">
         <v>9</v>
       </c>
-      <c r="BD84">
-        <v>3.1</v>
-      </c>
-      <c r="BE84">
-        <v>8</v>
-      </c>
       <c r="BF84">
-        <v>1.48</v>
+        <v>1.72</v>
       </c>
       <c r="BG84">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="BH84">
-        <v>3.72</v>
+        <v>4.1</v>
       </c>
       <c r="BI84">
+        <v>1.38</v>
+      </c>
+      <c r="BJ84">
+        <v>2.8</v>
+      </c>
+      <c r="BK84">
+        <v>1.74</v>
+      </c>
+      <c r="BL84">
+        <v>2.26</v>
+      </c>
+      <c r="BM84">
+        <v>1.97</v>
+      </c>
+      <c r="BN84">
+        <v>1.73</v>
+      </c>
+      <c r="BO84">
+        <v>2.4</v>
+      </c>
+      <c r="BP84">
         <v>1.42</v>
-      </c>
-      <c r="BJ84">
-        <v>2.65</v>
-      </c>
-      <c r="BK84">
-        <v>1.73</v>
-      </c>
-      <c r="BL84">
-        <v>2.05</v>
-      </c>
-      <c r="BM84">
-        <v>2.17</v>
-      </c>
-      <c r="BN84">
-        <v>1.58</v>
-      </c>
-      <c r="BO84">
-        <v>2.83</v>
-      </c>
-      <c r="BP84">
-        <v>1.33</v>
       </c>
     </row>
     <row r="85" spans="1:68">
@@ -18305,7 +18305,7 @@
         <v>84</v>
       </c>
       <c r="B85">
-        <v>7811560</v>
+        <v>7811561</v>
       </c>
       <c r="C85" t="s">
         <v>68</v>
@@ -18314,196 +18314,196 @@
         <v>69</v>
       </c>
       <c r="E85" s="2">
-        <v>45843.45833333334</v>
+        <v>45843.54166666666</v>
       </c>
       <c r="F85">
         <v>0</v>
       </c>
       <c r="G85" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H85" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="I85">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J85">
         <v>0</v>
       </c>
       <c r="K85">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L85">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M85">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N85">
         <v>2</v>
       </c>
       <c r="O85" t="s">
-        <v>141</v>
+        <v>84</v>
       </c>
       <c r="P85" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q85">
-        <v>3.27</v>
+        <v>3.9</v>
       </c>
       <c r="R85">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="S85">
-        <v>2.7</v>
+        <v>2.32</v>
       </c>
       <c r="T85">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="U85">
-        <v>4</v>
+        <v>3.42</v>
       </c>
       <c r="V85">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="W85">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="X85">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="Y85">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z85">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="AA85">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="AB85">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="AC85">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AD85">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="AE85">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AF85">
-        <v>7</v>
+        <v>4.95</v>
       </c>
       <c r="AG85">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="AH85">
-        <v>2.56</v>
+        <v>2.37</v>
       </c>
       <c r="AI85">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="AJ85">
-        <v>3.1</v>
+        <v>2.54</v>
       </c>
       <c r="AK85">
+        <v>1.29</v>
+      </c>
+      <c r="AL85">
+        <v>1.26</v>
+      </c>
+      <c r="AM85">
         <v>1.25</v>
       </c>
-      <c r="AL85">
-        <v>1.25</v>
-      </c>
-      <c r="AM85">
-        <v>1.44</v>
-      </c>
       <c r="AN85">
-        <v>1.86</v>
+        <v>1.33</v>
       </c>
       <c r="AO85">
-        <v>1.71</v>
+        <v>1.43</v>
       </c>
       <c r="AP85">
-        <v>1.75</v>
+        <v>1.14</v>
       </c>
       <c r="AQ85">
         <v>1.63</v>
       </c>
       <c r="AR85">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AS85">
-        <v>2.21</v>
+        <v>1.99</v>
       </c>
       <c r="AT85">
-        <v>4.02</v>
+        <v>3.72</v>
       </c>
       <c r="AU85">
+        <v>4</v>
+      </c>
+      <c r="AV85">
         <v>3</v>
       </c>
-      <c r="AV85">
+      <c r="AW85">
+        <v>9</v>
+      </c>
+      <c r="AX85">
+        <v>4</v>
+      </c>
+      <c r="AY85">
+        <v>13</v>
+      </c>
+      <c r="AZ85">
         <v>7</v>
       </c>
-      <c r="AW85">
-        <v>5</v>
-      </c>
-      <c r="AX85">
+      <c r="BA85">
         <v>9</v>
       </c>
-      <c r="AY85">
-        <v>8</v>
-      </c>
-      <c r="AZ85">
-        <v>16</v>
-      </c>
-      <c r="BA85">
-        <v>4</v>
-      </c>
       <c r="BB85">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="BC85">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BD85">
-        <v>2.4</v>
+        <v>2.69</v>
       </c>
       <c r="BE85">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BF85">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="BG85">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="BH85">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="BI85">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="BJ85">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="BK85">
         <v>1.74</v>
       </c>
       <c r="BL85">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="BM85">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="BN85">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="BO85">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="BP85">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="86" spans="1:68">
@@ -18511,7 +18511,7 @@
         <v>85</v>
       </c>
       <c r="B86">
-        <v>7811561</v>
+        <v>7811562</v>
       </c>
       <c r="C86" t="s">
         <v>68</v>
@@ -18520,196 +18520,196 @@
         <v>69</v>
       </c>
       <c r="E86" s="2">
-        <v>45843.54166666666</v>
+        <v>45844.41666666666</v>
       </c>
       <c r="F86">
         <v>0</v>
       </c>
       <c r="G86" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H86" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="I86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J86">
         <v>0</v>
       </c>
       <c r="K86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M86">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N86">
         <v>2</v>
       </c>
       <c r="O86" t="s">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="P86" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q86">
-        <v>3.9</v>
+        <v>2.53</v>
       </c>
       <c r="R86">
-        <v>2.34</v>
+        <v>2.1</v>
       </c>
       <c r="S86">
-        <v>2.32</v>
+        <v>4.8</v>
       </c>
       <c r="T86">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="U86">
-        <v>3.42</v>
+        <v>2.75</v>
       </c>
       <c r="V86">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="W86">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="X86">
-        <v>4.8</v>
+        <v>6.5</v>
       </c>
       <c r="Y86">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="Z86">
-        <v>3.75</v>
+        <v>1.8</v>
       </c>
       <c r="AA86">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="AB86">
-        <v>1.81</v>
+        <v>4.2</v>
       </c>
       <c r="AC86">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AD86">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="AE86">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AF86">
-        <v>4.95</v>
+        <v>3.5</v>
       </c>
       <c r="AG86">
-        <v>1.51</v>
+        <v>1.95</v>
       </c>
       <c r="AH86">
-        <v>2.37</v>
+        <v>1.8</v>
       </c>
       <c r="AI86">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="AJ86">
-        <v>2.54</v>
+        <v>1.91</v>
       </c>
       <c r="AK86">
         <v>1.29</v>
       </c>
       <c r="AL86">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AM86">
-        <v>1.25</v>
+        <v>1.91</v>
       </c>
       <c r="AN86">
+        <v>0.8</v>
+      </c>
+      <c r="AO86">
+        <v>1.14</v>
+      </c>
+      <c r="AP86">
+        <v>0.83</v>
+      </c>
+      <c r="AQ86">
+        <v>1.13</v>
+      </c>
+      <c r="AR86">
+        <v>1.14</v>
+      </c>
+      <c r="AS86">
+        <v>1.06</v>
+      </c>
+      <c r="AT86">
+        <v>2.2</v>
+      </c>
+      <c r="AU86">
+        <v>7</v>
+      </c>
+      <c r="AV86">
+        <v>9</v>
+      </c>
+      <c r="AW86">
+        <v>10</v>
+      </c>
+      <c r="AX86">
+        <v>8</v>
+      </c>
+      <c r="AY86">
+        <v>17</v>
+      </c>
+      <c r="AZ86">
+        <v>17</v>
+      </c>
+      <c r="BA86">
+        <v>7</v>
+      </c>
+      <c r="BB86">
+        <v>4</v>
+      </c>
+      <c r="BC86">
+        <v>11</v>
+      </c>
+      <c r="BD86">
+        <v>1.62</v>
+      </c>
+      <c r="BE86">
+        <v>8.1</v>
+      </c>
+      <c r="BF86">
+        <v>2.86</v>
+      </c>
+      <c r="BG86">
+        <v>1.27</v>
+      </c>
+      <c r="BH86">
+        <v>3.8</v>
+      </c>
+      <c r="BI86">
+        <v>1.39</v>
+      </c>
+      <c r="BJ86">
+        <v>2.67</v>
+      </c>
+      <c r="BK86">
+        <v>1.73</v>
+      </c>
+      <c r="BL86">
+        <v>2</v>
+      </c>
+      <c r="BM86">
+        <v>2.1</v>
+      </c>
+      <c r="BN86">
+        <v>1.65</v>
+      </c>
+      <c r="BO86">
+        <v>3</v>
+      </c>
+      <c r="BP86">
         <v>1.33</v>
-      </c>
-      <c r="AO86">
-        <v>1.43</v>
-      </c>
-      <c r="AP86">
-        <v>1.14</v>
-      </c>
-      <c r="AQ86">
-        <v>1.63</v>
-      </c>
-      <c r="AR86">
-        <v>1.73</v>
-      </c>
-      <c r="AS86">
-        <v>1.99</v>
-      </c>
-      <c r="AT86">
-        <v>3.72</v>
-      </c>
-      <c r="AU86">
-        <v>4</v>
-      </c>
-      <c r="AV86">
-        <v>3</v>
-      </c>
-      <c r="AW86">
-        <v>9</v>
-      </c>
-      <c r="AX86">
-        <v>4</v>
-      </c>
-      <c r="AY86">
-        <v>13</v>
-      </c>
-      <c r="AZ86">
-        <v>7</v>
-      </c>
-      <c r="BA86">
-        <v>9</v>
-      </c>
-      <c r="BB86">
-        <v>3</v>
-      </c>
-      <c r="BC86">
-        <v>12</v>
-      </c>
-      <c r="BD86">
-        <v>2.69</v>
-      </c>
-      <c r="BE86">
-        <v>8.6</v>
-      </c>
-      <c r="BF86">
-        <v>1.62</v>
-      </c>
-      <c r="BG86">
-        <v>1.18</v>
-      </c>
-      <c r="BH86">
-        <v>4.05</v>
-      </c>
-      <c r="BI86">
-        <v>1.32</v>
-      </c>
-      <c r="BJ86">
-        <v>3.2</v>
-      </c>
-      <c r="BK86">
-        <v>1.74</v>
-      </c>
-      <c r="BL86">
-        <v>2.1</v>
-      </c>
-      <c r="BM86">
-        <v>1.96</v>
-      </c>
-      <c r="BN86">
-        <v>1.79</v>
-      </c>
-      <c r="BO86">
-        <v>2.43</v>
-      </c>
-      <c r="BP86">
-        <v>1.49</v>
       </c>
     </row>
     <row r="87" spans="1:68">
@@ -18717,7 +18717,7 @@
         <v>86</v>
       </c>
       <c r="B87">
-        <v>7811562</v>
+        <v>7811563</v>
       </c>
       <c r="C87" t="s">
         <v>68</v>
@@ -18726,196 +18726,196 @@
         <v>69</v>
       </c>
       <c r="E87" s="2">
-        <v>45844.41666666666</v>
+        <v>45844.52083333334</v>
       </c>
       <c r="F87">
         <v>0</v>
       </c>
       <c r="G87" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H87" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I87">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K87">
         <v>1</v>
       </c>
       <c r="L87">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M87">
         <v>1</v>
       </c>
       <c r="N87">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O87" t="s">
-        <v>142</v>
+        <v>84</v>
       </c>
       <c r="P87" t="s">
-        <v>205</v>
+        <v>91</v>
       </c>
       <c r="Q87">
-        <v>2.53</v>
+        <v>3.95</v>
       </c>
       <c r="R87">
-        <v>2.1</v>
+        <v>2.37</v>
       </c>
       <c r="S87">
-        <v>4.8</v>
+        <v>2.35</v>
       </c>
       <c r="T87">
-        <v>1.37</v>
+        <v>1.2</v>
       </c>
       <c r="U87">
-        <v>2.75</v>
+        <v>3.72</v>
       </c>
       <c r="V87">
-        <v>2.75</v>
+        <v>2.26</v>
       </c>
       <c r="W87">
-        <v>1.36</v>
+        <v>1.65</v>
       </c>
       <c r="X87">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="Y87">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Z87">
+        <v>4.09</v>
+      </c>
+      <c r="AA87">
+        <v>4</v>
+      </c>
+      <c r="AB87">
         <v>1.8</v>
       </c>
-      <c r="AA87">
-        <v>3.7</v>
-      </c>
-      <c r="AB87">
-        <v>4.2</v>
-      </c>
       <c r="AC87">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AD87">
-        <v>9.5</v>
+        <v>15</v>
       </c>
       <c r="AE87">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="AF87">
-        <v>3.5</v>
+        <v>5.43</v>
       </c>
       <c r="AG87">
-        <v>1.95</v>
+        <v>1.45</v>
       </c>
       <c r="AH87">
-        <v>1.8</v>
+        <v>2.45</v>
       </c>
       <c r="AI87">
-        <v>1.83</v>
+        <v>1.44</v>
       </c>
       <c r="AJ87">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="AK87">
+        <v>1.25</v>
+      </c>
+      <c r="AL87">
+        <v>1.23</v>
+      </c>
+      <c r="AM87">
+        <v>1.25</v>
+      </c>
+      <c r="AN87">
         <v>1.29</v>
       </c>
-      <c r="AL87">
-        <v>1.3</v>
-      </c>
-      <c r="AM87">
-        <v>1.91</v>
-      </c>
-      <c r="AN87">
-        <v>0.8</v>
-      </c>
       <c r="AO87">
-        <v>1</v>
+        <v>2.33</v>
       </c>
       <c r="AP87">
-        <v>0.83</v>
+        <v>1.13</v>
       </c>
       <c r="AQ87">
-        <v>1</v>
+        <v>2.43</v>
       </c>
       <c r="AR87">
-        <v>1.14</v>
+        <v>1.61</v>
       </c>
       <c r="AS87">
-        <v>1.06</v>
+        <v>2.01</v>
       </c>
       <c r="AT87">
-        <v>2.2</v>
+        <v>3.62</v>
       </c>
       <c r="AU87">
+        <v>5</v>
+      </c>
+      <c r="AV87">
+        <v>8</v>
+      </c>
+      <c r="AW87">
         <v>7</v>
       </c>
-      <c r="AV87">
+      <c r="AX87">
+        <v>6</v>
+      </c>
+      <c r="AY87">
+        <v>12</v>
+      </c>
+      <c r="AZ87">
+        <v>14</v>
+      </c>
+      <c r="BA87">
+        <v>8</v>
+      </c>
+      <c r="BB87">
+        <v>6</v>
+      </c>
+      <c r="BC87">
+        <v>14</v>
+      </c>
+      <c r="BD87">
+        <v>3.08</v>
+      </c>
+      <c r="BE87">
         <v>9</v>
       </c>
-      <c r="AW87">
-        <v>10</v>
-      </c>
-      <c r="AX87">
-        <v>8</v>
-      </c>
-      <c r="AY87">
-        <v>17</v>
-      </c>
-      <c r="AZ87">
-        <v>17</v>
-      </c>
-      <c r="BA87">
-        <v>7</v>
-      </c>
-      <c r="BB87">
-        <v>4</v>
-      </c>
-      <c r="BC87">
-        <v>11</v>
-      </c>
-      <c r="BD87">
-        <v>1.62</v>
-      </c>
-      <c r="BE87">
-        <v>8.1</v>
-      </c>
       <c r="BF87">
-        <v>2.86</v>
+        <v>1.53</v>
       </c>
       <c r="BG87">
-        <v>1.27</v>
+        <v>1.13</v>
       </c>
       <c r="BH87">
-        <v>3.8</v>
+        <v>4.9</v>
       </c>
       <c r="BI87">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="BJ87">
-        <v>2.67</v>
+        <v>3.45</v>
       </c>
       <c r="BK87">
-        <v>1.73</v>
+        <v>1.56</v>
       </c>
       <c r="BL87">
-        <v>2</v>
+        <v>2.55</v>
       </c>
       <c r="BM87">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="BN87">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="BO87">
-        <v>3</v>
+        <v>2.16</v>
       </c>
       <c r="BP87">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="88" spans="1:68">
@@ -18923,7 +18923,7 @@
         <v>87</v>
       </c>
       <c r="B88">
-        <v>7811563</v>
+        <v>7811576</v>
       </c>
       <c r="C88" t="s">
         <v>68</v>
@@ -18932,401 +18932,195 @@
         <v>69</v>
       </c>
       <c r="E88" s="2">
-        <v>45844.52083333334</v>
+        <v>45845.5</v>
       </c>
       <c r="F88">
         <v>0</v>
       </c>
       <c r="G88" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H88" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="I88">
         <v>0</v>
       </c>
       <c r="J88">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K88">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L88">
         <v>0</v>
       </c>
       <c r="M88">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N88">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O88" t="s">
         <v>84</v>
       </c>
       <c r="P88" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="Q88">
-        <v>3.95</v>
+        <v>3.43</v>
       </c>
       <c r="R88">
-        <v>2.37</v>
+        <v>2.42</v>
       </c>
       <c r="S88">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="T88">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="U88">
-        <v>3.72</v>
+        <v>3.65</v>
       </c>
       <c r="V88">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="W88">
         <v>1.65</v>
       </c>
       <c r="X88">
+        <v>4.4</v>
+      </c>
+      <c r="Y88">
+        <v>1.16</v>
+      </c>
+      <c r="Z88">
+        <v>3.09</v>
+      </c>
+      <c r="AA88">
+        <v>3.39</v>
+      </c>
+      <c r="AB88">
+        <v>2</v>
+      </c>
+      <c r="AC88">
+        <v>1.01</v>
+      </c>
+      <c r="AD88">
+        <v>10</v>
+      </c>
+      <c r="AE88">
+        <v>1.14</v>
+      </c>
+      <c r="AF88">
+        <v>5.4</v>
+      </c>
+      <c r="AG88">
+        <v>1.65</v>
+      </c>
+      <c r="AH88">
+        <v>2</v>
+      </c>
+      <c r="AI88">
+        <v>1.4</v>
+      </c>
+      <c r="AJ88">
+        <v>2.62</v>
+      </c>
+      <c r="AK88">
+        <v>1.88</v>
+      </c>
+      <c r="AL88">
+        <v>1.28</v>
+      </c>
+      <c r="AM88">
+        <v>1.3</v>
+      </c>
+      <c r="AN88">
+        <v>0.86</v>
+      </c>
+      <c r="AO88">
+        <v>1.14</v>
+      </c>
+      <c r="AP88">
+        <v>0.88</v>
+      </c>
+      <c r="AQ88">
+        <v>1.13</v>
+      </c>
+      <c r="AR88">
+        <v>1.62</v>
+      </c>
+      <c r="AS88">
+        <v>1.35</v>
+      </c>
+      <c r="AT88">
+        <v>2.97</v>
+      </c>
+      <c r="AU88">
+        <v>3</v>
+      </c>
+      <c r="AV88">
         <v>5</v>
       </c>
-      <c r="Y88">
-        <v>1.1</v>
-      </c>
-      <c r="Z88">
-        <v>4.09</v>
-      </c>
-      <c r="AA88">
-        <v>4</v>
-      </c>
-      <c r="AB88">
-        <v>1.8</v>
-      </c>
-      <c r="AC88">
-        <v>1.03</v>
-      </c>
-      <c r="AD88">
-        <v>15</v>
-      </c>
-      <c r="AE88">
-        <v>1.11</v>
-      </c>
-      <c r="AF88">
-        <v>5.43</v>
-      </c>
-      <c r="AG88">
-        <v>1.45</v>
-      </c>
-      <c r="AH88">
-        <v>2.45</v>
-      </c>
-      <c r="AI88">
-        <v>1.44</v>
-      </c>
-      <c r="AJ88">
-        <v>2.5</v>
-      </c>
-      <c r="AK88">
-        <v>1.25</v>
-      </c>
-      <c r="AL88">
-        <v>1.23</v>
-      </c>
-      <c r="AM88">
-        <v>1.25</v>
-      </c>
-      <c r="AN88">
-        <v>1.29</v>
-      </c>
-      <c r="AO88">
-        <v>2.33</v>
-      </c>
-      <c r="AP88">
-        <v>1.13</v>
-      </c>
-      <c r="AQ88">
-        <v>2.43</v>
-      </c>
-      <c r="AR88">
-        <v>1.61</v>
-      </c>
-      <c r="AS88">
-        <v>2.01</v>
-      </c>
-      <c r="AT88">
-        <v>3.62</v>
-      </c>
-      <c r="AU88">
-        <v>5</v>
-      </c>
-      <c r="AV88">
+      <c r="AW88">
+        <v>13</v>
+      </c>
+      <c r="AX88">
+        <v>3</v>
+      </c>
+      <c r="AY88">
+        <v>16</v>
+      </c>
+      <c r="AZ88">
         <v>8</v>
       </c>
-      <c r="AW88">
-        <v>7</v>
-      </c>
-      <c r="AX88">
-        <v>6</v>
-      </c>
-      <c r="AY88">
-        <v>12</v>
-      </c>
-      <c r="AZ88">
-        <v>14</v>
-      </c>
       <c r="BA88">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BB88">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BC88">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BD88">
-        <v>3.08</v>
+        <v>2.46</v>
       </c>
       <c r="BE88">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF88">
-        <v>1.53</v>
+        <v>1.72</v>
       </c>
       <c r="BG88">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="BH88">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="BI88">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="BJ88">
-        <v>3.45</v>
+        <v>3.05</v>
       </c>
       <c r="BK88">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="BL88">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="BM88">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="BN88">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="BO88">
-        <v>2.16</v>
+        <v>2.36</v>
       </c>
       <c r="BP88">
-        <v>1.55</v>
-      </c>
-    </row>
-    <row r="89" spans="1:68">
-      <c r="A89" s="1">
-        <v>88</v>
-      </c>
-      <c r="B89">
-        <v>7811576</v>
-      </c>
-      <c r="C89" t="s">
-        <v>68</v>
-      </c>
-      <c r="D89" t="s">
-        <v>69</v>
-      </c>
-      <c r="E89" s="2">
-        <v>45845.5</v>
-      </c>
-      <c r="F89">
-        <v>0</v>
-      </c>
-      <c r="G89" t="s">
-        <v>73</v>
-      </c>
-      <c r="H89" t="s">
-        <v>81</v>
-      </c>
-      <c r="I89">
-        <v>0</v>
-      </c>
-      <c r="J89">
-        <v>0</v>
-      </c>
-      <c r="K89">
-        <v>0</v>
-      </c>
-      <c r="L89">
-        <v>0</v>
-      </c>
-      <c r="M89">
-        <v>0</v>
-      </c>
-      <c r="N89">
-        <v>0</v>
-      </c>
-      <c r="O89" t="s">
-        <v>84</v>
-      </c>
-      <c r="P89" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q89">
-        <v>3.43</v>
-      </c>
-      <c r="R89">
-        <v>2.42</v>
-      </c>
-      <c r="S89">
-        <v>2.3</v>
-      </c>
-      <c r="T89">
-        <v>1.22</v>
-      </c>
-      <c r="U89">
-        <v>3.65</v>
-      </c>
-      <c r="V89">
-        <v>2.1</v>
-      </c>
-      <c r="W89">
-        <v>1.65</v>
-      </c>
-      <c r="X89">
-        <v>4.4</v>
-      </c>
-      <c r="Y89">
-        <v>1.16</v>
-      </c>
-      <c r="Z89">
-        <v>3.09</v>
-      </c>
-      <c r="AA89">
-        <v>3.39</v>
-      </c>
-      <c r="AB89">
-        <v>2</v>
-      </c>
-      <c r="AC89">
-        <v>1.01</v>
-      </c>
-      <c r="AD89">
-        <v>10</v>
-      </c>
-      <c r="AE89">
-        <v>1.14</v>
-      </c>
-      <c r="AF89">
-        <v>5.4</v>
-      </c>
-      <c r="AG89">
-        <v>1.65</v>
-      </c>
-      <c r="AH89">
-        <v>2</v>
-      </c>
-      <c r="AI89">
-        <v>1.4</v>
-      </c>
-      <c r="AJ89">
-        <v>2.62</v>
-      </c>
-      <c r="AK89">
-        <v>1.88</v>
-      </c>
-      <c r="AL89">
-        <v>1.28</v>
-      </c>
-      <c r="AM89">
-        <v>1.3</v>
-      </c>
-      <c r="AN89">
-        <v>0.86</v>
-      </c>
-      <c r="AO89">
-        <v>1.14</v>
-      </c>
-      <c r="AP89">
-        <v>0.88</v>
-      </c>
-      <c r="AQ89">
-        <v>1.13</v>
-      </c>
-      <c r="AR89">
-        <v>1.62</v>
-      </c>
-      <c r="AS89">
-        <v>1.35</v>
-      </c>
-      <c r="AT89">
-        <v>2.97</v>
-      </c>
-      <c r="AU89">
-        <v>3</v>
-      </c>
-      <c r="AV89">
-        <v>5</v>
-      </c>
-      <c r="AW89">
-        <v>13</v>
-      </c>
-      <c r="AX89">
-        <v>3</v>
-      </c>
-      <c r="AY89">
-        <v>16</v>
-      </c>
-      <c r="AZ89">
-        <v>8</v>
-      </c>
-      <c r="BA89">
-        <v>9</v>
-      </c>
-      <c r="BB89">
-        <v>2</v>
-      </c>
-      <c r="BC89">
-        <v>11</v>
-      </c>
-      <c r="BD89">
-        <v>2.46</v>
-      </c>
-      <c r="BE89">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF89">
-        <v>1.72</v>
-      </c>
-      <c r="BG89">
-        <v>1.17</v>
-      </c>
-      <c r="BH89">
-        <v>4.2</v>
-      </c>
-      <c r="BI89">
-        <v>1.33</v>
-      </c>
-      <c r="BJ89">
-        <v>3.05</v>
-      </c>
-      <c r="BK89">
-        <v>1.6</v>
-      </c>
-      <c r="BL89">
-        <v>2.3</v>
-      </c>
-      <c r="BM89">
-        <v>1.91</v>
-      </c>
-      <c r="BN89">
-        <v>1.83</v>
-      </c>
-      <c r="BO89">
-        <v>2.36</v>
-      </c>
-      <c r="BP89">
         <v>1.5</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="207">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -443,6 +443,9 @@
   </si>
   <si>
     <t>['35']</t>
+  </si>
+  <si>
+    <t>['40', '21', '45+1']</t>
   </si>
   <si>
     <t>['4', '14']</t>
@@ -993,7 +996,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP88"/>
+  <dimension ref="A1:BP89"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1249,7 +1252,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q2">
         <v>3.2</v>
@@ -1455,7 +1458,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q3">
         <v>3.25</v>
@@ -1533,7 +1536,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ3">
         <v>1.29</v>
@@ -1661,7 +1664,7 @@
         <v>84</v>
       </c>
       <c r="P4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q4">
         <v>3.1</v>
@@ -1742,7 +1745,7 @@
         <v>1</v>
       </c>
       <c r="AQ4">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2073,7 +2076,7 @@
         <v>85</v>
       </c>
       <c r="P6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q6">
         <v>2.3</v>
@@ -2279,7 +2282,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q7">
         <v>3.4</v>
@@ -2485,7 +2488,7 @@
         <v>87</v>
       </c>
       <c r="P8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q8">
         <v>4.1</v>
@@ -2897,7 +2900,7 @@
         <v>89</v>
       </c>
       <c r="P10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q10">
         <v>1.7</v>
@@ -2978,7 +2981,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ10">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AR10">
         <v>1.48</v>
@@ -3103,7 +3106,7 @@
         <v>84</v>
       </c>
       <c r="P11" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q11">
         <v>2.25</v>
@@ -3387,7 +3390,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ12">
         <v>1.13</v>
@@ -3721,7 +3724,7 @@
         <v>84</v>
       </c>
       <c r="P14" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q14">
         <v>3.1</v>
@@ -3927,7 +3930,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q15">
         <v>3.2</v>
@@ -4133,7 +4136,7 @@
         <v>93</v>
       </c>
       <c r="P16" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q16">
         <v>4.79</v>
@@ -4339,7 +4342,7 @@
         <v>84</v>
       </c>
       <c r="P17" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q17">
         <v>4.17</v>
@@ -4626,7 +4629,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ18">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AR18">
         <v>1.27</v>
@@ -4751,7 +4754,7 @@
         <v>84</v>
       </c>
       <c r="P19" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q19">
         <v>1.72</v>
@@ -5163,7 +5166,7 @@
         <v>96</v>
       </c>
       <c r="P21" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q21">
         <v>2.2</v>
@@ -5369,7 +5372,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q22">
         <v>4.75</v>
@@ -5575,7 +5578,7 @@
         <v>98</v>
       </c>
       <c r="P23" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q23">
         <v>2.3</v>
@@ -5781,7 +5784,7 @@
         <v>99</v>
       </c>
       <c r="P24" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q24">
         <v>2.25</v>
@@ -5987,7 +5990,7 @@
         <v>100</v>
       </c>
       <c r="P25" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q25">
         <v>3.75</v>
@@ -6193,7 +6196,7 @@
         <v>101</v>
       </c>
       <c r="P26" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q26">
         <v>6.5</v>
@@ -6399,7 +6402,7 @@
         <v>102</v>
       </c>
       <c r="P27" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q27">
         <v>1.85</v>
@@ -6605,7 +6608,7 @@
         <v>84</v>
       </c>
       <c r="P28" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q28">
         <v>2.5</v>
@@ -6686,7 +6689,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ28">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AR28">
         <v>1.83</v>
@@ -6811,7 +6814,7 @@
         <v>103</v>
       </c>
       <c r="P29" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q29">
         <v>2.7</v>
@@ -7635,7 +7638,7 @@
         <v>106</v>
       </c>
       <c r="P33" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q33">
         <v>2.93</v>
@@ -7713,7 +7716,7 @@
         <v>0</v>
       </c>
       <c r="AP33">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ33">
         <v>1.63</v>
@@ -7841,7 +7844,7 @@
         <v>107</v>
       </c>
       <c r="P34" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q34">
         <v>2.26</v>
@@ -8253,7 +8256,7 @@
         <v>109</v>
       </c>
       <c r="P36" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q36">
         <v>6.4</v>
@@ -8459,7 +8462,7 @@
         <v>110</v>
       </c>
       <c r="P37" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q37">
         <v>3.84</v>
@@ -8665,7 +8668,7 @@
         <v>84</v>
       </c>
       <c r="P38" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q38">
         <v>5.25</v>
@@ -8871,7 +8874,7 @@
         <v>111</v>
       </c>
       <c r="P39" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -9077,7 +9080,7 @@
         <v>112</v>
       </c>
       <c r="P40" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q40">
         <v>2.85</v>
@@ -9283,7 +9286,7 @@
         <v>113</v>
       </c>
       <c r="P41" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q41">
         <v>4.02</v>
@@ -9489,7 +9492,7 @@
         <v>84</v>
       </c>
       <c r="P42" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q42">
         <v>2.1</v>
@@ -9695,7 +9698,7 @@
         <v>114</v>
       </c>
       <c r="P43" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q43">
         <v>2.75</v>
@@ -9773,7 +9776,7 @@
         <v>1</v>
       </c>
       <c r="AP43">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ43">
         <v>1.63</v>
@@ -9901,7 +9904,7 @@
         <v>115</v>
       </c>
       <c r="P44" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q44">
         <v>1.68</v>
@@ -10188,7 +10191,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ45">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AR45">
         <v>1.67</v>
@@ -10313,7 +10316,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q46">
         <v>1.91</v>
@@ -10931,7 +10934,7 @@
         <v>118</v>
       </c>
       <c r="P49" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q49">
         <v>3.45</v>
@@ -11343,7 +11346,7 @@
         <v>84</v>
       </c>
       <c r="P51" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q51">
         <v>6.5</v>
@@ -11549,7 +11552,7 @@
         <v>84</v>
       </c>
       <c r="P52" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q52">
         <v>2.18</v>
@@ -11755,7 +11758,7 @@
         <v>84</v>
       </c>
       <c r="P53" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q53">
         <v>3.85</v>
@@ -11961,7 +11964,7 @@
         <v>119</v>
       </c>
       <c r="P54" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q54">
         <v>2.66</v>
@@ -12167,7 +12170,7 @@
         <v>120</v>
       </c>
       <c r="P55" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q55">
         <v>3</v>
@@ -12373,7 +12376,7 @@
         <v>121</v>
       </c>
       <c r="P56" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q56">
         <v>3.35</v>
@@ -12785,7 +12788,7 @@
         <v>84</v>
       </c>
       <c r="P58" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q58">
         <v>3.3</v>
@@ -12991,7 +12994,7 @@
         <v>84</v>
       </c>
       <c r="P59" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q59">
         <v>5.5</v>
@@ -13197,7 +13200,7 @@
         <v>122</v>
       </c>
       <c r="P60" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q60">
         <v>2.11</v>
@@ -13275,7 +13278,7 @@
         <v>0.67</v>
       </c>
       <c r="AP60">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ60">
         <v>1</v>
@@ -13403,7 +13406,7 @@
         <v>84</v>
       </c>
       <c r="P61" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q61">
         <v>4.5</v>
@@ -13815,7 +13818,7 @@
         <v>84</v>
       </c>
       <c r="P63" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q63">
         <v>2.87</v>
@@ -14021,7 +14024,7 @@
         <v>124</v>
       </c>
       <c r="P64" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q64">
         <v>1.85</v>
@@ -14102,7 +14105,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ64">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AR64">
         <v>1.77</v>
@@ -14227,7 +14230,7 @@
         <v>125</v>
       </c>
       <c r="P65" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q65">
         <v>4.28</v>
@@ -14433,7 +14436,7 @@
         <v>126</v>
       </c>
       <c r="P66" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q66">
         <v>2.19</v>
@@ -14845,7 +14848,7 @@
         <v>128</v>
       </c>
       <c r="P68" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q68">
         <v>3.3</v>
@@ -15051,7 +15054,7 @@
         <v>129</v>
       </c>
       <c r="P69" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q69">
         <v>2.03</v>
@@ -15541,7 +15544,7 @@
         <v>0.75</v>
       </c>
       <c r="AP71">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ71">
         <v>0.5</v>
@@ -15669,7 +15672,7 @@
         <v>131</v>
       </c>
       <c r="P72" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q72">
         <v>4.6</v>
@@ -16287,7 +16290,7 @@
         <v>84</v>
       </c>
       <c r="P75" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q75">
         <v>4</v>
@@ -16493,7 +16496,7 @@
         <v>134</v>
       </c>
       <c r="P76" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q76">
         <v>3.28</v>
@@ -16574,7 +16577,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ76">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AR76">
         <v>1.66</v>
@@ -16699,7 +16702,7 @@
         <v>135</v>
       </c>
       <c r="P77" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q77">
         <v>3.6</v>
@@ -16905,7 +16908,7 @@
         <v>136</v>
       </c>
       <c r="P78" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q78">
         <v>2.17</v>
@@ -17189,7 +17192,7 @@
         <v>1.17</v>
       </c>
       <c r="AP79">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ79">
         <v>1.13</v>
@@ -17317,7 +17320,7 @@
         <v>137</v>
       </c>
       <c r="P80" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q80">
         <v>1.52</v>
@@ -17523,7 +17526,7 @@
         <v>138</v>
       </c>
       <c r="P81" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q81">
         <v>2.38</v>
@@ -17729,7 +17732,7 @@
         <v>139</v>
       </c>
       <c r="P82" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q82">
         <v>1.68</v>
@@ -17810,7 +17813,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ82">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AR82">
         <v>2.02</v>
@@ -17935,7 +17938,7 @@
         <v>140</v>
       </c>
       <c r="P83" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q83">
         <v>3.6</v>
@@ -18141,7 +18144,7 @@
         <v>141</v>
       </c>
       <c r="P84" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q84">
         <v>3.27</v>
@@ -18347,7 +18350,7 @@
         <v>84</v>
       </c>
       <c r="P85" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q85">
         <v>3.9</v>
@@ -18553,7 +18556,7 @@
         <v>142</v>
       </c>
       <c r="P86" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q86">
         <v>2.53</v>
@@ -19122,6 +19125,212 @@
       </c>
       <c r="BP88">
         <v>1.5</v>
+      </c>
+    </row>
+    <row r="89" spans="1:68">
+      <c r="A89" s="1">
+        <v>88</v>
+      </c>
+      <c r="B89">
+        <v>7811579</v>
+      </c>
+      <c r="C89" t="s">
+        <v>68</v>
+      </c>
+      <c r="D89" t="s">
+        <v>69</v>
+      </c>
+      <c r="E89" s="2">
+        <v>45850.45833333334</v>
+      </c>
+      <c r="F89">
+        <v>0</v>
+      </c>
+      <c r="G89" t="s">
+        <v>71</v>
+      </c>
+      <c r="H89" t="s">
+        <v>80</v>
+      </c>
+      <c r="I89">
+        <v>3</v>
+      </c>
+      <c r="J89">
+        <v>0</v>
+      </c>
+      <c r="K89">
+        <v>3</v>
+      </c>
+      <c r="L89">
+        <v>3</v>
+      </c>
+      <c r="M89">
+        <v>1</v>
+      </c>
+      <c r="N89">
+        <v>4</v>
+      </c>
+      <c r="O89" t="s">
+        <v>143</v>
+      </c>
+      <c r="P89" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q89">
+        <v>1.77</v>
+      </c>
+      <c r="R89">
+        <v>2.58</v>
+      </c>
+      <c r="S89">
+        <v>6.5</v>
+      </c>
+      <c r="T89">
+        <v>1.25</v>
+      </c>
+      <c r="U89">
+        <v>3.5</v>
+      </c>
+      <c r="V89">
+        <v>2.2</v>
+      </c>
+      <c r="W89">
+        <v>1.62</v>
+      </c>
+      <c r="X89">
+        <v>5</v>
+      </c>
+      <c r="Y89">
+        <v>1.17</v>
+      </c>
+      <c r="Z89">
+        <v>1.2</v>
+      </c>
+      <c r="AA89">
+        <v>5.4</v>
+      </c>
+      <c r="AB89">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC89">
+        <v>1.03</v>
+      </c>
+      <c r="AD89">
+        <v>10</v>
+      </c>
+      <c r="AE89">
+        <v>1.17</v>
+      </c>
+      <c r="AF89">
+        <v>5</v>
+      </c>
+      <c r="AG89">
+        <v>1.52</v>
+      </c>
+      <c r="AH89">
+        <v>2.35</v>
+      </c>
+      <c r="AI89">
+        <v>1.92</v>
+      </c>
+      <c r="AJ89">
+        <v>1.85</v>
+      </c>
+      <c r="AK89">
+        <v>1.17</v>
+      </c>
+      <c r="AL89">
+        <v>1.16</v>
+      </c>
+      <c r="AM89">
+        <v>3.4</v>
+      </c>
+      <c r="AN89">
+        <v>1.86</v>
+      </c>
+      <c r="AO89">
+        <v>1.25</v>
+      </c>
+      <c r="AP89">
+        <v>2</v>
+      </c>
+      <c r="AQ89">
+        <v>1.11</v>
+      </c>
+      <c r="AR89">
+        <v>2.05</v>
+      </c>
+      <c r="AS89">
+        <v>1.34</v>
+      </c>
+      <c r="AT89">
+        <v>3.39</v>
+      </c>
+      <c r="AU89">
+        <v>9</v>
+      </c>
+      <c r="AV89">
+        <v>6</v>
+      </c>
+      <c r="AW89">
+        <v>7</v>
+      </c>
+      <c r="AX89">
+        <v>8</v>
+      </c>
+      <c r="AY89">
+        <v>16</v>
+      </c>
+      <c r="AZ89">
+        <v>14</v>
+      </c>
+      <c r="BA89">
+        <v>10</v>
+      </c>
+      <c r="BB89">
+        <v>8</v>
+      </c>
+      <c r="BC89">
+        <v>18</v>
+      </c>
+      <c r="BD89">
+        <v>1.17</v>
+      </c>
+      <c r="BE89">
+        <v>12</v>
+      </c>
+      <c r="BF89">
+        <v>5.8</v>
+      </c>
+      <c r="BG89">
+        <v>1.16</v>
+      </c>
+      <c r="BH89">
+        <v>4.15</v>
+      </c>
+      <c r="BI89">
+        <v>1.34</v>
+      </c>
+      <c r="BJ89">
+        <v>2.88</v>
+      </c>
+      <c r="BK89">
+        <v>1.62</v>
+      </c>
+      <c r="BL89">
+        <v>2.16</v>
+      </c>
+      <c r="BM89">
+        <v>2</v>
+      </c>
+      <c r="BN89">
+        <v>1.65</v>
+      </c>
+      <c r="BO89">
+        <v>2.56</v>
+      </c>
+      <c r="BP89">
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="208">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -445,7 +445,10 @@
     <t>['35']</t>
   </si>
   <si>
-    <t>['40', '21', '45+1']</t>
+    <t>['40', '21', '45']</t>
+  </si>
+  <si>
+    <t>['56', '71']</t>
   </si>
   <si>
     <t>['4', '14']</t>
@@ -996,7 +999,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP89"/>
+  <dimension ref="A1:BP90"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1252,7 +1255,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q2">
         <v>3.2</v>
@@ -1458,7 +1461,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q3">
         <v>3.25</v>
@@ -1664,7 +1667,7 @@
         <v>84</v>
       </c>
       <c r="P4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q4">
         <v>3.1</v>
@@ -2076,7 +2079,7 @@
         <v>85</v>
       </c>
       <c r="P6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q6">
         <v>2.3</v>
@@ -2282,7 +2285,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q7">
         <v>3.4</v>
@@ -2488,7 +2491,7 @@
         <v>87</v>
       </c>
       <c r="P8" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q8">
         <v>4.1</v>
@@ -2900,7 +2903,7 @@
         <v>89</v>
       </c>
       <c r="P10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q10">
         <v>1.7</v>
@@ -3106,7 +3109,7 @@
         <v>84</v>
       </c>
       <c r="P11" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q11">
         <v>2.25</v>
@@ -3724,7 +3727,7 @@
         <v>84</v>
       </c>
       <c r="P14" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q14">
         <v>3.1</v>
@@ -3930,7 +3933,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q15">
         <v>3.2</v>
@@ -4136,7 +4139,7 @@
         <v>93</v>
       </c>
       <c r="P16" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q16">
         <v>4.79</v>
@@ -4342,7 +4345,7 @@
         <v>84</v>
       </c>
       <c r="P17" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q17">
         <v>4.17</v>
@@ -4754,7 +4757,7 @@
         <v>84</v>
       </c>
       <c r="P19" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q19">
         <v>1.72</v>
@@ -5166,7 +5169,7 @@
         <v>96</v>
       </c>
       <c r="P21" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q21">
         <v>2.2</v>
@@ -5372,7 +5375,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q22">
         <v>4.75</v>
@@ -5578,7 +5581,7 @@
         <v>98</v>
       </c>
       <c r="P23" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q23">
         <v>2.3</v>
@@ -5784,7 +5787,7 @@
         <v>99</v>
       </c>
       <c r="P24" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q24">
         <v>2.25</v>
@@ -5990,7 +5993,7 @@
         <v>100</v>
       </c>
       <c r="P25" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q25">
         <v>3.75</v>
@@ -6068,7 +6071,7 @@
         <v>1</v>
       </c>
       <c r="AP25">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AQ25">
         <v>1.29</v>
@@ -6196,7 +6199,7 @@
         <v>101</v>
       </c>
       <c r="P26" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q26">
         <v>6.5</v>
@@ -6402,7 +6405,7 @@
         <v>102</v>
       </c>
       <c r="P27" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q27">
         <v>1.85</v>
@@ -6483,7 +6486,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ27">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AR27">
         <v>2.08</v>
@@ -6608,7 +6611,7 @@
         <v>84</v>
       </c>
       <c r="P28" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q28">
         <v>2.5</v>
@@ -6814,7 +6817,7 @@
         <v>103</v>
       </c>
       <c r="P29" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q29">
         <v>2.7</v>
@@ -7510,7 +7513,7 @@
         <v>1.5</v>
       </c>
       <c r="AP32">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AQ32">
         <v>1.13</v>
@@ -7638,7 +7641,7 @@
         <v>106</v>
       </c>
       <c r="P33" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q33">
         <v>2.93</v>
@@ -7844,7 +7847,7 @@
         <v>107</v>
       </c>
       <c r="P34" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q34">
         <v>2.26</v>
@@ -7925,7 +7928,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ34">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AR34">
         <v>1.49</v>
@@ -8256,7 +8259,7 @@
         <v>109</v>
       </c>
       <c r="P36" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q36">
         <v>6.4</v>
@@ -8462,7 +8465,7 @@
         <v>110</v>
       </c>
       <c r="P37" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q37">
         <v>3.84</v>
@@ -8668,7 +8671,7 @@
         <v>84</v>
       </c>
       <c r="P38" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q38">
         <v>5.25</v>
@@ -8874,7 +8877,7 @@
         <v>111</v>
       </c>
       <c r="P39" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -9080,7 +9083,7 @@
         <v>112</v>
       </c>
       <c r="P40" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q40">
         <v>2.85</v>
@@ -9158,7 +9161,7 @@
         <v>2</v>
       </c>
       <c r="AP40">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AQ40">
         <v>1.57</v>
@@ -9286,7 +9289,7 @@
         <v>113</v>
       </c>
       <c r="P41" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q41">
         <v>4.02</v>
@@ -9492,7 +9495,7 @@
         <v>84</v>
       </c>
       <c r="P42" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q42">
         <v>2.1</v>
@@ -9698,7 +9701,7 @@
         <v>114</v>
       </c>
       <c r="P43" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q43">
         <v>2.75</v>
@@ -9904,7 +9907,7 @@
         <v>115</v>
       </c>
       <c r="P44" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q44">
         <v>1.68</v>
@@ -10316,7 +10319,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q46">
         <v>1.91</v>
@@ -10809,7 +10812,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ48">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AR48">
         <v>1.4</v>
@@ -10934,7 +10937,7 @@
         <v>118</v>
       </c>
       <c r="P49" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q49">
         <v>3.45</v>
@@ -11346,7 +11349,7 @@
         <v>84</v>
       </c>
       <c r="P51" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q51">
         <v>6.5</v>
@@ -11552,7 +11555,7 @@
         <v>84</v>
       </c>
       <c r="P52" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q52">
         <v>2.18</v>
@@ -11758,7 +11761,7 @@
         <v>84</v>
       </c>
       <c r="P53" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q53">
         <v>3.85</v>
@@ -11964,7 +11967,7 @@
         <v>119</v>
       </c>
       <c r="P54" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q54">
         <v>2.66</v>
@@ -12170,7 +12173,7 @@
         <v>120</v>
       </c>
       <c r="P55" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q55">
         <v>3</v>
@@ -12376,7 +12379,7 @@
         <v>121</v>
       </c>
       <c r="P56" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q56">
         <v>3.35</v>
@@ -12788,7 +12791,7 @@
         <v>84</v>
       </c>
       <c r="P58" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q58">
         <v>3.3</v>
@@ -12866,7 +12869,7 @@
         <v>0.75</v>
       </c>
       <c r="AP58">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AQ58">
         <v>1.63</v>
@@ -12994,7 +12997,7 @@
         <v>84</v>
       </c>
       <c r="P59" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q59">
         <v>5.5</v>
@@ -13200,7 +13203,7 @@
         <v>122</v>
       </c>
       <c r="P60" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q60">
         <v>2.11</v>
@@ -13281,7 +13284,7 @@
         <v>2</v>
       </c>
       <c r="AQ60">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AR60">
         <v>1.95</v>
@@ -13406,7 +13409,7 @@
         <v>84</v>
       </c>
       <c r="P61" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q61">
         <v>4.5</v>
@@ -13690,7 +13693,7 @@
         <v>1</v>
       </c>
       <c r="AP62">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AQ62">
         <v>0.5</v>
@@ -13818,7 +13821,7 @@
         <v>84</v>
       </c>
       <c r="P63" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q63">
         <v>2.87</v>
@@ -14024,7 +14027,7 @@
         <v>124</v>
       </c>
       <c r="P64" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q64">
         <v>1.85</v>
@@ -14230,7 +14233,7 @@
         <v>125</v>
       </c>
       <c r="P65" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q65">
         <v>4.28</v>
@@ -14436,7 +14439,7 @@
         <v>126</v>
       </c>
       <c r="P66" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q66">
         <v>2.19</v>
@@ -14848,7 +14851,7 @@
         <v>128</v>
       </c>
       <c r="P68" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q68">
         <v>3.3</v>
@@ -15054,7 +15057,7 @@
         <v>129</v>
       </c>
       <c r="P69" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q69">
         <v>2.03</v>
@@ -15135,7 +15138,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ69">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AR69">
         <v>1.98</v>
@@ -15672,7 +15675,7 @@
         <v>131</v>
       </c>
       <c r="P72" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q72">
         <v>4.6</v>
@@ -15750,7 +15753,7 @@
         <v>2.6</v>
       </c>
       <c r="AP72">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AQ72">
         <v>2.43</v>
@@ -16290,7 +16293,7 @@
         <v>84</v>
       </c>
       <c r="P75" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q75">
         <v>4</v>
@@ -16496,7 +16499,7 @@
         <v>134</v>
       </c>
       <c r="P76" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q76">
         <v>3.28</v>
@@ -16702,7 +16705,7 @@
         <v>135</v>
       </c>
       <c r="P77" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q77">
         <v>3.6</v>
@@ -16908,7 +16911,7 @@
         <v>136</v>
       </c>
       <c r="P78" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q78">
         <v>2.17</v>
@@ -17320,7 +17323,7 @@
         <v>137</v>
       </c>
       <c r="P80" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q80">
         <v>1.52</v>
@@ -17526,7 +17529,7 @@
         <v>138</v>
       </c>
       <c r="P81" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q81">
         <v>2.38</v>
@@ -17607,7 +17610,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ81">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AR81">
         <v>1.73</v>
@@ -17732,7 +17735,7 @@
         <v>139</v>
       </c>
       <c r="P82" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q82">
         <v>1.68</v>
@@ -17938,7 +17941,7 @@
         <v>140</v>
       </c>
       <c r="P83" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q83">
         <v>3.6</v>
@@ -18144,7 +18147,7 @@
         <v>141</v>
       </c>
       <c r="P84" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q84">
         <v>3.27</v>
@@ -18350,7 +18353,7 @@
         <v>84</v>
       </c>
       <c r="P85" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q85">
         <v>3.9</v>
@@ -18556,7 +18559,7 @@
         <v>142</v>
       </c>
       <c r="P86" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q86">
         <v>2.53</v>
@@ -19267,22 +19270,22 @@
         <v>3.39</v>
       </c>
       <c r="AU89">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AV89">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW89">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AX89">
         <v>8</v>
       </c>
       <c r="AY89">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ89">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA89">
         <v>10</v>
@@ -19331,6 +19334,212 @@
       </c>
       <c r="BP89">
         <v>1.4</v>
+      </c>
+    </row>
+    <row r="90" spans="1:68">
+      <c r="A90" s="1">
+        <v>89</v>
+      </c>
+      <c r="B90">
+        <v>7811581</v>
+      </c>
+      <c r="C90" t="s">
+        <v>68</v>
+      </c>
+      <c r="D90" t="s">
+        <v>69</v>
+      </c>
+      <c r="E90" s="2">
+        <v>45851.41666666666</v>
+      </c>
+      <c r="F90">
+        <v>0</v>
+      </c>
+      <c r="G90" t="s">
+        <v>81</v>
+      </c>
+      <c r="H90" t="s">
+        <v>75</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>0</v>
+      </c>
+      <c r="K90">
+        <v>0</v>
+      </c>
+      <c r="L90">
+        <v>2</v>
+      </c>
+      <c r="M90">
+        <v>0</v>
+      </c>
+      <c r="N90">
+        <v>2</v>
+      </c>
+      <c r="O90" t="s">
+        <v>144</v>
+      </c>
+      <c r="P90" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q90">
+        <v>2.5</v>
+      </c>
+      <c r="R90">
+        <v>2.25</v>
+      </c>
+      <c r="S90">
+        <v>3.45</v>
+      </c>
+      <c r="T90">
+        <v>1.29</v>
+      </c>
+      <c r="U90">
+        <v>3.6</v>
+      </c>
+      <c r="V90">
+        <v>2.25</v>
+      </c>
+      <c r="W90">
+        <v>1.55</v>
+      </c>
+      <c r="X90">
+        <v>5</v>
+      </c>
+      <c r="Y90">
+        <v>1.15</v>
+      </c>
+      <c r="Z90">
+        <v>2.19</v>
+      </c>
+      <c r="AA90">
+        <v>3.79</v>
+      </c>
+      <c r="AB90">
+        <v>3.14</v>
+      </c>
+      <c r="AC90">
+        <v>1.04</v>
+      </c>
+      <c r="AD90">
+        <v>15</v>
+      </c>
+      <c r="AE90">
+        <v>1.2</v>
+      </c>
+      <c r="AF90">
+        <v>5.08</v>
+      </c>
+      <c r="AG90">
+        <v>1.57</v>
+      </c>
+      <c r="AH90">
+        <v>2.25</v>
+      </c>
+      <c r="AI90">
+        <v>1.51</v>
+      </c>
+      <c r="AJ90">
+        <v>2.45</v>
+      </c>
+      <c r="AK90">
+        <v>1.29</v>
+      </c>
+      <c r="AL90">
+        <v>1.26</v>
+      </c>
+      <c r="AM90">
+        <v>1.67</v>
+      </c>
+      <c r="AN90">
+        <v>1.33</v>
+      </c>
+      <c r="AO90">
+        <v>1</v>
+      </c>
+      <c r="AP90">
+        <v>1.57</v>
+      </c>
+      <c r="AQ90">
+        <v>0.86</v>
+      </c>
+      <c r="AR90">
+        <v>1.7</v>
+      </c>
+      <c r="AS90">
+        <v>1.58</v>
+      </c>
+      <c r="AT90">
+        <v>3.28</v>
+      </c>
+      <c r="AU90">
+        <v>5</v>
+      </c>
+      <c r="AV90">
+        <v>2</v>
+      </c>
+      <c r="AW90">
+        <v>5</v>
+      </c>
+      <c r="AX90">
+        <v>15</v>
+      </c>
+      <c r="AY90">
+        <v>10</v>
+      </c>
+      <c r="AZ90">
+        <v>17</v>
+      </c>
+      <c r="BA90">
+        <v>5</v>
+      </c>
+      <c r="BB90">
+        <v>6</v>
+      </c>
+      <c r="BC90">
+        <v>11</v>
+      </c>
+      <c r="BD90">
+        <v>2.05</v>
+      </c>
+      <c r="BE90">
+        <v>7.4</v>
+      </c>
+      <c r="BF90">
+        <v>2.14</v>
+      </c>
+      <c r="BG90">
+        <v>1.08</v>
+      </c>
+      <c r="BH90">
+        <v>5</v>
+      </c>
+      <c r="BI90">
+        <v>1.2</v>
+      </c>
+      <c r="BJ90">
+        <v>3.72</v>
+      </c>
+      <c r="BK90">
+        <v>1.39</v>
+      </c>
+      <c r="BL90">
+        <v>2.67</v>
+      </c>
+      <c r="BM90">
+        <v>1.71</v>
+      </c>
+      <c r="BN90">
+        <v>1.96</v>
+      </c>
+      <c r="BO90">
+        <v>2.12</v>
+      </c>
+      <c r="BP90">
+        <v>1.63</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="210">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -451,6 +451,9 @@
     <t>['56', '71']</t>
   </si>
   <si>
+    <t>['75', '58', '55']</t>
+  </si>
+  <si>
     <t>['4', '14']</t>
   </si>
   <si>
@@ -638,6 +641,9 @@
   </si>
   <si>
     <t>['50']</t>
+  </si>
+  <si>
+    <t>['43', '89']</t>
   </si>
 </sst>
 </file>
@@ -999,7 +1005,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP90"/>
+  <dimension ref="A1:BP91"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1255,7 +1261,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q2">
         <v>3.2</v>
@@ -1461,7 +1467,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q3">
         <v>3.25</v>
@@ -1667,7 +1673,7 @@
         <v>84</v>
       </c>
       <c r="P4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q4">
         <v>3.1</v>
@@ -2079,7 +2085,7 @@
         <v>85</v>
       </c>
       <c r="P6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q6">
         <v>2.3</v>
@@ -2285,7 +2291,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q7">
         <v>3.4</v>
@@ -2491,7 +2497,7 @@
         <v>87</v>
       </c>
       <c r="P8" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q8">
         <v>4.1</v>
@@ -2903,7 +2909,7 @@
         <v>89</v>
       </c>
       <c r="P10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q10">
         <v>1.7</v>
@@ -3109,7 +3115,7 @@
         <v>84</v>
       </c>
       <c r="P11" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q11">
         <v>2.25</v>
@@ -3727,7 +3733,7 @@
         <v>84</v>
       </c>
       <c r="P14" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q14">
         <v>3.1</v>
@@ -3933,7 +3939,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q15">
         <v>3.2</v>
@@ -4139,7 +4145,7 @@
         <v>93</v>
       </c>
       <c r="P16" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q16">
         <v>4.79</v>
@@ -4345,7 +4351,7 @@
         <v>84</v>
       </c>
       <c r="P17" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q17">
         <v>4.17</v>
@@ -4757,7 +4763,7 @@
         <v>84</v>
       </c>
       <c r="P19" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q19">
         <v>1.72</v>
@@ -5169,7 +5175,7 @@
         <v>96</v>
       </c>
       <c r="P21" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q21">
         <v>2.2</v>
@@ -5375,7 +5381,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q22">
         <v>4.75</v>
@@ -5453,7 +5459,7 @@
         <v>3</v>
       </c>
       <c r="AP22">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="AQ22">
         <v>2.43</v>
@@ -5581,7 +5587,7 @@
         <v>98</v>
       </c>
       <c r="P23" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q23">
         <v>2.3</v>
@@ -5662,7 +5668,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ23">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AR23">
         <v>0</v>
@@ -5787,7 +5793,7 @@
         <v>99</v>
       </c>
       <c r="P24" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q24">
         <v>2.25</v>
@@ -5993,7 +5999,7 @@
         <v>100</v>
       </c>
       <c r="P25" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q25">
         <v>3.75</v>
@@ -6199,7 +6205,7 @@
         <v>101</v>
       </c>
       <c r="P26" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q26">
         <v>6.5</v>
@@ -6405,7 +6411,7 @@
         <v>102</v>
       </c>
       <c r="P27" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q27">
         <v>1.85</v>
@@ -6611,7 +6617,7 @@
         <v>84</v>
       </c>
       <c r="P28" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q28">
         <v>2.5</v>
@@ -6817,7 +6823,7 @@
         <v>103</v>
       </c>
       <c r="P29" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q29">
         <v>2.7</v>
@@ -7641,7 +7647,7 @@
         <v>106</v>
       </c>
       <c r="P33" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q33">
         <v>2.93</v>
@@ -7847,7 +7853,7 @@
         <v>107</v>
       </c>
       <c r="P34" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q34">
         <v>2.26</v>
@@ -8134,7 +8140,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ35">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AR35">
         <v>1.73</v>
@@ -8259,7 +8265,7 @@
         <v>109</v>
       </c>
       <c r="P36" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q36">
         <v>6.4</v>
@@ -8465,7 +8471,7 @@
         <v>110</v>
       </c>
       <c r="P37" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q37">
         <v>3.84</v>
@@ -8543,7 +8549,7 @@
         <v>1</v>
       </c>
       <c r="AP37">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="AQ37">
         <v>1.13</v>
@@ -8671,7 +8677,7 @@
         <v>84</v>
       </c>
       <c r="P38" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q38">
         <v>5.25</v>
@@ -8877,7 +8883,7 @@
         <v>111</v>
       </c>
       <c r="P39" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -9083,7 +9089,7 @@
         <v>112</v>
       </c>
       <c r="P40" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q40">
         <v>2.85</v>
@@ -9289,7 +9295,7 @@
         <v>113</v>
       </c>
       <c r="P41" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q41">
         <v>4.02</v>
@@ -9495,7 +9501,7 @@
         <v>84</v>
       </c>
       <c r="P42" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q42">
         <v>2.1</v>
@@ -9573,7 +9579,7 @@
         <v>1</v>
       </c>
       <c r="AP42">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="AQ42">
         <v>1.13</v>
@@ -9701,7 +9707,7 @@
         <v>114</v>
       </c>
       <c r="P43" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q43">
         <v>2.75</v>
@@ -9907,7 +9913,7 @@
         <v>115</v>
       </c>
       <c r="P44" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q44">
         <v>1.68</v>
@@ -9988,7 +9994,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ44">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AR44">
         <v>1.82</v>
@@ -10319,7 +10325,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q46">
         <v>1.91</v>
@@ -10937,7 +10943,7 @@
         <v>118</v>
       </c>
       <c r="P49" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q49">
         <v>3.45</v>
@@ -11349,7 +11355,7 @@
         <v>84</v>
       </c>
       <c r="P51" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q51">
         <v>6.5</v>
@@ -11555,7 +11561,7 @@
         <v>84</v>
       </c>
       <c r="P52" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q52">
         <v>2.18</v>
@@ -11761,7 +11767,7 @@
         <v>84</v>
       </c>
       <c r="P53" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q53">
         <v>3.85</v>
@@ -11967,7 +11973,7 @@
         <v>119</v>
       </c>
       <c r="P54" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q54">
         <v>2.66</v>
@@ -12173,7 +12179,7 @@
         <v>120</v>
       </c>
       <c r="P55" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q55">
         <v>3</v>
@@ -12379,7 +12385,7 @@
         <v>121</v>
       </c>
       <c r="P56" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q56">
         <v>3.35</v>
@@ -12457,7 +12463,7 @@
         <v>1.4</v>
       </c>
       <c r="AP56">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="AQ56">
         <v>1.57</v>
@@ -12791,7 +12797,7 @@
         <v>84</v>
       </c>
       <c r="P58" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q58">
         <v>3.3</v>
@@ -12997,7 +13003,7 @@
         <v>84</v>
       </c>
       <c r="P59" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q59">
         <v>5.5</v>
@@ -13203,7 +13209,7 @@
         <v>122</v>
       </c>
       <c r="P60" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q60">
         <v>2.11</v>
@@ -13409,7 +13415,7 @@
         <v>84</v>
       </c>
       <c r="P61" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q61">
         <v>4.5</v>
@@ -13487,7 +13493,7 @@
         <v>1.4</v>
       </c>
       <c r="AP61">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="AQ61">
         <v>1.63</v>
@@ -13696,7 +13702,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ62">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AR62">
         <v>1.67</v>
@@ -13821,7 +13827,7 @@
         <v>84</v>
       </c>
       <c r="P63" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q63">
         <v>2.87</v>
@@ -14027,7 +14033,7 @@
         <v>124</v>
       </c>
       <c r="P64" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q64">
         <v>1.85</v>
@@ -14233,7 +14239,7 @@
         <v>125</v>
       </c>
       <c r="P65" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q65">
         <v>4.28</v>
@@ -14439,7 +14445,7 @@
         <v>126</v>
       </c>
       <c r="P66" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q66">
         <v>2.19</v>
@@ -14851,7 +14857,7 @@
         <v>128</v>
       </c>
       <c r="P68" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q68">
         <v>3.3</v>
@@ -15057,7 +15063,7 @@
         <v>129</v>
       </c>
       <c r="P69" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q69">
         <v>2.03</v>
@@ -15550,7 +15556,7 @@
         <v>2</v>
       </c>
       <c r="AQ71">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AR71">
         <v>1.89</v>
@@ -15675,7 +15681,7 @@
         <v>131</v>
       </c>
       <c r="P72" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q72">
         <v>4.6</v>
@@ -16293,7 +16299,7 @@
         <v>84</v>
       </c>
       <c r="P75" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q75">
         <v>4</v>
@@ -16499,7 +16505,7 @@
         <v>134</v>
       </c>
       <c r="P76" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q76">
         <v>3.28</v>
@@ -16705,7 +16711,7 @@
         <v>135</v>
       </c>
       <c r="P77" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q77">
         <v>3.6</v>
@@ -16783,7 +16789,7 @@
         <v>1.67</v>
       </c>
       <c r="AP77">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="AQ77">
         <v>1.43</v>
@@ -16911,7 +16917,7 @@
         <v>136</v>
       </c>
       <c r="P78" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q78">
         <v>2.17</v>
@@ -17323,7 +17329,7 @@
         <v>137</v>
       </c>
       <c r="P80" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q80">
         <v>1.52</v>
@@ -17404,7 +17410,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ80">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AR80">
         <v>1.74</v>
@@ -17529,7 +17535,7 @@
         <v>138</v>
       </c>
       <c r="P81" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q81">
         <v>2.38</v>
@@ -17735,7 +17741,7 @@
         <v>139</v>
       </c>
       <c r="P82" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q82">
         <v>1.68</v>
@@ -17941,7 +17947,7 @@
         <v>140</v>
       </c>
       <c r="P83" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q83">
         <v>3.6</v>
@@ -18019,7 +18025,7 @@
         <v>1.33</v>
       </c>
       <c r="AP83">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="AQ83">
         <v>1.29</v>
@@ -18147,7 +18153,7 @@
         <v>141</v>
       </c>
       <c r="P84" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q84">
         <v>3.27</v>
@@ -18353,7 +18359,7 @@
         <v>84</v>
       </c>
       <c r="P85" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q85">
         <v>3.9</v>
@@ -18559,7 +18565,7 @@
         <v>142</v>
       </c>
       <c r="P86" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q86">
         <v>2.53</v>
@@ -19270,22 +19276,22 @@
         <v>3.39</v>
       </c>
       <c r="AU89">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV89">
+        <v>6</v>
+      </c>
+      <c r="AW89">
         <v>7</v>
-      </c>
-      <c r="AW89">
-        <v>5</v>
       </c>
       <c r="AX89">
         <v>8</v>
       </c>
       <c r="AY89">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ89">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA89">
         <v>10</v>
@@ -19476,22 +19482,22 @@
         <v>3.28</v>
       </c>
       <c r="AU90">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV90">
         <v>2</v>
       </c>
       <c r="AW90">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX90">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AY90">
         <v>10</v>
       </c>
       <c r="AZ90">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BA90">
         <v>5</v>
@@ -19540,6 +19546,212 @@
       </c>
       <c r="BP90">
         <v>1.63</v>
+      </c>
+    </row>
+    <row r="91" spans="1:68">
+      <c r="A91" s="1">
+        <v>90</v>
+      </c>
+      <c r="B91">
+        <v>7811582</v>
+      </c>
+      <c r="C91" t="s">
+        <v>68</v>
+      </c>
+      <c r="D91" t="s">
+        <v>69</v>
+      </c>
+      <c r="E91" s="2">
+        <v>45851.52083333334</v>
+      </c>
+      <c r="F91">
+        <v>0</v>
+      </c>
+      <c r="G91" t="s">
+        <v>79</v>
+      </c>
+      <c r="H91" t="s">
+        <v>73</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>1</v>
+      </c>
+      <c r="K91">
+        <v>1</v>
+      </c>
+      <c r="L91">
+        <v>3</v>
+      </c>
+      <c r="M91">
+        <v>2</v>
+      </c>
+      <c r="N91">
+        <v>5</v>
+      </c>
+      <c r="O91" t="s">
+        <v>145</v>
+      </c>
+      <c r="P91" t="s">
+        <v>209</v>
+      </c>
+      <c r="Q91">
+        <v>2.38</v>
+      </c>
+      <c r="R91">
+        <v>2.24</v>
+      </c>
+      <c r="S91">
+        <v>4.4</v>
+      </c>
+      <c r="T91">
+        <v>1.3</v>
+      </c>
+      <c r="U91">
+        <v>3.3</v>
+      </c>
+      <c r="V91">
+        <v>2.4</v>
+      </c>
+      <c r="W91">
+        <v>1.55</v>
+      </c>
+      <c r="X91">
+        <v>5.5</v>
+      </c>
+      <c r="Y91">
+        <v>1.13</v>
+      </c>
+      <c r="Z91">
+        <v>1.72</v>
+      </c>
+      <c r="AA91">
+        <v>3.9</v>
+      </c>
+      <c r="AB91">
+        <v>4.37</v>
+      </c>
+      <c r="AC91">
+        <v>1.03</v>
+      </c>
+      <c r="AD91">
+        <v>12</v>
+      </c>
+      <c r="AE91">
+        <v>1.17</v>
+      </c>
+      <c r="AF91">
+        <v>4.3</v>
+      </c>
+      <c r="AG91">
+        <v>1.65</v>
+      </c>
+      <c r="AH91">
+        <v>2.1</v>
+      </c>
+      <c r="AI91">
+        <v>1.57</v>
+      </c>
+      <c r="AJ91">
+        <v>2.2</v>
+      </c>
+      <c r="AK91">
+        <v>1.25</v>
+      </c>
+      <c r="AL91">
+        <v>1.25</v>
+      </c>
+      <c r="AM91">
+        <v>2.09</v>
+      </c>
+      <c r="AN91">
+        <v>0.71</v>
+      </c>
+      <c r="AO91">
+        <v>0.5</v>
+      </c>
+      <c r="AP91">
+        <v>1</v>
+      </c>
+      <c r="AQ91">
+        <v>0.43</v>
+      </c>
+      <c r="AR91">
+        <v>1.28</v>
+      </c>
+      <c r="AS91">
+        <v>1.28</v>
+      </c>
+      <c r="AT91">
+        <v>2.56</v>
+      </c>
+      <c r="AU91">
+        <v>7</v>
+      </c>
+      <c r="AV91">
+        <v>6</v>
+      </c>
+      <c r="AW91">
+        <v>7</v>
+      </c>
+      <c r="AX91">
+        <v>3</v>
+      </c>
+      <c r="AY91">
+        <v>14</v>
+      </c>
+      <c r="AZ91">
+        <v>9</v>
+      </c>
+      <c r="BA91">
+        <v>6</v>
+      </c>
+      <c r="BB91">
+        <v>2</v>
+      </c>
+      <c r="BC91">
+        <v>8</v>
+      </c>
+      <c r="BD91">
+        <v>1.59</v>
+      </c>
+      <c r="BE91">
+        <v>8.5</v>
+      </c>
+      <c r="BF91">
+        <v>2.91</v>
+      </c>
+      <c r="BG91">
+        <v>1.22</v>
+      </c>
+      <c r="BH91">
+        <v>3.9</v>
+      </c>
+      <c r="BI91">
+        <v>1.43</v>
+      </c>
+      <c r="BJ91">
+        <v>2.63</v>
+      </c>
+      <c r="BK91">
+        <v>1.71</v>
+      </c>
+      <c r="BL91">
+        <v>2.06</v>
+      </c>
+      <c r="BM91">
+        <v>2.12</v>
+      </c>
+      <c r="BN91">
+        <v>1.67</v>
+      </c>
+      <c r="BO91">
+        <v>2.67</v>
+      </c>
+      <c r="BP91">
+        <v>1.42</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="212">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -454,6 +454,9 @@
     <t>['75', '58', '55']</t>
   </si>
   <si>
+    <t>['22', '84', '89']</t>
+  </si>
+  <si>
     <t>['4', '14']</t>
   </si>
   <si>
@@ -644,6 +647,9 @@
   </si>
   <si>
     <t>['43', '89']</t>
+  </si>
+  <si>
+    <t>['47', '74']</t>
   </si>
 </sst>
 </file>
@@ -1005,7 +1011,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP91"/>
+  <dimension ref="A1:BP92"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1261,7 +1267,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q2">
         <v>3.2</v>
@@ -1339,7 +1345,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AQ2">
         <v>1.63</v>
@@ -1467,7 +1473,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q3">
         <v>3.25</v>
@@ -1673,7 +1679,7 @@
         <v>84</v>
       </c>
       <c r="P4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q4">
         <v>3.1</v>
@@ -2085,7 +2091,7 @@
         <v>85</v>
       </c>
       <c r="P6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q6">
         <v>2.3</v>
@@ -2291,7 +2297,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q7">
         <v>3.4</v>
@@ -2497,7 +2503,7 @@
         <v>87</v>
       </c>
       <c r="P8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q8">
         <v>4.1</v>
@@ -2578,7 +2584,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ8">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR8">
         <v>1.58</v>
@@ -2909,7 +2915,7 @@
         <v>89</v>
       </c>
       <c r="P10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q10">
         <v>1.7</v>
@@ -2987,7 +2993,7 @@
         <v>3</v>
       </c>
       <c r="AP10">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AQ10">
         <v>1.11</v>
@@ -3115,7 +3121,7 @@
         <v>84</v>
       </c>
       <c r="P11" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q11">
         <v>2.25</v>
@@ -3733,7 +3739,7 @@
         <v>84</v>
       </c>
       <c r="P14" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q14">
         <v>3.1</v>
@@ -3939,7 +3945,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q15">
         <v>3.2</v>
@@ -4145,7 +4151,7 @@
         <v>93</v>
       </c>
       <c r="P16" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q16">
         <v>4.79</v>
@@ -4351,7 +4357,7 @@
         <v>84</v>
       </c>
       <c r="P17" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q17">
         <v>4.17</v>
@@ -4763,7 +4769,7 @@
         <v>84</v>
       </c>
       <c r="P19" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q19">
         <v>1.72</v>
@@ -5175,7 +5181,7 @@
         <v>96</v>
       </c>
       <c r="P21" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q21">
         <v>2.2</v>
@@ -5381,7 +5387,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q22">
         <v>4.75</v>
@@ -5587,7 +5593,7 @@
         <v>98</v>
       </c>
       <c r="P23" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q23">
         <v>2.3</v>
@@ -5793,7 +5799,7 @@
         <v>99</v>
       </c>
       <c r="P24" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q24">
         <v>2.25</v>
@@ -5874,7 +5880,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ24">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR24">
         <v>1.6</v>
@@ -5999,7 +6005,7 @@
         <v>100</v>
       </c>
       <c r="P25" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q25">
         <v>3.75</v>
@@ -6205,7 +6211,7 @@
         <v>101</v>
       </c>
       <c r="P26" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q26">
         <v>6.5</v>
@@ -6411,7 +6417,7 @@
         <v>102</v>
       </c>
       <c r="P27" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q27">
         <v>1.85</v>
@@ -6617,7 +6623,7 @@
         <v>84</v>
       </c>
       <c r="P28" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q28">
         <v>2.5</v>
@@ -6823,7 +6829,7 @@
         <v>103</v>
       </c>
       <c r="P29" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q29">
         <v>2.7</v>
@@ -7647,7 +7653,7 @@
         <v>106</v>
       </c>
       <c r="P33" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q33">
         <v>2.93</v>
@@ -7853,7 +7859,7 @@
         <v>107</v>
       </c>
       <c r="P34" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q34">
         <v>2.26</v>
@@ -7931,7 +7937,7 @@
         <v>1</v>
       </c>
       <c r="AP34">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AQ34">
         <v>0.86</v>
@@ -8265,7 +8271,7 @@
         <v>109</v>
       </c>
       <c r="P36" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q36">
         <v>6.4</v>
@@ -8471,7 +8477,7 @@
         <v>110</v>
       </c>
       <c r="P37" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q37">
         <v>3.84</v>
@@ -8677,7 +8683,7 @@
         <v>84</v>
       </c>
       <c r="P38" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q38">
         <v>5.25</v>
@@ -8883,7 +8889,7 @@
         <v>111</v>
       </c>
       <c r="P39" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -8964,7 +8970,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ39">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR39">
         <v>1.9</v>
@@ -9089,7 +9095,7 @@
         <v>112</v>
       </c>
       <c r="P40" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q40">
         <v>2.85</v>
@@ -9295,7 +9301,7 @@
         <v>113</v>
       </c>
       <c r="P41" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q41">
         <v>4.02</v>
@@ -9501,7 +9507,7 @@
         <v>84</v>
       </c>
       <c r="P42" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q42">
         <v>2.1</v>
@@ -9707,7 +9713,7 @@
         <v>114</v>
       </c>
       <c r="P43" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q43">
         <v>2.75</v>
@@ -9913,7 +9919,7 @@
         <v>115</v>
       </c>
       <c r="P44" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q44">
         <v>1.68</v>
@@ -10325,7 +10331,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q46">
         <v>1.91</v>
@@ -10609,7 +10615,7 @@
         <v>2.33</v>
       </c>
       <c r="AP47">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AQ47">
         <v>1.29</v>
@@ -10943,7 +10949,7 @@
         <v>118</v>
       </c>
       <c r="P49" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q49">
         <v>3.45</v>
@@ -11227,7 +11233,7 @@
         <v>0.6</v>
       </c>
       <c r="AP50">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AQ50">
         <v>0.57</v>
@@ -11355,7 +11361,7 @@
         <v>84</v>
       </c>
       <c r="P51" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q51">
         <v>6.5</v>
@@ -11561,7 +11567,7 @@
         <v>84</v>
       </c>
       <c r="P52" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q52">
         <v>2.18</v>
@@ -11642,7 +11648,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ52">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR52">
         <v>1.97</v>
@@ -11767,7 +11773,7 @@
         <v>84</v>
       </c>
       <c r="P53" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q53">
         <v>3.85</v>
@@ -11973,7 +11979,7 @@
         <v>119</v>
       </c>
       <c r="P54" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q54">
         <v>2.66</v>
@@ -12179,7 +12185,7 @@
         <v>120</v>
       </c>
       <c r="P55" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q55">
         <v>3</v>
@@ -12260,7 +12266,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ55">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR55">
         <v>1.69</v>
@@ -12385,7 +12391,7 @@
         <v>121</v>
       </c>
       <c r="P56" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q56">
         <v>3.35</v>
@@ -12797,7 +12803,7 @@
         <v>84</v>
       </c>
       <c r="P58" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q58">
         <v>3.3</v>
@@ -13003,7 +13009,7 @@
         <v>84</v>
       </c>
       <c r="P59" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q59">
         <v>5.5</v>
@@ -13209,7 +13215,7 @@
         <v>122</v>
       </c>
       <c r="P60" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q60">
         <v>2.11</v>
@@ -13415,7 +13421,7 @@
         <v>84</v>
       </c>
       <c r="P61" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q61">
         <v>4.5</v>
@@ -13827,7 +13833,7 @@
         <v>84</v>
       </c>
       <c r="P63" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q63">
         <v>2.87</v>
@@ -14033,7 +14039,7 @@
         <v>124</v>
       </c>
       <c r="P64" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q64">
         <v>1.85</v>
@@ -14239,7 +14245,7 @@
         <v>125</v>
       </c>
       <c r="P65" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q65">
         <v>4.28</v>
@@ -14320,7 +14326,7 @@
         <v>1</v>
       </c>
       <c r="AQ65">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR65">
         <v>1.16</v>
@@ -14445,7 +14451,7 @@
         <v>126</v>
       </c>
       <c r="P66" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q66">
         <v>2.19</v>
@@ -14523,7 +14529,7 @@
         <v>1.33</v>
       </c>
       <c r="AP66">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AQ66">
         <v>1.57</v>
@@ -14857,7 +14863,7 @@
         <v>128</v>
       </c>
       <c r="P68" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q68">
         <v>3.3</v>
@@ -15063,7 +15069,7 @@
         <v>129</v>
       </c>
       <c r="P69" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q69">
         <v>2.03</v>
@@ -15681,7 +15687,7 @@
         <v>131</v>
       </c>
       <c r="P72" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q72">
         <v>4.6</v>
@@ -16299,7 +16305,7 @@
         <v>84</v>
       </c>
       <c r="P75" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q75">
         <v>4</v>
@@ -16505,7 +16511,7 @@
         <v>134</v>
       </c>
       <c r="P76" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q76">
         <v>3.28</v>
@@ -16711,7 +16717,7 @@
         <v>135</v>
       </c>
       <c r="P77" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q77">
         <v>3.6</v>
@@ -16792,7 +16798,7 @@
         <v>1</v>
       </c>
       <c r="AQ77">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR77">
         <v>1.34</v>
@@ -16917,7 +16923,7 @@
         <v>136</v>
       </c>
       <c r="P78" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q78">
         <v>2.17</v>
@@ -17329,7 +17335,7 @@
         <v>137</v>
       </c>
       <c r="P80" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q80">
         <v>1.52</v>
@@ -17407,7 +17413,7 @@
         <v>0.6</v>
       </c>
       <c r="AP80">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AQ80">
         <v>0.43</v>
@@ -17535,7 +17541,7 @@
         <v>138</v>
       </c>
       <c r="P81" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q81">
         <v>2.38</v>
@@ -17741,7 +17747,7 @@
         <v>139</v>
       </c>
       <c r="P82" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q82">
         <v>1.68</v>
@@ -17947,7 +17953,7 @@
         <v>140</v>
       </c>
       <c r="P83" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q83">
         <v>3.6</v>
@@ -18153,7 +18159,7 @@
         <v>141</v>
       </c>
       <c r="P84" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q84">
         <v>3.27</v>
@@ -18359,7 +18365,7 @@
         <v>84</v>
       </c>
       <c r="P85" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q85">
         <v>3.9</v>
@@ -18565,7 +18571,7 @@
         <v>142</v>
       </c>
       <c r="P86" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q86">
         <v>2.53</v>
@@ -19595,7 +19601,7 @@
         <v>145</v>
       </c>
       <c r="P91" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q91">
         <v>2.38</v>
@@ -19752,6 +19758,212 @@
       </c>
       <c r="BP91">
         <v>1.42</v>
+      </c>
+    </row>
+    <row r="92" spans="1:68">
+      <c r="A92" s="1">
+        <v>91</v>
+      </c>
+      <c r="B92">
+        <v>7811580</v>
+      </c>
+      <c r="C92" t="s">
+        <v>68</v>
+      </c>
+      <c r="D92" t="s">
+        <v>69</v>
+      </c>
+      <c r="E92" s="2">
+        <v>45852.5</v>
+      </c>
+      <c r="F92">
+        <v>0</v>
+      </c>
+      <c r="G92" t="s">
+        <v>70</v>
+      </c>
+      <c r="H92" t="s">
+        <v>74</v>
+      </c>
+      <c r="I92">
+        <v>1</v>
+      </c>
+      <c r="J92">
+        <v>0</v>
+      </c>
+      <c r="K92">
+        <v>1</v>
+      </c>
+      <c r="L92">
+        <v>3</v>
+      </c>
+      <c r="M92">
+        <v>2</v>
+      </c>
+      <c r="N92">
+        <v>5</v>
+      </c>
+      <c r="O92" t="s">
+        <v>146</v>
+      </c>
+      <c r="P92" t="s">
+        <v>211</v>
+      </c>
+      <c r="Q92">
+        <v>1.93</v>
+      </c>
+      <c r="R92">
+        <v>2.58</v>
+      </c>
+      <c r="S92">
+        <v>5.2</v>
+      </c>
+      <c r="T92">
+        <v>1.25</v>
+      </c>
+      <c r="U92">
+        <v>3.8</v>
+      </c>
+      <c r="V92">
+        <v>2.19</v>
+      </c>
+      <c r="W92">
+        <v>1.74</v>
+      </c>
+      <c r="X92">
+        <v>4.8</v>
+      </c>
+      <c r="Y92">
+        <v>1.17</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+      <c r="AA92">
+        <v>0</v>
+      </c>
+      <c r="AB92">
+        <v>0</v>
+      </c>
+      <c r="AC92">
+        <v>1.03</v>
+      </c>
+      <c r="AD92">
+        <v>17</v>
+      </c>
+      <c r="AE92">
+        <v>1.15</v>
+      </c>
+      <c r="AF92">
+        <v>5</v>
+      </c>
+      <c r="AG92">
+        <v>1.47</v>
+      </c>
+      <c r="AH92">
+        <v>2.75</v>
+      </c>
+      <c r="AI92">
+        <v>1.65</v>
+      </c>
+      <c r="AJ92">
+        <v>2.15</v>
+      </c>
+      <c r="AK92">
+        <v>1.15</v>
+      </c>
+      <c r="AL92">
+        <v>0</v>
+      </c>
+      <c r="AM92">
+        <v>2.5</v>
+      </c>
+      <c r="AN92">
+        <v>2.29</v>
+      </c>
+      <c r="AO92">
+        <v>1.43</v>
+      </c>
+      <c r="AP92">
+        <v>2.38</v>
+      </c>
+      <c r="AQ92">
+        <v>1.25</v>
+      </c>
+      <c r="AR92">
+        <v>1.85</v>
+      </c>
+      <c r="AS92">
+        <v>1.25</v>
+      </c>
+      <c r="AT92">
+        <v>3.1</v>
+      </c>
+      <c r="AU92">
+        <v>7</v>
+      </c>
+      <c r="AV92">
+        <v>5</v>
+      </c>
+      <c r="AW92">
+        <v>6</v>
+      </c>
+      <c r="AX92">
+        <v>8</v>
+      </c>
+      <c r="AY92">
+        <v>13</v>
+      </c>
+      <c r="AZ92">
+        <v>13</v>
+      </c>
+      <c r="BA92">
+        <v>5</v>
+      </c>
+      <c r="BB92">
+        <v>4</v>
+      </c>
+      <c r="BC92">
+        <v>9</v>
+      </c>
+      <c r="BD92">
+        <v>1.25</v>
+      </c>
+      <c r="BE92">
+        <v>11</v>
+      </c>
+      <c r="BF92">
+        <v>4.6</v>
+      </c>
+      <c r="BG92">
+        <v>1.12</v>
+      </c>
+      <c r="BH92">
+        <v>6.37</v>
+      </c>
+      <c r="BI92">
+        <v>1.42</v>
+      </c>
+      <c r="BJ92">
+        <v>2.65</v>
+      </c>
+      <c r="BK92">
+        <v>1.55</v>
+      </c>
+      <c r="BL92">
+        <v>2.3</v>
+      </c>
+      <c r="BM92">
+        <v>1.83</v>
+      </c>
+      <c r="BN92">
+        <v>1.85</v>
+      </c>
+      <c r="BO92">
+        <v>2.3</v>
+      </c>
+      <c r="BP92">
+        <v>1.55</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
@@ -19900,22 +19900,22 @@
         <v>3.1</v>
       </c>
       <c r="AU92">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV92">
         <v>5</v>
       </c>
       <c r="AW92">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX92">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AY92">
         <v>13</v>
       </c>
       <c r="AZ92">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="BA92">
         <v>5</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="214">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -457,6 +457,9 @@
     <t>['22', '84', '89']</t>
   </si>
   <si>
+    <t>['28', '33']</t>
+  </si>
+  <si>
     <t>['4', '14']</t>
   </si>
   <si>
@@ -650,6 +653,9 @@
   </si>
   <si>
     <t>['47', '74']</t>
+  </si>
+  <si>
+    <t>['7', '31']</t>
   </si>
 </sst>
 </file>
@@ -1011,7 +1017,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP92"/>
+  <dimension ref="A1:BP93"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1267,7 +1273,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q2">
         <v>3.2</v>
@@ -1473,7 +1479,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q3">
         <v>3.25</v>
@@ -1679,7 +1685,7 @@
         <v>84</v>
       </c>
       <c r="P4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q4">
         <v>3.1</v>
@@ -1963,7 +1969,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AQ5">
         <v>1.57</v>
@@ -2091,7 +2097,7 @@
         <v>85</v>
       </c>
       <c r="P6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q6">
         <v>2.3</v>
@@ -2297,7 +2303,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q7">
         <v>3.4</v>
@@ -2503,7 +2509,7 @@
         <v>87</v>
       </c>
       <c r="P8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q8">
         <v>4.1</v>
@@ -2581,7 +2587,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AQ8">
         <v>1.25</v>
@@ -2915,7 +2921,7 @@
         <v>89</v>
       </c>
       <c r="P10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q10">
         <v>1.7</v>
@@ -3121,7 +3127,7 @@
         <v>84</v>
       </c>
       <c r="P11" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q11">
         <v>2.25</v>
@@ -3739,7 +3745,7 @@
         <v>84</v>
       </c>
       <c r="P14" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q14">
         <v>3.1</v>
@@ -3820,7 +3826,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ14">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="AR14">
         <v>2.17</v>
@@ -3945,7 +3951,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q15">
         <v>3.2</v>
@@ -4151,7 +4157,7 @@
         <v>93</v>
       </c>
       <c r="P16" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q16">
         <v>4.79</v>
@@ -4357,7 +4363,7 @@
         <v>84</v>
       </c>
       <c r="P17" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q17">
         <v>4.17</v>
@@ -4435,7 +4441,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AQ17">
         <v>1.63</v>
@@ -4769,7 +4775,7 @@
         <v>84</v>
       </c>
       <c r="P19" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q19">
         <v>1.72</v>
@@ -5181,7 +5187,7 @@
         <v>96</v>
       </c>
       <c r="P21" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q21">
         <v>2.2</v>
@@ -5387,7 +5393,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q22">
         <v>4.75</v>
@@ -5468,7 +5474,7 @@
         <v>1</v>
       </c>
       <c r="AQ22">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="AR22">
         <v>0</v>
@@ -5593,7 +5599,7 @@
         <v>98</v>
       </c>
       <c r="P23" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q23">
         <v>2.3</v>
@@ -5799,7 +5805,7 @@
         <v>99</v>
       </c>
       <c r="P24" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q24">
         <v>2.25</v>
@@ -6005,7 +6011,7 @@
         <v>100</v>
       </c>
       <c r="P25" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q25">
         <v>3.75</v>
@@ -6211,7 +6217,7 @@
         <v>101</v>
       </c>
       <c r="P26" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q26">
         <v>6.5</v>
@@ -6417,7 +6423,7 @@
         <v>102</v>
       </c>
       <c r="P27" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q27">
         <v>1.85</v>
@@ -6623,7 +6629,7 @@
         <v>84</v>
       </c>
       <c r="P28" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q28">
         <v>2.5</v>
@@ -6829,7 +6835,7 @@
         <v>103</v>
       </c>
       <c r="P29" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q29">
         <v>2.7</v>
@@ -6907,7 +6913,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AQ29">
         <v>0.57</v>
@@ -7653,7 +7659,7 @@
         <v>106</v>
       </c>
       <c r="P33" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q33">
         <v>2.93</v>
@@ -7859,7 +7865,7 @@
         <v>107</v>
       </c>
       <c r="P34" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q34">
         <v>2.26</v>
@@ -8271,7 +8277,7 @@
         <v>109</v>
       </c>
       <c r="P36" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q36">
         <v>6.4</v>
@@ -8352,7 +8358,7 @@
         <v>1</v>
       </c>
       <c r="AQ36">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="AR36">
         <v>1.26</v>
@@ -8477,7 +8483,7 @@
         <v>110</v>
       </c>
       <c r="P37" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q37">
         <v>3.84</v>
@@ -8683,7 +8689,7 @@
         <v>84</v>
       </c>
       <c r="P38" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q38">
         <v>5.25</v>
@@ -8889,7 +8895,7 @@
         <v>111</v>
       </c>
       <c r="P39" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -9095,7 +9101,7 @@
         <v>112</v>
       </c>
       <c r="P40" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q40">
         <v>2.85</v>
@@ -9301,7 +9307,7 @@
         <v>113</v>
       </c>
       <c r="P41" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q41">
         <v>4.02</v>
@@ -9507,7 +9513,7 @@
         <v>84</v>
       </c>
       <c r="P42" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q42">
         <v>2.1</v>
@@ -9713,7 +9719,7 @@
         <v>114</v>
       </c>
       <c r="P43" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q43">
         <v>2.75</v>
@@ -9919,7 +9925,7 @@
         <v>115</v>
       </c>
       <c r="P44" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q44">
         <v>1.68</v>
@@ -10331,7 +10337,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q46">
         <v>1.91</v>
@@ -10821,7 +10827,7 @@
         <v>0.5</v>
       </c>
       <c r="AP48">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AQ48">
         <v>0.86</v>
@@ -10949,7 +10955,7 @@
         <v>118</v>
       </c>
       <c r="P49" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q49">
         <v>3.45</v>
@@ -11361,7 +11367,7 @@
         <v>84</v>
       </c>
       <c r="P51" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q51">
         <v>6.5</v>
@@ -11567,7 +11573,7 @@
         <v>84</v>
       </c>
       <c r="P52" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q52">
         <v>2.18</v>
@@ -11773,7 +11779,7 @@
         <v>84</v>
       </c>
       <c r="P53" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q53">
         <v>3.85</v>
@@ -11854,7 +11860,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ53">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="AR53">
         <v>1.88</v>
@@ -11979,7 +11985,7 @@
         <v>119</v>
       </c>
       <c r="P54" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q54">
         <v>2.66</v>
@@ -12057,7 +12063,7 @@
         <v>1.5</v>
       </c>
       <c r="AP54">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AQ54">
         <v>1.13</v>
@@ -12185,7 +12191,7 @@
         <v>120</v>
       </c>
       <c r="P55" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q55">
         <v>3</v>
@@ -12391,7 +12397,7 @@
         <v>121</v>
       </c>
       <c r="P56" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q56">
         <v>3.35</v>
@@ -12803,7 +12809,7 @@
         <v>84</v>
       </c>
       <c r="P58" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q58">
         <v>3.3</v>
@@ -13009,7 +13015,7 @@
         <v>84</v>
       </c>
       <c r="P59" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q59">
         <v>5.5</v>
@@ -13090,7 +13096,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ59">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="AR59">
         <v>0.99</v>
@@ -13215,7 +13221,7 @@
         <v>122</v>
       </c>
       <c r="P60" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q60">
         <v>2.11</v>
@@ -13421,7 +13427,7 @@
         <v>84</v>
       </c>
       <c r="P61" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q61">
         <v>4.5</v>
@@ -13833,7 +13839,7 @@
         <v>84</v>
       </c>
       <c r="P63" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q63">
         <v>2.87</v>
@@ -14039,7 +14045,7 @@
         <v>124</v>
       </c>
       <c r="P64" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q64">
         <v>1.85</v>
@@ -14245,7 +14251,7 @@
         <v>125</v>
       </c>
       <c r="P65" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q65">
         <v>4.28</v>
@@ -14451,7 +14457,7 @@
         <v>126</v>
       </c>
       <c r="P66" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q66">
         <v>2.19</v>
@@ -14863,7 +14869,7 @@
         <v>128</v>
       </c>
       <c r="P68" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q68">
         <v>3.3</v>
@@ -15069,7 +15075,7 @@
         <v>129</v>
       </c>
       <c r="P69" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q69">
         <v>2.03</v>
@@ -15687,7 +15693,7 @@
         <v>131</v>
       </c>
       <c r="P72" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q72">
         <v>4.6</v>
@@ -15768,7 +15774,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ72">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="AR72">
         <v>1.7</v>
@@ -16305,7 +16311,7 @@
         <v>84</v>
       </c>
       <c r="P75" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q75">
         <v>4</v>
@@ -16511,7 +16517,7 @@
         <v>134</v>
       </c>
       <c r="P76" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q76">
         <v>3.28</v>
@@ -16589,7 +16595,7 @@
         <v>1.17</v>
       </c>
       <c r="AP76">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AQ76">
         <v>1.11</v>
@@ -16717,7 +16723,7 @@
         <v>135</v>
       </c>
       <c r="P77" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q77">
         <v>3.6</v>
@@ -16923,7 +16929,7 @@
         <v>136</v>
       </c>
       <c r="P78" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q78">
         <v>2.17</v>
@@ -17335,7 +17341,7 @@
         <v>137</v>
       </c>
       <c r="P80" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q80">
         <v>1.52</v>
@@ -17541,7 +17547,7 @@
         <v>138</v>
       </c>
       <c r="P81" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q81">
         <v>2.38</v>
@@ -17747,7 +17753,7 @@
         <v>139</v>
       </c>
       <c r="P82" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q82">
         <v>1.68</v>
@@ -17953,7 +17959,7 @@
         <v>140</v>
       </c>
       <c r="P83" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q83">
         <v>3.6</v>
@@ -18159,7 +18165,7 @@
         <v>141</v>
       </c>
       <c r="P84" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q84">
         <v>3.27</v>
@@ -18365,7 +18371,7 @@
         <v>84</v>
       </c>
       <c r="P85" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q85">
         <v>3.9</v>
@@ -18571,7 +18577,7 @@
         <v>142</v>
       </c>
       <c r="P86" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q86">
         <v>2.53</v>
@@ -18858,7 +18864,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ87">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="AR87">
         <v>1.61</v>
@@ -19061,7 +19067,7 @@
         <v>1.14</v>
       </c>
       <c r="AP88">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AQ88">
         <v>1.13</v>
@@ -19601,7 +19607,7 @@
         <v>145</v>
       </c>
       <c r="P91" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q91">
         <v>2.38</v>
@@ -19807,7 +19813,7 @@
         <v>146</v>
       </c>
       <c r="P92" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q92">
         <v>1.93</v>
@@ -19964,6 +19970,212 @@
       </c>
       <c r="BP92">
         <v>1.55</v>
+      </c>
+    </row>
+    <row r="93" spans="1:68">
+      <c r="A93" s="1">
+        <v>92</v>
+      </c>
+      <c r="B93">
+        <v>7811583</v>
+      </c>
+      <c r="C93" t="s">
+        <v>68</v>
+      </c>
+      <c r="D93" t="s">
+        <v>69</v>
+      </c>
+      <c r="E93" s="2">
+        <v>45856.5</v>
+      </c>
+      <c r="F93">
+        <v>0</v>
+      </c>
+      <c r="G93" t="s">
+        <v>73</v>
+      </c>
+      <c r="H93" t="s">
+        <v>71</v>
+      </c>
+      <c r="I93">
+        <v>2</v>
+      </c>
+      <c r="J93">
+        <v>2</v>
+      </c>
+      <c r="K93">
+        <v>4</v>
+      </c>
+      <c r="L93">
+        <v>2</v>
+      </c>
+      <c r="M93">
+        <v>2</v>
+      </c>
+      <c r="N93">
+        <v>4</v>
+      </c>
+      <c r="O93" t="s">
+        <v>147</v>
+      </c>
+      <c r="P93" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q93">
+        <v>7</v>
+      </c>
+      <c r="R93">
+        <v>3</v>
+      </c>
+      <c r="S93">
+        <v>1.77</v>
+      </c>
+      <c r="T93">
+        <v>1.22</v>
+      </c>
+      <c r="U93">
+        <v>3.8</v>
+      </c>
+      <c r="V93">
+        <v>1.98</v>
+      </c>
+      <c r="W93">
+        <v>1.73</v>
+      </c>
+      <c r="X93">
+        <v>4.3</v>
+      </c>
+      <c r="Y93">
+        <v>1.21</v>
+      </c>
+      <c r="Z93">
+        <v>8.5</v>
+      </c>
+      <c r="AA93">
+        <v>5.5</v>
+      </c>
+      <c r="AB93">
+        <v>1.28</v>
+      </c>
+      <c r="AC93">
+        <v>1</v>
+      </c>
+      <c r="AD93">
+        <v>12</v>
+      </c>
+      <c r="AE93">
+        <v>1.12</v>
+      </c>
+      <c r="AF93">
+        <v>5</v>
+      </c>
+      <c r="AG93">
+        <v>1.37</v>
+      </c>
+      <c r="AH93">
+        <v>2.85</v>
+      </c>
+      <c r="AI93">
+        <v>1.68</v>
+      </c>
+      <c r="AJ93">
+        <v>2.21</v>
+      </c>
+      <c r="AK93">
+        <v>1.14</v>
+      </c>
+      <c r="AL93">
+        <v>1.19</v>
+      </c>
+      <c r="AM93">
+        <v>1.06</v>
+      </c>
+      <c r="AN93">
+        <v>0.88</v>
+      </c>
+      <c r="AO93">
+        <v>2.43</v>
+      </c>
+      <c r="AP93">
+        <v>0.89</v>
+      </c>
+      <c r="AQ93">
+        <v>2.25</v>
+      </c>
+      <c r="AR93">
+        <v>1.63</v>
+      </c>
+      <c r="AS93">
+        <v>1.97</v>
+      </c>
+      <c r="AT93">
+        <v>3.6</v>
+      </c>
+      <c r="AU93">
+        <v>4</v>
+      </c>
+      <c r="AV93">
+        <v>6</v>
+      </c>
+      <c r="AW93">
+        <v>8</v>
+      </c>
+      <c r="AX93">
+        <v>14</v>
+      </c>
+      <c r="AY93">
+        <v>12</v>
+      </c>
+      <c r="AZ93">
+        <v>20</v>
+      </c>
+      <c r="BA93">
+        <v>4</v>
+      </c>
+      <c r="BB93">
+        <v>11</v>
+      </c>
+      <c r="BC93">
+        <v>15</v>
+      </c>
+      <c r="BD93">
+        <v>4.2</v>
+      </c>
+      <c r="BE93">
+        <v>12</v>
+      </c>
+      <c r="BF93">
+        <v>1.25</v>
+      </c>
+      <c r="BG93">
+        <v>1.15</v>
+      </c>
+      <c r="BH93">
+        <v>4.5</v>
+      </c>
+      <c r="BI93">
+        <v>1.29</v>
+      </c>
+      <c r="BJ93">
+        <v>2.8</v>
+      </c>
+      <c r="BK93">
+        <v>1.51</v>
+      </c>
+      <c r="BL93">
+        <v>2.38</v>
+      </c>
+      <c r="BM93">
+        <v>1.83</v>
+      </c>
+      <c r="BN93">
+        <v>1.91</v>
+      </c>
+      <c r="BO93">
+        <v>2.28</v>
+      </c>
+      <c r="BP93">
+        <v>1.58</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
@@ -20118,13 +20118,13 @@
         <v>6</v>
       </c>
       <c r="AW93">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX93">
         <v>14</v>
       </c>
       <c r="AY93">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ93">
         <v>20</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="216">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -460,6 +460,9 @@
     <t>['28', '33']</t>
   </si>
   <si>
+    <t>['89']</t>
+  </si>
+  <si>
     <t>['4', '14']</t>
   </si>
   <si>
@@ -656,6 +659,9 @@
   </si>
   <si>
     <t>['7', '31']</t>
+  </si>
+  <si>
+    <t>['80']</t>
   </si>
 </sst>
 </file>
@@ -1017,7 +1023,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP93"/>
+  <dimension ref="A1:BP94"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1273,7 +1279,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q2">
         <v>3.2</v>
@@ -1479,7 +1485,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q3">
         <v>3.25</v>
@@ -1560,7 +1566,7 @@
         <v>2</v>
       </c>
       <c r="AQ3">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1685,7 +1691,7 @@
         <v>84</v>
       </c>
       <c r="P4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q4">
         <v>3.1</v>
@@ -2097,7 +2103,7 @@
         <v>85</v>
       </c>
       <c r="P6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q6">
         <v>2.3</v>
@@ -2175,7 +2181,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ6">
         <v>0.57</v>
@@ -2303,7 +2309,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q7">
         <v>3.4</v>
@@ -2509,7 +2515,7 @@
         <v>87</v>
       </c>
       <c r="P8" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q8">
         <v>4.1</v>
@@ -2921,7 +2927,7 @@
         <v>89</v>
       </c>
       <c r="P10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q10">
         <v>1.7</v>
@@ -3127,7 +3133,7 @@
         <v>84</v>
       </c>
       <c r="P11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q11">
         <v>2.25</v>
@@ -3745,7 +3751,7 @@
         <v>84</v>
       </c>
       <c r="P14" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q14">
         <v>3.1</v>
@@ -3823,7 +3829,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ14">
         <v>2.25</v>
@@ -3951,7 +3957,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q15">
         <v>3.2</v>
@@ -4157,7 +4163,7 @@
         <v>93</v>
       </c>
       <c r="P16" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q16">
         <v>4.79</v>
@@ -4363,7 +4369,7 @@
         <v>84</v>
       </c>
       <c r="P17" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q17">
         <v>4.17</v>
@@ -4775,7 +4781,7 @@
         <v>84</v>
       </c>
       <c r="P19" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q19">
         <v>1.72</v>
@@ -5187,7 +5193,7 @@
         <v>96</v>
       </c>
       <c r="P21" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q21">
         <v>2.2</v>
@@ -5393,7 +5399,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q22">
         <v>4.75</v>
@@ -5599,7 +5605,7 @@
         <v>98</v>
       </c>
       <c r="P23" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q23">
         <v>2.3</v>
@@ -5805,7 +5811,7 @@
         <v>99</v>
       </c>
       <c r="P24" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q24">
         <v>2.25</v>
@@ -6011,7 +6017,7 @@
         <v>100</v>
       </c>
       <c r="P25" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q25">
         <v>3.75</v>
@@ -6092,7 +6098,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ25">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AR25">
         <v>0</v>
@@ -6217,7 +6223,7 @@
         <v>101</v>
       </c>
       <c r="P26" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q26">
         <v>6.5</v>
@@ -6423,7 +6429,7 @@
         <v>102</v>
       </c>
       <c r="P27" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q27">
         <v>1.85</v>
@@ -6629,7 +6635,7 @@
         <v>84</v>
       </c>
       <c r="P28" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q28">
         <v>2.5</v>
@@ -6835,7 +6841,7 @@
         <v>103</v>
       </c>
       <c r="P29" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q29">
         <v>2.7</v>
@@ -7119,7 +7125,7 @@
         <v>1.5</v>
       </c>
       <c r="AP30">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ30">
         <v>1.63</v>
@@ -7659,7 +7665,7 @@
         <v>106</v>
       </c>
       <c r="P33" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q33">
         <v>2.93</v>
@@ -7865,7 +7871,7 @@
         <v>107</v>
       </c>
       <c r="P34" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q34">
         <v>2.26</v>
@@ -8277,7 +8283,7 @@
         <v>109</v>
       </c>
       <c r="P36" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q36">
         <v>6.4</v>
@@ -8483,7 +8489,7 @@
         <v>110</v>
       </c>
       <c r="P37" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q37">
         <v>3.84</v>
@@ -8689,7 +8695,7 @@
         <v>84</v>
       </c>
       <c r="P38" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q38">
         <v>5.25</v>
@@ -8895,7 +8901,7 @@
         <v>111</v>
       </c>
       <c r="P39" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -9101,7 +9107,7 @@
         <v>112</v>
       </c>
       <c r="P40" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q40">
         <v>2.85</v>
@@ -9307,7 +9313,7 @@
         <v>113</v>
       </c>
       <c r="P41" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q41">
         <v>4.02</v>
@@ -9388,7 +9394,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ41">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AR41">
         <v>1.76</v>
@@ -9513,7 +9519,7 @@
         <v>84</v>
       </c>
       <c r="P42" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q42">
         <v>2.1</v>
@@ -9719,7 +9725,7 @@
         <v>114</v>
       </c>
       <c r="P43" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q43">
         <v>2.75</v>
@@ -9925,7 +9931,7 @@
         <v>115</v>
       </c>
       <c r="P44" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q44">
         <v>1.68</v>
@@ -10209,7 +10215,7 @@
         <v>1.5</v>
       </c>
       <c r="AP45">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ45">
         <v>1.11</v>
@@ -10337,7 +10343,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q46">
         <v>1.91</v>
@@ -10624,7 +10630,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ47">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AR47">
         <v>1.71</v>
@@ -10955,7 +10961,7 @@
         <v>118</v>
       </c>
       <c r="P49" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q49">
         <v>3.45</v>
@@ -11367,7 +11373,7 @@
         <v>84</v>
       </c>
       <c r="P51" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q51">
         <v>6.5</v>
@@ -11573,7 +11579,7 @@
         <v>84</v>
       </c>
       <c r="P52" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q52">
         <v>2.18</v>
@@ -11779,7 +11785,7 @@
         <v>84</v>
       </c>
       <c r="P53" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q53">
         <v>3.85</v>
@@ -11985,7 +11991,7 @@
         <v>119</v>
       </c>
       <c r="P54" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q54">
         <v>2.66</v>
@@ -12191,7 +12197,7 @@
         <v>120</v>
       </c>
       <c r="P55" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q55">
         <v>3</v>
@@ -12397,7 +12403,7 @@
         <v>121</v>
       </c>
       <c r="P56" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q56">
         <v>3.35</v>
@@ -12684,7 +12690,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ57">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AR57">
         <v>2.2</v>
@@ -12809,7 +12815,7 @@
         <v>84</v>
       </c>
       <c r="P58" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q58">
         <v>3.3</v>
@@ -13015,7 +13021,7 @@
         <v>84</v>
       </c>
       <c r="P59" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q59">
         <v>5.5</v>
@@ -13221,7 +13227,7 @@
         <v>122</v>
       </c>
       <c r="P60" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q60">
         <v>2.11</v>
@@ -13427,7 +13433,7 @@
         <v>84</v>
       </c>
       <c r="P61" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q61">
         <v>4.5</v>
@@ -13839,7 +13845,7 @@
         <v>84</v>
       </c>
       <c r="P63" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q63">
         <v>2.87</v>
@@ -14045,7 +14051,7 @@
         <v>124</v>
       </c>
       <c r="P64" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q64">
         <v>1.85</v>
@@ -14251,7 +14257,7 @@
         <v>125</v>
       </c>
       <c r="P65" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q65">
         <v>4.28</v>
@@ -14457,7 +14463,7 @@
         <v>126</v>
       </c>
       <c r="P66" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q66">
         <v>2.19</v>
@@ -14744,7 +14750,7 @@
         <v>1</v>
       </c>
       <c r="AQ67">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AR67">
         <v>1.26</v>
@@ -14869,7 +14875,7 @@
         <v>128</v>
       </c>
       <c r="P68" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q68">
         <v>3.3</v>
@@ -15075,7 +15081,7 @@
         <v>129</v>
       </c>
       <c r="P69" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q69">
         <v>2.03</v>
@@ -15359,7 +15365,7 @@
         <v>1.4</v>
       </c>
       <c r="AP70">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ70">
         <v>1.13</v>
@@ -15693,7 +15699,7 @@
         <v>131</v>
       </c>
       <c r="P72" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q72">
         <v>4.6</v>
@@ -16311,7 +16317,7 @@
         <v>84</v>
       </c>
       <c r="P75" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q75">
         <v>4</v>
@@ -16517,7 +16523,7 @@
         <v>134</v>
       </c>
       <c r="P76" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q76">
         <v>3.28</v>
@@ -16723,7 +16729,7 @@
         <v>135</v>
       </c>
       <c r="P77" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q77">
         <v>3.6</v>
@@ -16929,7 +16935,7 @@
         <v>136</v>
       </c>
       <c r="P78" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q78">
         <v>2.17</v>
@@ -17341,7 +17347,7 @@
         <v>137</v>
       </c>
       <c r="P80" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q80">
         <v>1.52</v>
@@ -17547,7 +17553,7 @@
         <v>138</v>
       </c>
       <c r="P81" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q81">
         <v>2.38</v>
@@ -17625,7 +17631,7 @@
         <v>0.6</v>
       </c>
       <c r="AP81">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ81">
         <v>0.86</v>
@@ -17753,7 +17759,7 @@
         <v>139</v>
       </c>
       <c r="P82" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q82">
         <v>1.68</v>
@@ -17959,7 +17965,7 @@
         <v>140</v>
       </c>
       <c r="P83" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q83">
         <v>3.6</v>
@@ -18040,7 +18046,7 @@
         <v>1</v>
       </c>
       <c r="AQ83">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AR83">
         <v>1.4</v>
@@ -18165,7 +18171,7 @@
         <v>141</v>
       </c>
       <c r="P84" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q84">
         <v>3.27</v>
@@ -18371,7 +18377,7 @@
         <v>84</v>
       </c>
       <c r="P85" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q85">
         <v>3.9</v>
@@ -18449,7 +18455,7 @@
         <v>1.43</v>
       </c>
       <c r="AP85">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ85">
         <v>1.63</v>
@@ -18577,7 +18583,7 @@
         <v>142</v>
       </c>
       <c r="P86" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q86">
         <v>2.53</v>
@@ -19607,7 +19613,7 @@
         <v>145</v>
       </c>
       <c r="P91" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q91">
         <v>2.38</v>
@@ -19813,7 +19819,7 @@
         <v>146</v>
       </c>
       <c r="P92" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q92">
         <v>1.93</v>
@@ -20019,7 +20025,7 @@
         <v>147</v>
       </c>
       <c r="P93" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q93">
         <v>7</v>
@@ -20176,6 +20182,212 @@
       </c>
       <c r="BP93">
         <v>1.58</v>
+      </c>
+    </row>
+    <row r="94" spans="1:68">
+      <c r="A94" s="1">
+        <v>93</v>
+      </c>
+      <c r="B94">
+        <v>7811584</v>
+      </c>
+      <c r="C94" t="s">
+        <v>68</v>
+      </c>
+      <c r="D94" t="s">
+        <v>69</v>
+      </c>
+      <c r="E94" s="2">
+        <v>45857.45833333334</v>
+      </c>
+      <c r="F94">
+        <v>0</v>
+      </c>
+      <c r="G94" t="s">
+        <v>74</v>
+      </c>
+      <c r="H94" t="s">
+        <v>77</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>0</v>
+      </c>
+      <c r="K94">
+        <v>0</v>
+      </c>
+      <c r="L94">
+        <v>1</v>
+      </c>
+      <c r="M94">
+        <v>1</v>
+      </c>
+      <c r="N94">
+        <v>2</v>
+      </c>
+      <c r="O94" t="s">
+        <v>148</v>
+      </c>
+      <c r="P94" t="s">
+        <v>215</v>
+      </c>
+      <c r="Q94">
+        <v>3.37</v>
+      </c>
+      <c r="R94">
+        <v>2.24</v>
+      </c>
+      <c r="S94">
+        <v>2.7</v>
+      </c>
+      <c r="T94">
+        <v>1.33</v>
+      </c>
+      <c r="U94">
+        <v>3</v>
+      </c>
+      <c r="V94">
+        <v>2.4</v>
+      </c>
+      <c r="W94">
+        <v>1.5</v>
+      </c>
+      <c r="X94">
+        <v>5.5</v>
+      </c>
+      <c r="Y94">
+        <v>1.11</v>
+      </c>
+      <c r="Z94">
+        <v>3</v>
+      </c>
+      <c r="AA94">
+        <v>3.55</v>
+      </c>
+      <c r="AB94">
+        <v>2.25</v>
+      </c>
+      <c r="AC94">
+        <v>1.04</v>
+      </c>
+      <c r="AD94">
+        <v>8.5</v>
+      </c>
+      <c r="AE94">
+        <v>1.22</v>
+      </c>
+      <c r="AF94">
+        <v>3.8</v>
+      </c>
+      <c r="AG94">
+        <v>1.76</v>
+      </c>
+      <c r="AH94">
+        <v>2</v>
+      </c>
+      <c r="AI94">
+        <v>1.62</v>
+      </c>
+      <c r="AJ94">
+        <v>2.2</v>
+      </c>
+      <c r="AK94">
+        <v>1.29</v>
+      </c>
+      <c r="AL94">
+        <v>1.3</v>
+      </c>
+      <c r="AM94">
+        <v>1.4</v>
+      </c>
+      <c r="AN94">
+        <v>1.14</v>
+      </c>
+      <c r="AO94">
+        <v>1.29</v>
+      </c>
+      <c r="AP94">
+        <v>1.13</v>
+      </c>
+      <c r="AQ94">
+        <v>1.25</v>
+      </c>
+      <c r="AR94">
+        <v>1.68</v>
+      </c>
+      <c r="AS94">
+        <v>1.58</v>
+      </c>
+      <c r="AT94">
+        <v>3.26</v>
+      </c>
+      <c r="AU94">
+        <v>4</v>
+      </c>
+      <c r="AV94">
+        <v>3</v>
+      </c>
+      <c r="AW94">
+        <v>10</v>
+      </c>
+      <c r="AX94">
+        <v>5</v>
+      </c>
+      <c r="AY94">
+        <v>14</v>
+      </c>
+      <c r="AZ94">
+        <v>8</v>
+      </c>
+      <c r="BA94">
+        <v>4</v>
+      </c>
+      <c r="BB94">
+        <v>1</v>
+      </c>
+      <c r="BC94">
+        <v>5</v>
+      </c>
+      <c r="BD94">
+        <v>2.61</v>
+      </c>
+      <c r="BE94">
+        <v>8.4</v>
+      </c>
+      <c r="BF94">
+        <v>1.7</v>
+      </c>
+      <c r="BG94">
+        <v>1.12</v>
+      </c>
+      <c r="BH94">
+        <v>3.65</v>
+      </c>
+      <c r="BI94">
+        <v>1.31</v>
+      </c>
+      <c r="BJ94">
+        <v>3.05</v>
+      </c>
+      <c r="BK94">
+        <v>1.65</v>
+      </c>
+      <c r="BL94">
+        <v>2.34</v>
+      </c>
+      <c r="BM94">
+        <v>1.87</v>
+      </c>
+      <c r="BN94">
+        <v>1.83</v>
+      </c>
+      <c r="BO94">
+        <v>2.32</v>
+      </c>
+      <c r="BP94">
+        <v>1.56</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
@@ -20118,22 +20118,22 @@
         <v>3.6</v>
       </c>
       <c r="AU93">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV93">
+        <v>7</v>
+      </c>
+      <c r="AW93">
+        <v>3</v>
+      </c>
+      <c r="AX93">
         <v>6</v>
       </c>
-      <c r="AW93">
-        <v>9</v>
-      </c>
-      <c r="AX93">
-        <v>14</v>
-      </c>
       <c r="AY93">
+        <v>6</v>
+      </c>
+      <c r="AZ93">
         <v>13</v>
-      </c>
-      <c r="AZ93">
-        <v>20</v>
       </c>
       <c r="BA93">
         <v>4</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="220">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -463,6 +463,12 @@
     <t>['89']</t>
   </si>
   <si>
+    <t>['60', '63', '85']</t>
+  </si>
+  <si>
+    <t>['24', '32', '56']</t>
+  </si>
+  <si>
     <t>['4', '14']</t>
   </si>
   <si>
@@ -662,6 +668,12 @@
   </si>
   <si>
     <t>['80']</t>
+  </si>
+  <si>
+    <t>['58']</t>
+  </si>
+  <si>
+    <t>['90']</t>
   </si>
 </sst>
 </file>
@@ -1023,7 +1035,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP94"/>
+  <dimension ref="A1:BP97"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1279,7 +1291,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="Q2">
         <v>3.2</v>
@@ -1485,7 +1497,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="Q3">
         <v>3.25</v>
@@ -1691,7 +1703,7 @@
         <v>84</v>
       </c>
       <c r="P4" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="Q4">
         <v>3.1</v>
@@ -2103,7 +2115,7 @@
         <v>85</v>
       </c>
       <c r="P6" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="Q6">
         <v>2.3</v>
@@ -2184,7 +2196,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ6">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2309,7 +2321,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="Q7">
         <v>3.4</v>
@@ -2390,7 +2402,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ7">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2515,7 +2527,7 @@
         <v>87</v>
       </c>
       <c r="P8" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="Q8">
         <v>4.1</v>
@@ -2799,7 +2811,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ9">
         <v>1.63</v>
@@ -2927,7 +2939,7 @@
         <v>89</v>
       </c>
       <c r="P10" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="Q10">
         <v>1.7</v>
@@ -3133,7 +3145,7 @@
         <v>84</v>
       </c>
       <c r="P11" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="Q11">
         <v>2.25</v>
@@ -3420,7 +3432,7 @@
         <v>2</v>
       </c>
       <c r="AQ12">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR12">
         <v>1.71</v>
@@ -3626,7 +3638,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ13">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3751,7 +3763,7 @@
         <v>84</v>
       </c>
       <c r="P14" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="Q14">
         <v>3.1</v>
@@ -3957,7 +3969,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Q15">
         <v>3.2</v>
@@ -4038,7 +4050,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ15">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AR15">
         <v>1.98</v>
@@ -4163,7 +4175,7 @@
         <v>93</v>
       </c>
       <c r="P16" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q16">
         <v>4.79</v>
@@ -4369,7 +4381,7 @@
         <v>84</v>
       </c>
       <c r="P17" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="Q17">
         <v>4.17</v>
@@ -4450,7 +4462,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ17">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR17">
         <v>1.59</v>
@@ -4781,7 +4793,7 @@
         <v>84</v>
       </c>
       <c r="P19" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="Q19">
         <v>1.72</v>
@@ -4859,10 +4871,10 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ19">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5193,7 +5205,7 @@
         <v>96</v>
       </c>
       <c r="P21" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Q21">
         <v>2.2</v>
@@ -5271,10 +5283,10 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ21">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AR21">
         <v>2.05</v>
@@ -5399,7 +5411,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Q22">
         <v>4.75</v>
@@ -5605,7 +5617,7 @@
         <v>98</v>
       </c>
       <c r="P23" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q23">
         <v>2.3</v>
@@ -5683,7 +5695,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AQ23">
         <v>0.43</v>
@@ -5811,7 +5823,7 @@
         <v>99</v>
       </c>
       <c r="P24" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q24">
         <v>2.25</v>
@@ -5889,7 +5901,7 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ24">
         <v>1.25</v>
@@ -6017,7 +6029,7 @@
         <v>100</v>
       </c>
       <c r="P25" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q25">
         <v>3.75</v>
@@ -6223,7 +6235,7 @@
         <v>101</v>
       </c>
       <c r="P26" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q26">
         <v>6.5</v>
@@ -6304,7 +6316,7 @@
         <v>1</v>
       </c>
       <c r="AQ26">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR26">
         <v>1.17</v>
@@ -6429,7 +6441,7 @@
         <v>102</v>
       </c>
       <c r="P27" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q27">
         <v>1.85</v>
@@ -6507,7 +6519,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ27">
         <v>0.86</v>
@@ -6635,7 +6647,7 @@
         <v>84</v>
       </c>
       <c r="P28" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q28">
         <v>2.5</v>
@@ -6841,7 +6853,7 @@
         <v>103</v>
       </c>
       <c r="P29" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q29">
         <v>2.7</v>
@@ -6922,7 +6934,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ29">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AR29">
         <v>1.44</v>
@@ -7128,7 +7140,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ30">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR30">
         <v>1.89</v>
@@ -7665,7 +7677,7 @@
         <v>106</v>
       </c>
       <c r="P33" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q33">
         <v>2.93</v>
@@ -7871,7 +7883,7 @@
         <v>107</v>
       </c>
       <c r="P34" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q34">
         <v>2.26</v>
@@ -8283,7 +8295,7 @@
         <v>109</v>
       </c>
       <c r="P36" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q36">
         <v>6.4</v>
@@ -8489,7 +8501,7 @@
         <v>110</v>
       </c>
       <c r="P37" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q37">
         <v>3.84</v>
@@ -8570,7 +8582,7 @@
         <v>1</v>
       </c>
       <c r="AQ37">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR37">
         <v>1.04</v>
@@ -8695,7 +8707,7 @@
         <v>84</v>
       </c>
       <c r="P38" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q38">
         <v>5.25</v>
@@ -8773,7 +8785,7 @@
         <v>0.33</v>
       </c>
       <c r="AP38">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AQ38">
         <v>1.63</v>
@@ -8901,7 +8913,7 @@
         <v>111</v>
       </c>
       <c r="P39" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -8979,7 +8991,7 @@
         <v>0.5</v>
       </c>
       <c r="AP39">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ39">
         <v>1.25</v>
@@ -9107,7 +9119,7 @@
         <v>112</v>
       </c>
       <c r="P40" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q40">
         <v>2.85</v>
@@ -9313,7 +9325,7 @@
         <v>113</v>
       </c>
       <c r="P41" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q41">
         <v>4.02</v>
@@ -9519,7 +9531,7 @@
         <v>84</v>
       </c>
       <c r="P42" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q42">
         <v>2.1</v>
@@ -9725,7 +9737,7 @@
         <v>114</v>
       </c>
       <c r="P43" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q43">
         <v>2.75</v>
@@ -9806,7 +9818,7 @@
         <v>2</v>
       </c>
       <c r="AQ43">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR43">
         <v>2.09</v>
@@ -9931,7 +9943,7 @@
         <v>115</v>
       </c>
       <c r="P44" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q44">
         <v>1.68</v>
@@ -10009,7 +10021,7 @@
         <v>1.5</v>
       </c>
       <c r="AP44">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ44">
         <v>0.43</v>
@@ -10343,7 +10355,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q46">
         <v>1.91</v>
@@ -10421,7 +10433,7 @@
         <v>1.75</v>
       </c>
       <c r="AP46">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ46">
         <v>1.57</v>
@@ -10961,7 +10973,7 @@
         <v>118</v>
       </c>
       <c r="P49" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q49">
         <v>3.45</v>
@@ -11039,10 +11051,10 @@
         <v>1.5</v>
       </c>
       <c r="AP49">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AQ49">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR49">
         <v>0.93</v>
@@ -11248,7 +11260,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ50">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AR50">
         <v>1.72</v>
@@ -11373,7 +11385,7 @@
         <v>84</v>
       </c>
       <c r="P51" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q51">
         <v>6.5</v>
@@ -11579,7 +11591,7 @@
         <v>84</v>
       </c>
       <c r="P52" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q52">
         <v>2.18</v>
@@ -11785,7 +11797,7 @@
         <v>84</v>
       </c>
       <c r="P53" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q53">
         <v>3.85</v>
@@ -11863,7 +11875,7 @@
         <v>2.33</v>
       </c>
       <c r="AP53">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ53">
         <v>2.25</v>
@@ -11991,7 +12003,7 @@
         <v>119</v>
       </c>
       <c r="P54" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q54">
         <v>2.66</v>
@@ -12197,7 +12209,7 @@
         <v>120</v>
       </c>
       <c r="P55" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q55">
         <v>3</v>
@@ -12403,7 +12415,7 @@
         <v>121</v>
       </c>
       <c r="P56" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q56">
         <v>3.35</v>
@@ -12687,7 +12699,7 @@
         <v>1.75</v>
       </c>
       <c r="AP57">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ57">
         <v>1.25</v>
@@ -12815,7 +12827,7 @@
         <v>84</v>
       </c>
       <c r="P58" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q58">
         <v>3.3</v>
@@ -12896,7 +12908,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ58">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR58">
         <v>1.88</v>
@@ -13021,7 +13033,7 @@
         <v>84</v>
       </c>
       <c r="P59" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q59">
         <v>5.5</v>
@@ -13099,7 +13111,7 @@
         <v>2.5</v>
       </c>
       <c r="AP59">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AQ59">
         <v>2.25</v>
@@ -13227,7 +13239,7 @@
         <v>122</v>
       </c>
       <c r="P60" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q60">
         <v>2.11</v>
@@ -13433,7 +13445,7 @@
         <v>84</v>
       </c>
       <c r="P61" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q61">
         <v>4.5</v>
@@ -13845,7 +13857,7 @@
         <v>84</v>
       </c>
       <c r="P63" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q63">
         <v>2.87</v>
@@ -13926,7 +13938,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ63">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR63">
         <v>2.11</v>
@@ -14051,7 +14063,7 @@
         <v>124</v>
       </c>
       <c r="P64" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q64">
         <v>1.85</v>
@@ -14129,7 +14141,7 @@
         <v>1.4</v>
       </c>
       <c r="AP64">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ64">
         <v>1.11</v>
@@ -14257,7 +14269,7 @@
         <v>125</v>
       </c>
       <c r="P65" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q65">
         <v>4.28</v>
@@ -14463,7 +14475,7 @@
         <v>126</v>
       </c>
       <c r="P66" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q66">
         <v>2.19</v>
@@ -14875,7 +14887,7 @@
         <v>128</v>
       </c>
       <c r="P68" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q68">
         <v>3.3</v>
@@ -14953,10 +14965,10 @@
         <v>0.67</v>
       </c>
       <c r="AP68">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AQ68">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AR68">
         <v>0.97</v>
@@ -15081,7 +15093,7 @@
         <v>129</v>
       </c>
       <c r="P69" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q69">
         <v>2.03</v>
@@ -15159,7 +15171,7 @@
         <v>0.75</v>
       </c>
       <c r="AP69">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ69">
         <v>0.86</v>
@@ -15368,7 +15380,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ70">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR70">
         <v>1.74</v>
@@ -15699,7 +15711,7 @@
         <v>131</v>
       </c>
       <c r="P72" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q72">
         <v>4.6</v>
@@ -16189,7 +16201,7 @@
         <v>1.4</v>
       </c>
       <c r="AP74">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ74">
         <v>1.13</v>
@@ -16317,7 +16329,7 @@
         <v>84</v>
       </c>
       <c r="P75" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q75">
         <v>4</v>
@@ -16398,7 +16410,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ75">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR75">
         <v>1.69</v>
@@ -16523,7 +16535,7 @@
         <v>134</v>
       </c>
       <c r="P76" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q76">
         <v>3.28</v>
@@ -16729,7 +16741,7 @@
         <v>135</v>
       </c>
       <c r="P77" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q77">
         <v>3.6</v>
@@ -16935,7 +16947,7 @@
         <v>136</v>
       </c>
       <c r="P78" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q78">
         <v>2.17</v>
@@ -17016,7 +17028,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ78">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR78">
         <v>1.93</v>
@@ -17347,7 +17359,7 @@
         <v>137</v>
       </c>
       <c r="P80" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q80">
         <v>1.52</v>
@@ -17553,7 +17565,7 @@
         <v>138</v>
       </c>
       <c r="P81" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q81">
         <v>2.38</v>
@@ -17759,7 +17771,7 @@
         <v>139</v>
       </c>
       <c r="P82" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q82">
         <v>1.68</v>
@@ -17837,7 +17849,7 @@
         <v>1</v>
       </c>
       <c r="AP82">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ82">
         <v>1.11</v>
@@ -17965,7 +17977,7 @@
         <v>140</v>
       </c>
       <c r="P83" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q83">
         <v>3.6</v>
@@ -18171,7 +18183,7 @@
         <v>141</v>
       </c>
       <c r="P84" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q84">
         <v>3.27</v>
@@ -18249,10 +18261,10 @@
         <v>1.71</v>
       </c>
       <c r="AP84">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ84">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR84">
         <v>1.81</v>
@@ -18377,7 +18389,7 @@
         <v>84</v>
       </c>
       <c r="P85" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q85">
         <v>3.9</v>
@@ -18583,7 +18595,7 @@
         <v>142</v>
       </c>
       <c r="P86" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q86">
         <v>2.53</v>
@@ -18661,7 +18673,7 @@
         <v>1.14</v>
       </c>
       <c r="AP86">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AQ86">
         <v>1.13</v>
@@ -19076,7 +19088,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ88">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR88">
         <v>1.62</v>
@@ -19613,7 +19625,7 @@
         <v>145</v>
       </c>
       <c r="P91" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q91">
         <v>2.38</v>
@@ -19819,7 +19831,7 @@
         <v>146</v>
       </c>
       <c r="P92" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q92">
         <v>1.93</v>
@@ -20025,7 +20037,7 @@
         <v>147</v>
       </c>
       <c r="P93" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q93">
         <v>7</v>
@@ -20231,7 +20243,7 @@
         <v>148</v>
       </c>
       <c r="P94" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q94">
         <v>3.37</v>
@@ -20388,6 +20400,624 @@
       </c>
       <c r="BP94">
         <v>1.56</v>
+      </c>
+    </row>
+    <row r="95" spans="1:68">
+      <c r="A95" s="1">
+        <v>94</v>
+      </c>
+      <c r="B95">
+        <v>7811586</v>
+      </c>
+      <c r="C95" t="s">
+        <v>68</v>
+      </c>
+      <c r="D95" t="s">
+        <v>69</v>
+      </c>
+      <c r="E95" s="2">
+        <v>45858.41666666666</v>
+      </c>
+      <c r="F95">
+        <v>0</v>
+      </c>
+      <c r="G95" t="s">
+        <v>76</v>
+      </c>
+      <c r="H95" t="s">
+        <v>81</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>1</v>
+      </c>
+      <c r="K95">
+        <v>1</v>
+      </c>
+      <c r="L95">
+        <v>3</v>
+      </c>
+      <c r="M95">
+        <v>1</v>
+      </c>
+      <c r="N95">
+        <v>4</v>
+      </c>
+      <c r="O95" t="s">
+        <v>149</v>
+      </c>
+      <c r="P95" t="s">
+        <v>188</v>
+      </c>
+      <c r="Q95">
+        <v>2.23</v>
+      </c>
+      <c r="R95">
+        <v>2.4</v>
+      </c>
+      <c r="S95">
+        <v>4.33</v>
+      </c>
+      <c r="T95">
+        <v>1.25</v>
+      </c>
+      <c r="U95">
+        <v>3.6</v>
+      </c>
+      <c r="V95">
+        <v>2.2</v>
+      </c>
+      <c r="W95">
+        <v>1.6</v>
+      </c>
+      <c r="X95">
+        <v>4.4</v>
+      </c>
+      <c r="Y95">
+        <v>1.15</v>
+      </c>
+      <c r="Z95">
+        <v>1.75</v>
+      </c>
+      <c r="AA95">
+        <v>4.1</v>
+      </c>
+      <c r="AB95">
+        <v>4.2</v>
+      </c>
+      <c r="AC95">
+        <v>1.02</v>
+      </c>
+      <c r="AD95">
+        <v>15</v>
+      </c>
+      <c r="AE95">
+        <v>1.17</v>
+      </c>
+      <c r="AF95">
+        <v>4.75</v>
+      </c>
+      <c r="AG95">
+        <v>1.5</v>
+      </c>
+      <c r="AH95">
+        <v>2.63</v>
+      </c>
+      <c r="AI95">
+        <v>1.53</v>
+      </c>
+      <c r="AJ95">
+        <v>2.6</v>
+      </c>
+      <c r="AK95">
+        <v>1.22</v>
+      </c>
+      <c r="AL95">
+        <v>1.22</v>
+      </c>
+      <c r="AM95">
+        <v>2.18</v>
+      </c>
+      <c r="AN95">
+        <v>1.75</v>
+      </c>
+      <c r="AO95">
+        <v>1.13</v>
+      </c>
+      <c r="AP95">
+        <v>1.89</v>
+      </c>
+      <c r="AQ95">
+        <v>1</v>
+      </c>
+      <c r="AR95">
+        <v>1.69</v>
+      </c>
+      <c r="AS95">
+        <v>1.31</v>
+      </c>
+      <c r="AT95">
+        <v>3</v>
+      </c>
+      <c r="AU95">
+        <v>7</v>
+      </c>
+      <c r="AV95">
+        <v>3</v>
+      </c>
+      <c r="AW95">
+        <v>8</v>
+      </c>
+      <c r="AX95">
+        <v>5</v>
+      </c>
+      <c r="AY95">
+        <v>15</v>
+      </c>
+      <c r="AZ95">
+        <v>8</v>
+      </c>
+      <c r="BA95">
+        <v>9</v>
+      </c>
+      <c r="BB95">
+        <v>1</v>
+      </c>
+      <c r="BC95">
+        <v>10</v>
+      </c>
+      <c r="BD95">
+        <v>1.44</v>
+      </c>
+      <c r="BE95">
+        <v>9</v>
+      </c>
+      <c r="BF95">
+        <v>3</v>
+      </c>
+      <c r="BG95">
+        <v>1.09</v>
+      </c>
+      <c r="BH95">
+        <v>5.3</v>
+      </c>
+      <c r="BI95">
+        <v>1.22</v>
+      </c>
+      <c r="BJ95">
+        <v>3.5</v>
+      </c>
+      <c r="BK95">
+        <v>1.42</v>
+      </c>
+      <c r="BL95">
+        <v>2.57</v>
+      </c>
+      <c r="BM95">
+        <v>1.73</v>
+      </c>
+      <c r="BN95">
+        <v>2.1</v>
+      </c>
+      <c r="BO95">
+        <v>2.14</v>
+      </c>
+      <c r="BP95">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="96" spans="1:68">
+      <c r="A96" s="1">
+        <v>95</v>
+      </c>
+      <c r="B96">
+        <v>7811585</v>
+      </c>
+      <c r="C96" t="s">
+        <v>68</v>
+      </c>
+      <c r="D96" t="s">
+        <v>69</v>
+      </c>
+      <c r="E96" s="2">
+        <v>45858.52083333334</v>
+      </c>
+      <c r="F96">
+        <v>0</v>
+      </c>
+      <c r="G96" t="s">
+        <v>80</v>
+      </c>
+      <c r="H96" t="s">
+        <v>70</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>0</v>
+      </c>
+      <c r="K96">
+        <v>0</v>
+      </c>
+      <c r="L96">
+        <v>0</v>
+      </c>
+      <c r="M96">
+        <v>1</v>
+      </c>
+      <c r="N96">
+        <v>1</v>
+      </c>
+      <c r="O96" t="s">
+        <v>84</v>
+      </c>
+      <c r="P96" t="s">
+        <v>218</v>
+      </c>
+      <c r="Q96">
+        <v>4.1</v>
+      </c>
+      <c r="R96">
+        <v>2.5</v>
+      </c>
+      <c r="S96">
+        <v>1.97</v>
+      </c>
+      <c r="T96">
+        <v>1.23</v>
+      </c>
+      <c r="U96">
+        <v>3.3</v>
+      </c>
+      <c r="V96">
+        <v>2.3</v>
+      </c>
+      <c r="W96">
+        <v>1.55</v>
+      </c>
+      <c r="X96">
+        <v>5.2</v>
+      </c>
+      <c r="Y96">
+        <v>1.09</v>
+      </c>
+      <c r="Z96">
+        <v>5.7</v>
+      </c>
+      <c r="AA96">
+        <v>4.5</v>
+      </c>
+      <c r="AB96">
+        <v>1.53</v>
+      </c>
+      <c r="AC96">
+        <v>1.03</v>
+      </c>
+      <c r="AD96">
+        <v>9.5</v>
+      </c>
+      <c r="AE96">
+        <v>1.17</v>
+      </c>
+      <c r="AF96">
+        <v>5</v>
+      </c>
+      <c r="AG96">
+        <v>1.62</v>
+      </c>
+      <c r="AH96">
+        <v>2.4</v>
+      </c>
+      <c r="AI96">
+        <v>1.65</v>
+      </c>
+      <c r="AJ96">
+        <v>2.1</v>
+      </c>
+      <c r="AK96">
+        <v>1.22</v>
+      </c>
+      <c r="AL96">
+        <v>1.22</v>
+      </c>
+      <c r="AM96">
+        <v>1.15</v>
+      </c>
+      <c r="AN96">
+        <v>0.83</v>
+      </c>
+      <c r="AO96">
+        <v>1.63</v>
+      </c>
+      <c r="AP96">
+        <v>0.71</v>
+      </c>
+      <c r="AQ96">
+        <v>1.78</v>
+      </c>
+      <c r="AR96">
+        <v>1.29</v>
+      </c>
+      <c r="AS96">
+        <v>2.17</v>
+      </c>
+      <c r="AT96">
+        <v>3.46</v>
+      </c>
+      <c r="AU96">
+        <v>2</v>
+      </c>
+      <c r="AV96">
+        <v>11</v>
+      </c>
+      <c r="AW96">
+        <v>1</v>
+      </c>
+      <c r="AX96">
+        <v>10</v>
+      </c>
+      <c r="AY96">
+        <v>3</v>
+      </c>
+      <c r="AZ96">
+        <v>21</v>
+      </c>
+      <c r="BA96">
+        <v>1</v>
+      </c>
+      <c r="BB96">
+        <v>17</v>
+      </c>
+      <c r="BC96">
+        <v>18</v>
+      </c>
+      <c r="BD96">
+        <v>3.75</v>
+      </c>
+      <c r="BE96">
+        <v>10</v>
+      </c>
+      <c r="BF96">
+        <v>1.36</v>
+      </c>
+      <c r="BG96">
+        <v>1.25</v>
+      </c>
+      <c r="BH96">
+        <v>3.45</v>
+      </c>
+      <c r="BI96">
+        <v>1.36</v>
+      </c>
+      <c r="BJ96">
+        <v>2.8</v>
+      </c>
+      <c r="BK96">
+        <v>1.64</v>
+      </c>
+      <c r="BL96">
+        <v>2.12</v>
+      </c>
+      <c r="BM96">
+        <v>2.01</v>
+      </c>
+      <c r="BN96">
+        <v>1.75</v>
+      </c>
+      <c r="BO96">
+        <v>2.62</v>
+      </c>
+      <c r="BP96">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="97" spans="1:68">
+      <c r="A97" s="1">
+        <v>96</v>
+      </c>
+      <c r="B97">
+        <v>7811587</v>
+      </c>
+      <c r="C97" t="s">
+        <v>68</v>
+      </c>
+      <c r="D97" t="s">
+        <v>69</v>
+      </c>
+      <c r="E97" s="2">
+        <v>45858.52083333334</v>
+      </c>
+      <c r="F97">
+        <v>0</v>
+      </c>
+      <c r="G97" t="s">
+        <v>78</v>
+      </c>
+      <c r="H97" t="s">
+        <v>79</v>
+      </c>
+      <c r="I97">
+        <v>2</v>
+      </c>
+      <c r="J97">
+        <v>0</v>
+      </c>
+      <c r="K97">
+        <v>2</v>
+      </c>
+      <c r="L97">
+        <v>3</v>
+      </c>
+      <c r="M97">
+        <v>1</v>
+      </c>
+      <c r="N97">
+        <v>4</v>
+      </c>
+      <c r="O97" t="s">
+        <v>150</v>
+      </c>
+      <c r="P97" t="s">
+        <v>219</v>
+      </c>
+      <c r="Q97">
+        <v>2.05</v>
+      </c>
+      <c r="R97">
+        <v>2.55</v>
+      </c>
+      <c r="S97">
+        <v>5.05</v>
+      </c>
+      <c r="T97">
+        <v>1.29</v>
+      </c>
+      <c r="U97">
+        <v>3.6</v>
+      </c>
+      <c r="V97">
+        <v>2.2</v>
+      </c>
+      <c r="W97">
+        <v>1.55</v>
+      </c>
+      <c r="X97">
+        <v>5</v>
+      </c>
+      <c r="Y97">
+        <v>1.13</v>
+      </c>
+      <c r="Z97">
+        <v>1.59</v>
+      </c>
+      <c r="AA97">
+        <v>4.25</v>
+      </c>
+      <c r="AB97">
+        <v>5.61</v>
+      </c>
+      <c r="AC97">
+        <v>1.01</v>
+      </c>
+      <c r="AD97">
+        <v>11</v>
+      </c>
+      <c r="AE97">
+        <v>1.12</v>
+      </c>
+      <c r="AF97">
+        <v>4.33</v>
+      </c>
+      <c r="AG97">
+        <v>1.65</v>
+      </c>
+      <c r="AH97">
+        <v>2.15</v>
+      </c>
+      <c r="AI97">
+        <v>1.67</v>
+      </c>
+      <c r="AJ97">
+        <v>2.1</v>
+      </c>
+      <c r="AK97">
+        <v>1.13</v>
+      </c>
+      <c r="AL97">
+        <v>1.16</v>
+      </c>
+      <c r="AM97">
+        <v>2.38</v>
+      </c>
+      <c r="AN97">
+        <v>1.86</v>
+      </c>
+      <c r="AO97">
+        <v>0.57</v>
+      </c>
+      <c r="AP97">
+        <v>2</v>
+      </c>
+      <c r="AQ97">
+        <v>0.5</v>
+      </c>
+      <c r="AR97">
+        <v>2.02</v>
+      </c>
+      <c r="AS97">
+        <v>1.16</v>
+      </c>
+      <c r="AT97">
+        <v>3.18</v>
+      </c>
+      <c r="AU97">
+        <v>8</v>
+      </c>
+      <c r="AV97">
+        <v>6</v>
+      </c>
+      <c r="AW97">
+        <v>5</v>
+      </c>
+      <c r="AX97">
+        <v>7</v>
+      </c>
+      <c r="AY97">
+        <v>13</v>
+      </c>
+      <c r="AZ97">
+        <v>13</v>
+      </c>
+      <c r="BA97">
+        <v>4</v>
+      </c>
+      <c r="BB97">
+        <v>8</v>
+      </c>
+      <c r="BC97">
+        <v>12</v>
+      </c>
+      <c r="BD97">
+        <v>1.3</v>
+      </c>
+      <c r="BE97">
+        <v>10</v>
+      </c>
+      <c r="BF97">
+        <v>4.76</v>
+      </c>
+      <c r="BG97">
+        <v>1.16</v>
+      </c>
+      <c r="BH97">
+        <v>4.35</v>
+      </c>
+      <c r="BI97">
+        <v>1.25</v>
+      </c>
+      <c r="BJ97">
+        <v>3.1</v>
+      </c>
+      <c r="BK97">
+        <v>1.52</v>
+      </c>
+      <c r="BL97">
+        <v>2.42</v>
+      </c>
+      <c r="BM97">
+        <v>1.88</v>
+      </c>
+      <c r="BN97">
+        <v>1.93</v>
+      </c>
+      <c r="BO97">
+        <v>2.35</v>
+      </c>
+      <c r="BP97">
+        <v>1.49</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
@@ -286,13 +286,13 @@
     <t>['15', '23']</t>
   </si>
   <si>
-    <t>['37', '89', '88']</t>
+    <t>['89', '90+2', '37']</t>
   </si>
   <si>
     <t>['23']</t>
   </si>
   <si>
-    <t>['56', '77']</t>
+    <t>['77', '56']</t>
   </si>
   <si>
     <t>['45']</t>
@@ -301,7 +301,7 @@
     <t>['84']</t>
   </si>
   <si>
-    <t>['37', '43', '80', '83']</t>
+    <t>['43', '80', '37', '83']</t>
   </si>
   <si>
     <t>['42', '52', '65']</t>
@@ -316,13 +316,16 @@
     <t>['4', '45+1', '88']</t>
   </si>
   <si>
-    <t>['-1']</t>
-  </si>
-  <si>
-    <t>['17', '29', '61']</t>
-  </si>
-  <si>
-    <t>['22', '76']</t>
+    <t>['28']</t>
+  </si>
+  <si>
+    <t>['17', '28', '61']</t>
+  </si>
+  <si>
+    <t>['21', '76']</t>
+  </si>
+  <si>
+    <t>['90+2']</t>
   </si>
   <si>
     <t>['90+3']</t>
@@ -331,7 +334,7 @@
     <t>['45+1']</t>
   </si>
   <si>
-    <t>['3', '6']</t>
+    <t>['6', '3']</t>
   </si>
   <si>
     <t>['73']</t>
@@ -343,10 +346,10 @@
     <t>['25', '44', '57']</t>
   </si>
   <si>
-    <t>['12', '71']</t>
-  </si>
-  <si>
-    <t>['47', '50']</t>
+    <t>['11', '71']</t>
+  </si>
+  <si>
+    <t>['50', '47']</t>
   </si>
   <si>
     <t>['23', '50']</t>
@@ -358,22 +361,22 @@
     <t>['75']</t>
   </si>
   <si>
-    <t>['6', '81', '89']</t>
-  </si>
-  <si>
-    <t>['7', '66', '70', '90+1']</t>
+    <t>['6', '89', '81']</t>
+  </si>
+  <si>
+    <t>['7', '70', '66', '90+1']</t>
   </si>
   <si>
     <t>['8', '15', '35', '56']</t>
   </si>
   <si>
-    <t>['56', '70', '89']</t>
+    <t>['70', '56', '89']</t>
   </si>
   <si>
     <t>['1']</t>
   </si>
   <si>
-    <t>['49', '68']</t>
+    <t>['68', '49']</t>
   </si>
   <si>
     <t>['45+1', '76']</t>
@@ -412,7 +415,7 @@
     <t>['12', '26']</t>
   </si>
   <si>
-    <t>['2', '8', '71']</t>
+    <t>['3', '8', '71']</t>
   </si>
   <si>
     <t>['18', '6', '16', '64']</t>
@@ -454,7 +457,7 @@
     <t>['75', '58', '55']</t>
   </si>
   <si>
-    <t>['22', '84', '89']</t>
+    <t>['23', '85', '89']</t>
   </si>
   <si>
     <t>['28', '33']</t>
@@ -490,10 +493,7 @@
     <t>['81']</t>
   </si>
   <si>
-    <t>['28']</t>
-  </si>
-  <si>
-    <t>['31', '57']</t>
+    <t>['57', '31']</t>
   </si>
   <si>
     <t>['19']</t>
@@ -502,7 +502,7 @@
     <t>['57', '84']</t>
   </si>
   <si>
-    <t>['27', '55', '58', '64', '72']</t>
+    <t>['64', '27', '55', '72', '57']</t>
   </si>
   <si>
     <t>['59']</t>
@@ -511,19 +511,19 @@
     <t>['38']</t>
   </si>
   <si>
-    <t>['28', '36', '81', '88']</t>
-  </si>
-  <si>
-    <t>['33', '63', '74']</t>
+    <t>['81', '88', '36', '28']</t>
+  </si>
+  <si>
+    <t>['32', '63', '74']</t>
   </si>
   <si>
     <t>['62']</t>
   </si>
   <si>
-    <t>['-1', '-1']</t>
-  </si>
-  <si>
-    <t>['54', '60']</t>
+    <t>['47', '77']</t>
+  </si>
+  <si>
+    <t>['59', '54']</t>
   </si>
   <si>
     <t>['90', '90+6']</t>
@@ -538,16 +538,16 @@
     <t>['24']</t>
   </si>
   <si>
-    <t>['41', '87']</t>
-  </si>
-  <si>
-    <t>['70', '83']</t>
+    <t>['87', '41']</t>
+  </si>
+  <si>
+    <t>['83', '70']</t>
   </si>
   <si>
     <t>['58', '65', '87']</t>
   </si>
   <si>
-    <t>['65', '72', '82']</t>
+    <t>['72', '82', '65']</t>
   </si>
   <si>
     <t>['5', '63', '90+1']</t>
@@ -556,7 +556,7 @@
     <t>['25', '71']</t>
   </si>
   <si>
-    <t>['16', '89', '90+3']</t>
+    <t>['16', '90+3', '89']</t>
   </si>
   <si>
     <t>['56']</t>
@@ -574,7 +574,7 @@
     <t>['42']</t>
   </si>
   <si>
-    <t>['31', '53', '76', '87']</t>
+    <t>['87', '31', '53', '76']</t>
   </si>
   <si>
     <t>['26', '65']</t>
@@ -592,7 +592,7 @@
     <t>['62', '88']</t>
   </si>
   <si>
-    <t>['87', '90+4']</t>
+    <t>['90+4', '87']</t>
   </si>
   <si>
     <t>['61']</t>
@@ -610,7 +610,7 @@
     <t>['87']</t>
   </si>
   <si>
-    <t>['6', '54', '57', '66', '80']</t>
+    <t>['6', '54', '57', '80', '66']</t>
   </si>
   <si>
     <t>['45+2', '69', '90']</t>
@@ -661,7 +661,7 @@
     <t>['43', '89']</t>
   </si>
   <si>
-    <t>['47', '74']</t>
+    <t>['48', '75']</t>
   </si>
   <si>
     <t>['7', '31']</t>
@@ -1291,7 +1291,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q2">
         <v>3.2</v>
@@ -1497,7 +1497,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q3">
         <v>3.25</v>
@@ -1703,7 +1703,7 @@
         <v>84</v>
       </c>
       <c r="P4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q4">
         <v>3.1</v>
@@ -1909,7 +1909,7 @@
         <v>84</v>
       </c>
       <c r="P5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Q5">
         <v>4</v>
@@ -2115,7 +2115,7 @@
         <v>85</v>
       </c>
       <c r="P6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q6">
         <v>2.3</v>
@@ -2321,7 +2321,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q7">
         <v>3.4</v>
@@ -2527,7 +2527,7 @@
         <v>87</v>
       </c>
       <c r="P8" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q8">
         <v>4.1</v>
@@ -2939,7 +2939,7 @@
         <v>89</v>
       </c>
       <c r="P10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q10">
         <v>1.7</v>
@@ -3032,22 +3032,22 @@
         <v>2.65</v>
       </c>
       <c r="AU10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AX10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AY10">
+        <v>9</v>
+      </c>
+      <c r="AZ10">
         <v>8</v>
-      </c>
-      <c r="AZ10">
-        <v>5</v>
       </c>
       <c r="BA10">
         <v>4</v>
@@ -3145,7 +3145,7 @@
         <v>84</v>
       </c>
       <c r="P11" t="s">
-        <v>158</v>
+        <v>100</v>
       </c>
       <c r="Q11">
         <v>2.25</v>
@@ -3238,22 +3238,22 @@
         <v>1.83</v>
       </c>
       <c r="AU11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV11">
         <v>5</v>
       </c>
       <c r="AW11">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AX11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY11">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AZ11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA11">
         <v>7</v>
@@ -3444,22 +3444,22 @@
         <v>3.53</v>
       </c>
       <c r="AU12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV12">
         <v>3</v>
       </c>
       <c r="AW12">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="AX12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY12">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="AZ12">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BA12">
         <v>12</v>
@@ -3650,22 +3650,22 @@
         <v>1.14</v>
       </c>
       <c r="AU13">
+        <v>5</v>
+      </c>
+      <c r="AV13">
         <v>6</v>
       </c>
-      <c r="AV13">
-        <v>5</v>
-      </c>
       <c r="AW13">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AX13">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AY13">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AZ13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA13">
         <v>1</v>
@@ -3859,28 +3859,28 @@
         <v>5</v>
       </c>
       <c r="AV14">
+        <v>7</v>
+      </c>
+      <c r="AW14">
+        <v>4</v>
+      </c>
+      <c r="AX14">
+        <v>1</v>
+      </c>
+      <c r="AY14">
+        <v>9</v>
+      </c>
+      <c r="AZ14">
         <v>8</v>
-      </c>
-      <c r="AW14">
-        <v>10</v>
-      </c>
-      <c r="AX14">
-        <v>3</v>
-      </c>
-      <c r="AY14">
-        <v>15</v>
-      </c>
-      <c r="AZ14">
-        <v>11</v>
       </c>
       <c r="BA14">
         <v>10</v>
       </c>
       <c r="BB14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BC14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BD14">
         <v>2.15</v>
@@ -4053,13 +4053,13 @@
         <v>0.5</v>
       </c>
       <c r="AR15">
-        <v>1.98</v>
+        <v>1.82</v>
       </c>
       <c r="AS15">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AT15">
-        <v>3.18</v>
+        <v>2.99</v>
       </c>
       <c r="AU15">
         <v>5</v>
@@ -4068,16 +4068,16 @@
         <v>3</v>
       </c>
       <c r="AW15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX15">
+        <v>3</v>
+      </c>
+      <c r="AY15">
+        <v>11</v>
+      </c>
+      <c r="AZ15">
         <v>6</v>
-      </c>
-      <c r="AY15">
-        <v>12</v>
-      </c>
-      <c r="AZ15">
-        <v>9</v>
       </c>
       <c r="BA15">
         <v>5</v>
@@ -4274,16 +4274,16 @@
         <v>5</v>
       </c>
       <c r="AW16">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AX16">
+        <v>10</v>
+      </c>
+      <c r="AY16">
+        <v>6</v>
+      </c>
+      <c r="AZ16">
         <v>15</v>
-      </c>
-      <c r="AY16">
-        <v>7</v>
-      </c>
-      <c r="AZ16">
-        <v>20</v>
       </c>
       <c r="BA16">
         <v>4</v>
@@ -4480,16 +4480,16 @@
         <v>9</v>
       </c>
       <c r="AW17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX17">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AY17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ17">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="BA17">
         <v>4</v>
@@ -4671,31 +4671,31 @@
         <v>1.11</v>
       </c>
       <c r="AR18">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="AS18">
-        <v>0.9399999999999999</v>
+        <v>1.07</v>
       </c>
       <c r="AT18">
-        <v>2.21</v>
+        <v>2.08</v>
       </c>
       <c r="AU18">
+        <v>3</v>
+      </c>
+      <c r="AV18">
         <v>6</v>
       </c>
-      <c r="AV18">
-        <v>5</v>
-      </c>
       <c r="AW18">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AX18">
         <v>2</v>
       </c>
       <c r="AY18">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AZ18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA18">
         <v>6</v>
@@ -4880,10 +4880,10 @@
         <v>0</v>
       </c>
       <c r="AS19">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AT19">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AU19">
         <v>4</v>
@@ -4892,16 +4892,16 @@
         <v>5</v>
       </c>
       <c r="AW19">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY19">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA19">
         <v>8</v>
@@ -4999,7 +4999,7 @@
         <v>95</v>
       </c>
       <c r="P20" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q20">
         <v>1.91</v>
@@ -5083,22 +5083,22 @@
         <v>1.13</v>
       </c>
       <c r="AR20">
-        <v>1.66</v>
+        <v>1.18</v>
       </c>
       <c r="AS20">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AT20">
-        <v>2.78</v>
+        <v>2.24</v>
       </c>
       <c r="AU20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV20">
         <v>3</v>
       </c>
       <c r="AW20">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AX20">
         <v>7</v>
@@ -5292,10 +5292,10 @@
         <v>2.05</v>
       </c>
       <c r="AS21">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="AT21">
-        <v>3.17</v>
+        <v>3.09</v>
       </c>
       <c r="AU21">
         <v>6</v>
@@ -5304,16 +5304,16 @@
         <v>4</v>
       </c>
       <c r="AW21">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AX21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY21">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ21">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA21">
         <v>10</v>
@@ -5498,28 +5498,28 @@
         <v>0</v>
       </c>
       <c r="AS22">
-        <v>1.69</v>
+        <v>1.44</v>
       </c>
       <c r="AT22">
-        <v>1.69</v>
+        <v>1.44</v>
       </c>
       <c r="AU22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV22">
         <v>9</v>
       </c>
       <c r="AW22">
+        <v>4</v>
+      </c>
+      <c r="AX22">
+        <v>1</v>
+      </c>
+      <c r="AY22">
         <v>6</v>
       </c>
-      <c r="AX22">
-        <v>5</v>
-      </c>
-      <c r="AY22">
-        <v>9</v>
-      </c>
       <c r="AZ22">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="BA22">
         <v>2</v>
@@ -5713,19 +5713,19 @@
         <v>3</v>
       </c>
       <c r="AV23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX23">
         <v>5</v>
       </c>
       <c r="AY23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ23">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA23">
         <v>3</v>
@@ -5907,13 +5907,13 @@
         <v>1.25</v>
       </c>
       <c r="AR24">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AS24">
         <v>2.25</v>
       </c>
       <c r="AT24">
-        <v>3.85</v>
+        <v>3.91</v>
       </c>
       <c r="AU24">
         <v>7</v>
@@ -5922,13 +5922,13 @@
         <v>2</v>
       </c>
       <c r="AW24">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AX24">
         <v>1</v>
       </c>
       <c r="AY24">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AZ24">
         <v>3</v>
@@ -6008,13 +6008,13 @@
         <v>77</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25">
         <v>0</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25">
         <v>1</v>
@@ -6122,22 +6122,22 @@
         <v>0.88</v>
       </c>
       <c r="AU25">
+        <v>7</v>
+      </c>
+      <c r="AV25">
+        <v>7</v>
+      </c>
+      <c r="AW25">
+        <v>1</v>
+      </c>
+      <c r="AX25">
+        <v>4</v>
+      </c>
+      <c r="AY25">
         <v>8</v>
       </c>
-      <c r="AV25">
-        <v>9</v>
-      </c>
-      <c r="AW25">
-        <v>7</v>
-      </c>
-      <c r="AX25">
+      <c r="AZ25">
         <v>11</v>
-      </c>
-      <c r="AY25">
-        <v>15</v>
-      </c>
-      <c r="AZ25">
-        <v>20</v>
       </c>
       <c r="BA25">
         <v>7</v>
@@ -6319,13 +6319,13 @@
         <v>1.78</v>
       </c>
       <c r="AR26">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AS26">
-        <v>2.57</v>
+        <v>2.31</v>
       </c>
       <c r="AT26">
-        <v>3.74</v>
+        <v>3.44</v>
       </c>
       <c r="AU26">
         <v>6</v>
@@ -6334,16 +6334,16 @@
         <v>9</v>
       </c>
       <c r="AW26">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AX26">
+        <v>8</v>
+      </c>
+      <c r="AY26">
+        <v>10</v>
+      </c>
+      <c r="AZ26">
         <v>17</v>
-      </c>
-      <c r="AY26">
-        <v>13</v>
-      </c>
-      <c r="AZ26">
-        <v>26</v>
       </c>
       <c r="BA26">
         <v>0</v>
@@ -6525,13 +6525,13 @@
         <v>0.86</v>
       </c>
       <c r="AR27">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="AS27">
         <v>0</v>
       </c>
       <c r="AT27">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="AU27">
         <v>8</v>
@@ -6543,13 +6543,13 @@
         <v>3</v>
       </c>
       <c r="AX27">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AY27">
         <v>11</v>
       </c>
       <c r="AZ27">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="BA27">
         <v>3</v>
@@ -6731,31 +6731,31 @@
         <v>1.11</v>
       </c>
       <c r="AR28">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AS28">
-        <v>1.02</v>
+        <v>1.15</v>
       </c>
       <c r="AT28">
         <v>2.85</v>
       </c>
       <c r="AU28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV28">
         <v>4</v>
       </c>
       <c r="AW28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX28">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY28">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AZ28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA28">
         <v>3</v>
@@ -6937,31 +6937,31 @@
         <v>0.5</v>
       </c>
       <c r="AR29">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AS29">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AT29">
-        <v>2.58</v>
+        <v>2.55</v>
       </c>
       <c r="AU29">
+        <v>4</v>
+      </c>
+      <c r="AV29">
+        <v>7</v>
+      </c>
+      <c r="AW29">
+        <v>1</v>
+      </c>
+      <c r="AX29">
+        <v>4</v>
+      </c>
+      <c r="AY29">
         <v>5</v>
       </c>
-      <c r="AV29">
-        <v>9</v>
-      </c>
-      <c r="AW29">
-        <v>4</v>
-      </c>
-      <c r="AX29">
-        <v>6</v>
-      </c>
-      <c r="AY29">
-        <v>9</v>
-      </c>
       <c r="AZ29">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BA29">
         <v>4</v>
@@ -7056,7 +7056,7 @@
         <v>1</v>
       </c>
       <c r="O30" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P30" t="s">
         <v>84</v>
@@ -7143,31 +7143,31 @@
         <v>1.78</v>
       </c>
       <c r="AR30">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AS30">
-        <v>2.6</v>
+        <v>2.19</v>
       </c>
       <c r="AT30">
-        <v>4.49</v>
+        <v>3.89</v>
       </c>
       <c r="AU30">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV30">
         <v>5</v>
       </c>
       <c r="AW30">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AX30">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AY30">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AZ30">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="BA30">
         <v>3</v>
@@ -7262,7 +7262,7 @@
         <v>1</v>
       </c>
       <c r="O31" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="P31" t="s">
         <v>84</v>
@@ -7349,31 +7349,31 @@
         <v>1.57</v>
       </c>
       <c r="AR31">
-        <v>1.87</v>
+        <v>1.57</v>
       </c>
       <c r="AS31">
-        <v>2.39</v>
+        <v>2.23</v>
       </c>
       <c r="AT31">
-        <v>4.26</v>
+        <v>3.8</v>
       </c>
       <c r="AU31">
         <v>4</v>
       </c>
       <c r="AV31">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AW31">
         <v>7</v>
       </c>
       <c r="AX31">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AY31">
         <v>11</v>
       </c>
       <c r="AZ31">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="BA31">
         <v>4</v>
@@ -7468,7 +7468,7 @@
         <v>2</v>
       </c>
       <c r="O32" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P32" t="s">
         <v>84</v>
@@ -7555,13 +7555,13 @@
         <v>1.13</v>
       </c>
       <c r="AR32">
-        <v>1.86</v>
+        <v>1.34</v>
       </c>
       <c r="AS32">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AT32">
-        <v>2.93</v>
+        <v>2.37</v>
       </c>
       <c r="AU32">
         <v>7</v>
@@ -7570,16 +7570,16 @@
         <v>3</v>
       </c>
       <c r="AW32">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="AX32">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AY32">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="AZ32">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA32">
         <v>4</v>
@@ -7674,7 +7674,7 @@
         <v>2</v>
       </c>
       <c r="O33" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P33" t="s">
         <v>173</v>
@@ -7761,31 +7761,31 @@
         <v>1.63</v>
       </c>
       <c r="AR33">
-        <v>1.89</v>
+        <v>1.54</v>
       </c>
       <c r="AS33">
         <v>1.51</v>
       </c>
       <c r="AT33">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="AU33">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AV33">
         <v>7</v>
       </c>
       <c r="AW33">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="AX33">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AY33">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="AZ33">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="BA33">
         <v>10</v>
@@ -7880,7 +7880,7 @@
         <v>5</v>
       </c>
       <c r="O34" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="P34" t="s">
         <v>174</v>
@@ -7970,28 +7970,28 @@
         <v>1.49</v>
       </c>
       <c r="AS34">
-        <v>1.94</v>
+        <v>1.76</v>
       </c>
       <c r="AT34">
-        <v>3.43</v>
+        <v>3.25</v>
       </c>
       <c r="AU34">
+        <v>8</v>
+      </c>
+      <c r="AV34">
+        <v>7</v>
+      </c>
+      <c r="AW34">
+        <v>4</v>
+      </c>
+      <c r="AX34">
+        <v>2</v>
+      </c>
+      <c r="AY34">
+        <v>12</v>
+      </c>
+      <c r="AZ34">
         <v>9</v>
-      </c>
-      <c r="AV34">
-        <v>6</v>
-      </c>
-      <c r="AW34">
-        <v>8</v>
-      </c>
-      <c r="AX34">
-        <v>5</v>
-      </c>
-      <c r="AY34">
-        <v>17</v>
-      </c>
-      <c r="AZ34">
-        <v>11</v>
       </c>
       <c r="BA34">
         <v>11</v>
@@ -8086,7 +8086,7 @@
         <v>3</v>
       </c>
       <c r="O35" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P35" t="s">
         <v>84</v>
@@ -8173,31 +8173,31 @@
         <v>0.43</v>
       </c>
       <c r="AR35">
-        <v>1.73</v>
+        <v>1.51</v>
       </c>
       <c r="AS35">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="AT35">
-        <v>3.52</v>
+        <v>3.17</v>
       </c>
       <c r="AU35">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AV35">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW35">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="AX35">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AY35">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="AZ35">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA35">
         <v>10</v>
@@ -8292,7 +8292,7 @@
         <v>4</v>
       </c>
       <c r="O36" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="P36" t="s">
         <v>175</v>
@@ -8379,31 +8379,31 @@
         <v>2.25</v>
       </c>
       <c r="AR36">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="AS36">
-        <v>1.77</v>
+        <v>1.51</v>
       </c>
       <c r="AT36">
-        <v>3.03</v>
+        <v>2.68</v>
       </c>
       <c r="AU36">
+        <v>6</v>
+      </c>
+      <c r="AV36">
+        <v>7</v>
+      </c>
+      <c r="AW36">
+        <v>2</v>
+      </c>
+      <c r="AX36">
         <v>4</v>
       </c>
-      <c r="AV36">
+      <c r="AY36">
         <v>8</v>
       </c>
-      <c r="AW36">
-        <v>5</v>
-      </c>
-      <c r="AX36">
-        <v>14</v>
-      </c>
-      <c r="AY36">
-        <v>9</v>
-      </c>
       <c r="AZ36">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="BA36">
         <v>1</v>
@@ -8498,7 +8498,7 @@
         <v>5</v>
       </c>
       <c r="O37" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P37" t="s">
         <v>176</v>
@@ -8585,13 +8585,13 @@
         <v>1</v>
       </c>
       <c r="AR37">
-        <v>1.04</v>
+        <v>0.79</v>
       </c>
       <c r="AS37">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AT37">
-        <v>2.28</v>
+        <v>2.01</v>
       </c>
       <c r="AU37">
         <v>5</v>
@@ -8600,16 +8600,16 @@
         <v>7</v>
       </c>
       <c r="AW37">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AX37">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AY37">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AZ37">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA37">
         <v>3</v>
@@ -8791,31 +8791,31 @@
         <v>1.63</v>
       </c>
       <c r="AR38">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AS38">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AT38">
-        <v>2.83</v>
+        <v>2.66</v>
       </c>
       <c r="AU38">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AV38">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW38">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AX38">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AY38">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AZ38">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BA38">
         <v>4</v>
@@ -8910,7 +8910,7 @@
         <v>5</v>
       </c>
       <c r="O39" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P39" t="s">
         <v>178</v>
@@ -8997,31 +8997,31 @@
         <v>1.25</v>
       </c>
       <c r="AR39">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AS39">
         <v>1.38</v>
       </c>
       <c r="AT39">
-        <v>3.28</v>
+        <v>3.26</v>
       </c>
       <c r="AU39">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AV39">
         <v>4</v>
       </c>
       <c r="AW39">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AX39">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY39">
         <v>15</v>
       </c>
       <c r="AZ39">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA39">
         <v>11</v>
@@ -9116,7 +9116,7 @@
         <v>4</v>
       </c>
       <c r="O40" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P40" t="s">
         <v>179</v>
@@ -9203,16 +9203,16 @@
         <v>1.57</v>
       </c>
       <c r="AR40">
-        <v>2.02</v>
+        <v>1.47</v>
       </c>
       <c r="AS40">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="AT40">
-        <v>4.16</v>
+        <v>3.35</v>
       </c>
       <c r="AU40">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV40">
         <v>4</v>
@@ -9221,13 +9221,13 @@
         <v>10</v>
       </c>
       <c r="AX40">
+        <v>4</v>
+      </c>
+      <c r="AY40">
+        <v>14</v>
+      </c>
+      <c r="AZ40">
         <v>8</v>
-      </c>
-      <c r="AY40">
-        <v>15</v>
-      </c>
-      <c r="AZ40">
-        <v>12</v>
       </c>
       <c r="BA40">
         <v>8</v>
@@ -9322,7 +9322,7 @@
         <v>4</v>
       </c>
       <c r="O41" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="P41" t="s">
         <v>180</v>
@@ -9409,31 +9409,31 @@
         <v>1.25</v>
       </c>
       <c r="AR41">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AS41">
-        <v>1.6</v>
+        <v>1.24</v>
       </c>
       <c r="AT41">
-        <v>3.36</v>
+        <v>2.96</v>
       </c>
       <c r="AU41">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV41">
         <v>5</v>
       </c>
       <c r="AW41">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="AX41">
+        <v>2</v>
+      </c>
+      <c r="AY41">
         <v>5</v>
       </c>
-      <c r="AY41">
-        <v>13</v>
-      </c>
       <c r="AZ41">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BA41">
         <v>8</v>
@@ -9615,31 +9615,31 @@
         <v>1.13</v>
       </c>
       <c r="AR42">
-        <v>1.2</v>
+        <v>0.95</v>
       </c>
       <c r="AS42">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="AT42">
-        <v>2.35</v>
+        <v>2.04</v>
       </c>
       <c r="AU42">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV42">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AW42">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="AX42">
         <v>1</v>
       </c>
       <c r="AY42">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="AZ42">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BA42">
         <v>6</v>
@@ -9734,7 +9734,7 @@
         <v>4</v>
       </c>
       <c r="O43" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P43" t="s">
         <v>182</v>
@@ -9821,13 +9821,13 @@
         <v>1.78</v>
       </c>
       <c r="AR43">
-        <v>2.09</v>
+        <v>1.59</v>
       </c>
       <c r="AS43">
-        <v>2.31</v>
+        <v>1.85</v>
       </c>
       <c r="AT43">
-        <v>4.4</v>
+        <v>3.44</v>
       </c>
       <c r="AU43">
         <v>7</v>
@@ -9836,16 +9836,16 @@
         <v>4</v>
       </c>
       <c r="AW43">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AX43">
+        <v>5</v>
+      </c>
+      <c r="AY43">
+        <v>8</v>
+      </c>
+      <c r="AZ43">
         <v>9</v>
-      </c>
-      <c r="AY43">
-        <v>11</v>
-      </c>
-      <c r="AZ43">
-        <v>13</v>
       </c>
       <c r="BA43">
         <v>3</v>
@@ -9940,7 +9940,7 @@
         <v>5</v>
       </c>
       <c r="O44" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P44" t="s">
         <v>183</v>
@@ -10027,13 +10027,13 @@
         <v>0.43</v>
       </c>
       <c r="AR44">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="AS44">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AT44">
-        <v>3.07</v>
+        <v>2.92</v>
       </c>
       <c r="AU44">
         <v>14</v>
@@ -10042,16 +10042,16 @@
         <v>4</v>
       </c>
       <c r="AW44">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="AX44">
+        <v>3</v>
+      </c>
+      <c r="AY44">
+        <v>20</v>
+      </c>
+      <c r="AZ44">
         <v>7</v>
-      </c>
-      <c r="AY44">
-        <v>27</v>
-      </c>
-      <c r="AZ44">
-        <v>11</v>
       </c>
       <c r="BA44">
         <v>12</v>
@@ -10233,31 +10233,31 @@
         <v>1.11</v>
       </c>
       <c r="AR45">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="AS45">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="AT45">
-        <v>2.78</v>
+        <v>2.65</v>
       </c>
       <c r="AU45">
+        <v>4</v>
+      </c>
+      <c r="AV45">
+        <v>3</v>
+      </c>
+      <c r="AW45">
+        <v>3</v>
+      </c>
+      <c r="AX45">
+        <v>6</v>
+      </c>
+      <c r="AY45">
         <v>7</v>
       </c>
-      <c r="AV45">
-        <v>4</v>
-      </c>
-      <c r="AW45">
-        <v>8</v>
-      </c>
-      <c r="AX45">
-        <v>7</v>
-      </c>
-      <c r="AY45">
-        <v>15</v>
-      </c>
       <c r="AZ45">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA45">
         <v>6</v>
@@ -10352,7 +10352,7 @@
         <v>6</v>
       </c>
       <c r="O46" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P46" t="s">
         <v>184</v>
@@ -10439,31 +10439,31 @@
         <v>1.57</v>
       </c>
       <c r="AR46">
-        <v>2.31</v>
+        <v>2.11</v>
       </c>
       <c r="AS46">
-        <v>1.95</v>
+        <v>1.69</v>
       </c>
       <c r="AT46">
-        <v>4.26</v>
+        <v>3.8</v>
       </c>
       <c r="AU46">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AV46">
+        <v>6</v>
+      </c>
+      <c r="AW46">
+        <v>6</v>
+      </c>
+      <c r="AX46">
         <v>5</v>
       </c>
-      <c r="AW46">
-        <v>7</v>
-      </c>
-      <c r="AX46">
-        <v>16</v>
-      </c>
       <c r="AY46">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AZ46">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="BA46">
         <v>2</v>
@@ -10558,7 +10558,7 @@
         <v>3</v>
       </c>
       <c r="O47" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P47" t="s">
         <v>84</v>
@@ -10645,13 +10645,13 @@
         <v>1.25</v>
       </c>
       <c r="AR47">
-        <v>1.71</v>
+        <v>1.59</v>
       </c>
       <c r="AS47">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AT47">
-        <v>3.21</v>
+        <v>2.79</v>
       </c>
       <c r="AU47">
         <v>5</v>
@@ -10660,16 +10660,16 @@
         <v>3</v>
       </c>
       <c r="AW47">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AX47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY47">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AZ47">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA47">
         <v>9</v>
@@ -10851,31 +10851,31 @@
         <v>0.86</v>
       </c>
       <c r="AR48">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AS48">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AT48">
-        <v>3.07</v>
+        <v>2.88</v>
       </c>
       <c r="AU48">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV48">
         <v>5</v>
       </c>
       <c r="AW48">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AX48">
+        <v>3</v>
+      </c>
+      <c r="AY48">
         <v>8</v>
       </c>
-      <c r="AY48">
-        <v>14</v>
-      </c>
       <c r="AZ48">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="BA48">
         <v>5</v>
@@ -10970,7 +10970,7 @@
         <v>2</v>
       </c>
       <c r="O49" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P49" t="s">
         <v>185</v>
@@ -11057,31 +11057,31 @@
         <v>1</v>
       </c>
       <c r="AR49">
-        <v>0.93</v>
+        <v>0.85</v>
       </c>
       <c r="AS49">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AT49">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="AU49">
         <v>3</v>
       </c>
       <c r="AV49">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW49">
         <v>6</v>
       </c>
       <c r="AX49">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AY49">
         <v>9</v>
       </c>
       <c r="AZ49">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BA49">
         <v>3</v>
@@ -11263,13 +11263,13 @@
         <v>0.5</v>
       </c>
       <c r="AR50">
-        <v>1.72</v>
+        <v>1.53</v>
       </c>
       <c r="AS50">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AT50">
-        <v>3.01</v>
+        <v>2.7</v>
       </c>
       <c r="AU50">
         <v>6</v>
@@ -11278,16 +11278,16 @@
         <v>2</v>
       </c>
       <c r="AW50">
+        <v>4</v>
+      </c>
+      <c r="AX50">
+        <v>3</v>
+      </c>
+      <c r="AY50">
         <v>10</v>
       </c>
-      <c r="AX50">
-        <v>6</v>
-      </c>
-      <c r="AY50">
-        <v>16</v>
-      </c>
       <c r="AZ50">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BA50">
         <v>5</v>
@@ -11469,31 +11469,31 @@
         <v>1.63</v>
       </c>
       <c r="AR51">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AS51">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="AT51">
-        <v>2.82</v>
+        <v>2.63</v>
       </c>
       <c r="AU51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV51">
         <v>10</v>
       </c>
       <c r="AW51">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AX51">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AY51">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AZ51">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="BA51">
         <v>4</v>
@@ -11675,13 +11675,13 @@
         <v>1.25</v>
       </c>
       <c r="AR52">
-        <v>1.97</v>
+        <v>1.74</v>
       </c>
       <c r="AS52">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AT52">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="AU52">
         <v>5</v>
@@ -11690,16 +11690,16 @@
         <v>5</v>
       </c>
       <c r="AW52">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="AX52">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AY52">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="AZ52">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA52">
         <v>7</v>
@@ -11881,31 +11881,31 @@
         <v>2.25</v>
       </c>
       <c r="AR53">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AS53">
-        <v>2.04</v>
+        <v>1.62</v>
       </c>
       <c r="AT53">
-        <v>3.92</v>
+        <v>3.52</v>
       </c>
       <c r="AU53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV53">
         <v>8</v>
       </c>
       <c r="AW53">
+        <v>3</v>
+      </c>
+      <c r="AX53">
+        <v>2</v>
+      </c>
+      <c r="AY53">
+        <v>5</v>
+      </c>
+      <c r="AZ53">
         <v>10</v>
-      </c>
-      <c r="AX53">
-        <v>10</v>
-      </c>
-      <c r="AY53">
-        <v>13</v>
-      </c>
-      <c r="AZ53">
-        <v>18</v>
       </c>
       <c r="BA53">
         <v>5</v>
@@ -12000,7 +12000,7 @@
         <v>4</v>
       </c>
       <c r="O54" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P54" t="s">
         <v>189</v>
@@ -12087,31 +12087,31 @@
         <v>1.13</v>
       </c>
       <c r="AR54">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
       <c r="AS54">
-        <v>1.1</v>
+        <v>0.99</v>
       </c>
       <c r="AT54">
-        <v>2.53</v>
+        <v>2.28</v>
       </c>
       <c r="AU54">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AV54">
         <v>7</v>
       </c>
       <c r="AW54">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="AX54">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AY54">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="AZ54">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA54">
         <v>8</v>
@@ -12206,7 +12206,7 @@
         <v>3</v>
       </c>
       <c r="O55" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P55" t="s">
         <v>190</v>
@@ -12293,13 +12293,13 @@
         <v>1.25</v>
       </c>
       <c r="AR55">
-        <v>1.69</v>
+        <v>1.54</v>
       </c>
       <c r="AS55">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AT55">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="AU55">
         <v>6</v>
@@ -12308,16 +12308,16 @@
         <v>4</v>
       </c>
       <c r="AW55">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="AX55">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AY55">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="AZ55">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="BA55">
         <v>4</v>
@@ -12412,7 +12412,7 @@
         <v>4</v>
       </c>
       <c r="O56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="P56" t="s">
         <v>191</v>
@@ -12499,28 +12499,28 @@
         <v>1.57</v>
       </c>
       <c r="AR56">
-        <v>1.46</v>
+        <v>1.1</v>
       </c>
       <c r="AS56">
-        <v>1.98</v>
+        <v>1.66</v>
       </c>
       <c r="AT56">
-        <v>3.44</v>
+        <v>2.76</v>
       </c>
       <c r="AU56">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AV56">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AW56">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AX56">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AY56">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AZ56">
         <v>9</v>
@@ -12705,31 +12705,31 @@
         <v>1.25</v>
       </c>
       <c r="AR57">
-        <v>2.2</v>
+        <v>1.96</v>
       </c>
       <c r="AS57">
-        <v>1.31</v>
+        <v>1.07</v>
       </c>
       <c r="AT57">
-        <v>3.51</v>
+        <v>3.03</v>
       </c>
       <c r="AU57">
         <v>3</v>
       </c>
       <c r="AV57">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW57">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AX57">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AY57">
+        <v>5</v>
+      </c>
+      <c r="AZ57">
         <v>9</v>
-      </c>
-      <c r="AZ57">
-        <v>15</v>
       </c>
       <c r="BA57">
         <v>4</v>
@@ -12911,31 +12911,31 @@
         <v>1.78</v>
       </c>
       <c r="AR58">
-        <v>1.88</v>
+        <v>1.47</v>
       </c>
       <c r="AS58">
-        <v>2.07</v>
+        <v>1.66</v>
       </c>
       <c r="AT58">
-        <v>3.95</v>
+        <v>3.13</v>
       </c>
       <c r="AU58">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AV58">
         <v>8</v>
       </c>
       <c r="AW58">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AX58">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AY58">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AZ58">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="BA58">
         <v>3</v>
@@ -13117,13 +13117,13 @@
         <v>2.25</v>
       </c>
       <c r="AR59">
-        <v>0.99</v>
+        <v>0.93</v>
       </c>
       <c r="AS59">
-        <v>2.05</v>
+        <v>1.61</v>
       </c>
       <c r="AT59">
-        <v>3.04</v>
+        <v>2.54</v>
       </c>
       <c r="AU59">
         <v>0</v>
@@ -13132,16 +13132,16 @@
         <v>5</v>
       </c>
       <c r="AW59">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX59">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY59">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ59">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA59">
         <v>4</v>
@@ -13209,7 +13209,7 @@
         <v>45822.33333333334</v>
       </c>
       <c r="F60">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G60" t="s">
         <v>71</v>
@@ -13236,7 +13236,7 @@
         <v>2</v>
       </c>
       <c r="O60" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="P60" t="s">
         <v>194</v>
@@ -13323,31 +13323,31 @@
         <v>0.86</v>
       </c>
       <c r="AR60">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="AS60">
-        <v>1.6</v>
+        <v>1.41</v>
       </c>
       <c r="AT60">
-        <v>3.55</v>
+        <v>2.94</v>
       </c>
       <c r="AU60">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV60">
         <v>5</v>
       </c>
       <c r="AW60">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="AX60">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AY60">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="AZ60">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BA60">
         <v>7</v>
@@ -13415,7 +13415,7 @@
         <v>45822.45833333334</v>
       </c>
       <c r="F61">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G61" t="s">
         <v>79</v>
@@ -13529,31 +13529,31 @@
         <v>1.63</v>
       </c>
       <c r="AR61">
-        <v>1.48</v>
+        <v>1.18</v>
       </c>
       <c r="AS61">
-        <v>1.85</v>
+        <v>1.64</v>
       </c>
       <c r="AT61">
-        <v>3.33</v>
+        <v>2.82</v>
       </c>
       <c r="AU61">
         <v>2</v>
       </c>
       <c r="AV61">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AW61">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AX61">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="AY61">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ61">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="BA61">
         <v>2</v>
@@ -13621,7 +13621,7 @@
         <v>45822.54166666666</v>
       </c>
       <c r="F62">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G62" t="s">
         <v>81</v>
@@ -13648,10 +13648,10 @@
         <v>3</v>
       </c>
       <c r="O62" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P62" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q62">
         <v>2.26</v>
@@ -13735,13 +13735,13 @@
         <v>0.43</v>
       </c>
       <c r="AR62">
-        <v>1.67</v>
+        <v>1.22</v>
       </c>
       <c r="AS62">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AT62">
-        <v>2.89</v>
+        <v>2.32</v>
       </c>
       <c r="AU62">
         <v>7</v>
@@ -13750,16 +13750,16 @@
         <v>7</v>
       </c>
       <c r="AW62">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AX62">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AY62">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AZ62">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA62">
         <v>8</v>
@@ -13827,7 +13827,7 @@
         <v>45822.54166666666</v>
       </c>
       <c r="F63">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G63" t="s">
         <v>77</v>
@@ -13941,31 +13941,31 @@
         <v>1.78</v>
       </c>
       <c r="AR63">
-        <v>2.11</v>
+        <v>1.77</v>
       </c>
       <c r="AS63">
-        <v>2.17</v>
+        <v>1.74</v>
       </c>
       <c r="AT63">
-        <v>4.28</v>
+        <v>3.51</v>
       </c>
       <c r="AU63">
         <v>3</v>
       </c>
       <c r="AV63">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW63">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AX63">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="AY63">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AZ63">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="BA63">
         <v>5</v>
@@ -14033,7 +14033,7 @@
         <v>45822.54166666666</v>
       </c>
       <c r="F64">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G64" t="s">
         <v>76</v>
@@ -14060,7 +14060,7 @@
         <v>4</v>
       </c>
       <c r="O64" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="P64" t="s">
         <v>197</v>
@@ -14147,28 +14147,28 @@
         <v>1.11</v>
       </c>
       <c r="AR64">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AS64">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AT64">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="AU64">
+        <v>8</v>
+      </c>
+      <c r="AV64">
+        <v>4</v>
+      </c>
+      <c r="AW64">
         <v>7</v>
       </c>
-      <c r="AV64">
-        <v>3</v>
-      </c>
-      <c r="AW64">
-        <v>11</v>
-      </c>
       <c r="AX64">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY64">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AZ64">
         <v>5</v>
@@ -14239,7 +14239,7 @@
         <v>45822.54166666666</v>
       </c>
       <c r="F65">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G65" t="s">
         <v>72</v>
@@ -14266,7 +14266,7 @@
         <v>6</v>
       </c>
       <c r="O65" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P65" t="s">
         <v>198</v>
@@ -14353,13 +14353,13 @@
         <v>1.25</v>
       </c>
       <c r="AR65">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AS65">
-        <v>1.21</v>
+        <v>1.09</v>
       </c>
       <c r="AT65">
-        <v>2.37</v>
+        <v>2.2</v>
       </c>
       <c r="AU65">
         <v>4</v>
@@ -14368,16 +14368,16 @@
         <v>7</v>
       </c>
       <c r="AW65">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="AX65">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY65">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="AZ65">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA65">
         <v>9</v>
@@ -14445,7 +14445,7 @@
         <v>45826.45833333334</v>
       </c>
       <c r="F66">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G66" t="s">
         <v>70</v>
@@ -14472,7 +14472,7 @@
         <v>5</v>
       </c>
       <c r="O66" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="P66" t="s">
         <v>199</v>
@@ -14559,31 +14559,31 @@
         <v>1.57</v>
       </c>
       <c r="AR66">
-        <v>1.76</v>
+        <v>1.53</v>
       </c>
       <c r="AS66">
-        <v>1.84</v>
+        <v>1.59</v>
       </c>
       <c r="AT66">
-        <v>3.6</v>
+        <v>3.12</v>
       </c>
       <c r="AU66">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV66">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW66">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AX66">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY66">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AZ66">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA66">
         <v>11</v>
@@ -14651,7 +14651,7 @@
         <v>45826.45833333334</v>
       </c>
       <c r="F67">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G67" t="s">
         <v>72</v>
@@ -14678,7 +14678,7 @@
         <v>1</v>
       </c>
       <c r="O67" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="P67" t="s">
         <v>84</v>
@@ -14765,13 +14765,13 @@
         <v>1.25</v>
       </c>
       <c r="AR67">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="AS67">
-        <v>1.36</v>
+        <v>1.08</v>
       </c>
       <c r="AT67">
-        <v>2.62</v>
+        <v>2.23</v>
       </c>
       <c r="AU67">
         <v>3</v>
@@ -14780,16 +14780,16 @@
         <v>6</v>
       </c>
       <c r="AW67">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AX67">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="AY67">
+        <v>6</v>
+      </c>
+      <c r="AZ67">
         <v>12</v>
-      </c>
-      <c r="AZ67">
-        <v>25</v>
       </c>
       <c r="BA67">
         <v>2</v>
@@ -14857,7 +14857,7 @@
         <v>45826.625</v>
       </c>
       <c r="F68">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G68" t="s">
         <v>80</v>
@@ -14884,7 +14884,7 @@
         <v>3</v>
       </c>
       <c r="O68" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="P68" t="s">
         <v>200</v>
@@ -14971,28 +14971,28 @@
         <v>0.5</v>
       </c>
       <c r="AR68">
-        <v>0.97</v>
+        <v>0.91</v>
       </c>
       <c r="AS68">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="AT68">
-        <v>2.19</v>
+        <v>2</v>
       </c>
       <c r="AU68">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV68">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AW68">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AX68">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AY68">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ68">
         <v>5</v>
@@ -15063,7 +15063,7 @@
         <v>45826.625</v>
       </c>
       <c r="F69">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G69" t="s">
         <v>78</v>
@@ -15090,7 +15090,7 @@
         <v>4</v>
       </c>
       <c r="O69" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P69" t="s">
         <v>201</v>
@@ -15177,31 +15177,31 @@
         <v>0.86</v>
       </c>
       <c r="AR69">
-        <v>1.98</v>
+        <v>1.74</v>
       </c>
       <c r="AS69">
-        <v>1.52</v>
+        <v>1.33</v>
       </c>
       <c r="AT69">
-        <v>3.5</v>
+        <v>3.07</v>
       </c>
       <c r="AU69">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AV69">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW69">
+        <v>3</v>
+      </c>
+      <c r="AX69">
         <v>5</v>
       </c>
-      <c r="AX69">
-        <v>8</v>
-      </c>
       <c r="AY69">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AZ69">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA69">
         <v>5</v>
@@ -15269,7 +15269,7 @@
         <v>45826.625</v>
       </c>
       <c r="F70">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G70" t="s">
         <v>74</v>
@@ -15383,31 +15383,31 @@
         <v>1</v>
       </c>
       <c r="AR70">
-        <v>1.74</v>
+        <v>1.41</v>
       </c>
       <c r="AS70">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="AT70">
-        <v>3.09</v>
+        <v>2.67</v>
       </c>
       <c r="AU70">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV70">
         <v>4</v>
       </c>
       <c r="AW70">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AX70">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AY70">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AZ70">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA70">
         <v>10</v>
@@ -15475,7 +15475,7 @@
         <v>45827.5</v>
       </c>
       <c r="F71">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G71" t="s">
         <v>71</v>
@@ -15502,7 +15502,7 @@
         <v>5</v>
       </c>
       <c r="O71" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P71" t="s">
         <v>84</v>
@@ -15589,31 +15589,31 @@
         <v>0.43</v>
       </c>
       <c r="AR71">
-        <v>1.89</v>
+        <v>1.47</v>
       </c>
       <c r="AS71">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="AT71">
-        <v>3.2</v>
+        <v>2.66</v>
       </c>
       <c r="AU71">
         <v>11</v>
       </c>
       <c r="AV71">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW71">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AX71">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AY71">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AZ71">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA71">
         <v>5</v>
@@ -15681,7 +15681,7 @@
         <v>45835.5</v>
       </c>
       <c r="F72">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G72" t="s">
         <v>81</v>
@@ -15708,7 +15708,7 @@
         <v>4</v>
       </c>
       <c r="O72" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="P72" t="s">
         <v>202</v>
@@ -15795,13 +15795,13 @@
         <v>2.25</v>
       </c>
       <c r="AR72">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="AS72">
-        <v>1.95</v>
+        <v>1.61</v>
       </c>
       <c r="AT72">
-        <v>3.65</v>
+        <v>2.91</v>
       </c>
       <c r="AU72">
         <v>8</v>
@@ -15810,16 +15810,16 @@
         <v>8</v>
       </c>
       <c r="AW72">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AX72">
+        <v>5</v>
+      </c>
+      <c r="AY72">
         <v>11</v>
       </c>
-      <c r="AY72">
-        <v>15</v>
-      </c>
       <c r="AZ72">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="BA72">
         <v>2</v>
@@ -15887,7 +15887,7 @@
         <v>45835.58333333334</v>
       </c>
       <c r="F73">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G73" t="s">
         <v>77</v>
@@ -15914,7 +15914,7 @@
         <v>3</v>
       </c>
       <c r="O73" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="P73" t="s">
         <v>84</v>
@@ -16001,13 +16001,13 @@
         <v>1.63</v>
       </c>
       <c r="AR73">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AS73">
-        <v>1.99</v>
+        <v>1.69</v>
       </c>
       <c r="AT73">
-        <v>3.99</v>
+        <v>3.36</v>
       </c>
       <c r="AU73">
         <v>7</v>
@@ -16093,7 +16093,7 @@
         <v>45836.25</v>
       </c>
       <c r="F74">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G74" t="s">
         <v>76</v>
@@ -16120,10 +16120,10 @@
         <v>5</v>
       </c>
       <c r="O74" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P74" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q74">
         <v>1.77</v>
@@ -16207,31 +16207,31 @@
         <v>1.13</v>
       </c>
       <c r="AR74">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AS74">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AT74">
-        <v>3.03</v>
+        <v>2.82</v>
       </c>
       <c r="AU74">
         <v>7</v>
       </c>
       <c r="AV74">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW74">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AX74">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AY74">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ74">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA74">
         <v>11</v>
@@ -16299,7 +16299,7 @@
         <v>45836.5</v>
       </c>
       <c r="F75">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G75" t="s">
         <v>75</v>
@@ -16413,31 +16413,31 @@
         <v>1.78</v>
       </c>
       <c r="AR75">
-        <v>1.69</v>
+        <v>1.49</v>
       </c>
       <c r="AS75">
-        <v>2.12</v>
+        <v>1.65</v>
       </c>
       <c r="AT75">
-        <v>3.81</v>
+        <v>3.14</v>
       </c>
       <c r="AU75">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV75">
         <v>12</v>
       </c>
       <c r="AW75">
+        <v>1</v>
+      </c>
+      <c r="AX75">
+        <v>7</v>
+      </c>
+      <c r="AY75">
         <v>5</v>
       </c>
-      <c r="AX75">
-        <v>9</v>
-      </c>
-      <c r="AY75">
-        <v>10</v>
-      </c>
       <c r="AZ75">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BA75">
         <v>3</v>
@@ -16505,7 +16505,7 @@
         <v>45836.58333333334</v>
       </c>
       <c r="F76">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G76" t="s">
         <v>73</v>
@@ -16532,7 +16532,7 @@
         <v>5</v>
       </c>
       <c r="O76" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P76" t="s">
         <v>204</v>
@@ -16619,31 +16619,31 @@
         <v>1.11</v>
       </c>
       <c r="AR76">
-        <v>1.66</v>
+        <v>1.4</v>
       </c>
       <c r="AS76">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AT76">
-        <v>2.74</v>
+        <v>2.51</v>
       </c>
       <c r="AU76">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV76">
         <v>11</v>
       </c>
       <c r="AW76">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX76">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY76">
         <v>9</v>
       </c>
       <c r="AZ76">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA76">
         <v>5</v>
@@ -16711,7 +16711,7 @@
         <v>45836.70833333334</v>
       </c>
       <c r="F77">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G77" t="s">
         <v>79</v>
@@ -16738,7 +16738,7 @@
         <v>3</v>
       </c>
       <c r="O77" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P77" t="s">
         <v>205</v>
@@ -16825,31 +16825,31 @@
         <v>1.25</v>
       </c>
       <c r="AR77">
-        <v>1.34</v>
+        <v>1.09</v>
       </c>
       <c r="AS77">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="AT77">
-        <v>2.6</v>
+        <v>2.23</v>
       </c>
       <c r="AU77">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV77">
         <v>6</v>
       </c>
       <c r="AW77">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AX77">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY77">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AZ77">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA77">
         <v>5</v>
@@ -16917,7 +16917,7 @@
         <v>45839.5</v>
       </c>
       <c r="F78">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G78" t="s">
         <v>77</v>
@@ -16944,7 +16944,7 @@
         <v>8</v>
       </c>
       <c r="O78" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P78" t="s">
         <v>206</v>
@@ -17031,31 +17031,31 @@
         <v>1</v>
       </c>
       <c r="AR78">
-        <v>1.93</v>
+        <v>1.64</v>
       </c>
       <c r="AS78">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AT78">
-        <v>3.28</v>
+        <v>2.89</v>
       </c>
       <c r="AU78">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AV78">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AW78">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AX78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY78">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="AZ78">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="BA78">
         <v>8</v>
@@ -17123,7 +17123,7 @@
         <v>45840.5</v>
       </c>
       <c r="F79">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G79" t="s">
         <v>71</v>
@@ -17237,13 +17237,13 @@
         <v>1.13</v>
       </c>
       <c r="AR79">
-        <v>2</v>
+        <v>1.61</v>
       </c>
       <c r="AS79">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AT79">
-        <v>3.08</v>
+        <v>2.61</v>
       </c>
       <c r="AU79">
         <v>3</v>
@@ -17252,16 +17252,16 @@
         <v>3</v>
       </c>
       <c r="AW79">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="AX79">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AY79">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="AZ79">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA79">
         <v>12</v>
@@ -17329,7 +17329,7 @@
         <v>45840.5</v>
       </c>
       <c r="F80">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G80" t="s">
         <v>70</v>
@@ -17356,7 +17356,7 @@
         <v>3</v>
       </c>
       <c r="O80" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P80" t="s">
         <v>207</v>
@@ -17443,31 +17443,31 @@
         <v>0.43</v>
       </c>
       <c r="AR80">
-        <v>1.74</v>
+        <v>1.51</v>
       </c>
       <c r="AS80">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AT80">
-        <v>3.04</v>
+        <v>2.7</v>
       </c>
       <c r="AU80">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV80">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW80">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="AX80">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AY80">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="AZ80">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA80">
         <v>4</v>
@@ -17535,7 +17535,7 @@
         <v>45840.5</v>
       </c>
       <c r="F81">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G81" t="s">
         <v>74</v>
@@ -17562,7 +17562,7 @@
         <v>3</v>
       </c>
       <c r="O81" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P81" t="s">
         <v>208</v>
@@ -17649,13 +17649,13 @@
         <v>0.86</v>
       </c>
       <c r="AR81">
-        <v>1.73</v>
+        <v>1.41</v>
       </c>
       <c r="AS81">
-        <v>1.49</v>
+        <v>1.32</v>
       </c>
       <c r="AT81">
-        <v>3.22</v>
+        <v>2.73</v>
       </c>
       <c r="AU81">
         <v>5</v>
@@ -17664,16 +17664,16 @@
         <v>6</v>
       </c>
       <c r="AW81">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AX81">
+        <v>6</v>
+      </c>
+      <c r="AY81">
+        <v>11</v>
+      </c>
+      <c r="AZ81">
         <v>12</v>
-      </c>
-      <c r="AY81">
-        <v>14</v>
-      </c>
-      <c r="AZ81">
-        <v>18</v>
       </c>
       <c r="BA81">
         <v>8</v>
@@ -17741,7 +17741,7 @@
         <v>45840.5</v>
       </c>
       <c r="F82">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G82" t="s">
         <v>78</v>
@@ -17768,7 +17768,7 @@
         <v>5</v>
       </c>
       <c r="O82" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P82" t="s">
         <v>209</v>
@@ -17855,31 +17855,31 @@
         <v>1.11</v>
       </c>
       <c r="AR82">
-        <v>2.02</v>
+        <v>1.75</v>
       </c>
       <c r="AS82">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AT82">
-        <v>3.31</v>
+        <v>3.06</v>
       </c>
       <c r="AU82">
         <v>8</v>
       </c>
       <c r="AV82">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW82">
         <v>6</v>
       </c>
       <c r="AX82">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY82">
         <v>14</v>
       </c>
       <c r="AZ82">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA82">
         <v>6</v>
@@ -17947,7 +17947,7 @@
         <v>45842.5</v>
       </c>
       <c r="F83">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G83" t="s">
         <v>79</v>
@@ -17974,7 +17974,7 @@
         <v>4</v>
       </c>
       <c r="O83" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="P83" t="s">
         <v>210</v>
@@ -18061,31 +18061,31 @@
         <v>1.25</v>
       </c>
       <c r="AR83">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AS83">
-        <v>1.58</v>
+        <v>1.21</v>
       </c>
       <c r="AT83">
-        <v>2.98</v>
+        <v>2.38</v>
       </c>
       <c r="AU83">
         <v>3</v>
       </c>
       <c r="AV83">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW83">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX83">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AY83">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AZ83">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA83">
         <v>2</v>
@@ -18153,7 +18153,7 @@
         <v>45843.45833333334</v>
       </c>
       <c r="F84">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G84" t="s">
         <v>76</v>
@@ -18180,7 +18180,7 @@
         <v>2</v>
       </c>
       <c r="O84" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P84" t="s">
         <v>211</v>
@@ -18267,13 +18267,13 @@
         <v>1.78</v>
       </c>
       <c r="AR84">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="AS84">
-        <v>2.21</v>
+        <v>1.79</v>
       </c>
       <c r="AT84">
-        <v>4.02</v>
+        <v>3.49</v>
       </c>
       <c r="AU84">
         <v>3</v>
@@ -18282,16 +18282,16 @@
         <v>7</v>
       </c>
       <c r="AW84">
+        <v>2</v>
+      </c>
+      <c r="AX84">
         <v>5</v>
       </c>
-      <c r="AX84">
-        <v>9</v>
-      </c>
       <c r="AY84">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AZ84">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="BA84">
         <v>4</v>
@@ -18359,7 +18359,7 @@
         <v>45843.54166666666</v>
       </c>
       <c r="F85">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G85" t="s">
         <v>74</v>
@@ -18473,31 +18473,31 @@
         <v>1.63</v>
       </c>
       <c r="AR85">
-        <v>1.73</v>
+        <v>1.43</v>
       </c>
       <c r="AS85">
-        <v>1.99</v>
+        <v>1.74</v>
       </c>
       <c r="AT85">
-        <v>3.72</v>
+        <v>3.17</v>
       </c>
       <c r="AU85">
+        <v>2</v>
+      </c>
+      <c r="AV85">
         <v>4</v>
       </c>
-      <c r="AV85">
-        <v>3</v>
-      </c>
       <c r="AW85">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AX85">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AY85">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="AZ85">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA85">
         <v>9</v>
@@ -18565,7 +18565,7 @@
         <v>45844.41666666666</v>
       </c>
       <c r="F86">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G86" t="s">
         <v>80</v>
@@ -18592,7 +18592,7 @@
         <v>2</v>
       </c>
       <c r="O86" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P86" t="s">
         <v>213</v>
@@ -18679,31 +18679,31 @@
         <v>1.13</v>
       </c>
       <c r="AR86">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AS86">
-        <v>1.06</v>
+        <v>0.97</v>
       </c>
       <c r="AT86">
-        <v>2.2</v>
+        <v>2.03</v>
       </c>
       <c r="AU86">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV86">
         <v>9</v>
       </c>
       <c r="AW86">
+        <v>2</v>
+      </c>
+      <c r="AX86">
+        <v>4</v>
+      </c>
+      <c r="AY86">
         <v>10</v>
       </c>
-      <c r="AX86">
-        <v>8</v>
-      </c>
-      <c r="AY86">
-        <v>17</v>
-      </c>
       <c r="AZ86">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="BA86">
         <v>7</v>
@@ -18771,7 +18771,7 @@
         <v>45844.52083333334</v>
       </c>
       <c r="F87">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G87" t="s">
         <v>75</v>
@@ -18885,31 +18885,31 @@
         <v>2.25</v>
       </c>
       <c r="AR87">
-        <v>1.61</v>
+        <v>1.38</v>
       </c>
       <c r="AS87">
-        <v>2.01</v>
+        <v>1.66</v>
       </c>
       <c r="AT87">
-        <v>3.62</v>
+        <v>3.04</v>
       </c>
       <c r="AU87">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV87">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AW87">
+        <v>3</v>
+      </c>
+      <c r="AX87">
+        <v>3</v>
+      </c>
+      <c r="AY87">
         <v>7</v>
       </c>
-      <c r="AX87">
-        <v>6</v>
-      </c>
-      <c r="AY87">
-        <v>12</v>
-      </c>
       <c r="AZ87">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="BA87">
         <v>8</v>
@@ -18977,7 +18977,7 @@
         <v>45845.5</v>
       </c>
       <c r="F88">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G88" t="s">
         <v>73</v>
@@ -19091,31 +19091,31 @@
         <v>1</v>
       </c>
       <c r="AR88">
-        <v>1.62</v>
+        <v>1.39</v>
       </c>
       <c r="AS88">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AT88">
-        <v>2.97</v>
+        <v>2.64</v>
       </c>
       <c r="AU88">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV88">
         <v>5</v>
       </c>
       <c r="AW88">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="AX88">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AY88">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AZ88">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA88">
         <v>9</v>
@@ -19183,7 +19183,7 @@
         <v>45850.45833333334</v>
       </c>
       <c r="F89">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G89" t="s">
         <v>71</v>
@@ -19210,7 +19210,7 @@
         <v>4</v>
       </c>
       <c r="O89" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="P89" t="s">
         <v>83</v>
@@ -19297,31 +19297,31 @@
         <v>1.11</v>
       </c>
       <c r="AR89">
-        <v>2.05</v>
+        <v>1.59</v>
       </c>
       <c r="AS89">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AT89">
-        <v>3.39</v>
+        <v>2.92</v>
       </c>
       <c r="AU89">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AV89">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW89">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AX89">
         <v>8</v>
       </c>
       <c r="AY89">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ89">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA89">
         <v>10</v>
@@ -19389,7 +19389,7 @@
         <v>45851.41666666666</v>
       </c>
       <c r="F90">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G90" t="s">
         <v>81</v>
@@ -19416,7 +19416,7 @@
         <v>2</v>
       </c>
       <c r="O90" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="P90" t="s">
         <v>84</v>
@@ -19503,13 +19503,13 @@
         <v>0.86</v>
       </c>
       <c r="AR90">
-        <v>1.7</v>
+        <v>1.33</v>
       </c>
       <c r="AS90">
-        <v>1.58</v>
+        <v>1.39</v>
       </c>
       <c r="AT90">
-        <v>3.28</v>
+        <v>2.72</v>
       </c>
       <c r="AU90">
         <v>4</v>
@@ -19518,16 +19518,16 @@
         <v>2</v>
       </c>
       <c r="AW90">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AX90">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AY90">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AZ90">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BA90">
         <v>5</v>
@@ -19595,7 +19595,7 @@
         <v>45851.52083333334</v>
       </c>
       <c r="F91">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G91" t="s">
         <v>79</v>
@@ -19622,7 +19622,7 @@
         <v>5</v>
       </c>
       <c r="O91" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="P91" t="s">
         <v>214</v>
@@ -19709,13 +19709,13 @@
         <v>0.43</v>
       </c>
       <c r="AR91">
-        <v>1.28</v>
+        <v>1.08</v>
       </c>
       <c r="AS91">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="AT91">
-        <v>2.56</v>
+        <v>2.26</v>
       </c>
       <c r="AU91">
         <v>7</v>
@@ -19724,13 +19724,13 @@
         <v>6</v>
       </c>
       <c r="AW91">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AX91">
         <v>3</v>
       </c>
       <c r="AY91">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AZ91">
         <v>9</v>
@@ -19801,7 +19801,7 @@
         <v>45852.5</v>
       </c>
       <c r="F92">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G92" t="s">
         <v>70</v>
@@ -19828,7 +19828,7 @@
         <v>5</v>
       </c>
       <c r="O92" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P92" t="s">
         <v>215</v>
@@ -19915,28 +19915,28 @@
         <v>1.25</v>
       </c>
       <c r="AR92">
-        <v>1.85</v>
+        <v>1.59</v>
       </c>
       <c r="AS92">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AT92">
-        <v>3.1</v>
+        <v>2.74</v>
       </c>
       <c r="AU92">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV92">
+        <v>4</v>
+      </c>
+      <c r="AW92">
+        <v>3</v>
+      </c>
+      <c r="AX92">
         <v>5</v>
       </c>
-      <c r="AW92">
-        <v>5</v>
-      </c>
-      <c r="AX92">
-        <v>4</v>
-      </c>
       <c r="AY92">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AZ92">
         <v>9</v>
@@ -20007,7 +20007,7 @@
         <v>45856.5</v>
       </c>
       <c r="F93">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G93" t="s">
         <v>73</v>
@@ -20034,7 +20034,7 @@
         <v>4</v>
       </c>
       <c r="O93" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P93" t="s">
         <v>216</v>
@@ -20121,13 +20121,13 @@
         <v>2.25</v>
       </c>
       <c r="AR93">
-        <v>1.63</v>
+        <v>1.39</v>
       </c>
       <c r="AS93">
-        <v>1.97</v>
+        <v>1.61</v>
       </c>
       <c r="AT93">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="AU93">
         <v>3</v>
@@ -20213,7 +20213,7 @@
         <v>45857.45833333334</v>
       </c>
       <c r="F94">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G94" t="s">
         <v>74</v>
@@ -20240,7 +20240,7 @@
         <v>2</v>
       </c>
       <c r="O94" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P94" t="s">
         <v>217</v>
@@ -20327,13 +20327,13 @@
         <v>1.25</v>
       </c>
       <c r="AR94">
-        <v>1.68</v>
+        <v>1.36</v>
       </c>
       <c r="AS94">
-        <v>1.58</v>
+        <v>1.26</v>
       </c>
       <c r="AT94">
-        <v>3.26</v>
+        <v>2.62</v>
       </c>
       <c r="AU94">
         <v>4</v>
@@ -20419,7 +20419,7 @@
         <v>45858.41666666666</v>
       </c>
       <c r="F95">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G95" t="s">
         <v>76</v>
@@ -20446,7 +20446,7 @@
         <v>4</v>
       </c>
       <c r="O95" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P95" t="s">
         <v>188</v>
@@ -20533,13 +20533,13 @@
         <v>1</v>
       </c>
       <c r="AR95">
-        <v>1.69</v>
+        <v>1.58</v>
       </c>
       <c r="AS95">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AT95">
-        <v>3</v>
+        <v>2.79</v>
       </c>
       <c r="AU95">
         <v>7</v>
@@ -20625,7 +20625,7 @@
         <v>45858.52083333334</v>
       </c>
       <c r="F96">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G96" t="s">
         <v>80</v>
@@ -20739,31 +20739,31 @@
         <v>1.78</v>
       </c>
       <c r="AR96">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="AS96">
-        <v>2.17</v>
+        <v>1.77</v>
       </c>
       <c r="AT96">
-        <v>3.46</v>
+        <v>2.93</v>
       </c>
       <c r="AU96">
         <v>2</v>
       </c>
       <c r="AV96">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AW96">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX96">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AY96">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AZ96">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="BA96">
         <v>1</v>
@@ -20831,7 +20831,7 @@
         <v>45858.52083333334</v>
       </c>
       <c r="F97">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G97" t="s">
         <v>78</v>
@@ -20858,7 +20858,7 @@
         <v>4</v>
       </c>
       <c r="O97" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="P97" t="s">
         <v>219</v>
@@ -20945,40 +20945,40 @@
         <v>0.5</v>
       </c>
       <c r="AR97">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="AS97">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="AT97">
-        <v>3.18</v>
+        <v>2.87</v>
       </c>
       <c r="AU97">
         <v>8</v>
       </c>
       <c r="AV97">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW97">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AX97">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AY97">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AZ97">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="BA97">
         <v>4</v>
       </c>
       <c r="BB97">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC97">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BD97">
         <v>1.3</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
@@ -466,7 +466,7 @@
     <t>['89']</t>
   </si>
   <si>
-    <t>['60', '63', '85']</t>
+    <t>['59', '63', '85']</t>
   </si>
   <si>
     <t>['24', '32', '56']</t>
@@ -20542,22 +20542,22 @@
         <v>2.79</v>
       </c>
       <c r="AU95">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AV95">
         <v>3</v>
       </c>
       <c r="AW95">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AX95">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY95">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AZ95">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA95">
         <v>9</v>
@@ -20751,19 +20751,19 @@
         <v>2</v>
       </c>
       <c r="AV96">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AW96">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX96">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AY96">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AZ96">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA96">
         <v>1</v>
@@ -20957,28 +20957,28 @@
         <v>8</v>
       </c>
       <c r="AV97">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AW97">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AX97">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AY97">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AZ97">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BA97">
         <v>4</v>
       </c>
       <c r="BB97">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BC97">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BD97">
         <v>1.3</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="222">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -472,6 +472,9 @@
     <t>['24', '32', '56']</t>
   </si>
   <si>
+    <t>['57']</t>
+  </si>
+  <si>
     <t>['4', '14']</t>
   </si>
   <si>
@@ -674,6 +677,9 @@
   </si>
   <si>
     <t>['90']</t>
+  </si>
+  <si>
+    <t>['8']</t>
   </si>
 </sst>
 </file>
@@ -1035,7 +1041,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP97"/>
+  <dimension ref="A1:BP98"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1291,7 +1297,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q2">
         <v>3.2</v>
@@ -1497,7 +1503,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q3">
         <v>3.25</v>
@@ -1703,7 +1709,7 @@
         <v>84</v>
       </c>
       <c r="P4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q4">
         <v>3.1</v>
@@ -2115,7 +2121,7 @@
         <v>85</v>
       </c>
       <c r="P6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q6">
         <v>2.3</v>
@@ -2321,7 +2327,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q7">
         <v>3.4</v>
@@ -2527,7 +2533,7 @@
         <v>87</v>
       </c>
       <c r="P8" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q8">
         <v>4.1</v>
@@ -2939,7 +2945,7 @@
         <v>89</v>
       </c>
       <c r="P10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q10">
         <v>1.7</v>
@@ -3763,7 +3769,7 @@
         <v>84</v>
       </c>
       <c r="P14" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q14">
         <v>3.1</v>
@@ -3969,7 +3975,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q15">
         <v>3.2</v>
@@ -4175,7 +4181,7 @@
         <v>93</v>
       </c>
       <c r="P16" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q16">
         <v>4.79</v>
@@ -4381,7 +4387,7 @@
         <v>84</v>
       </c>
       <c r="P17" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q17">
         <v>4.17</v>
@@ -4793,7 +4799,7 @@
         <v>84</v>
       </c>
       <c r="P19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q19">
         <v>1.72</v>
@@ -5205,7 +5211,7 @@
         <v>96</v>
       </c>
       <c r="P21" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q21">
         <v>2.2</v>
@@ -5411,7 +5417,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q22">
         <v>4.75</v>
@@ -5617,7 +5623,7 @@
         <v>98</v>
       </c>
       <c r="P23" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q23">
         <v>2.3</v>
@@ -5823,7 +5829,7 @@
         <v>99</v>
       </c>
       <c r="P24" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q24">
         <v>2.25</v>
@@ -6029,7 +6035,7 @@
         <v>100</v>
       </c>
       <c r="P25" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q25">
         <v>3.75</v>
@@ -6235,7 +6241,7 @@
         <v>101</v>
       </c>
       <c r="P26" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q26">
         <v>6.5</v>
@@ -6441,7 +6447,7 @@
         <v>102</v>
       </c>
       <c r="P27" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q27">
         <v>1.85</v>
@@ -6522,7 +6528,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ27">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AR27">
         <v>2.04</v>
@@ -6647,7 +6653,7 @@
         <v>84</v>
       </c>
       <c r="P28" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q28">
         <v>2.5</v>
@@ -6853,7 +6859,7 @@
         <v>103</v>
       </c>
       <c r="P29" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q29">
         <v>2.7</v>
@@ -7677,7 +7683,7 @@
         <v>107</v>
       </c>
       <c r="P33" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q33">
         <v>2.93</v>
@@ -7883,7 +7889,7 @@
         <v>108</v>
       </c>
       <c r="P34" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q34">
         <v>2.26</v>
@@ -7964,7 +7970,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ34">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AR34">
         <v>1.49</v>
@@ -8295,7 +8301,7 @@
         <v>110</v>
       </c>
       <c r="P36" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q36">
         <v>6.4</v>
@@ -8501,7 +8507,7 @@
         <v>111</v>
       </c>
       <c r="P37" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q37">
         <v>3.84</v>
@@ -8707,7 +8713,7 @@
         <v>84</v>
       </c>
       <c r="P38" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q38">
         <v>5.25</v>
@@ -8913,7 +8919,7 @@
         <v>112</v>
       </c>
       <c r="P39" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -9119,7 +9125,7 @@
         <v>113</v>
       </c>
       <c r="P40" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q40">
         <v>2.85</v>
@@ -9325,7 +9331,7 @@
         <v>114</v>
       </c>
       <c r="P41" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q41">
         <v>4.02</v>
@@ -9531,7 +9537,7 @@
         <v>84</v>
       </c>
       <c r="P42" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q42">
         <v>2.1</v>
@@ -9737,7 +9743,7 @@
         <v>115</v>
       </c>
       <c r="P43" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q43">
         <v>2.75</v>
@@ -9943,7 +9949,7 @@
         <v>116</v>
       </c>
       <c r="P44" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q44">
         <v>1.68</v>
@@ -10355,7 +10361,7 @@
         <v>117</v>
       </c>
       <c r="P46" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q46">
         <v>1.91</v>
@@ -10848,7 +10854,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ48">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AR48">
         <v>1.34</v>
@@ -10973,7 +10979,7 @@
         <v>119</v>
       </c>
       <c r="P49" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q49">
         <v>3.45</v>
@@ -11385,7 +11391,7 @@
         <v>84</v>
       </c>
       <c r="P51" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q51">
         <v>6.5</v>
@@ -11591,7 +11597,7 @@
         <v>84</v>
       </c>
       <c r="P52" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q52">
         <v>2.18</v>
@@ -11797,7 +11803,7 @@
         <v>84</v>
       </c>
       <c r="P53" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q53">
         <v>3.85</v>
@@ -12003,7 +12009,7 @@
         <v>120</v>
       </c>
       <c r="P54" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q54">
         <v>2.66</v>
@@ -12209,7 +12215,7 @@
         <v>121</v>
       </c>
       <c r="P55" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q55">
         <v>3</v>
@@ -12415,7 +12421,7 @@
         <v>122</v>
       </c>
       <c r="P56" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q56">
         <v>3.35</v>
@@ -12827,7 +12833,7 @@
         <v>84</v>
       </c>
       <c r="P58" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q58">
         <v>3.3</v>
@@ -13033,7 +13039,7 @@
         <v>84</v>
       </c>
       <c r="P59" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q59">
         <v>5.5</v>
@@ -13239,7 +13245,7 @@
         <v>123</v>
       </c>
       <c r="P60" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q60">
         <v>2.11</v>
@@ -13320,7 +13326,7 @@
         <v>2</v>
       </c>
       <c r="AQ60">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AR60">
         <v>1.53</v>
@@ -13445,7 +13451,7 @@
         <v>84</v>
       </c>
       <c r="P61" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q61">
         <v>4.5</v>
@@ -13857,7 +13863,7 @@
         <v>84</v>
       </c>
       <c r="P63" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q63">
         <v>2.87</v>
@@ -14063,7 +14069,7 @@
         <v>125</v>
       </c>
       <c r="P64" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q64">
         <v>1.85</v>
@@ -14269,7 +14275,7 @@
         <v>126</v>
       </c>
       <c r="P65" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q65">
         <v>4.28</v>
@@ -14475,7 +14481,7 @@
         <v>127</v>
       </c>
       <c r="P66" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q66">
         <v>2.19</v>
@@ -14887,7 +14893,7 @@
         <v>129</v>
       </c>
       <c r="P68" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q68">
         <v>3.3</v>
@@ -15093,7 +15099,7 @@
         <v>130</v>
       </c>
       <c r="P69" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q69">
         <v>2.03</v>
@@ -15174,7 +15180,7 @@
         <v>2</v>
       </c>
       <c r="AQ69">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AR69">
         <v>1.74</v>
@@ -15711,7 +15717,7 @@
         <v>132</v>
       </c>
       <c r="P72" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q72">
         <v>4.6</v>
@@ -16329,7 +16335,7 @@
         <v>84</v>
       </c>
       <c r="P75" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q75">
         <v>4</v>
@@ -16535,7 +16541,7 @@
         <v>135</v>
       </c>
       <c r="P76" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q76">
         <v>3.28</v>
@@ -16741,7 +16747,7 @@
         <v>136</v>
       </c>
       <c r="P77" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q77">
         <v>3.6</v>
@@ -16947,7 +16953,7 @@
         <v>137</v>
       </c>
       <c r="P78" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q78">
         <v>2.17</v>
@@ -17359,7 +17365,7 @@
         <v>138</v>
       </c>
       <c r="P80" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q80">
         <v>1.52</v>
@@ -17565,7 +17571,7 @@
         <v>139</v>
       </c>
       <c r="P81" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q81">
         <v>2.38</v>
@@ -17646,7 +17652,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ81">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AR81">
         <v>1.41</v>
@@ -17771,7 +17777,7 @@
         <v>140</v>
       </c>
       <c r="P82" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q82">
         <v>1.68</v>
@@ -17977,7 +17983,7 @@
         <v>141</v>
       </c>
       <c r="P83" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q83">
         <v>3.6</v>
@@ -18183,7 +18189,7 @@
         <v>142</v>
       </c>
       <c r="P84" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q84">
         <v>3.27</v>
@@ -18389,7 +18395,7 @@
         <v>84</v>
       </c>
       <c r="P85" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q85">
         <v>3.9</v>
@@ -18595,7 +18601,7 @@
         <v>143</v>
       </c>
       <c r="P86" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q86">
         <v>2.53</v>
@@ -19500,7 +19506,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ90">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AR90">
         <v>1.33</v>
@@ -19625,7 +19631,7 @@
         <v>146</v>
       </c>
       <c r="P91" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q91">
         <v>2.38</v>
@@ -19831,7 +19837,7 @@
         <v>147</v>
       </c>
       <c r="P92" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q92">
         <v>1.93</v>
@@ -20037,7 +20043,7 @@
         <v>148</v>
       </c>
       <c r="P93" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q93">
         <v>7</v>
@@ -20243,7 +20249,7 @@
         <v>149</v>
       </c>
       <c r="P94" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q94">
         <v>3.37</v>
@@ -20449,7 +20455,7 @@
         <v>150</v>
       </c>
       <c r="P95" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q95">
         <v>2.23</v>
@@ -20542,22 +20548,22 @@
         <v>2.79</v>
       </c>
       <c r="AU95">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AV95">
         <v>3</v>
       </c>
       <c r="AW95">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AX95">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY95">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AZ95">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA95">
         <v>9</v>
@@ -20655,7 +20661,7 @@
         <v>84</v>
       </c>
       <c r="P96" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q96">
         <v>4.1</v>
@@ -20751,19 +20757,19 @@
         <v>2</v>
       </c>
       <c r="AV96">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AW96">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX96">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AY96">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AZ96">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA96">
         <v>1</v>
@@ -20861,7 +20867,7 @@
         <v>151</v>
       </c>
       <c r="P97" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q97">
         <v>2.05</v>
@@ -20957,28 +20963,28 @@
         <v>8</v>
       </c>
       <c r="AV97">
+        <v>5</v>
+      </c>
+      <c r="AW97">
         <v>7</v>
       </c>
-      <c r="AW97">
-        <v>4</v>
-      </c>
       <c r="AX97">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AY97">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AZ97">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="BA97">
         <v>4</v>
       </c>
       <c r="BB97">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC97">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BD97">
         <v>1.3</v>
@@ -21018,6 +21024,212 @@
       </c>
       <c r="BP97">
         <v>1.49</v>
+      </c>
+    </row>
+    <row r="98" spans="1:68">
+      <c r="A98" s="1">
+        <v>97</v>
+      </c>
+      <c r="B98">
+        <v>7811588</v>
+      </c>
+      <c r="C98" t="s">
+        <v>68</v>
+      </c>
+      <c r="D98" t="s">
+        <v>69</v>
+      </c>
+      <c r="E98" s="2">
+        <v>45859.5</v>
+      </c>
+      <c r="F98">
+        <v>16</v>
+      </c>
+      <c r="G98" t="s">
+        <v>72</v>
+      </c>
+      <c r="H98" t="s">
+        <v>75</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>1</v>
+      </c>
+      <c r="K98">
+        <v>1</v>
+      </c>
+      <c r="L98">
+        <v>1</v>
+      </c>
+      <c r="M98">
+        <v>1</v>
+      </c>
+      <c r="N98">
+        <v>2</v>
+      </c>
+      <c r="O98" t="s">
+        <v>152</v>
+      </c>
+      <c r="P98" t="s">
+        <v>221</v>
+      </c>
+      <c r="Q98">
+        <v>3.66</v>
+      </c>
+      <c r="R98">
+        <v>2.24</v>
+      </c>
+      <c r="S98">
+        <v>2.51</v>
+      </c>
+      <c r="T98">
+        <v>1.3</v>
+      </c>
+      <c r="U98">
+        <v>3.2</v>
+      </c>
+      <c r="V98">
+        <v>2.3</v>
+      </c>
+      <c r="W98">
+        <v>1.53</v>
+      </c>
+      <c r="X98">
+        <v>5.5</v>
+      </c>
+      <c r="Y98">
+        <v>1.11</v>
+      </c>
+      <c r="Z98">
+        <v>3.64</v>
+      </c>
+      <c r="AA98">
+        <v>3.4</v>
+      </c>
+      <c r="AB98">
+        <v>1.81</v>
+      </c>
+      <c r="AC98">
+        <v>1.04</v>
+      </c>
+      <c r="AD98">
+        <v>13.3</v>
+      </c>
+      <c r="AE98">
+        <v>1.2</v>
+      </c>
+      <c r="AF98">
+        <v>4.05</v>
+      </c>
+      <c r="AG98">
+        <v>1.6</v>
+      </c>
+      <c r="AH98">
+        <v>2.25</v>
+      </c>
+      <c r="AI98">
+        <v>1.57</v>
+      </c>
+      <c r="AJ98">
+        <v>2.25</v>
+      </c>
+      <c r="AK98">
+        <v>1.72</v>
+      </c>
+      <c r="AL98">
+        <v>1.26</v>
+      </c>
+      <c r="AM98">
+        <v>1.29</v>
+      </c>
+      <c r="AN98">
+        <v>1</v>
+      </c>
+      <c r="AO98">
+        <v>0.86</v>
+      </c>
+      <c r="AP98">
+        <v>1</v>
+      </c>
+      <c r="AQ98">
+        <v>0.88</v>
+      </c>
+      <c r="AR98">
+        <v>1.11</v>
+      </c>
+      <c r="AS98">
+        <v>1.38</v>
+      </c>
+      <c r="AT98">
+        <v>2.49</v>
+      </c>
+      <c r="AU98">
+        <v>6</v>
+      </c>
+      <c r="AV98">
+        <v>5</v>
+      </c>
+      <c r="AW98">
+        <v>12</v>
+      </c>
+      <c r="AX98">
+        <v>6</v>
+      </c>
+      <c r="AY98">
+        <v>18</v>
+      </c>
+      <c r="AZ98">
+        <v>11</v>
+      </c>
+      <c r="BA98">
+        <v>10</v>
+      </c>
+      <c r="BB98">
+        <v>5</v>
+      </c>
+      <c r="BC98">
+        <v>15</v>
+      </c>
+      <c r="BD98">
+        <v>2.28</v>
+      </c>
+      <c r="BE98">
+        <v>7.1</v>
+      </c>
+      <c r="BF98">
+        <v>1.78</v>
+      </c>
+      <c r="BG98">
+        <v>1.09</v>
+      </c>
+      <c r="BH98">
+        <v>4.4</v>
+      </c>
+      <c r="BI98">
+        <v>1.22</v>
+      </c>
+      <c r="BJ98">
+        <v>3.5</v>
+      </c>
+      <c r="BK98">
+        <v>1.47</v>
+      </c>
+      <c r="BL98">
+        <v>2.4</v>
+      </c>
+      <c r="BM98">
+        <v>1.74</v>
+      </c>
+      <c r="BN98">
+        <v>1.98</v>
+      </c>
+      <c r="BO98">
+        <v>2.35</v>
+      </c>
+      <c r="BP98">
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Finland Veikkausliiga_2025.xlsx
@@ -21166,22 +21166,22 @@
         <v>2.49</v>
       </c>
       <c r="AU98">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AV98">
         <v>5</v>
       </c>
       <c r="AW98">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AX98">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AY98">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AZ98">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA98">
         <v>10</v>
